--- a/workout_plan_new.xlsx
+++ b/workout_plan_new.xlsx
@@ -46,38 +46,38 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="005260C5"/>
-        <bgColor rgb="005260C5"/>
+        <fgColor rgb="005288C5"/>
+        <bgColor rgb="005288C5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="006571CC"/>
-        <bgColor rgb="006571CC"/>
+        <fgColor rgb="006595CC"/>
+        <bgColor rgb="006595CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="007983D2"/>
-        <bgColor rgb="007983D2"/>
+        <fgColor rgb="0079A2D2"/>
+        <bgColor rgb="0079A2D2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="008C95D8"/>
-        <bgColor rgb="008C95D8"/>
+        <fgColor rgb="008CAFD8"/>
+        <bgColor rgb="008CAFD8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="009FA6DF"/>
-        <bgColor rgb="009FA6DF"/>
+        <fgColor rgb="009FBDDF"/>
+        <bgColor rgb="009FBDDF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00B2B8E5"/>
-        <bgColor rgb="00B2B8E5"/>
+        <fgColor rgb="00B2CAE5"/>
+        <bgColor rgb="00B2CAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -986,18 +986,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:AA71"/>
+  <dimension ref="B1:AF71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="56" customWidth="1" min="11" max="11"/>
+    <col width="33.59999999999999" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="38.5" customWidth="1" min="16" max="16"/>
+    <col width="33.59999999999999" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="38.5" customWidth="1" min="21" max="21"/>
+    <col width="33.59999999999999" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="24" max="24"/>
-    <col width="34.3" customWidth="1" min="26" max="26"/>
+    <col width="35" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="33.59999999999999" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -1027,7 +1028,12 @@
       <c r="X2" s="2" t="n"/>
       <c r="Y2" s="2" t="n"/>
       <c r="Z2" s="2" t="n"/>
-      <c r="AA2" s="3" t="n"/>
+      <c r="AA2" s="2" t="n"/>
+      <c r="AB2" s="2" t="n"/>
+      <c r="AC2" s="2" t="n"/>
+      <c r="AD2" s="2" t="n"/>
+      <c r="AE2" s="2" t="n"/>
+      <c r="AF2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="B3" s="4" t="n"/>
@@ -1059,7 +1065,12 @@
       <c r="X3" s="6" t="n"/>
       <c r="Y3" s="6" t="n"/>
       <c r="Z3" s="6" t="n"/>
-      <c r="AA3" s="7" t="n"/>
+      <c r="AA3" s="6" t="n"/>
+      <c r="AB3" s="6" t="n"/>
+      <c r="AC3" s="6" t="n"/>
+      <c r="AD3" s="6" t="n"/>
+      <c r="AE3" s="6" t="n"/>
+      <c r="AF3" s="7" t="n"/>
     </row>
     <row r="4">
       <c r="B4" s="4" t="n"/>
@@ -1087,7 +1098,12 @@
       <c r="X4" s="8" t="n"/>
       <c r="Y4" s="8" t="n"/>
       <c r="Z4" s="8" t="n"/>
-      <c r="AA4" s="7" t="n"/>
+      <c r="AA4" s="8" t="n"/>
+      <c r="AB4" s="8" t="n"/>
+      <c r="AC4" s="8" t="n"/>
+      <c r="AD4" s="8" t="n"/>
+      <c r="AE4" s="8" t="n"/>
+      <c r="AF4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="B5" s="4" t="n"/>
@@ -1115,7 +1131,12 @@
       <c r="X5" s="8" t="n"/>
       <c r="Y5" s="8" t="n"/>
       <c r="Z5" s="8" t="n"/>
-      <c r="AA5" s="7" t="n"/>
+      <c r="AA5" s="8" t="n"/>
+      <c r="AB5" s="8" t="n"/>
+      <c r="AC5" s="8" t="n"/>
+      <c r="AD5" s="8" t="n"/>
+      <c r="AE5" s="8" t="n"/>
+      <c r="AF5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="4" t="n"/>
@@ -1159,7 +1180,16 @@
       <c r="X6" s="6" t="n"/>
       <c r="Y6" s="6" t="n"/>
       <c r="Z6" s="6" t="n"/>
-      <c r="AA6" s="7" t="n"/>
+      <c r="AA6" s="8" t="n"/>
+      <c r="AB6" s="9" t="inlineStr">
+        <is>
+          <t>Set 5</t>
+        </is>
+      </c>
+      <c r="AC6" s="6" t="n"/>
+      <c r="AD6" s="6" t="n"/>
+      <c r="AE6" s="6" t="n"/>
+      <c r="AF6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="4" t="n"/>
@@ -1251,7 +1281,28 @@
           <t>Notes</t>
         </is>
       </c>
-      <c r="AA7" s="7" t="n"/>
+      <c r="AA7" s="8" t="n"/>
+      <c r="AB7" s="9" t="inlineStr">
+        <is>
+          <t>Reps</t>
+        </is>
+      </c>
+      <c r="AC7" s="9" t="inlineStr">
+        <is>
+          <t>Weights</t>
+        </is>
+      </c>
+      <c r="AD7" s="9" t="inlineStr">
+        <is>
+          <t>%1RM</t>
+        </is>
+      </c>
+      <c r="AE7" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="AF7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="4" t="n"/>
@@ -1279,7 +1330,12 @@
       <c r="X8" s="8" t="n"/>
       <c r="Y8" s="8" t="n"/>
       <c r="Z8" s="8" t="n"/>
-      <c r="AA8" s="7" t="n"/>
+      <c r="AA8" s="8" t="n"/>
+      <c r="AB8" s="8" t="n"/>
+      <c r="AC8" s="8" t="n"/>
+      <c r="AD8" s="8" t="n"/>
+      <c r="AE8" s="8" t="n"/>
+      <c r="AF8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="4" t="n"/>
@@ -1311,7 +1367,12 @@
       <c r="X9" s="12" t="n"/>
       <c r="Y9" s="12" t="n"/>
       <c r="Z9" s="12" t="n"/>
-      <c r="AA9" s="7" t="n"/>
+      <c r="AA9" s="8" t="n"/>
+      <c r="AB9" s="12" t="n"/>
+      <c r="AC9" s="12" t="n"/>
+      <c r="AD9" s="12" t="n"/>
+      <c r="AE9" s="12" t="n"/>
+      <c r="AF9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="4" t="n"/>
@@ -1339,7 +1400,12 @@
       <c r="X10" s="12" t="n"/>
       <c r="Y10" s="12" t="n"/>
       <c r="Z10" s="12" t="n"/>
-      <c r="AA10" s="7" t="n"/>
+      <c r="AA10" s="8" t="n"/>
+      <c r="AB10" s="12" t="n"/>
+      <c r="AC10" s="12" t="n"/>
+      <c r="AD10" s="12" t="n"/>
+      <c r="AE10" s="12" t="n"/>
+      <c r="AF10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="4" t="n"/>
@@ -1367,7 +1433,12 @@
       <c r="X11" s="12" t="n"/>
       <c r="Y11" s="12" t="n"/>
       <c r="Z11" s="12" t="n"/>
-      <c r="AA11" s="7" t="n"/>
+      <c r="AA11" s="8" t="n"/>
+      <c r="AB11" s="12" t="n"/>
+      <c r="AC11" s="12" t="n"/>
+      <c r="AD11" s="12" t="n"/>
+      <c r="AE11" s="12" t="n"/>
+      <c r="AF11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="4" t="n"/>
@@ -1395,7 +1466,12 @@
       <c r="X12" s="12" t="n"/>
       <c r="Y12" s="12" t="n"/>
       <c r="Z12" s="12" t="n"/>
-      <c r="AA12" s="7" t="n"/>
+      <c r="AA12" s="8" t="n"/>
+      <c r="AB12" s="12" t="n"/>
+      <c r="AC12" s="12" t="n"/>
+      <c r="AD12" s="12" t="n"/>
+      <c r="AE12" s="12" t="n"/>
+      <c r="AF12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="4" t="n"/>
@@ -1423,7 +1499,12 @@
       <c r="X13" s="12" t="n"/>
       <c r="Y13" s="12" t="n"/>
       <c r="Z13" s="12" t="n"/>
-      <c r="AA13" s="7" t="n"/>
+      <c r="AA13" s="8" t="n"/>
+      <c r="AB13" s="12" t="n"/>
+      <c r="AC13" s="12" t="n"/>
+      <c r="AD13" s="12" t="n"/>
+      <c r="AE13" s="12" t="n"/>
+      <c r="AF13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="4" t="n"/>
@@ -1451,7 +1532,12 @@
       <c r="X14" s="12" t="n"/>
       <c r="Y14" s="12" t="n"/>
       <c r="Z14" s="12" t="n"/>
-      <c r="AA14" s="7" t="n"/>
+      <c r="AA14" s="8" t="n"/>
+      <c r="AB14" s="12" t="n"/>
+      <c r="AC14" s="12" t="n"/>
+      <c r="AD14" s="12" t="n"/>
+      <c r="AE14" s="12" t="n"/>
+      <c r="AF14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="B15" s="4" t="n"/>
@@ -1479,7 +1565,12 @@
       <c r="X15" s="12" t="n"/>
       <c r="Y15" s="12" t="n"/>
       <c r="Z15" s="12" t="n"/>
-      <c r="AA15" s="7" t="n"/>
+      <c r="AA15" s="8" t="n"/>
+      <c r="AB15" s="12" t="n"/>
+      <c r="AC15" s="12" t="n"/>
+      <c r="AD15" s="12" t="n"/>
+      <c r="AE15" s="12" t="n"/>
+      <c r="AF15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="B16" s="4" t="n"/>
@@ -1507,7 +1598,12 @@
       <c r="X16" s="12" t="n"/>
       <c r="Y16" s="12" t="n"/>
       <c r="Z16" s="12" t="n"/>
-      <c r="AA16" s="7" t="n"/>
+      <c r="AA16" s="8" t="n"/>
+      <c r="AB16" s="12" t="n"/>
+      <c r="AC16" s="12" t="n"/>
+      <c r="AD16" s="12" t="n"/>
+      <c r="AE16" s="12" t="n"/>
+      <c r="AF16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="4" t="n"/>
@@ -1535,7 +1631,12 @@
       <c r="X17" s="8" t="n"/>
       <c r="Y17" s="8" t="n"/>
       <c r="Z17" s="8" t="n"/>
-      <c r="AA17" s="7" t="n"/>
+      <c r="AA17" s="8" t="n"/>
+      <c r="AB17" s="8" t="n"/>
+      <c r="AC17" s="8" t="n"/>
+      <c r="AD17" s="8" t="n"/>
+      <c r="AE17" s="8" t="n"/>
+      <c r="AF17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="4" t="n"/>
@@ -1547,7 +1648,7 @@
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>Back Squat</t>
+          <t>Weighted Pull-Ups</t>
         </is>
       </c>
       <c r="F18" s="6" t="n"/>
@@ -1557,7 +1658,7 @@
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>157.5kg</t>
+          <t>62.5kg</t>
         </is>
       </c>
       <c r="J18" s="15" t="n">
@@ -1565,7 +1666,7 @@
       </c>
       <c r="K18" s="16" t="inlineStr">
         <is>
-          <t>Focus on explosive power with controlled descent.</t>
+          <t>Wave 1 – Controlled explosive reps; full ROM.</t>
         </is>
       </c>
       <c r="L18" s="8" t="n"/>
@@ -1574,15 +1675,15 @@
       </c>
       <c r="N18" s="14" t="inlineStr">
         <is>
-          <t>157.5kg</t>
+          <t>67.5kg</t>
         </is>
       </c>
       <c r="O18" s="15" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="P18" s="16" t="inlineStr">
         <is>
-          <t>Focus on explosive power with controlled descent.</t>
+          <t>Wave 1 – Maintain bar speed and tight form.</t>
         </is>
       </c>
       <c r="Q18" s="8" t="n"/>
@@ -1591,35 +1692,52 @@
       </c>
       <c r="S18" s="14" t="inlineStr">
         <is>
-          <t>157.5kg</t>
+          <t>72.5kg</t>
         </is>
       </c>
       <c r="T18" s="15" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="U18" s="16" t="inlineStr">
         <is>
-          <t>Focus on explosive power with controlled descent.</t>
+          <t>Wave 1 – Top triple; stay clean under fatigue.</t>
         </is>
       </c>
       <c r="V18" s="8" t="n"/>
       <c r="W18" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X18" s="14" t="inlineStr">
         <is>
-          <t>157.5kg</t>
+          <t>72.5kg</t>
         </is>
       </c>
       <c r="Y18" s="15" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="Z18" s="16" t="inlineStr">
         <is>
-          <t>Focus on explosive power with controlled descent.</t>
-        </is>
-      </c>
-      <c r="AA18" s="7" t="n"/>
+          <t>Wave 2 – Match previous intensity with sharp reps.</t>
+        </is>
+      </c>
+      <c r="AA18" s="8" t="n"/>
+      <c r="AB18" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC18" s="14" t="inlineStr">
+        <is>
+          <t>75kg</t>
+        </is>
+      </c>
+      <c r="AD18" s="15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AE18" s="16" t="inlineStr">
+        <is>
+          <t>Wave 2 – Push but no grind; clean finish.</t>
+        </is>
+      </c>
+      <c r="AF18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="B19" s="4" t="n"/>
@@ -1627,205 +1745,183 @@
       <c r="D19" s="8" t="n"/>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>Paused Squat</t>
+          <t>Weighted Dips</t>
         </is>
       </c>
       <c r="F19" s="6" t="n"/>
       <c r="G19" s="8" t="n"/>
       <c r="H19" s="14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I19" s="14" t="inlineStr">
         <is>
-          <t>147.5kg</t>
+          <t>32.5kg</t>
         </is>
       </c>
       <c r="J19" s="15" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="K19" s="16" t="inlineStr">
         <is>
-          <t>Emphasize a strong pause at the bottom for stability.</t>
+          <t>Smooth controlled descent; avoid flaring.</t>
         </is>
       </c>
       <c r="L19" s="8" t="n"/>
       <c r="M19" s="14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N19" s="14" t="inlineStr">
         <is>
-          <t>147.5kg</t>
+          <t>32.5kg</t>
         </is>
       </c>
       <c r="O19" s="15" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="P19" s="16" t="inlineStr">
         <is>
-          <t>Emphasize a strong pause at the bottom for stability.</t>
+          <t>Smooth controlled descent; avoid flaring.</t>
         </is>
       </c>
       <c r="Q19" s="8" t="n"/>
-      <c r="R19" s="12" t="n"/>
-      <c r="S19" s="12" t="n"/>
-      <c r="T19" s="12" t="n"/>
-      <c r="U19" s="12" t="n"/>
+      <c r="R19" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="S19" s="14" t="inlineStr">
+        <is>
+          <t>32.5kg</t>
+        </is>
+      </c>
+      <c r="T19" s="15" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="U19" s="16" t="inlineStr">
+        <is>
+          <t>Smooth controlled descent; avoid flaring.</t>
+        </is>
+      </c>
       <c r="V19" s="8" t="n"/>
-      <c r="W19" s="12" t="n"/>
-      <c r="X19" s="12" t="n"/>
-      <c r="Y19" s="12" t="n"/>
-      <c r="Z19" s="12" t="n"/>
-      <c r="AA19" s="7" t="n"/>
+      <c r="W19" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="X19" s="14" t="inlineStr">
+        <is>
+          <t>32.5kg</t>
+        </is>
+      </c>
+      <c r="Y19" s="15" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="Z19" s="16" t="inlineStr">
+        <is>
+          <t>Smooth controlled descent; avoid flaring.</t>
+        </is>
+      </c>
+      <c r="AA19" s="8" t="n"/>
+      <c r="AB19" s="12" t="n"/>
+      <c r="AC19" s="12" t="n"/>
+      <c r="AD19" s="12" t="n"/>
+      <c r="AE19" s="12" t="n"/>
+      <c r="AF19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="B20" s="4" t="n"/>
       <c r="C20" s="6" t="n"/>
       <c r="D20" s="8" t="n"/>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>Leg Press</t>
-        </is>
-      </c>
+      <c r="E20" s="11" t="inlineStr"/>
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="8" t="n"/>
-      <c r="H20" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="I20" s="14" t="inlineStr"/>
-      <c r="J20" s="14" t="inlineStr"/>
-      <c r="K20" s="16" t="inlineStr">
-        <is>
-          <t>Focus on full range of motion and controlled execution.</t>
-        </is>
-      </c>
+      <c r="H20" s="12" t="n"/>
+      <c r="I20" s="12" t="n"/>
+      <c r="J20" s="12" t="n"/>
+      <c r="K20" s="12" t="n"/>
       <c r="L20" s="8" t="n"/>
-      <c r="M20" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="N20" s="14" t="inlineStr"/>
-      <c r="O20" s="14" t="inlineStr"/>
-      <c r="P20" s="16" t="inlineStr">
-        <is>
-          <t>Focus on full range of motion and controlled execution.</t>
-        </is>
-      </c>
+      <c r="M20" s="12" t="n"/>
+      <c r="N20" s="12" t="n"/>
+      <c r="O20" s="12" t="n"/>
+      <c r="P20" s="12" t="n"/>
       <c r="Q20" s="8" t="n"/>
-      <c r="R20" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="S20" s="14" t="inlineStr"/>
-      <c r="T20" s="14" t="inlineStr"/>
-      <c r="U20" s="16" t="inlineStr">
-        <is>
-          <t>Focus on full range of motion and controlled execution.</t>
-        </is>
-      </c>
+      <c r="R20" s="12" t="n"/>
+      <c r="S20" s="12" t="n"/>
+      <c r="T20" s="12" t="n"/>
+      <c r="U20" s="12" t="n"/>
       <c r="V20" s="8" t="n"/>
       <c r="W20" s="12" t="n"/>
       <c r="X20" s="12" t="n"/>
       <c r="Y20" s="12" t="n"/>
       <c r="Z20" s="12" t="n"/>
-      <c r="AA20" s="7" t="n"/>
+      <c r="AA20" s="8" t="n"/>
+      <c r="AB20" s="12" t="n"/>
+      <c r="AC20" s="12" t="n"/>
+      <c r="AD20" s="12" t="n"/>
+      <c r="AE20" s="12" t="n"/>
+      <c r="AF20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="4" t="n"/>
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="8" t="n"/>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>Leg Extensions</t>
-        </is>
-      </c>
+      <c r="E21" s="11" t="inlineStr"/>
       <c r="F21" s="6" t="n"/>
       <c r="G21" s="8" t="n"/>
-      <c r="H21" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="I21" s="14" t="inlineStr"/>
-      <c r="J21" s="14" t="inlineStr"/>
-      <c r="K21" s="16" t="inlineStr">
-        <is>
-          <t>Moderate load; smooth, controlled movement.</t>
-        </is>
-      </c>
+      <c r="H21" s="12" t="n"/>
+      <c r="I21" s="12" t="n"/>
+      <c r="J21" s="12" t="n"/>
+      <c r="K21" s="12" t="n"/>
       <c r="L21" s="8" t="n"/>
-      <c r="M21" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="N21" s="14" t="inlineStr"/>
-      <c r="O21" s="14" t="inlineStr"/>
-      <c r="P21" s="16" t="inlineStr">
-        <is>
-          <t>Moderate load; smooth, controlled movement.</t>
-        </is>
-      </c>
+      <c r="M21" s="12" t="n"/>
+      <c r="N21" s="12" t="n"/>
+      <c r="O21" s="12" t="n"/>
+      <c r="P21" s="12" t="n"/>
       <c r="Q21" s="8" t="n"/>
-      <c r="R21" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="S21" s="14" t="inlineStr"/>
-      <c r="T21" s="14" t="inlineStr"/>
-      <c r="U21" s="16" t="inlineStr">
-        <is>
-          <t>Moderate load; smooth, controlled movement.</t>
-        </is>
-      </c>
+      <c r="R21" s="12" t="n"/>
+      <c r="S21" s="12" t="n"/>
+      <c r="T21" s="12" t="n"/>
+      <c r="U21" s="12" t="n"/>
       <c r="V21" s="8" t="n"/>
       <c r="W21" s="12" t="n"/>
       <c r="X21" s="12" t="n"/>
       <c r="Y21" s="12" t="n"/>
       <c r="Z21" s="12" t="n"/>
-      <c r="AA21" s="7" t="n"/>
+      <c r="AA21" s="8" t="n"/>
+      <c r="AB21" s="12" t="n"/>
+      <c r="AC21" s="12" t="n"/>
+      <c r="AD21" s="12" t="n"/>
+      <c r="AE21" s="12" t="n"/>
+      <c r="AF21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="B22" s="4" t="n"/>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="8" t="n"/>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>Leg Curls</t>
-        </is>
-      </c>
+      <c r="E22" s="11" t="inlineStr"/>
       <c r="F22" s="6" t="n"/>
       <c r="G22" s="8" t="n"/>
-      <c r="H22" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="I22" s="14" t="inlineStr"/>
-      <c r="J22" s="14" t="inlineStr"/>
-      <c r="K22" s="16" t="inlineStr">
-        <is>
-          <t>Maintain a controlled tempo to target the hamstrings.</t>
-        </is>
-      </c>
+      <c r="H22" s="12" t="n"/>
+      <c r="I22" s="12" t="n"/>
+      <c r="J22" s="12" t="n"/>
+      <c r="K22" s="12" t="n"/>
       <c r="L22" s="8" t="n"/>
-      <c r="M22" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="N22" s="14" t="inlineStr"/>
-      <c r="O22" s="14" t="inlineStr"/>
-      <c r="P22" s="16" t="inlineStr">
-        <is>
-          <t>Maintain a controlled tempo to target the hamstrings.</t>
-        </is>
-      </c>
+      <c r="M22" s="12" t="n"/>
+      <c r="N22" s="12" t="n"/>
+      <c r="O22" s="12" t="n"/>
+      <c r="P22" s="12" t="n"/>
       <c r="Q22" s="8" t="n"/>
-      <c r="R22" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="S22" s="14" t="inlineStr"/>
-      <c r="T22" s="14" t="inlineStr"/>
-      <c r="U22" s="16" t="inlineStr">
-        <is>
-          <t>Maintain a controlled tempo to target the hamstrings.</t>
-        </is>
-      </c>
+      <c r="R22" s="12" t="n"/>
+      <c r="S22" s="12" t="n"/>
+      <c r="T22" s="12" t="n"/>
+      <c r="U22" s="12" t="n"/>
       <c r="V22" s="8" t="n"/>
       <c r="W22" s="12" t="n"/>
       <c r="X22" s="12" t="n"/>
       <c r="Y22" s="12" t="n"/>
       <c r="Z22" s="12" t="n"/>
-      <c r="AA22" s="7" t="n"/>
+      <c r="AA22" s="8" t="n"/>
+      <c r="AB22" s="12" t="n"/>
+      <c r="AC22" s="12" t="n"/>
+      <c r="AD22" s="12" t="n"/>
+      <c r="AE22" s="12" t="n"/>
+      <c r="AF22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="B23" s="4" t="n"/>
@@ -1853,7 +1949,12 @@
       <c r="X23" s="12" t="n"/>
       <c r="Y23" s="12" t="n"/>
       <c r="Z23" s="12" t="n"/>
-      <c r="AA23" s="7" t="n"/>
+      <c r="AA23" s="8" t="n"/>
+      <c r="AB23" s="12" t="n"/>
+      <c r="AC23" s="12" t="n"/>
+      <c r="AD23" s="12" t="n"/>
+      <c r="AE23" s="12" t="n"/>
+      <c r="AF23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="B24" s="4" t="n"/>
@@ -1881,7 +1982,12 @@
       <c r="X24" s="12" t="n"/>
       <c r="Y24" s="12" t="n"/>
       <c r="Z24" s="12" t="n"/>
-      <c r="AA24" s="7" t="n"/>
+      <c r="AA24" s="8" t="n"/>
+      <c r="AB24" s="12" t="n"/>
+      <c r="AC24" s="12" t="n"/>
+      <c r="AD24" s="12" t="n"/>
+      <c r="AE24" s="12" t="n"/>
+      <c r="AF24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="4" t="n"/>
@@ -1909,7 +2015,12 @@
       <c r="X25" s="12" t="n"/>
       <c r="Y25" s="12" t="n"/>
       <c r="Z25" s="12" t="n"/>
-      <c r="AA25" s="7" t="n"/>
+      <c r="AA25" s="8" t="n"/>
+      <c r="AB25" s="12" t="n"/>
+      <c r="AC25" s="12" t="n"/>
+      <c r="AD25" s="12" t="n"/>
+      <c r="AE25" s="12" t="n"/>
+      <c r="AF25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="B26" s="4" t="n"/>
@@ -1937,7 +2048,12 @@
       <c r="X26" s="8" t="n"/>
       <c r="Y26" s="8" t="n"/>
       <c r="Z26" s="8" t="n"/>
-      <c r="AA26" s="7" t="n"/>
+      <c r="AA26" s="8" t="n"/>
+      <c r="AB26" s="8" t="n"/>
+      <c r="AC26" s="8" t="n"/>
+      <c r="AD26" s="8" t="n"/>
+      <c r="AE26" s="8" t="n"/>
+      <c r="AF26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="B27" s="4" t="n"/>
@@ -1969,7 +2085,12 @@
       <c r="X27" s="12" t="n"/>
       <c r="Y27" s="12" t="n"/>
       <c r="Z27" s="12" t="n"/>
-      <c r="AA27" s="7" t="n"/>
+      <c r="AA27" s="8" t="n"/>
+      <c r="AB27" s="12" t="n"/>
+      <c r="AC27" s="12" t="n"/>
+      <c r="AD27" s="12" t="n"/>
+      <c r="AE27" s="12" t="n"/>
+      <c r="AF27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="B28" s="4" t="n"/>
@@ -1997,7 +2118,12 @@
       <c r="X28" s="12" t="n"/>
       <c r="Y28" s="12" t="n"/>
       <c r="Z28" s="12" t="n"/>
-      <c r="AA28" s="7" t="n"/>
+      <c r="AA28" s="8" t="n"/>
+      <c r="AB28" s="12" t="n"/>
+      <c r="AC28" s="12" t="n"/>
+      <c r="AD28" s="12" t="n"/>
+      <c r="AE28" s="12" t="n"/>
+      <c r="AF28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="4" t="n"/>
@@ -2025,7 +2151,12 @@
       <c r="X29" s="12" t="n"/>
       <c r="Y29" s="12" t="n"/>
       <c r="Z29" s="12" t="n"/>
-      <c r="AA29" s="7" t="n"/>
+      <c r="AA29" s="8" t="n"/>
+      <c r="AB29" s="12" t="n"/>
+      <c r="AC29" s="12" t="n"/>
+      <c r="AD29" s="12" t="n"/>
+      <c r="AE29" s="12" t="n"/>
+      <c r="AF29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="B30" s="4" t="n"/>
@@ -2053,7 +2184,12 @@
       <c r="X30" s="12" t="n"/>
       <c r="Y30" s="12" t="n"/>
       <c r="Z30" s="12" t="n"/>
-      <c r="AA30" s="7" t="n"/>
+      <c r="AA30" s="8" t="n"/>
+      <c r="AB30" s="12" t="n"/>
+      <c r="AC30" s="12" t="n"/>
+      <c r="AD30" s="12" t="n"/>
+      <c r="AE30" s="12" t="n"/>
+      <c r="AF30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="B31" s="4" t="n"/>
@@ -2081,7 +2217,12 @@
       <c r="X31" s="12" t="n"/>
       <c r="Y31" s="12" t="n"/>
       <c r="Z31" s="12" t="n"/>
-      <c r="AA31" s="7" t="n"/>
+      <c r="AA31" s="8" t="n"/>
+      <c r="AB31" s="12" t="n"/>
+      <c r="AC31" s="12" t="n"/>
+      <c r="AD31" s="12" t="n"/>
+      <c r="AE31" s="12" t="n"/>
+      <c r="AF31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="B32" s="4" t="n"/>
@@ -2109,7 +2250,12 @@
       <c r="X32" s="12" t="n"/>
       <c r="Y32" s="12" t="n"/>
       <c r="Z32" s="12" t="n"/>
-      <c r="AA32" s="7" t="n"/>
+      <c r="AA32" s="8" t="n"/>
+      <c r="AB32" s="12" t="n"/>
+      <c r="AC32" s="12" t="n"/>
+      <c r="AD32" s="12" t="n"/>
+      <c r="AE32" s="12" t="n"/>
+      <c r="AF32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="B33" s="4" t="n"/>
@@ -2137,7 +2283,12 @@
       <c r="X33" s="12" t="n"/>
       <c r="Y33" s="12" t="n"/>
       <c r="Z33" s="12" t="n"/>
-      <c r="AA33" s="7" t="n"/>
+      <c r="AA33" s="8" t="n"/>
+      <c r="AB33" s="12" t="n"/>
+      <c r="AC33" s="12" t="n"/>
+      <c r="AD33" s="12" t="n"/>
+      <c r="AE33" s="12" t="n"/>
+      <c r="AF33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="B34" s="4" t="n"/>
@@ -2165,7 +2316,12 @@
       <c r="X34" s="12" t="n"/>
       <c r="Y34" s="12" t="n"/>
       <c r="Z34" s="12" t="n"/>
-      <c r="AA34" s="7" t="n"/>
+      <c r="AA34" s="8" t="n"/>
+      <c r="AB34" s="12" t="n"/>
+      <c r="AC34" s="12" t="n"/>
+      <c r="AD34" s="12" t="n"/>
+      <c r="AE34" s="12" t="n"/>
+      <c r="AF34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="B35" s="4" t="n"/>
@@ -2193,7 +2349,12 @@
       <c r="X35" s="8" t="n"/>
       <c r="Y35" s="8" t="n"/>
       <c r="Z35" s="8" t="n"/>
-      <c r="AA35" s="7" t="n"/>
+      <c r="AA35" s="8" t="n"/>
+      <c r="AB35" s="8" t="n"/>
+      <c r="AC35" s="8" t="n"/>
+      <c r="AD35" s="8" t="n"/>
+      <c r="AE35" s="8" t="n"/>
+      <c r="AF35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="B36" s="4" t="n"/>
@@ -2205,7 +2366,7 @@
       <c r="D36" s="8" t="n"/>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>Weighted Pull-Ups</t>
+          <t>Squat</t>
         </is>
       </c>
       <c r="F36" s="6" t="n"/>
@@ -2215,7 +2376,7 @@
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>70kg</t>
+          <t>142.5kg</t>
         </is>
       </c>
       <c r="J36" s="15" t="n">
@@ -2223,7 +2384,7 @@
       </c>
       <c r="K36" s="16" t="inlineStr">
         <is>
-          <t>Focus on strict form and full range of motion.</t>
+          <t>Wave 1 – Maintain bracing and depth.</t>
         </is>
       </c>
       <c r="L36" s="8" t="n"/>
@@ -2232,15 +2393,15 @@
       </c>
       <c r="N36" s="14" t="inlineStr">
         <is>
-          <t>70kg</t>
+          <t>152.5kg</t>
         </is>
       </c>
       <c r="O36" s="15" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="P36" s="16" t="inlineStr">
         <is>
-          <t>Focus on strict form and full range of motion.</t>
+          <t>Wave 1 – Build pressure from the hole.</t>
         </is>
       </c>
       <c r="Q36" s="8" t="n"/>
@@ -2249,35 +2410,52 @@
       </c>
       <c r="S36" s="14" t="inlineStr">
         <is>
-          <t>70kg</t>
+          <t>162.5kg</t>
         </is>
       </c>
       <c r="T36" s="15" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="U36" s="16" t="inlineStr">
         <is>
-          <t>Focus on strict form and full range of motion.</t>
+          <t>Wave 1 – Top triple; aggressive bar speed.</t>
         </is>
       </c>
       <c r="V36" s="8" t="n"/>
       <c r="W36" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X36" s="14" t="inlineStr">
         <is>
-          <t>70kg</t>
+          <t>157.5kg</t>
         </is>
       </c>
       <c r="Y36" s="15" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="Z36" s="16" t="inlineStr">
         <is>
-          <t>Focus on strict form and full range of motion.</t>
-        </is>
-      </c>
-      <c r="AA36" s="7" t="n"/>
+          <t>Wave 2 – Repeat with speed and stability.</t>
+        </is>
+      </c>
+      <c r="AA36" s="8" t="n"/>
+      <c r="AB36" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC36" s="14" t="inlineStr">
+        <is>
+          <t>165kg</t>
+        </is>
+      </c>
+      <c r="AD36" s="15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AE36" s="16" t="inlineStr">
+        <is>
+          <t>Wave 2 – Final top double with crisp form.</t>
+        </is>
+      </c>
+      <c r="AF36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="B37" s="4" t="n"/>
@@ -2291,41 +2469,41 @@
       <c r="F37" s="6" t="n"/>
       <c r="G37" s="8" t="n"/>
       <c r="H37" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I37" s="14" t="inlineStr">
         <is>
-          <t>20kg</t>
+          <t>17.5kg</t>
         </is>
       </c>
       <c r="J37" s="15" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="K37" s="16" t="inlineStr">
         <is>
-          <t>Perform with explosive yet controlled movement.</t>
+          <t>Controlled swing, fast transition over bar.</t>
         </is>
       </c>
       <c r="L37" s="8" t="n"/>
       <c r="M37" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N37" s="14" t="inlineStr">
         <is>
-          <t>20kg</t>
+          <t>17.5kg</t>
         </is>
       </c>
       <c r="O37" s="15" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="P37" s="16" t="inlineStr">
         <is>
-          <t>Perform with explosive yet controlled movement.</t>
+          <t>Controlled swing, fast transition over bar.</t>
         </is>
       </c>
       <c r="Q37" s="8" t="n"/>
       <c r="R37" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S37" s="14" t="inlineStr">
         <is>
@@ -2333,87 +2511,69 @@
         </is>
       </c>
       <c r="T37" s="15" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="U37" s="16" t="inlineStr">
         <is>
-          <t>Perform with explosive yet controlled movement.</t>
+          <t>Explosive power with clean lockout.</t>
         </is>
       </c>
       <c r="V37" s="8" t="n"/>
-      <c r="W37" s="12" t="n"/>
-      <c r="X37" s="12" t="n"/>
-      <c r="Y37" s="12" t="n"/>
-      <c r="Z37" s="12" t="n"/>
-      <c r="AA37" s="7" t="n"/>
+      <c r="W37" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X37" s="14" t="inlineStr">
+        <is>
+          <t>20kg</t>
+        </is>
+      </c>
+      <c r="Y37" s="15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z37" s="16" t="inlineStr">
+        <is>
+          <t>Explosive power with clean lockout.</t>
+        </is>
+      </c>
+      <c r="AA37" s="8" t="n"/>
+      <c r="AB37" s="12" t="n"/>
+      <c r="AC37" s="12" t="n"/>
+      <c r="AD37" s="12" t="n"/>
+      <c r="AE37" s="12" t="n"/>
+      <c r="AF37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="B38" s="4" t="n"/>
       <c r="C38" s="6" t="n"/>
       <c r="D38" s="8" t="n"/>
-      <c r="E38" s="13" t="inlineStr">
-        <is>
-          <t>Weighted Ring Dips</t>
-        </is>
-      </c>
+      <c r="E38" s="11" t="inlineStr"/>
       <c r="F38" s="6" t="n"/>
       <c r="G38" s="8" t="n"/>
-      <c r="H38" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="I38" s="14" t="inlineStr">
-        <is>
-          <t>45kg</t>
-        </is>
-      </c>
-      <c r="J38" s="15" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K38" s="16" t="inlineStr">
-        <is>
-          <t>Keep strict technique under load.</t>
-        </is>
-      </c>
+      <c r="H38" s="12" t="n"/>
+      <c r="I38" s="12" t="n"/>
+      <c r="J38" s="12" t="n"/>
+      <c r="K38" s="12" t="n"/>
       <c r="L38" s="8" t="n"/>
-      <c r="M38" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="N38" s="14" t="inlineStr">
-        <is>
-          <t>45kg</t>
-        </is>
-      </c>
-      <c r="O38" s="15" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="P38" s="16" t="inlineStr">
-        <is>
-          <t>Keep strict technique under load.</t>
-        </is>
-      </c>
+      <c r="M38" s="12" t="n"/>
+      <c r="N38" s="12" t="n"/>
+      <c r="O38" s="12" t="n"/>
+      <c r="P38" s="12" t="n"/>
       <c r="Q38" s="8" t="n"/>
-      <c r="R38" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="S38" s="14" t="inlineStr">
-        <is>
-          <t>45kg</t>
-        </is>
-      </c>
-      <c r="T38" s="15" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="U38" s="16" t="inlineStr">
-        <is>
-          <t>Keep strict technique under load.</t>
-        </is>
-      </c>
+      <c r="R38" s="12" t="n"/>
+      <c r="S38" s="12" t="n"/>
+      <c r="T38" s="12" t="n"/>
+      <c r="U38" s="12" t="n"/>
       <c r="V38" s="8" t="n"/>
       <c r="W38" s="12" t="n"/>
       <c r="X38" s="12" t="n"/>
       <c r="Y38" s="12" t="n"/>
       <c r="Z38" s="12" t="n"/>
-      <c r="AA38" s="7" t="n"/>
+      <c r="AA38" s="8" t="n"/>
+      <c r="AB38" s="12" t="n"/>
+      <c r="AC38" s="12" t="n"/>
+      <c r="AD38" s="12" t="n"/>
+      <c r="AE38" s="12" t="n"/>
+      <c r="AF38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="B39" s="4" t="n"/>
@@ -2441,7 +2601,12 @@
       <c r="X39" s="12" t="n"/>
       <c r="Y39" s="12" t="n"/>
       <c r="Z39" s="12" t="n"/>
-      <c r="AA39" s="7" t="n"/>
+      <c r="AA39" s="8" t="n"/>
+      <c r="AB39" s="12" t="n"/>
+      <c r="AC39" s="12" t="n"/>
+      <c r="AD39" s="12" t="n"/>
+      <c r="AE39" s="12" t="n"/>
+      <c r="AF39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="B40" s="4" t="n"/>
@@ -2469,7 +2634,12 @@
       <c r="X40" s="12" t="n"/>
       <c r="Y40" s="12" t="n"/>
       <c r="Z40" s="12" t="n"/>
-      <c r="AA40" s="7" t="n"/>
+      <c r="AA40" s="8" t="n"/>
+      <c r="AB40" s="12" t="n"/>
+      <c r="AC40" s="12" t="n"/>
+      <c r="AD40" s="12" t="n"/>
+      <c r="AE40" s="12" t="n"/>
+      <c r="AF40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="B41" s="4" t="n"/>
@@ -2497,7 +2667,12 @@
       <c r="X41" s="12" t="n"/>
       <c r="Y41" s="12" t="n"/>
       <c r="Z41" s="12" t="n"/>
-      <c r="AA41" s="7" t="n"/>
+      <c r="AA41" s="8" t="n"/>
+      <c r="AB41" s="12" t="n"/>
+      <c r="AC41" s="12" t="n"/>
+      <c r="AD41" s="12" t="n"/>
+      <c r="AE41" s="12" t="n"/>
+      <c r="AF41" s="7" t="n"/>
     </row>
     <row r="42">
       <c r="B42" s="4" t="n"/>
@@ -2525,7 +2700,12 @@
       <c r="X42" s="12" t="n"/>
       <c r="Y42" s="12" t="n"/>
       <c r="Z42" s="12" t="n"/>
-      <c r="AA42" s="7" t="n"/>
+      <c r="AA42" s="8" t="n"/>
+      <c r="AB42" s="12" t="n"/>
+      <c r="AC42" s="12" t="n"/>
+      <c r="AD42" s="12" t="n"/>
+      <c r="AE42" s="12" t="n"/>
+      <c r="AF42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="B43" s="4" t="n"/>
@@ -2553,7 +2733,12 @@
       <c r="X43" s="12" t="n"/>
       <c r="Y43" s="12" t="n"/>
       <c r="Z43" s="12" t="n"/>
-      <c r="AA43" s="7" t="n"/>
+      <c r="AA43" s="8" t="n"/>
+      <c r="AB43" s="12" t="n"/>
+      <c r="AC43" s="12" t="n"/>
+      <c r="AD43" s="12" t="n"/>
+      <c r="AE43" s="12" t="n"/>
+      <c r="AF43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="B44" s="4" t="n"/>
@@ -2581,7 +2766,12 @@
       <c r="X44" s="8" t="n"/>
       <c r="Y44" s="8" t="n"/>
       <c r="Z44" s="8" t="n"/>
-      <c r="AA44" s="7" t="n"/>
+      <c r="AA44" s="8" t="n"/>
+      <c r="AB44" s="8" t="n"/>
+      <c r="AC44" s="8" t="n"/>
+      <c r="AD44" s="8" t="n"/>
+      <c r="AE44" s="8" t="n"/>
+      <c r="AF44" s="7" t="n"/>
     </row>
     <row r="45">
       <c r="B45" s="4" t="n"/>
@@ -2591,57 +2781,183 @@
         </is>
       </c>
       <c r="D45" s="8" t="n"/>
-      <c r="E45" s="11" t="inlineStr"/>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>Weighted Pull-Ups</t>
+        </is>
+      </c>
       <c r="F45" s="6" t="n"/>
       <c r="G45" s="8" t="n"/>
-      <c r="H45" s="12" t="n"/>
-      <c r="I45" s="12" t="n"/>
-      <c r="J45" s="12" t="n"/>
-      <c r="K45" s="12" t="n"/>
+      <c r="H45" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I45" s="14" t="inlineStr">
+        <is>
+          <t>55kg</t>
+        </is>
+      </c>
+      <c r="J45" s="15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K45" s="16" t="inlineStr">
+        <is>
+          <t>Tight scap engagement, even pull.</t>
+        </is>
+      </c>
       <c r="L45" s="8" t="n"/>
-      <c r="M45" s="12" t="n"/>
-      <c r="N45" s="12" t="n"/>
-      <c r="O45" s="12" t="n"/>
-      <c r="P45" s="12" t="n"/>
+      <c r="M45" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="N45" s="14" t="inlineStr">
+        <is>
+          <t>55kg</t>
+        </is>
+      </c>
+      <c r="O45" s="15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P45" s="16" t="inlineStr">
+        <is>
+          <t>Tight scap engagement, even pull.</t>
+        </is>
+      </c>
       <c r="Q45" s="8" t="n"/>
-      <c r="R45" s="12" t="n"/>
-      <c r="S45" s="12" t="n"/>
-      <c r="T45" s="12" t="n"/>
-      <c r="U45" s="12" t="n"/>
+      <c r="R45" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="S45" s="14" t="inlineStr">
+        <is>
+          <t>55kg</t>
+        </is>
+      </c>
+      <c r="T45" s="15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="U45" s="16" t="inlineStr">
+        <is>
+          <t>Tight scap engagement, even pull.</t>
+        </is>
+      </c>
       <c r="V45" s="8" t="n"/>
-      <c r="W45" s="12" t="n"/>
-      <c r="X45" s="12" t="n"/>
-      <c r="Y45" s="12" t="n"/>
-      <c r="Z45" s="12" t="n"/>
-      <c r="AA45" s="7" t="n"/>
+      <c r="W45" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="X45" s="14" t="inlineStr">
+        <is>
+          <t>55kg</t>
+        </is>
+      </c>
+      <c r="Y45" s="15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Z45" s="16" t="inlineStr">
+        <is>
+          <t>Tight scap engagement, even pull.</t>
+        </is>
+      </c>
+      <c r="AA45" s="8" t="n"/>
+      <c r="AB45" s="12" t="n"/>
+      <c r="AC45" s="12" t="n"/>
+      <c r="AD45" s="12" t="n"/>
+      <c r="AE45" s="12" t="n"/>
+      <c r="AF45" s="7" t="n"/>
     </row>
     <row r="46">
       <c r="B46" s="4" t="n"/>
       <c r="C46" s="6" t="n"/>
       <c r="D46" s="8" t="n"/>
-      <c r="E46" s="11" t="inlineStr"/>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>Weighted Dips</t>
+        </is>
+      </c>
       <c r="F46" s="6" t="n"/>
       <c r="G46" s="8" t="n"/>
-      <c r="H46" s="12" t="n"/>
-      <c r="I46" s="12" t="n"/>
-      <c r="J46" s="12" t="n"/>
-      <c r="K46" s="12" t="n"/>
+      <c r="H46" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I46" s="14" t="inlineStr">
+        <is>
+          <t>55kg</t>
+        </is>
+      </c>
+      <c r="J46" s="15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K46" s="16" t="inlineStr">
+        <is>
+          <t>Controlled descent, strong lockout.</t>
+        </is>
+      </c>
       <c r="L46" s="8" t="n"/>
-      <c r="M46" s="12" t="n"/>
-      <c r="N46" s="12" t="n"/>
-      <c r="O46" s="12" t="n"/>
-      <c r="P46" s="12" t="n"/>
+      <c r="M46" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="N46" s="14" t="inlineStr">
+        <is>
+          <t>55kg</t>
+        </is>
+      </c>
+      <c r="O46" s="15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P46" s="16" t="inlineStr">
+        <is>
+          <t>Controlled descent, strong lockout.</t>
+        </is>
+      </c>
       <c r="Q46" s="8" t="n"/>
-      <c r="R46" s="12" t="n"/>
-      <c r="S46" s="12" t="n"/>
-      <c r="T46" s="12" t="n"/>
-      <c r="U46" s="12" t="n"/>
+      <c r="R46" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="S46" s="14" t="inlineStr">
+        <is>
+          <t>55kg</t>
+        </is>
+      </c>
+      <c r="T46" s="15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="U46" s="16" t="inlineStr">
+        <is>
+          <t>Controlled descent, strong lockout.</t>
+        </is>
+      </c>
       <c r="V46" s="8" t="n"/>
-      <c r="W46" s="12" t="n"/>
-      <c r="X46" s="12" t="n"/>
-      <c r="Y46" s="12" t="n"/>
-      <c r="Z46" s="12" t="n"/>
-      <c r="AA46" s="7" t="n"/>
+      <c r="W46" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="X46" s="14" t="inlineStr">
+        <is>
+          <t>55kg</t>
+        </is>
+      </c>
+      <c r="Y46" s="15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Z46" s="16" t="inlineStr">
+        <is>
+          <t>Controlled descent, strong lockout.</t>
+        </is>
+      </c>
+      <c r="AA46" s="8" t="n"/>
+      <c r="AB46" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC46" s="14" t="inlineStr">
+        <is>
+          <t>55kg</t>
+        </is>
+      </c>
+      <c r="AD46" s="15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AE46" s="16" t="inlineStr">
+        <is>
+          <t>Controlled descent, strong lockout.</t>
+        </is>
+      </c>
+      <c r="AF46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="B47" s="4" t="n"/>
@@ -2669,7 +2985,12 @@
       <c r="X47" s="12" t="n"/>
       <c r="Y47" s="12" t="n"/>
       <c r="Z47" s="12" t="n"/>
-      <c r="AA47" s="7" t="n"/>
+      <c r="AA47" s="8" t="n"/>
+      <c r="AB47" s="12" t="n"/>
+      <c r="AC47" s="12" t="n"/>
+      <c r="AD47" s="12" t="n"/>
+      <c r="AE47" s="12" t="n"/>
+      <c r="AF47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="B48" s="4" t="n"/>
@@ -2697,7 +3018,12 @@
       <c r="X48" s="12" t="n"/>
       <c r="Y48" s="12" t="n"/>
       <c r="Z48" s="12" t="n"/>
-      <c r="AA48" s="7" t="n"/>
+      <c r="AA48" s="8" t="n"/>
+      <c r="AB48" s="12" t="n"/>
+      <c r="AC48" s="12" t="n"/>
+      <c r="AD48" s="12" t="n"/>
+      <c r="AE48" s="12" t="n"/>
+      <c r="AF48" s="7" t="n"/>
     </row>
     <row r="49">
       <c r="B49" s="4" t="n"/>
@@ -2725,7 +3051,12 @@
       <c r="X49" s="12" t="n"/>
       <c r="Y49" s="12" t="n"/>
       <c r="Z49" s="12" t="n"/>
-      <c r="AA49" s="7" t="n"/>
+      <c r="AA49" s="8" t="n"/>
+      <c r="AB49" s="12" t="n"/>
+      <c r="AC49" s="12" t="n"/>
+      <c r="AD49" s="12" t="n"/>
+      <c r="AE49" s="12" t="n"/>
+      <c r="AF49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="B50" s="4" t="n"/>
@@ -2753,7 +3084,12 @@
       <c r="X50" s="12" t="n"/>
       <c r="Y50" s="12" t="n"/>
       <c r="Z50" s="12" t="n"/>
-      <c r="AA50" s="7" t="n"/>
+      <c r="AA50" s="8" t="n"/>
+      <c r="AB50" s="12" t="n"/>
+      <c r="AC50" s="12" t="n"/>
+      <c r="AD50" s="12" t="n"/>
+      <c r="AE50" s="12" t="n"/>
+      <c r="AF50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="B51" s="4" t="n"/>
@@ -2781,7 +3117,12 @@
       <c r="X51" s="12" t="n"/>
       <c r="Y51" s="12" t="n"/>
       <c r="Z51" s="12" t="n"/>
-      <c r="AA51" s="7" t="n"/>
+      <c r="AA51" s="8" t="n"/>
+      <c r="AB51" s="12" t="n"/>
+      <c r="AC51" s="12" t="n"/>
+      <c r="AD51" s="12" t="n"/>
+      <c r="AE51" s="12" t="n"/>
+      <c r="AF51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="B52" s="4" t="n"/>
@@ -2809,7 +3150,12 @@
       <c r="X52" s="12" t="n"/>
       <c r="Y52" s="12" t="n"/>
       <c r="Z52" s="12" t="n"/>
-      <c r="AA52" s="7" t="n"/>
+      <c r="AA52" s="8" t="n"/>
+      <c r="AB52" s="12" t="n"/>
+      <c r="AC52" s="12" t="n"/>
+      <c r="AD52" s="12" t="n"/>
+      <c r="AE52" s="12" t="n"/>
+      <c r="AF52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="B53" s="4" t="n"/>
@@ -2837,7 +3183,12 @@
       <c r="X53" s="8" t="n"/>
       <c r="Y53" s="8" t="n"/>
       <c r="Z53" s="8" t="n"/>
-      <c r="AA53" s="7" t="n"/>
+      <c r="AA53" s="8" t="n"/>
+      <c r="AB53" s="8" t="n"/>
+      <c r="AC53" s="8" t="n"/>
+      <c r="AD53" s="8" t="n"/>
+      <c r="AE53" s="8" t="n"/>
+      <c r="AF53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="B54" s="4" t="n"/>
@@ -2847,21 +3198,13 @@
         </is>
       </c>
       <c r="D54" s="8" t="n"/>
-      <c r="E54" s="13" t="inlineStr">
-        <is>
-          <t>Mobility &amp; Recovery Work</t>
-        </is>
-      </c>
+      <c r="E54" s="11" t="inlineStr"/>
       <c r="F54" s="6" t="n"/>
       <c r="G54" s="8" t="n"/>
-      <c r="H54" s="14" t="inlineStr"/>
-      <c r="I54" s="14" t="inlineStr"/>
-      <c r="J54" s="14" t="inlineStr"/>
-      <c r="K54" s="16" t="inlineStr">
-        <is>
-          <t>25 minutes of dynamic stretching, handstands, foam rolling, and mobility drills.</t>
-        </is>
-      </c>
+      <c r="H54" s="12" t="n"/>
+      <c r="I54" s="12" t="n"/>
+      <c r="J54" s="12" t="n"/>
+      <c r="K54" s="12" t="n"/>
       <c r="L54" s="8" t="n"/>
       <c r="M54" s="12" t="n"/>
       <c r="N54" s="12" t="n"/>
@@ -2877,7 +3220,12 @@
       <c r="X54" s="12" t="n"/>
       <c r="Y54" s="12" t="n"/>
       <c r="Z54" s="12" t="n"/>
-      <c r="AA54" s="7" t="n"/>
+      <c r="AA54" s="8" t="n"/>
+      <c r="AB54" s="12" t="n"/>
+      <c r="AC54" s="12" t="n"/>
+      <c r="AD54" s="12" t="n"/>
+      <c r="AE54" s="12" t="n"/>
+      <c r="AF54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="B55" s="4" t="n"/>
@@ -2905,7 +3253,12 @@
       <c r="X55" s="12" t="n"/>
       <c r="Y55" s="12" t="n"/>
       <c r="Z55" s="12" t="n"/>
-      <c r="AA55" s="7" t="n"/>
+      <c r="AA55" s="8" t="n"/>
+      <c r="AB55" s="12" t="n"/>
+      <c r="AC55" s="12" t="n"/>
+      <c r="AD55" s="12" t="n"/>
+      <c r="AE55" s="12" t="n"/>
+      <c r="AF55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="B56" s="4" t="n"/>
@@ -2933,7 +3286,12 @@
       <c r="X56" s="12" t="n"/>
       <c r="Y56" s="12" t="n"/>
       <c r="Z56" s="12" t="n"/>
-      <c r="AA56" s="7" t="n"/>
+      <c r="AA56" s="8" t="n"/>
+      <c r="AB56" s="12" t="n"/>
+      <c r="AC56" s="12" t="n"/>
+      <c r="AD56" s="12" t="n"/>
+      <c r="AE56" s="12" t="n"/>
+      <c r="AF56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="B57" s="4" t="n"/>
@@ -2961,7 +3319,12 @@
       <c r="X57" s="12" t="n"/>
       <c r="Y57" s="12" t="n"/>
       <c r="Z57" s="12" t="n"/>
-      <c r="AA57" s="7" t="n"/>
+      <c r="AA57" s="8" t="n"/>
+      <c r="AB57" s="12" t="n"/>
+      <c r="AC57" s="12" t="n"/>
+      <c r="AD57" s="12" t="n"/>
+      <c r="AE57" s="12" t="n"/>
+      <c r="AF57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="B58" s="4" t="n"/>
@@ -2989,7 +3352,12 @@
       <c r="X58" s="12" t="n"/>
       <c r="Y58" s="12" t="n"/>
       <c r="Z58" s="12" t="n"/>
-      <c r="AA58" s="7" t="n"/>
+      <c r="AA58" s="8" t="n"/>
+      <c r="AB58" s="12" t="n"/>
+      <c r="AC58" s="12" t="n"/>
+      <c r="AD58" s="12" t="n"/>
+      <c r="AE58" s="12" t="n"/>
+      <c r="AF58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="B59" s="4" t="n"/>
@@ -3017,7 +3385,12 @@
       <c r="X59" s="12" t="n"/>
       <c r="Y59" s="12" t="n"/>
       <c r="Z59" s="12" t="n"/>
-      <c r="AA59" s="7" t="n"/>
+      <c r="AA59" s="8" t="n"/>
+      <c r="AB59" s="12" t="n"/>
+      <c r="AC59" s="12" t="n"/>
+      <c r="AD59" s="12" t="n"/>
+      <c r="AE59" s="12" t="n"/>
+      <c r="AF59" s="7" t="n"/>
     </row>
     <row r="60">
       <c r="B60" s="4" t="n"/>
@@ -3045,7 +3418,12 @@
       <c r="X60" s="12" t="n"/>
       <c r="Y60" s="12" t="n"/>
       <c r="Z60" s="12" t="n"/>
-      <c r="AA60" s="7" t="n"/>
+      <c r="AA60" s="8" t="n"/>
+      <c r="AB60" s="12" t="n"/>
+      <c r="AC60" s="12" t="n"/>
+      <c r="AD60" s="12" t="n"/>
+      <c r="AE60" s="12" t="n"/>
+      <c r="AF60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="B61" s="4" t="n"/>
@@ -3073,7 +3451,12 @@
       <c r="X61" s="12" t="n"/>
       <c r="Y61" s="12" t="n"/>
       <c r="Z61" s="12" t="n"/>
-      <c r="AA61" s="7" t="n"/>
+      <c r="AA61" s="8" t="n"/>
+      <c r="AB61" s="12" t="n"/>
+      <c r="AC61" s="12" t="n"/>
+      <c r="AD61" s="12" t="n"/>
+      <c r="AE61" s="12" t="n"/>
+      <c r="AF61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="B62" s="4" t="n"/>
@@ -3101,7 +3484,12 @@
       <c r="X62" s="8" t="n"/>
       <c r="Y62" s="8" t="n"/>
       <c r="Z62" s="8" t="n"/>
-      <c r="AA62" s="7" t="n"/>
+      <c r="AA62" s="8" t="n"/>
+      <c r="AB62" s="8" t="n"/>
+      <c r="AC62" s="8" t="n"/>
+      <c r="AD62" s="8" t="n"/>
+      <c r="AE62" s="8" t="n"/>
+      <c r="AF62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="B63" s="4" t="n"/>
@@ -3111,57 +3499,171 @@
         </is>
       </c>
       <c r="D63" s="8" t="n"/>
-      <c r="E63" s="11" t="inlineStr"/>
+      <c r="E63" s="13" t="inlineStr">
+        <is>
+          <t>Squat</t>
+        </is>
+      </c>
       <c r="F63" s="6" t="n"/>
       <c r="G63" s="8" t="n"/>
-      <c r="H63" s="12" t="n"/>
-      <c r="I63" s="12" t="n"/>
-      <c r="J63" s="12" t="n"/>
-      <c r="K63" s="12" t="n"/>
+      <c r="H63" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I63" s="14" t="inlineStr">
+        <is>
+          <t>102.5kg</t>
+        </is>
+      </c>
+      <c r="J63" s="15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K63" s="16" t="inlineStr">
+        <is>
+          <t>Tempo 3-0-1 or paused squats, stay snappy.</t>
+        </is>
+      </c>
       <c r="L63" s="8" t="n"/>
-      <c r="M63" s="12" t="n"/>
-      <c r="N63" s="12" t="n"/>
-      <c r="O63" s="12" t="n"/>
-      <c r="P63" s="12" t="n"/>
+      <c r="M63" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N63" s="14" t="inlineStr">
+        <is>
+          <t>102.5kg</t>
+        </is>
+      </c>
+      <c r="O63" s="15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P63" s="16" t="inlineStr">
+        <is>
+          <t>Tempo 3-0-1 or paused squats, stay snappy.</t>
+        </is>
+      </c>
       <c r="Q63" s="8" t="n"/>
-      <c r="R63" s="12" t="n"/>
-      <c r="S63" s="12" t="n"/>
-      <c r="T63" s="12" t="n"/>
-      <c r="U63" s="12" t="n"/>
+      <c r="R63" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="S63" s="14" t="inlineStr">
+        <is>
+          <t>102.5kg</t>
+        </is>
+      </c>
+      <c r="T63" s="15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U63" s="16" t="inlineStr">
+        <is>
+          <t>Tempo 3-0-1 or paused squats, stay snappy.</t>
+        </is>
+      </c>
       <c r="V63" s="8" t="n"/>
       <c r="W63" s="12" t="n"/>
       <c r="X63" s="12" t="n"/>
       <c r="Y63" s="12" t="n"/>
       <c r="Z63" s="12" t="n"/>
-      <c r="AA63" s="7" t="n"/>
+      <c r="AA63" s="8" t="n"/>
+      <c r="AB63" s="12" t="n"/>
+      <c r="AC63" s="12" t="n"/>
+      <c r="AD63" s="12" t="n"/>
+      <c r="AE63" s="12" t="n"/>
+      <c r="AF63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="B64" s="4" t="n"/>
       <c r="C64" s="6" t="n"/>
       <c r="D64" s="8" t="n"/>
-      <c r="E64" s="11" t="inlineStr"/>
+      <c r="E64" s="13" t="inlineStr">
+        <is>
+          <t>Weighted Muscle-Ups</t>
+        </is>
+      </c>
       <c r="F64" s="6" t="n"/>
       <c r="G64" s="8" t="n"/>
-      <c r="H64" s="12" t="n"/>
-      <c r="I64" s="12" t="n"/>
-      <c r="J64" s="12" t="n"/>
-      <c r="K64" s="12" t="n"/>
+      <c r="H64" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" s="14" t="inlineStr">
+        <is>
+          <t>16.2kg</t>
+        </is>
+      </c>
+      <c r="J64" s="15" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="K64" s="16" t="inlineStr">
+        <is>
+          <t>Every minute on the minute; crisp and fast reps.</t>
+        </is>
+      </c>
       <c r="L64" s="8" t="n"/>
-      <c r="M64" s="12" t="n"/>
-      <c r="N64" s="12" t="n"/>
-      <c r="O64" s="12" t="n"/>
-      <c r="P64" s="12" t="n"/>
+      <c r="M64" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N64" s="14" t="inlineStr">
+        <is>
+          <t>16.2kg</t>
+        </is>
+      </c>
+      <c r="O64" s="15" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="P64" s="16" t="inlineStr">
+        <is>
+          <t>Every minute on the minute; crisp and fast reps.</t>
+        </is>
+      </c>
       <c r="Q64" s="8" t="n"/>
-      <c r="R64" s="12" t="n"/>
-      <c r="S64" s="12" t="n"/>
-      <c r="T64" s="12" t="n"/>
-      <c r="U64" s="12" t="n"/>
+      <c r="R64" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S64" s="14" t="inlineStr">
+        <is>
+          <t>16.2kg</t>
+        </is>
+      </c>
+      <c r="T64" s="15" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="U64" s="16" t="inlineStr">
+        <is>
+          <t>Every minute on the minute; crisp and fast reps.</t>
+        </is>
+      </c>
       <c r="V64" s="8" t="n"/>
-      <c r="W64" s="12" t="n"/>
-      <c r="X64" s="12" t="n"/>
-      <c r="Y64" s="12" t="n"/>
-      <c r="Z64" s="12" t="n"/>
-      <c r="AA64" s="7" t="n"/>
+      <c r="W64" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X64" s="14" t="inlineStr">
+        <is>
+          <t>16.2kg</t>
+        </is>
+      </c>
+      <c r="Y64" s="15" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="Z64" s="16" t="inlineStr">
+        <is>
+          <t>Every minute on the minute; crisp and fast reps.</t>
+        </is>
+      </c>
+      <c r="AA64" s="8" t="n"/>
+      <c r="AB64" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC64" s="14" t="inlineStr">
+        <is>
+          <t>16.2kg</t>
+        </is>
+      </c>
+      <c r="AD64" s="15" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AE64" s="16" t="inlineStr">
+        <is>
+          <t>Every minute on the minute; crisp and fast reps.</t>
+        </is>
+      </c>
+      <c r="AF64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="B65" s="4" t="n"/>
@@ -3189,7 +3691,12 @@
       <c r="X65" s="12" t="n"/>
       <c r="Y65" s="12" t="n"/>
       <c r="Z65" s="12" t="n"/>
-      <c r="AA65" s="7" t="n"/>
+      <c r="AA65" s="8" t="n"/>
+      <c r="AB65" s="12" t="n"/>
+      <c r="AC65" s="12" t="n"/>
+      <c r="AD65" s="12" t="n"/>
+      <c r="AE65" s="12" t="n"/>
+      <c r="AF65" s="7" t="n"/>
     </row>
     <row r="66">
       <c r="B66" s="4" t="n"/>
@@ -3217,7 +3724,12 @@
       <c r="X66" s="12" t="n"/>
       <c r="Y66" s="12" t="n"/>
       <c r="Z66" s="12" t="n"/>
-      <c r="AA66" s="7" t="n"/>
+      <c r="AA66" s="8" t="n"/>
+      <c r="AB66" s="12" t="n"/>
+      <c r="AC66" s="12" t="n"/>
+      <c r="AD66" s="12" t="n"/>
+      <c r="AE66" s="12" t="n"/>
+      <c r="AF66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="B67" s="4" t="n"/>
@@ -3245,7 +3757,12 @@
       <c r="X67" s="12" t="n"/>
       <c r="Y67" s="12" t="n"/>
       <c r="Z67" s="12" t="n"/>
-      <c r="AA67" s="7" t="n"/>
+      <c r="AA67" s="8" t="n"/>
+      <c r="AB67" s="12" t="n"/>
+      <c r="AC67" s="12" t="n"/>
+      <c r="AD67" s="12" t="n"/>
+      <c r="AE67" s="12" t="n"/>
+      <c r="AF67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="B68" s="4" t="n"/>
@@ -3273,7 +3790,12 @@
       <c r="X68" s="12" t="n"/>
       <c r="Y68" s="12" t="n"/>
       <c r="Z68" s="12" t="n"/>
-      <c r="AA68" s="7" t="n"/>
+      <c r="AA68" s="8" t="n"/>
+      <c r="AB68" s="12" t="n"/>
+      <c r="AC68" s="12" t="n"/>
+      <c r="AD68" s="12" t="n"/>
+      <c r="AE68" s="12" t="n"/>
+      <c r="AF68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="B69" s="4" t="n"/>
@@ -3301,7 +3823,12 @@
       <c r="X69" s="12" t="n"/>
       <c r="Y69" s="12" t="n"/>
       <c r="Z69" s="12" t="n"/>
-      <c r="AA69" s="7" t="n"/>
+      <c r="AA69" s="8" t="n"/>
+      <c r="AB69" s="12" t="n"/>
+      <c r="AC69" s="12" t="n"/>
+      <c r="AD69" s="12" t="n"/>
+      <c r="AE69" s="12" t="n"/>
+      <c r="AF69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="B70" s="4" t="n"/>
@@ -3329,7 +3856,12 @@
       <c r="X70" s="12" t="n"/>
       <c r="Y70" s="12" t="n"/>
       <c r="Z70" s="12" t="n"/>
-      <c r="AA70" s="7" t="n"/>
+      <c r="AA70" s="8" t="n"/>
+      <c r="AB70" s="12" t="n"/>
+      <c r="AC70" s="12" t="n"/>
+      <c r="AD70" s="12" t="n"/>
+      <c r="AE70" s="12" t="n"/>
+      <c r="AF70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="B71" s="17" t="n"/>
@@ -3357,10 +3889,15 @@
       <c r="X71" s="18" t="n"/>
       <c r="Y71" s="18" t="n"/>
       <c r="Z71" s="18" t="n"/>
-      <c r="AA71" s="19" t="n"/>
+      <c r="AA71" s="18" t="n"/>
+      <c r="AB71" s="18" t="n"/>
+      <c r="AC71" s="18" t="n"/>
+      <c r="AD71" s="18" t="n"/>
+      <c r="AE71" s="18" t="n"/>
+      <c r="AF71" s="19" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="68">
+  <mergeCells count="69">
     <mergeCell ref="E43:F43"/>
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="E50:F50"/>
@@ -3369,6 +3906,7 @@
     <mergeCell ref="E68:F68"/>
     <mergeCell ref="E33:F33"/>
     <mergeCell ref="E67:F67"/>
+    <mergeCell ref="C3:AE3"/>
     <mergeCell ref="E42:F42"/>
     <mergeCell ref="E23:F23"/>
     <mergeCell ref="E14:F14"/>
@@ -3386,9 +3924,10 @@
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="E63:F63"/>
     <mergeCell ref="E28:F28"/>
+    <mergeCell ref="AB6:AE6"/>
     <mergeCell ref="E13:F13"/>
+    <mergeCell ref="C63:C70"/>
     <mergeCell ref="E69:F69"/>
-    <mergeCell ref="C63:C70"/>
     <mergeCell ref="E60:F60"/>
     <mergeCell ref="E40:F40"/>
     <mergeCell ref="E9:F9"/>
@@ -3416,7 +3955,6 @@
     <mergeCell ref="C36:C43"/>
     <mergeCell ref="C27:C34"/>
     <mergeCell ref="E57:F57"/>
-    <mergeCell ref="C3:Z3"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="E54:F54"/>
     <mergeCell ref="E32:F32"/>
@@ -3470,13 +4008,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>78</v>
+        <v>81.17647058823529</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>78</v>
+        <v>81.17647058823529</v>
       </c>
     </row>
   </sheetData>

--- a/workout_plan_new.xlsx
+++ b/workout_plan_new.xlsx
@@ -46,38 +46,38 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="005288C5"/>
-        <bgColor rgb="005288C5"/>
+        <fgColor rgb="005265C5"/>
+        <bgColor rgb="005265C5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="006595CC"/>
-        <bgColor rgb="006595CC"/>
+        <fgColor rgb="006576CC"/>
+        <bgColor rgb="006576CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0079A2D2"/>
-        <bgColor rgb="0079A2D2"/>
+        <fgColor rgb="007987D2"/>
+        <bgColor rgb="007987D2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="008CAFD8"/>
-        <bgColor rgb="008CAFD8"/>
+        <fgColor rgb="008C99D8"/>
+        <bgColor rgb="008C99D8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="009FBDDF"/>
-        <bgColor rgb="009FBDDF"/>
+        <fgColor rgb="009FAADF"/>
+        <bgColor rgb="009FAADF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00B2CAE5"/>
-        <bgColor rgb="00B2CAE5"/>
+        <fgColor rgb="00B2BBE5"/>
+        <bgColor rgb="00B2BBE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -316,12 +316,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Charts'!$A$2</f>
+              <f>'Charts'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Charts'!$B$2</f>
+              <f>'Charts'!$B$2:$B$4</f>
             </numRef>
           </val>
         </ser>
@@ -434,12 +434,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Charts'!$A$2</f>
+              <f>'Charts'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Charts'!$C$2</f>
+              <f>'Charts'!$C$2:$C$4</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Charts'!$A$2</f>
+              <f>'Charts'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Charts'!$D$2</f>
+              <f>'Charts'!$D$2:$D$4</f>
             </numRef>
           </val>
         </ser>
@@ -986,7 +986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:AF71"/>
+  <dimension ref="B1:CV71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="9" max="9"/>
@@ -999,6 +999,26 @@
     <col width="35" customWidth="1" min="26" max="26"/>
     <col width="13" customWidth="1" min="29" max="29"/>
     <col width="33.59999999999999" customWidth="1" min="31" max="31"/>
+    <col width="13" customWidth="1" min="43" max="43"/>
+    <col width="36.4" customWidth="1" min="45" max="45"/>
+    <col width="13" customWidth="1" min="48" max="48"/>
+    <col width="38.5" customWidth="1" min="50" max="50"/>
+    <col width="13" customWidth="1" min="53" max="53"/>
+    <col width="36.4" customWidth="1" min="55" max="55"/>
+    <col width="13" customWidth="1" min="58" max="58"/>
+    <col width="35" customWidth="1" min="60" max="60"/>
+    <col width="13" customWidth="1" min="63" max="63"/>
+    <col width="35" customWidth="1" min="65" max="65"/>
+    <col width="13" customWidth="1" min="77" max="77"/>
+    <col width="35" customWidth="1" min="79" max="79"/>
+    <col width="13" customWidth="1" min="82" max="82"/>
+    <col width="35" customWidth="1" min="84" max="84"/>
+    <col width="13" customWidth="1" min="87" max="87"/>
+    <col width="35" customWidth="1" min="89" max="89"/>
+    <col width="13" customWidth="1" min="92" max="92"/>
+    <col width="32.2" customWidth="1" min="94" max="94"/>
+    <col width="13" customWidth="1" min="97" max="97"/>
+    <col width="29.4" customWidth="1" min="99" max="99"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -1034,6 +1054,68 @@
       <c r="AD2" s="2" t="n"/>
       <c r="AE2" s="2" t="n"/>
       <c r="AF2" s="3" t="n"/>
+      <c r="AJ2" s="1" t="n"/>
+      <c r="AK2" s="2" t="n"/>
+      <c r="AL2" s="2" t="n"/>
+      <c r="AM2" s="2" t="n"/>
+      <c r="AN2" s="2" t="n"/>
+      <c r="AO2" s="2" t="n"/>
+      <c r="AP2" s="2" t="n"/>
+      <c r="AQ2" s="2" t="n"/>
+      <c r="AR2" s="2" t="n"/>
+      <c r="AS2" s="2" t="n"/>
+      <c r="AT2" s="2" t="n"/>
+      <c r="AU2" s="2" t="n"/>
+      <c r="AV2" s="2" t="n"/>
+      <c r="AW2" s="2" t="n"/>
+      <c r="AX2" s="2" t="n"/>
+      <c r="AY2" s="2" t="n"/>
+      <c r="AZ2" s="2" t="n"/>
+      <c r="BA2" s="2" t="n"/>
+      <c r="BB2" s="2" t="n"/>
+      <c r="BC2" s="2" t="n"/>
+      <c r="BD2" s="2" t="n"/>
+      <c r="BE2" s="2" t="n"/>
+      <c r="BF2" s="2" t="n"/>
+      <c r="BG2" s="2" t="n"/>
+      <c r="BH2" s="2" t="n"/>
+      <c r="BI2" s="2" t="n"/>
+      <c r="BJ2" s="2" t="n"/>
+      <c r="BK2" s="2" t="n"/>
+      <c r="BL2" s="2" t="n"/>
+      <c r="BM2" s="2" t="n"/>
+      <c r="BN2" s="3" t="n"/>
+      <c r="BR2" s="1" t="n"/>
+      <c r="BS2" s="2" t="n"/>
+      <c r="BT2" s="2" t="n"/>
+      <c r="BU2" s="2" t="n"/>
+      <c r="BV2" s="2" t="n"/>
+      <c r="BW2" s="2" t="n"/>
+      <c r="BX2" s="2" t="n"/>
+      <c r="BY2" s="2" t="n"/>
+      <c r="BZ2" s="2" t="n"/>
+      <c r="CA2" s="2" t="n"/>
+      <c r="CB2" s="2" t="n"/>
+      <c r="CC2" s="2" t="n"/>
+      <c r="CD2" s="2" t="n"/>
+      <c r="CE2" s="2" t="n"/>
+      <c r="CF2" s="2" t="n"/>
+      <c r="CG2" s="2" t="n"/>
+      <c r="CH2" s="2" t="n"/>
+      <c r="CI2" s="2" t="n"/>
+      <c r="CJ2" s="2" t="n"/>
+      <c r="CK2" s="2" t="n"/>
+      <c r="CL2" s="2" t="n"/>
+      <c r="CM2" s="2" t="n"/>
+      <c r="CN2" s="2" t="n"/>
+      <c r="CO2" s="2" t="n"/>
+      <c r="CP2" s="2" t="n"/>
+      <c r="CQ2" s="2" t="n"/>
+      <c r="CR2" s="2" t="n"/>
+      <c r="CS2" s="2" t="n"/>
+      <c r="CT2" s="2" t="n"/>
+      <c r="CU2" s="2" t="n"/>
+      <c r="CV2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="B3" s="4" t="n"/>
@@ -1071,6 +1153,76 @@
       <c r="AD3" s="6" t="n"/>
       <c r="AE3" s="6" t="n"/>
       <c r="AF3" s="7" t="n"/>
+      <c r="AJ3" s="4" t="n"/>
+      <c r="AK3" s="5" t="inlineStr">
+        <is>
+          <t>Week 2 - Week Commencing 31-03-2025</t>
+        </is>
+      </c>
+      <c r="AL3" s="6" t="n"/>
+      <c r="AM3" s="6" t="n"/>
+      <c r="AN3" s="6" t="n"/>
+      <c r="AO3" s="6" t="n"/>
+      <c r="AP3" s="6" t="n"/>
+      <c r="AQ3" s="6" t="n"/>
+      <c r="AR3" s="6" t="n"/>
+      <c r="AS3" s="6" t="n"/>
+      <c r="AT3" s="6" t="n"/>
+      <c r="AU3" s="6" t="n"/>
+      <c r="AV3" s="6" t="n"/>
+      <c r="AW3" s="6" t="n"/>
+      <c r="AX3" s="6" t="n"/>
+      <c r="AY3" s="6" t="n"/>
+      <c r="AZ3" s="6" t="n"/>
+      <c r="BA3" s="6" t="n"/>
+      <c r="BB3" s="6" t="n"/>
+      <c r="BC3" s="6" t="n"/>
+      <c r="BD3" s="6" t="n"/>
+      <c r="BE3" s="6" t="n"/>
+      <c r="BF3" s="6" t="n"/>
+      <c r="BG3" s="6" t="n"/>
+      <c r="BH3" s="6" t="n"/>
+      <c r="BI3" s="6" t="n"/>
+      <c r="BJ3" s="6" t="n"/>
+      <c r="BK3" s="6" t="n"/>
+      <c r="BL3" s="6" t="n"/>
+      <c r="BM3" s="6" t="n"/>
+      <c r="BN3" s="7" t="n"/>
+      <c r="BR3" s="4" t="n"/>
+      <c r="BS3" s="5" t="inlineStr">
+        <is>
+          <t>Week 3 - Week Commencing 07-04-2025</t>
+        </is>
+      </c>
+      <c r="BT3" s="6" t="n"/>
+      <c r="BU3" s="6" t="n"/>
+      <c r="BV3" s="6" t="n"/>
+      <c r="BW3" s="6" t="n"/>
+      <c r="BX3" s="6" t="n"/>
+      <c r="BY3" s="6" t="n"/>
+      <c r="BZ3" s="6" t="n"/>
+      <c r="CA3" s="6" t="n"/>
+      <c r="CB3" s="6" t="n"/>
+      <c r="CC3" s="6" t="n"/>
+      <c r="CD3" s="6" t="n"/>
+      <c r="CE3" s="6" t="n"/>
+      <c r="CF3" s="6" t="n"/>
+      <c r="CG3" s="6" t="n"/>
+      <c r="CH3" s="6" t="n"/>
+      <c r="CI3" s="6" t="n"/>
+      <c r="CJ3" s="6" t="n"/>
+      <c r="CK3" s="6" t="n"/>
+      <c r="CL3" s="6" t="n"/>
+      <c r="CM3" s="6" t="n"/>
+      <c r="CN3" s="6" t="n"/>
+      <c r="CO3" s="6" t="n"/>
+      <c r="CP3" s="6" t="n"/>
+      <c r="CQ3" s="6" t="n"/>
+      <c r="CR3" s="6" t="n"/>
+      <c r="CS3" s="6" t="n"/>
+      <c r="CT3" s="6" t="n"/>
+      <c r="CU3" s="6" t="n"/>
+      <c r="CV3" s="7" t="n"/>
     </row>
     <row r="4">
       <c r="B4" s="4" t="n"/>
@@ -1104,6 +1256,68 @@
       <c r="AD4" s="8" t="n"/>
       <c r="AE4" s="8" t="n"/>
       <c r="AF4" s="7" t="n"/>
+      <c r="AJ4" s="4" t="n"/>
+      <c r="AK4" s="8" t="n"/>
+      <c r="AL4" s="8" t="n"/>
+      <c r="AM4" s="8" t="n"/>
+      <c r="AN4" s="8" t="n"/>
+      <c r="AO4" s="8" t="n"/>
+      <c r="AP4" s="8" t="n"/>
+      <c r="AQ4" s="8" t="n"/>
+      <c r="AR4" s="8" t="n"/>
+      <c r="AS4" s="8" t="n"/>
+      <c r="AT4" s="8" t="n"/>
+      <c r="AU4" s="8" t="n"/>
+      <c r="AV4" s="8" t="n"/>
+      <c r="AW4" s="8" t="n"/>
+      <c r="AX4" s="8" t="n"/>
+      <c r="AY4" s="8" t="n"/>
+      <c r="AZ4" s="8" t="n"/>
+      <c r="BA4" s="8" t="n"/>
+      <c r="BB4" s="8" t="n"/>
+      <c r="BC4" s="8" t="n"/>
+      <c r="BD4" s="8" t="n"/>
+      <c r="BE4" s="8" t="n"/>
+      <c r="BF4" s="8" t="n"/>
+      <c r="BG4" s="8" t="n"/>
+      <c r="BH4" s="8" t="n"/>
+      <c r="BI4" s="8" t="n"/>
+      <c r="BJ4" s="8" t="n"/>
+      <c r="BK4" s="8" t="n"/>
+      <c r="BL4" s="8" t="n"/>
+      <c r="BM4" s="8" t="n"/>
+      <c r="BN4" s="7" t="n"/>
+      <c r="BR4" s="4" t="n"/>
+      <c r="BS4" s="8" t="n"/>
+      <c r="BT4" s="8" t="n"/>
+      <c r="BU4" s="8" t="n"/>
+      <c r="BV4" s="8" t="n"/>
+      <c r="BW4" s="8" t="n"/>
+      <c r="BX4" s="8" t="n"/>
+      <c r="BY4" s="8" t="n"/>
+      <c r="BZ4" s="8" t="n"/>
+      <c r="CA4" s="8" t="n"/>
+      <c r="CB4" s="8" t="n"/>
+      <c r="CC4" s="8" t="n"/>
+      <c r="CD4" s="8" t="n"/>
+      <c r="CE4" s="8" t="n"/>
+      <c r="CF4" s="8" t="n"/>
+      <c r="CG4" s="8" t="n"/>
+      <c r="CH4" s="8" t="n"/>
+      <c r="CI4" s="8" t="n"/>
+      <c r="CJ4" s="8" t="n"/>
+      <c r="CK4" s="8" t="n"/>
+      <c r="CL4" s="8" t="n"/>
+      <c r="CM4" s="8" t="n"/>
+      <c r="CN4" s="8" t="n"/>
+      <c r="CO4" s="8" t="n"/>
+      <c r="CP4" s="8" t="n"/>
+      <c r="CQ4" s="8" t="n"/>
+      <c r="CR4" s="8" t="n"/>
+      <c r="CS4" s="8" t="n"/>
+      <c r="CT4" s="8" t="n"/>
+      <c r="CU4" s="8" t="n"/>
+      <c r="CV4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="B5" s="4" t="n"/>
@@ -1137,6 +1351,68 @@
       <c r="AD5" s="8" t="n"/>
       <c r="AE5" s="8" t="n"/>
       <c r="AF5" s="7" t="n"/>
+      <c r="AJ5" s="4" t="n"/>
+      <c r="AK5" s="8" t="n"/>
+      <c r="AL5" s="8" t="n"/>
+      <c r="AM5" s="8" t="n"/>
+      <c r="AN5" s="8" t="n"/>
+      <c r="AO5" s="8" t="n"/>
+      <c r="AP5" s="8" t="n"/>
+      <c r="AQ5" s="8" t="n"/>
+      <c r="AR5" s="8" t="n"/>
+      <c r="AS5" s="8" t="n"/>
+      <c r="AT5" s="8" t="n"/>
+      <c r="AU5" s="8" t="n"/>
+      <c r="AV5" s="8" t="n"/>
+      <c r="AW5" s="8" t="n"/>
+      <c r="AX5" s="8" t="n"/>
+      <c r="AY5" s="8" t="n"/>
+      <c r="AZ5" s="8" t="n"/>
+      <c r="BA5" s="8" t="n"/>
+      <c r="BB5" s="8" t="n"/>
+      <c r="BC5" s="8" t="n"/>
+      <c r="BD5" s="8" t="n"/>
+      <c r="BE5" s="8" t="n"/>
+      <c r="BF5" s="8" t="n"/>
+      <c r="BG5" s="8" t="n"/>
+      <c r="BH5" s="8" t="n"/>
+      <c r="BI5" s="8" t="n"/>
+      <c r="BJ5" s="8" t="n"/>
+      <c r="BK5" s="8" t="n"/>
+      <c r="BL5" s="8" t="n"/>
+      <c r="BM5" s="8" t="n"/>
+      <c r="BN5" s="7" t="n"/>
+      <c r="BR5" s="4" t="n"/>
+      <c r="BS5" s="8" t="n"/>
+      <c r="BT5" s="8" t="n"/>
+      <c r="BU5" s="8" t="n"/>
+      <c r="BV5" s="8" t="n"/>
+      <c r="BW5" s="8" t="n"/>
+      <c r="BX5" s="8" t="n"/>
+      <c r="BY5" s="8" t="n"/>
+      <c r="BZ5" s="8" t="n"/>
+      <c r="CA5" s="8" t="n"/>
+      <c r="CB5" s="8" t="n"/>
+      <c r="CC5" s="8" t="n"/>
+      <c r="CD5" s="8" t="n"/>
+      <c r="CE5" s="8" t="n"/>
+      <c r="CF5" s="8" t="n"/>
+      <c r="CG5" s="8" t="n"/>
+      <c r="CH5" s="8" t="n"/>
+      <c r="CI5" s="8" t="n"/>
+      <c r="CJ5" s="8" t="n"/>
+      <c r="CK5" s="8" t="n"/>
+      <c r="CL5" s="8" t="n"/>
+      <c r="CM5" s="8" t="n"/>
+      <c r="CN5" s="8" t="n"/>
+      <c r="CO5" s="8" t="n"/>
+      <c r="CP5" s="8" t="n"/>
+      <c r="CQ5" s="8" t="n"/>
+      <c r="CR5" s="8" t="n"/>
+      <c r="CS5" s="8" t="n"/>
+      <c r="CT5" s="8" t="n"/>
+      <c r="CU5" s="8" t="n"/>
+      <c r="CV5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="4" t="n"/>
@@ -1190,6 +1466,108 @@
       <c r="AD6" s="6" t="n"/>
       <c r="AE6" s="6" t="n"/>
       <c r="AF6" s="7" t="n"/>
+      <c r="AJ6" s="4" t="n"/>
+      <c r="AK6" s="8" t="n"/>
+      <c r="AL6" s="8" t="n"/>
+      <c r="AM6" s="8" t="n"/>
+      <c r="AN6" s="8" t="n"/>
+      <c r="AO6" s="8" t="n"/>
+      <c r="AP6" s="9" t="inlineStr">
+        <is>
+          <t>Set 1</t>
+        </is>
+      </c>
+      <c r="AQ6" s="6" t="n"/>
+      <c r="AR6" s="6" t="n"/>
+      <c r="AS6" s="6" t="n"/>
+      <c r="AT6" s="8" t="n"/>
+      <c r="AU6" s="9" t="inlineStr">
+        <is>
+          <t>Set 2</t>
+        </is>
+      </c>
+      <c r="AV6" s="6" t="n"/>
+      <c r="AW6" s="6" t="n"/>
+      <c r="AX6" s="6" t="n"/>
+      <c r="AY6" s="8" t="n"/>
+      <c r="AZ6" s="9" t="inlineStr">
+        <is>
+          <t>Set 3</t>
+        </is>
+      </c>
+      <c r="BA6" s="6" t="n"/>
+      <c r="BB6" s="6" t="n"/>
+      <c r="BC6" s="6" t="n"/>
+      <c r="BD6" s="8" t="n"/>
+      <c r="BE6" s="9" t="inlineStr">
+        <is>
+          <t>Set 4</t>
+        </is>
+      </c>
+      <c r="BF6" s="6" t="n"/>
+      <c r="BG6" s="6" t="n"/>
+      <c r="BH6" s="6" t="n"/>
+      <c r="BI6" s="8" t="n"/>
+      <c r="BJ6" s="9" t="inlineStr">
+        <is>
+          <t>Set 5</t>
+        </is>
+      </c>
+      <c r="BK6" s="6" t="n"/>
+      <c r="BL6" s="6" t="n"/>
+      <c r="BM6" s="6" t="n"/>
+      <c r="BN6" s="7" t="n"/>
+      <c r="BR6" s="4" t="n"/>
+      <c r="BS6" s="8" t="n"/>
+      <c r="BT6" s="8" t="n"/>
+      <c r="BU6" s="8" t="n"/>
+      <c r="BV6" s="8" t="n"/>
+      <c r="BW6" s="8" t="n"/>
+      <c r="BX6" s="9" t="inlineStr">
+        <is>
+          <t>Set 1</t>
+        </is>
+      </c>
+      <c r="BY6" s="6" t="n"/>
+      <c r="BZ6" s="6" t="n"/>
+      <c r="CA6" s="6" t="n"/>
+      <c r="CB6" s="8" t="n"/>
+      <c r="CC6" s="9" t="inlineStr">
+        <is>
+          <t>Set 2</t>
+        </is>
+      </c>
+      <c r="CD6" s="6" t="n"/>
+      <c r="CE6" s="6" t="n"/>
+      <c r="CF6" s="6" t="n"/>
+      <c r="CG6" s="8" t="n"/>
+      <c r="CH6" s="9" t="inlineStr">
+        <is>
+          <t>Set 3</t>
+        </is>
+      </c>
+      <c r="CI6" s="6" t="n"/>
+      <c r="CJ6" s="6" t="n"/>
+      <c r="CK6" s="6" t="n"/>
+      <c r="CL6" s="8" t="n"/>
+      <c r="CM6" s="9" t="inlineStr">
+        <is>
+          <t>Set 4</t>
+        </is>
+      </c>
+      <c r="CN6" s="6" t="n"/>
+      <c r="CO6" s="6" t="n"/>
+      <c r="CP6" s="6" t="n"/>
+      <c r="CQ6" s="8" t="n"/>
+      <c r="CR6" s="9" t="inlineStr">
+        <is>
+          <t>Set 5</t>
+        </is>
+      </c>
+      <c r="CS6" s="6" t="n"/>
+      <c r="CT6" s="6" t="n"/>
+      <c r="CU6" s="6" t="n"/>
+      <c r="CV6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="4" t="n"/>
@@ -1303,6 +1681,228 @@
         </is>
       </c>
       <c r="AF7" s="7" t="n"/>
+      <c r="AJ7" s="4" t="n"/>
+      <c r="AK7" s="8" t="n"/>
+      <c r="AL7" s="8" t="n"/>
+      <c r="AM7" s="8" t="n"/>
+      <c r="AN7" s="8" t="n"/>
+      <c r="AO7" s="8" t="n"/>
+      <c r="AP7" s="9" t="inlineStr">
+        <is>
+          <t>Reps</t>
+        </is>
+      </c>
+      <c r="AQ7" s="9" t="inlineStr">
+        <is>
+          <t>Weights</t>
+        </is>
+      </c>
+      <c r="AR7" s="9" t="inlineStr">
+        <is>
+          <t>%1RM</t>
+        </is>
+      </c>
+      <c r="AS7" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="AT7" s="8" t="n"/>
+      <c r="AU7" s="9" t="inlineStr">
+        <is>
+          <t>Reps</t>
+        </is>
+      </c>
+      <c r="AV7" s="9" t="inlineStr">
+        <is>
+          <t>Weights</t>
+        </is>
+      </c>
+      <c r="AW7" s="9" t="inlineStr">
+        <is>
+          <t>%1RM</t>
+        </is>
+      </c>
+      <c r="AX7" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="AY7" s="8" t="n"/>
+      <c r="AZ7" s="9" t="inlineStr">
+        <is>
+          <t>Reps</t>
+        </is>
+      </c>
+      <c r="BA7" s="9" t="inlineStr">
+        <is>
+          <t>Weights</t>
+        </is>
+      </c>
+      <c r="BB7" s="9" t="inlineStr">
+        <is>
+          <t>%1RM</t>
+        </is>
+      </c>
+      <c r="BC7" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="BD7" s="8" t="n"/>
+      <c r="BE7" s="9" t="inlineStr">
+        <is>
+          <t>Reps</t>
+        </is>
+      </c>
+      <c r="BF7" s="9" t="inlineStr">
+        <is>
+          <t>Weights</t>
+        </is>
+      </c>
+      <c r="BG7" s="9" t="inlineStr">
+        <is>
+          <t>%1RM</t>
+        </is>
+      </c>
+      <c r="BH7" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="BI7" s="8" t="n"/>
+      <c r="BJ7" s="9" t="inlineStr">
+        <is>
+          <t>Reps</t>
+        </is>
+      </c>
+      <c r="BK7" s="9" t="inlineStr">
+        <is>
+          <t>Weights</t>
+        </is>
+      </c>
+      <c r="BL7" s="9" t="inlineStr">
+        <is>
+          <t>%1RM</t>
+        </is>
+      </c>
+      <c r="BM7" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="BN7" s="7" t="n"/>
+      <c r="BR7" s="4" t="n"/>
+      <c r="BS7" s="8" t="n"/>
+      <c r="BT7" s="8" t="n"/>
+      <c r="BU7" s="8" t="n"/>
+      <c r="BV7" s="8" t="n"/>
+      <c r="BW7" s="8" t="n"/>
+      <c r="BX7" s="9" t="inlineStr">
+        <is>
+          <t>Reps</t>
+        </is>
+      </c>
+      <c r="BY7" s="9" t="inlineStr">
+        <is>
+          <t>Weights</t>
+        </is>
+      </c>
+      <c r="BZ7" s="9" t="inlineStr">
+        <is>
+          <t>%1RM</t>
+        </is>
+      </c>
+      <c r="CA7" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="CB7" s="8" t="n"/>
+      <c r="CC7" s="9" t="inlineStr">
+        <is>
+          <t>Reps</t>
+        </is>
+      </c>
+      <c r="CD7" s="9" t="inlineStr">
+        <is>
+          <t>Weights</t>
+        </is>
+      </c>
+      <c r="CE7" s="9" t="inlineStr">
+        <is>
+          <t>%1RM</t>
+        </is>
+      </c>
+      <c r="CF7" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="CG7" s="8" t="n"/>
+      <c r="CH7" s="9" t="inlineStr">
+        <is>
+          <t>Reps</t>
+        </is>
+      </c>
+      <c r="CI7" s="9" t="inlineStr">
+        <is>
+          <t>Weights</t>
+        </is>
+      </c>
+      <c r="CJ7" s="9" t="inlineStr">
+        <is>
+          <t>%1RM</t>
+        </is>
+      </c>
+      <c r="CK7" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="CL7" s="8" t="n"/>
+      <c r="CM7" s="9" t="inlineStr">
+        <is>
+          <t>Reps</t>
+        </is>
+      </c>
+      <c r="CN7" s="9" t="inlineStr">
+        <is>
+          <t>Weights</t>
+        </is>
+      </c>
+      <c r="CO7" s="9" t="inlineStr">
+        <is>
+          <t>%1RM</t>
+        </is>
+      </c>
+      <c r="CP7" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="CQ7" s="8" t="n"/>
+      <c r="CR7" s="9" t="inlineStr">
+        <is>
+          <t>Reps</t>
+        </is>
+      </c>
+      <c r="CS7" s="9" t="inlineStr">
+        <is>
+          <t>Weights</t>
+        </is>
+      </c>
+      <c r="CT7" s="9" t="inlineStr">
+        <is>
+          <t>%1RM</t>
+        </is>
+      </c>
+      <c r="CU7" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="CV7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="4" t="n"/>
@@ -1336,6 +1936,68 @@
       <c r="AD8" s="8" t="n"/>
       <c r="AE8" s="8" t="n"/>
       <c r="AF8" s="7" t="n"/>
+      <c r="AJ8" s="4" t="n"/>
+      <c r="AK8" s="8" t="n"/>
+      <c r="AL8" s="8" t="n"/>
+      <c r="AM8" s="8" t="n"/>
+      <c r="AN8" s="8" t="n"/>
+      <c r="AO8" s="8" t="n"/>
+      <c r="AP8" s="8" t="n"/>
+      <c r="AQ8" s="8" t="n"/>
+      <c r="AR8" s="8" t="n"/>
+      <c r="AS8" s="8" t="n"/>
+      <c r="AT8" s="8" t="n"/>
+      <c r="AU8" s="8" t="n"/>
+      <c r="AV8" s="8" t="n"/>
+      <c r="AW8" s="8" t="n"/>
+      <c r="AX8" s="8" t="n"/>
+      <c r="AY8" s="8" t="n"/>
+      <c r="AZ8" s="8" t="n"/>
+      <c r="BA8" s="8" t="n"/>
+      <c r="BB8" s="8" t="n"/>
+      <c r="BC8" s="8" t="n"/>
+      <c r="BD8" s="8" t="n"/>
+      <c r="BE8" s="8" t="n"/>
+      <c r="BF8" s="8" t="n"/>
+      <c r="BG8" s="8" t="n"/>
+      <c r="BH8" s="8" t="n"/>
+      <c r="BI8" s="8" t="n"/>
+      <c r="BJ8" s="8" t="n"/>
+      <c r="BK8" s="8" t="n"/>
+      <c r="BL8" s="8" t="n"/>
+      <c r="BM8" s="8" t="n"/>
+      <c r="BN8" s="7" t="n"/>
+      <c r="BR8" s="4" t="n"/>
+      <c r="BS8" s="8" t="n"/>
+      <c r="BT8" s="8" t="n"/>
+      <c r="BU8" s="8" t="n"/>
+      <c r="BV8" s="8" t="n"/>
+      <c r="BW8" s="8" t="n"/>
+      <c r="BX8" s="8" t="n"/>
+      <c r="BY8" s="8" t="n"/>
+      <c r="BZ8" s="8" t="n"/>
+      <c r="CA8" s="8" t="n"/>
+      <c r="CB8" s="8" t="n"/>
+      <c r="CC8" s="8" t="n"/>
+      <c r="CD8" s="8" t="n"/>
+      <c r="CE8" s="8" t="n"/>
+      <c r="CF8" s="8" t="n"/>
+      <c r="CG8" s="8" t="n"/>
+      <c r="CH8" s="8" t="n"/>
+      <c r="CI8" s="8" t="n"/>
+      <c r="CJ8" s="8" t="n"/>
+      <c r="CK8" s="8" t="n"/>
+      <c r="CL8" s="8" t="n"/>
+      <c r="CM8" s="8" t="n"/>
+      <c r="CN8" s="8" t="n"/>
+      <c r="CO8" s="8" t="n"/>
+      <c r="CP8" s="8" t="n"/>
+      <c r="CQ8" s="8" t="n"/>
+      <c r="CR8" s="8" t="n"/>
+      <c r="CS8" s="8" t="n"/>
+      <c r="CT8" s="8" t="n"/>
+      <c r="CU8" s="8" t="n"/>
+      <c r="CV8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="4" t="n"/>
@@ -1373,6 +2035,76 @@
       <c r="AD9" s="12" t="n"/>
       <c r="AE9" s="12" t="n"/>
       <c r="AF9" s="7" t="n"/>
+      <c r="AJ9" s="4" t="n"/>
+      <c r="AK9" s="10" t="inlineStr">
+        <is>
+          <t>Day 1</t>
+        </is>
+      </c>
+      <c r="AL9" s="8" t="n"/>
+      <c r="AM9" s="11" t="inlineStr"/>
+      <c r="AN9" s="6" t="n"/>
+      <c r="AO9" s="8" t="n"/>
+      <c r="AP9" s="12" t="n"/>
+      <c r="AQ9" s="12" t="n"/>
+      <c r="AR9" s="12" t="n"/>
+      <c r="AS9" s="12" t="n"/>
+      <c r="AT9" s="8" t="n"/>
+      <c r="AU9" s="12" t="n"/>
+      <c r="AV9" s="12" t="n"/>
+      <c r="AW9" s="12" t="n"/>
+      <c r="AX9" s="12" t="n"/>
+      <c r="AY9" s="8" t="n"/>
+      <c r="AZ9" s="12" t="n"/>
+      <c r="BA9" s="12" t="n"/>
+      <c r="BB9" s="12" t="n"/>
+      <c r="BC9" s="12" t="n"/>
+      <c r="BD9" s="8" t="n"/>
+      <c r="BE9" s="12" t="n"/>
+      <c r="BF9" s="12" t="n"/>
+      <c r="BG9" s="12" t="n"/>
+      <c r="BH9" s="12" t="n"/>
+      <c r="BI9" s="8" t="n"/>
+      <c r="BJ9" s="12" t="n"/>
+      <c r="BK9" s="12" t="n"/>
+      <c r="BL9" s="12" t="n"/>
+      <c r="BM9" s="12" t="n"/>
+      <c r="BN9" s="7" t="n"/>
+      <c r="BR9" s="4" t="n"/>
+      <c r="BS9" s="10" t="inlineStr">
+        <is>
+          <t>Day 1</t>
+        </is>
+      </c>
+      <c r="BT9" s="8" t="n"/>
+      <c r="BU9" s="11" t="inlineStr"/>
+      <c r="BV9" s="6" t="n"/>
+      <c r="BW9" s="8" t="n"/>
+      <c r="BX9" s="12" t="n"/>
+      <c r="BY9" s="12" t="n"/>
+      <c r="BZ9" s="12" t="n"/>
+      <c r="CA9" s="12" t="n"/>
+      <c r="CB9" s="8" t="n"/>
+      <c r="CC9" s="12" t="n"/>
+      <c r="CD9" s="12" t="n"/>
+      <c r="CE9" s="12" t="n"/>
+      <c r="CF9" s="12" t="n"/>
+      <c r="CG9" s="8" t="n"/>
+      <c r="CH9" s="12" t="n"/>
+      <c r="CI9" s="12" t="n"/>
+      <c r="CJ9" s="12" t="n"/>
+      <c r="CK9" s="12" t="n"/>
+      <c r="CL9" s="8" t="n"/>
+      <c r="CM9" s="12" t="n"/>
+      <c r="CN9" s="12" t="n"/>
+      <c r="CO9" s="12" t="n"/>
+      <c r="CP9" s="12" t="n"/>
+      <c r="CQ9" s="8" t="n"/>
+      <c r="CR9" s="12" t="n"/>
+      <c r="CS9" s="12" t="n"/>
+      <c r="CT9" s="12" t="n"/>
+      <c r="CU9" s="12" t="n"/>
+      <c r="CV9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="4" t="n"/>
@@ -1406,6 +2138,68 @@
       <c r="AD10" s="12" t="n"/>
       <c r="AE10" s="12" t="n"/>
       <c r="AF10" s="7" t="n"/>
+      <c r="AJ10" s="4" t="n"/>
+      <c r="AK10" s="6" t="n"/>
+      <c r="AL10" s="8" t="n"/>
+      <c r="AM10" s="11" t="inlineStr"/>
+      <c r="AN10" s="6" t="n"/>
+      <c r="AO10" s="8" t="n"/>
+      <c r="AP10" s="12" t="n"/>
+      <c r="AQ10" s="12" t="n"/>
+      <c r="AR10" s="12" t="n"/>
+      <c r="AS10" s="12" t="n"/>
+      <c r="AT10" s="8" t="n"/>
+      <c r="AU10" s="12" t="n"/>
+      <c r="AV10" s="12" t="n"/>
+      <c r="AW10" s="12" t="n"/>
+      <c r="AX10" s="12" t="n"/>
+      <c r="AY10" s="8" t="n"/>
+      <c r="AZ10" s="12" t="n"/>
+      <c r="BA10" s="12" t="n"/>
+      <c r="BB10" s="12" t="n"/>
+      <c r="BC10" s="12" t="n"/>
+      <c r="BD10" s="8" t="n"/>
+      <c r="BE10" s="12" t="n"/>
+      <c r="BF10" s="12" t="n"/>
+      <c r="BG10" s="12" t="n"/>
+      <c r="BH10" s="12" t="n"/>
+      <c r="BI10" s="8" t="n"/>
+      <c r="BJ10" s="12" t="n"/>
+      <c r="BK10" s="12" t="n"/>
+      <c r="BL10" s="12" t="n"/>
+      <c r="BM10" s="12" t="n"/>
+      <c r="BN10" s="7" t="n"/>
+      <c r="BR10" s="4" t="n"/>
+      <c r="BS10" s="6" t="n"/>
+      <c r="BT10" s="8" t="n"/>
+      <c r="BU10" s="11" t="inlineStr"/>
+      <c r="BV10" s="6" t="n"/>
+      <c r="BW10" s="8" t="n"/>
+      <c r="BX10" s="12" t="n"/>
+      <c r="BY10" s="12" t="n"/>
+      <c r="BZ10" s="12" t="n"/>
+      <c r="CA10" s="12" t="n"/>
+      <c r="CB10" s="8" t="n"/>
+      <c r="CC10" s="12" t="n"/>
+      <c r="CD10" s="12" t="n"/>
+      <c r="CE10" s="12" t="n"/>
+      <c r="CF10" s="12" t="n"/>
+      <c r="CG10" s="8" t="n"/>
+      <c r="CH10" s="12" t="n"/>
+      <c r="CI10" s="12" t="n"/>
+      <c r="CJ10" s="12" t="n"/>
+      <c r="CK10" s="12" t="n"/>
+      <c r="CL10" s="8" t="n"/>
+      <c r="CM10" s="12" t="n"/>
+      <c r="CN10" s="12" t="n"/>
+      <c r="CO10" s="12" t="n"/>
+      <c r="CP10" s="12" t="n"/>
+      <c r="CQ10" s="8" t="n"/>
+      <c r="CR10" s="12" t="n"/>
+      <c r="CS10" s="12" t="n"/>
+      <c r="CT10" s="12" t="n"/>
+      <c r="CU10" s="12" t="n"/>
+      <c r="CV10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="4" t="n"/>
@@ -1439,6 +2233,68 @@
       <c r="AD11" s="12" t="n"/>
       <c r="AE11" s="12" t="n"/>
       <c r="AF11" s="7" t="n"/>
+      <c r="AJ11" s="4" t="n"/>
+      <c r="AK11" s="6" t="n"/>
+      <c r="AL11" s="8" t="n"/>
+      <c r="AM11" s="11" t="inlineStr"/>
+      <c r="AN11" s="6" t="n"/>
+      <c r="AO11" s="8" t="n"/>
+      <c r="AP11" s="12" t="n"/>
+      <c r="AQ11" s="12" t="n"/>
+      <c r="AR11" s="12" t="n"/>
+      <c r="AS11" s="12" t="n"/>
+      <c r="AT11" s="8" t="n"/>
+      <c r="AU11" s="12" t="n"/>
+      <c r="AV11" s="12" t="n"/>
+      <c r="AW11" s="12" t="n"/>
+      <c r="AX11" s="12" t="n"/>
+      <c r="AY11" s="8" t="n"/>
+      <c r="AZ11" s="12" t="n"/>
+      <c r="BA11" s="12" t="n"/>
+      <c r="BB11" s="12" t="n"/>
+      <c r="BC11" s="12" t="n"/>
+      <c r="BD11" s="8" t="n"/>
+      <c r="BE11" s="12" t="n"/>
+      <c r="BF11" s="12" t="n"/>
+      <c r="BG11" s="12" t="n"/>
+      <c r="BH11" s="12" t="n"/>
+      <c r="BI11" s="8" t="n"/>
+      <c r="BJ11" s="12" t="n"/>
+      <c r="BK11" s="12" t="n"/>
+      <c r="BL11" s="12" t="n"/>
+      <c r="BM11" s="12" t="n"/>
+      <c r="BN11" s="7" t="n"/>
+      <c r="BR11" s="4" t="n"/>
+      <c r="BS11" s="6" t="n"/>
+      <c r="BT11" s="8" t="n"/>
+      <c r="BU11" s="11" t="inlineStr"/>
+      <c r="BV11" s="6" t="n"/>
+      <c r="BW11" s="8" t="n"/>
+      <c r="BX11" s="12" t="n"/>
+      <c r="BY11" s="12" t="n"/>
+      <c r="BZ11" s="12" t="n"/>
+      <c r="CA11" s="12" t="n"/>
+      <c r="CB11" s="8" t="n"/>
+      <c r="CC11" s="12" t="n"/>
+      <c r="CD11" s="12" t="n"/>
+      <c r="CE11" s="12" t="n"/>
+      <c r="CF11" s="12" t="n"/>
+      <c r="CG11" s="8" t="n"/>
+      <c r="CH11" s="12" t="n"/>
+      <c r="CI11" s="12" t="n"/>
+      <c r="CJ11" s="12" t="n"/>
+      <c r="CK11" s="12" t="n"/>
+      <c r="CL11" s="8" t="n"/>
+      <c r="CM11" s="12" t="n"/>
+      <c r="CN11" s="12" t="n"/>
+      <c r="CO11" s="12" t="n"/>
+      <c r="CP11" s="12" t="n"/>
+      <c r="CQ11" s="8" t="n"/>
+      <c r="CR11" s="12" t="n"/>
+      <c r="CS11" s="12" t="n"/>
+      <c r="CT11" s="12" t="n"/>
+      <c r="CU11" s="12" t="n"/>
+      <c r="CV11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="4" t="n"/>
@@ -1472,6 +2328,68 @@
       <c r="AD12" s="12" t="n"/>
       <c r="AE12" s="12" t="n"/>
       <c r="AF12" s="7" t="n"/>
+      <c r="AJ12" s="4" t="n"/>
+      <c r="AK12" s="6" t="n"/>
+      <c r="AL12" s="8" t="n"/>
+      <c r="AM12" s="11" t="inlineStr"/>
+      <c r="AN12" s="6" t="n"/>
+      <c r="AO12" s="8" t="n"/>
+      <c r="AP12" s="12" t="n"/>
+      <c r="AQ12" s="12" t="n"/>
+      <c r="AR12" s="12" t="n"/>
+      <c r="AS12" s="12" t="n"/>
+      <c r="AT12" s="8" t="n"/>
+      <c r="AU12" s="12" t="n"/>
+      <c r="AV12" s="12" t="n"/>
+      <c r="AW12" s="12" t="n"/>
+      <c r="AX12" s="12" t="n"/>
+      <c r="AY12" s="8" t="n"/>
+      <c r="AZ12" s="12" t="n"/>
+      <c r="BA12" s="12" t="n"/>
+      <c r="BB12" s="12" t="n"/>
+      <c r="BC12" s="12" t="n"/>
+      <c r="BD12" s="8" t="n"/>
+      <c r="BE12" s="12" t="n"/>
+      <c r="BF12" s="12" t="n"/>
+      <c r="BG12" s="12" t="n"/>
+      <c r="BH12" s="12" t="n"/>
+      <c r="BI12" s="8" t="n"/>
+      <c r="BJ12" s="12" t="n"/>
+      <c r="BK12" s="12" t="n"/>
+      <c r="BL12" s="12" t="n"/>
+      <c r="BM12" s="12" t="n"/>
+      <c r="BN12" s="7" t="n"/>
+      <c r="BR12" s="4" t="n"/>
+      <c r="BS12" s="6" t="n"/>
+      <c r="BT12" s="8" t="n"/>
+      <c r="BU12" s="11" t="inlineStr"/>
+      <c r="BV12" s="6" t="n"/>
+      <c r="BW12" s="8" t="n"/>
+      <c r="BX12" s="12" t="n"/>
+      <c r="BY12" s="12" t="n"/>
+      <c r="BZ12" s="12" t="n"/>
+      <c r="CA12" s="12" t="n"/>
+      <c r="CB12" s="8" t="n"/>
+      <c r="CC12" s="12" t="n"/>
+      <c r="CD12" s="12" t="n"/>
+      <c r="CE12" s="12" t="n"/>
+      <c r="CF12" s="12" t="n"/>
+      <c r="CG12" s="8" t="n"/>
+      <c r="CH12" s="12" t="n"/>
+      <c r="CI12" s="12" t="n"/>
+      <c r="CJ12" s="12" t="n"/>
+      <c r="CK12" s="12" t="n"/>
+      <c r="CL12" s="8" t="n"/>
+      <c r="CM12" s="12" t="n"/>
+      <c r="CN12" s="12" t="n"/>
+      <c r="CO12" s="12" t="n"/>
+      <c r="CP12" s="12" t="n"/>
+      <c r="CQ12" s="8" t="n"/>
+      <c r="CR12" s="12" t="n"/>
+      <c r="CS12" s="12" t="n"/>
+      <c r="CT12" s="12" t="n"/>
+      <c r="CU12" s="12" t="n"/>
+      <c r="CV12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="4" t="n"/>
@@ -1505,6 +2423,68 @@
       <c r="AD13" s="12" t="n"/>
       <c r="AE13" s="12" t="n"/>
       <c r="AF13" s="7" t="n"/>
+      <c r="AJ13" s="4" t="n"/>
+      <c r="AK13" s="6" t="n"/>
+      <c r="AL13" s="8" t="n"/>
+      <c r="AM13" s="11" t="inlineStr"/>
+      <c r="AN13" s="6" t="n"/>
+      <c r="AO13" s="8" t="n"/>
+      <c r="AP13" s="12" t="n"/>
+      <c r="AQ13" s="12" t="n"/>
+      <c r="AR13" s="12" t="n"/>
+      <c r="AS13" s="12" t="n"/>
+      <c r="AT13" s="8" t="n"/>
+      <c r="AU13" s="12" t="n"/>
+      <c r="AV13" s="12" t="n"/>
+      <c r="AW13" s="12" t="n"/>
+      <c r="AX13" s="12" t="n"/>
+      <c r="AY13" s="8" t="n"/>
+      <c r="AZ13" s="12" t="n"/>
+      <c r="BA13" s="12" t="n"/>
+      <c r="BB13" s="12" t="n"/>
+      <c r="BC13" s="12" t="n"/>
+      <c r="BD13" s="8" t="n"/>
+      <c r="BE13" s="12" t="n"/>
+      <c r="BF13" s="12" t="n"/>
+      <c r="BG13" s="12" t="n"/>
+      <c r="BH13" s="12" t="n"/>
+      <c r="BI13" s="8" t="n"/>
+      <c r="BJ13" s="12" t="n"/>
+      <c r="BK13" s="12" t="n"/>
+      <c r="BL13" s="12" t="n"/>
+      <c r="BM13" s="12" t="n"/>
+      <c r="BN13" s="7" t="n"/>
+      <c r="BR13" s="4" t="n"/>
+      <c r="BS13" s="6" t="n"/>
+      <c r="BT13" s="8" t="n"/>
+      <c r="BU13" s="11" t="inlineStr"/>
+      <c r="BV13" s="6" t="n"/>
+      <c r="BW13" s="8" t="n"/>
+      <c r="BX13" s="12" t="n"/>
+      <c r="BY13" s="12" t="n"/>
+      <c r="BZ13" s="12" t="n"/>
+      <c r="CA13" s="12" t="n"/>
+      <c r="CB13" s="8" t="n"/>
+      <c r="CC13" s="12" t="n"/>
+      <c r="CD13" s="12" t="n"/>
+      <c r="CE13" s="12" t="n"/>
+      <c r="CF13" s="12" t="n"/>
+      <c r="CG13" s="8" t="n"/>
+      <c r="CH13" s="12" t="n"/>
+      <c r="CI13" s="12" t="n"/>
+      <c r="CJ13" s="12" t="n"/>
+      <c r="CK13" s="12" t="n"/>
+      <c r="CL13" s="8" t="n"/>
+      <c r="CM13" s="12" t="n"/>
+      <c r="CN13" s="12" t="n"/>
+      <c r="CO13" s="12" t="n"/>
+      <c r="CP13" s="12" t="n"/>
+      <c r="CQ13" s="8" t="n"/>
+      <c r="CR13" s="12" t="n"/>
+      <c r="CS13" s="12" t="n"/>
+      <c r="CT13" s="12" t="n"/>
+      <c r="CU13" s="12" t="n"/>
+      <c r="CV13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="4" t="n"/>
@@ -1538,6 +2518,68 @@
       <c r="AD14" s="12" t="n"/>
       <c r="AE14" s="12" t="n"/>
       <c r="AF14" s="7" t="n"/>
+      <c r="AJ14" s="4" t="n"/>
+      <c r="AK14" s="6" t="n"/>
+      <c r="AL14" s="8" t="n"/>
+      <c r="AM14" s="11" t="inlineStr"/>
+      <c r="AN14" s="6" t="n"/>
+      <c r="AO14" s="8" t="n"/>
+      <c r="AP14" s="12" t="n"/>
+      <c r="AQ14" s="12" t="n"/>
+      <c r="AR14" s="12" t="n"/>
+      <c r="AS14" s="12" t="n"/>
+      <c r="AT14" s="8" t="n"/>
+      <c r="AU14" s="12" t="n"/>
+      <c r="AV14" s="12" t="n"/>
+      <c r="AW14" s="12" t="n"/>
+      <c r="AX14" s="12" t="n"/>
+      <c r="AY14" s="8" t="n"/>
+      <c r="AZ14" s="12" t="n"/>
+      <c r="BA14" s="12" t="n"/>
+      <c r="BB14" s="12" t="n"/>
+      <c r="BC14" s="12" t="n"/>
+      <c r="BD14" s="8" t="n"/>
+      <c r="BE14" s="12" t="n"/>
+      <c r="BF14" s="12" t="n"/>
+      <c r="BG14" s="12" t="n"/>
+      <c r="BH14" s="12" t="n"/>
+      <c r="BI14" s="8" t="n"/>
+      <c r="BJ14" s="12" t="n"/>
+      <c r="BK14" s="12" t="n"/>
+      <c r="BL14" s="12" t="n"/>
+      <c r="BM14" s="12" t="n"/>
+      <c r="BN14" s="7" t="n"/>
+      <c r="BR14" s="4" t="n"/>
+      <c r="BS14" s="6" t="n"/>
+      <c r="BT14" s="8" t="n"/>
+      <c r="BU14" s="11" t="inlineStr"/>
+      <c r="BV14" s="6" t="n"/>
+      <c r="BW14" s="8" t="n"/>
+      <c r="BX14" s="12" t="n"/>
+      <c r="BY14" s="12" t="n"/>
+      <c r="BZ14" s="12" t="n"/>
+      <c r="CA14" s="12" t="n"/>
+      <c r="CB14" s="8" t="n"/>
+      <c r="CC14" s="12" t="n"/>
+      <c r="CD14" s="12" t="n"/>
+      <c r="CE14" s="12" t="n"/>
+      <c r="CF14" s="12" t="n"/>
+      <c r="CG14" s="8" t="n"/>
+      <c r="CH14" s="12" t="n"/>
+      <c r="CI14" s="12" t="n"/>
+      <c r="CJ14" s="12" t="n"/>
+      <c r="CK14" s="12" t="n"/>
+      <c r="CL14" s="8" t="n"/>
+      <c r="CM14" s="12" t="n"/>
+      <c r="CN14" s="12" t="n"/>
+      <c r="CO14" s="12" t="n"/>
+      <c r="CP14" s="12" t="n"/>
+      <c r="CQ14" s="8" t="n"/>
+      <c r="CR14" s="12" t="n"/>
+      <c r="CS14" s="12" t="n"/>
+      <c r="CT14" s="12" t="n"/>
+      <c r="CU14" s="12" t="n"/>
+      <c r="CV14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="B15" s="4" t="n"/>
@@ -1571,6 +2613,68 @@
       <c r="AD15" s="12" t="n"/>
       <c r="AE15" s="12" t="n"/>
       <c r="AF15" s="7" t="n"/>
+      <c r="AJ15" s="4" t="n"/>
+      <c r="AK15" s="6" t="n"/>
+      <c r="AL15" s="8" t="n"/>
+      <c r="AM15" s="11" t="inlineStr"/>
+      <c r="AN15" s="6" t="n"/>
+      <c r="AO15" s="8" t="n"/>
+      <c r="AP15" s="12" t="n"/>
+      <c r="AQ15" s="12" t="n"/>
+      <c r="AR15" s="12" t="n"/>
+      <c r="AS15" s="12" t="n"/>
+      <c r="AT15" s="8" t="n"/>
+      <c r="AU15" s="12" t="n"/>
+      <c r="AV15" s="12" t="n"/>
+      <c r="AW15" s="12" t="n"/>
+      <c r="AX15" s="12" t="n"/>
+      <c r="AY15" s="8" t="n"/>
+      <c r="AZ15" s="12" t="n"/>
+      <c r="BA15" s="12" t="n"/>
+      <c r="BB15" s="12" t="n"/>
+      <c r="BC15" s="12" t="n"/>
+      <c r="BD15" s="8" t="n"/>
+      <c r="BE15" s="12" t="n"/>
+      <c r="BF15" s="12" t="n"/>
+      <c r="BG15" s="12" t="n"/>
+      <c r="BH15" s="12" t="n"/>
+      <c r="BI15" s="8" t="n"/>
+      <c r="BJ15" s="12" t="n"/>
+      <c r="BK15" s="12" t="n"/>
+      <c r="BL15" s="12" t="n"/>
+      <c r="BM15" s="12" t="n"/>
+      <c r="BN15" s="7" t="n"/>
+      <c r="BR15" s="4" t="n"/>
+      <c r="BS15" s="6" t="n"/>
+      <c r="BT15" s="8" t="n"/>
+      <c r="BU15" s="11" t="inlineStr"/>
+      <c r="BV15" s="6" t="n"/>
+      <c r="BW15" s="8" t="n"/>
+      <c r="BX15" s="12" t="n"/>
+      <c r="BY15" s="12" t="n"/>
+      <c r="BZ15" s="12" t="n"/>
+      <c r="CA15" s="12" t="n"/>
+      <c r="CB15" s="8" t="n"/>
+      <c r="CC15" s="12" t="n"/>
+      <c r="CD15" s="12" t="n"/>
+      <c r="CE15" s="12" t="n"/>
+      <c r="CF15" s="12" t="n"/>
+      <c r="CG15" s="8" t="n"/>
+      <c r="CH15" s="12" t="n"/>
+      <c r="CI15" s="12" t="n"/>
+      <c r="CJ15" s="12" t="n"/>
+      <c r="CK15" s="12" t="n"/>
+      <c r="CL15" s="8" t="n"/>
+      <c r="CM15" s="12" t="n"/>
+      <c r="CN15" s="12" t="n"/>
+      <c r="CO15" s="12" t="n"/>
+      <c r="CP15" s="12" t="n"/>
+      <c r="CQ15" s="8" t="n"/>
+      <c r="CR15" s="12" t="n"/>
+      <c r="CS15" s="12" t="n"/>
+      <c r="CT15" s="12" t="n"/>
+      <c r="CU15" s="12" t="n"/>
+      <c r="CV15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="B16" s="4" t="n"/>
@@ -1604,6 +2708,68 @@
       <c r="AD16" s="12" t="n"/>
       <c r="AE16" s="12" t="n"/>
       <c r="AF16" s="7" t="n"/>
+      <c r="AJ16" s="4" t="n"/>
+      <c r="AK16" s="6" t="n"/>
+      <c r="AL16" s="8" t="n"/>
+      <c r="AM16" s="11" t="inlineStr"/>
+      <c r="AN16" s="6" t="n"/>
+      <c r="AO16" s="8" t="n"/>
+      <c r="AP16" s="12" t="n"/>
+      <c r="AQ16" s="12" t="n"/>
+      <c r="AR16" s="12" t="n"/>
+      <c r="AS16" s="12" t="n"/>
+      <c r="AT16" s="8" t="n"/>
+      <c r="AU16" s="12" t="n"/>
+      <c r="AV16" s="12" t="n"/>
+      <c r="AW16" s="12" t="n"/>
+      <c r="AX16" s="12" t="n"/>
+      <c r="AY16" s="8" t="n"/>
+      <c r="AZ16" s="12" t="n"/>
+      <c r="BA16" s="12" t="n"/>
+      <c r="BB16" s="12" t="n"/>
+      <c r="BC16" s="12" t="n"/>
+      <c r="BD16" s="8" t="n"/>
+      <c r="BE16" s="12" t="n"/>
+      <c r="BF16" s="12" t="n"/>
+      <c r="BG16" s="12" t="n"/>
+      <c r="BH16" s="12" t="n"/>
+      <c r="BI16" s="8" t="n"/>
+      <c r="BJ16" s="12" t="n"/>
+      <c r="BK16" s="12" t="n"/>
+      <c r="BL16" s="12" t="n"/>
+      <c r="BM16" s="12" t="n"/>
+      <c r="BN16" s="7" t="n"/>
+      <c r="BR16" s="4" t="n"/>
+      <c r="BS16" s="6" t="n"/>
+      <c r="BT16" s="8" t="n"/>
+      <c r="BU16" s="11" t="inlineStr"/>
+      <c r="BV16" s="6" t="n"/>
+      <c r="BW16" s="8" t="n"/>
+      <c r="BX16" s="12" t="n"/>
+      <c r="BY16" s="12" t="n"/>
+      <c r="BZ16" s="12" t="n"/>
+      <c r="CA16" s="12" t="n"/>
+      <c r="CB16" s="8" t="n"/>
+      <c r="CC16" s="12" t="n"/>
+      <c r="CD16" s="12" t="n"/>
+      <c r="CE16" s="12" t="n"/>
+      <c r="CF16" s="12" t="n"/>
+      <c r="CG16" s="8" t="n"/>
+      <c r="CH16" s="12" t="n"/>
+      <c r="CI16" s="12" t="n"/>
+      <c r="CJ16" s="12" t="n"/>
+      <c r="CK16" s="12" t="n"/>
+      <c r="CL16" s="8" t="n"/>
+      <c r="CM16" s="12" t="n"/>
+      <c r="CN16" s="12" t="n"/>
+      <c r="CO16" s="12" t="n"/>
+      <c r="CP16" s="12" t="n"/>
+      <c r="CQ16" s="8" t="n"/>
+      <c r="CR16" s="12" t="n"/>
+      <c r="CS16" s="12" t="n"/>
+      <c r="CT16" s="12" t="n"/>
+      <c r="CU16" s="12" t="n"/>
+      <c r="CV16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="4" t="n"/>
@@ -1637,6 +2803,68 @@
       <c r="AD17" s="8" t="n"/>
       <c r="AE17" s="8" t="n"/>
       <c r="AF17" s="7" t="n"/>
+      <c r="AJ17" s="4" t="n"/>
+      <c r="AK17" s="8" t="n"/>
+      <c r="AL17" s="8" t="n"/>
+      <c r="AM17" s="8" t="n"/>
+      <c r="AN17" s="8" t="n"/>
+      <c r="AO17" s="8" t="n"/>
+      <c r="AP17" s="8" t="n"/>
+      <c r="AQ17" s="8" t="n"/>
+      <c r="AR17" s="8" t="n"/>
+      <c r="AS17" s="8" t="n"/>
+      <c r="AT17" s="8" t="n"/>
+      <c r="AU17" s="8" t="n"/>
+      <c r="AV17" s="8" t="n"/>
+      <c r="AW17" s="8" t="n"/>
+      <c r="AX17" s="8" t="n"/>
+      <c r="AY17" s="8" t="n"/>
+      <c r="AZ17" s="8" t="n"/>
+      <c r="BA17" s="8" t="n"/>
+      <c r="BB17" s="8" t="n"/>
+      <c r="BC17" s="8" t="n"/>
+      <c r="BD17" s="8" t="n"/>
+      <c r="BE17" s="8" t="n"/>
+      <c r="BF17" s="8" t="n"/>
+      <c r="BG17" s="8" t="n"/>
+      <c r="BH17" s="8" t="n"/>
+      <c r="BI17" s="8" t="n"/>
+      <c r="BJ17" s="8" t="n"/>
+      <c r="BK17" s="8" t="n"/>
+      <c r="BL17" s="8" t="n"/>
+      <c r="BM17" s="8" t="n"/>
+      <c r="BN17" s="7" t="n"/>
+      <c r="BR17" s="4" t="n"/>
+      <c r="BS17" s="8" t="n"/>
+      <c r="BT17" s="8" t="n"/>
+      <c r="BU17" s="8" t="n"/>
+      <c r="BV17" s="8" t="n"/>
+      <c r="BW17" s="8" t="n"/>
+      <c r="BX17" s="8" t="n"/>
+      <c r="BY17" s="8" t="n"/>
+      <c r="BZ17" s="8" t="n"/>
+      <c r="CA17" s="8" t="n"/>
+      <c r="CB17" s="8" t="n"/>
+      <c r="CC17" s="8" t="n"/>
+      <c r="CD17" s="8" t="n"/>
+      <c r="CE17" s="8" t="n"/>
+      <c r="CF17" s="8" t="n"/>
+      <c r="CG17" s="8" t="n"/>
+      <c r="CH17" s="8" t="n"/>
+      <c r="CI17" s="8" t="n"/>
+      <c r="CJ17" s="8" t="n"/>
+      <c r="CK17" s="8" t="n"/>
+      <c r="CL17" s="8" t="n"/>
+      <c r="CM17" s="8" t="n"/>
+      <c r="CN17" s="8" t="n"/>
+      <c r="CO17" s="8" t="n"/>
+      <c r="CP17" s="8" t="n"/>
+      <c r="CQ17" s="8" t="n"/>
+      <c r="CR17" s="8" t="n"/>
+      <c r="CS17" s="8" t="n"/>
+      <c r="CT17" s="8" t="n"/>
+      <c r="CU17" s="8" t="n"/>
+      <c r="CV17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="4" t="n"/>
@@ -1738,6 +2966,204 @@
         </is>
       </c>
       <c r="AF18" s="7" t="n"/>
+      <c r="AJ18" s="4" t="n"/>
+      <c r="AK18" s="10" t="inlineStr">
+        <is>
+          <t>Day 2</t>
+        </is>
+      </c>
+      <c r="AL18" s="8" t="n"/>
+      <c r="AM18" s="13" t="inlineStr">
+        <is>
+          <t>Weighted Pull-Ups</t>
+        </is>
+      </c>
+      <c r="AN18" s="6" t="n"/>
+      <c r="AO18" s="8" t="n"/>
+      <c r="AP18" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ18" s="14" t="inlineStr">
+        <is>
+          <t>65kg</t>
+        </is>
+      </c>
+      <c r="AR18" s="15" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AS18" s="16" t="inlineStr">
+        <is>
+          <t>Wave 1 – Controlled reps; higher intensity.</t>
+        </is>
+      </c>
+      <c r="AT18" s="8" t="n"/>
+      <c r="AU18" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV18" s="14" t="inlineStr">
+        <is>
+          <t>72.5kg</t>
+        </is>
+      </c>
+      <c r="AW18" s="15" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AX18" s="16" t="inlineStr">
+        <is>
+          <t>Wave 1 – Maintain clean bar path and tempo.</t>
+        </is>
+      </c>
+      <c r="AY18" s="8" t="n"/>
+      <c r="AZ18" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA18" s="14" t="inlineStr">
+        <is>
+          <t>82.8kg</t>
+        </is>
+      </c>
+      <c r="BB18" s="15" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="BC18" s="16" t="inlineStr">
+        <is>
+          <t>Wave 1 – Strong finish, no grind.</t>
+        </is>
+      </c>
+      <c r="BD18" s="8" t="n"/>
+      <c r="BE18" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF18" s="14" t="inlineStr">
+        <is>
+          <t>72.5kg</t>
+        </is>
+      </c>
+      <c r="BG18" s="15" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BH18" s="16" t="inlineStr">
+        <is>
+          <t>Wave 2 – Push with perfect form.</t>
+        </is>
+      </c>
+      <c r="BI18" s="8" t="n"/>
+      <c r="BJ18" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK18" s="14" t="inlineStr">
+        <is>
+          <t>82.8kg</t>
+        </is>
+      </c>
+      <c r="BL18" s="15" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="BM18" s="16" t="inlineStr">
+        <is>
+          <t>Wave 2 – Final double with focus on bar speed.</t>
+        </is>
+      </c>
+      <c r="BN18" s="7" t="n"/>
+      <c r="BR18" s="4" t="n"/>
+      <c r="BS18" s="10" t="inlineStr">
+        <is>
+          <t>Day 2</t>
+        </is>
+      </c>
+      <c r="BT18" s="8" t="n"/>
+      <c r="BU18" s="13" t="inlineStr">
+        <is>
+          <t>Weighted Pull-Ups</t>
+        </is>
+      </c>
+      <c r="BV18" s="6" t="n"/>
+      <c r="BW18" s="8" t="n"/>
+      <c r="BX18" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BY18" s="14" t="inlineStr">
+        <is>
+          <t>67.5kg</t>
+        </is>
+      </c>
+      <c r="BZ18" s="15" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="CA18" s="16" t="inlineStr">
+        <is>
+          <t>Wave 1 – Controlled reps with strong intent.</t>
+        </is>
+      </c>
+      <c r="CB18" s="8" t="n"/>
+      <c r="CC18" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD18" s="14" t="inlineStr">
+        <is>
+          <t>75kg</t>
+        </is>
+      </c>
+      <c r="CE18" s="15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CF18" s="16" t="inlineStr">
+        <is>
+          <t>Wave 1 – Focus on clean bar path and power.</t>
+        </is>
+      </c>
+      <c r="CG18" s="8" t="n"/>
+      <c r="CH18" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI18" s="14" t="inlineStr">
+        <is>
+          <t>85.5kg</t>
+        </is>
+      </c>
+      <c r="CJ18" s="15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CK18" s="16" t="inlineStr">
+        <is>
+          <t>Wave 1 – Top single; crisp with no breakdown.</t>
+        </is>
+      </c>
+      <c r="CL18" s="8" t="n"/>
+      <c r="CM18" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN18" s="14" t="inlineStr">
+        <is>
+          <t>75kg</t>
+        </is>
+      </c>
+      <c r="CO18" s="15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CP18" s="16" t="inlineStr">
+        <is>
+          <t>Wave 2 – Clean reps at high intensity.</t>
+        </is>
+      </c>
+      <c r="CQ18" s="8" t="n"/>
+      <c r="CR18" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS18" s="14" t="inlineStr">
+        <is>
+          <t>85.5kg</t>
+        </is>
+      </c>
+      <c r="CT18" s="15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CU18" s="16" t="inlineStr">
+        <is>
+          <t>Wave 2 – Final single, no grinders.</t>
+        </is>
+      </c>
+      <c r="CV18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="B19" s="4" t="n"/>
@@ -1823,6 +3249,172 @@
       <c r="AD19" s="12" t="n"/>
       <c r="AE19" s="12" t="n"/>
       <c r="AF19" s="7" t="n"/>
+      <c r="AJ19" s="4" t="n"/>
+      <c r="AK19" s="6" t="n"/>
+      <c r="AL19" s="8" t="n"/>
+      <c r="AM19" s="13" t="inlineStr">
+        <is>
+          <t>Weighted Dips</t>
+        </is>
+      </c>
+      <c r="AN19" s="6" t="n"/>
+      <c r="AO19" s="8" t="n"/>
+      <c r="AP19" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ19" s="14" t="inlineStr">
+        <is>
+          <t>30kg</t>
+        </is>
+      </c>
+      <c r="AR19" s="15" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AS19" s="16" t="inlineStr">
+        <is>
+          <t>Volume-style; increase TUT slightly.</t>
+        </is>
+      </c>
+      <c r="AT19" s="8" t="n"/>
+      <c r="AU19" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV19" s="14" t="inlineStr">
+        <is>
+          <t>30kg</t>
+        </is>
+      </c>
+      <c r="AW19" s="15" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AX19" s="16" t="inlineStr">
+        <is>
+          <t>Volume-style; increase TUT slightly.</t>
+        </is>
+      </c>
+      <c r="AY19" s="8" t="n"/>
+      <c r="AZ19" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA19" s="14" t="inlineStr">
+        <is>
+          <t>30kg</t>
+        </is>
+      </c>
+      <c r="BB19" s="15" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BC19" s="16" t="inlineStr">
+        <is>
+          <t>Volume-style; increase TUT slightly.</t>
+        </is>
+      </c>
+      <c r="BD19" s="8" t="n"/>
+      <c r="BE19" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF19" s="14" t="inlineStr">
+        <is>
+          <t>30kg</t>
+        </is>
+      </c>
+      <c r="BG19" s="15" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BH19" s="16" t="inlineStr">
+        <is>
+          <t>Volume-style; increase TUT slightly.</t>
+        </is>
+      </c>
+      <c r="BI19" s="8" t="n"/>
+      <c r="BJ19" s="12" t="n"/>
+      <c r="BK19" s="12" t="n"/>
+      <c r="BL19" s="12" t="n"/>
+      <c r="BM19" s="12" t="n"/>
+      <c r="BN19" s="7" t="n"/>
+      <c r="BR19" s="4" t="n"/>
+      <c r="BS19" s="6" t="n"/>
+      <c r="BT19" s="8" t="n"/>
+      <c r="BU19" s="13" t="inlineStr">
+        <is>
+          <t>Weighted Dips</t>
+        </is>
+      </c>
+      <c r="BV19" s="6" t="n"/>
+      <c r="BW19" s="8" t="n"/>
+      <c r="BX19" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="BY19" s="14" t="inlineStr">
+        <is>
+          <t>27.5kg</t>
+        </is>
+      </c>
+      <c r="BZ19" s="15" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="CA19" s="16" t="inlineStr">
+        <is>
+          <t>Push light day volume with clean form.</t>
+        </is>
+      </c>
+      <c r="CB19" s="8" t="n"/>
+      <c r="CC19" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD19" s="14" t="inlineStr">
+        <is>
+          <t>27.5kg</t>
+        </is>
+      </c>
+      <c r="CE19" s="15" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="CF19" s="16" t="inlineStr">
+        <is>
+          <t>Push light day volume with clean form.</t>
+        </is>
+      </c>
+      <c r="CG19" s="8" t="n"/>
+      <c r="CH19" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="CI19" s="14" t="inlineStr">
+        <is>
+          <t>27.5kg</t>
+        </is>
+      </c>
+      <c r="CJ19" s="15" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="CK19" s="16" t="inlineStr">
+        <is>
+          <t>Push light day volume with clean form.</t>
+        </is>
+      </c>
+      <c r="CL19" s="8" t="n"/>
+      <c r="CM19" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="CN19" s="14" t="inlineStr">
+        <is>
+          <t>27.5kg</t>
+        </is>
+      </c>
+      <c r="CO19" s="15" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="CP19" s="16" t="inlineStr">
+        <is>
+          <t>Push light day volume with clean form.</t>
+        </is>
+      </c>
+      <c r="CQ19" s="8" t="n"/>
+      <c r="CR19" s="12" t="n"/>
+      <c r="CS19" s="12" t="n"/>
+      <c r="CT19" s="12" t="n"/>
+      <c r="CU19" s="12" t="n"/>
+      <c r="CV19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="B20" s="4" t="n"/>
@@ -1856,6 +3448,68 @@
       <c r="AD20" s="12" t="n"/>
       <c r="AE20" s="12" t="n"/>
       <c r="AF20" s="7" t="n"/>
+      <c r="AJ20" s="4" t="n"/>
+      <c r="AK20" s="6" t="n"/>
+      <c r="AL20" s="8" t="n"/>
+      <c r="AM20" s="11" t="inlineStr"/>
+      <c r="AN20" s="6" t="n"/>
+      <c r="AO20" s="8" t="n"/>
+      <c r="AP20" s="12" t="n"/>
+      <c r="AQ20" s="12" t="n"/>
+      <c r="AR20" s="12" t="n"/>
+      <c r="AS20" s="12" t="n"/>
+      <c r="AT20" s="8" t="n"/>
+      <c r="AU20" s="12" t="n"/>
+      <c r="AV20" s="12" t="n"/>
+      <c r="AW20" s="12" t="n"/>
+      <c r="AX20" s="12" t="n"/>
+      <c r="AY20" s="8" t="n"/>
+      <c r="AZ20" s="12" t="n"/>
+      <c r="BA20" s="12" t="n"/>
+      <c r="BB20" s="12" t="n"/>
+      <c r="BC20" s="12" t="n"/>
+      <c r="BD20" s="8" t="n"/>
+      <c r="BE20" s="12" t="n"/>
+      <c r="BF20" s="12" t="n"/>
+      <c r="BG20" s="12" t="n"/>
+      <c r="BH20" s="12" t="n"/>
+      <c r="BI20" s="8" t="n"/>
+      <c r="BJ20" s="12" t="n"/>
+      <c r="BK20" s="12" t="n"/>
+      <c r="BL20" s="12" t="n"/>
+      <c r="BM20" s="12" t="n"/>
+      <c r="BN20" s="7" t="n"/>
+      <c r="BR20" s="4" t="n"/>
+      <c r="BS20" s="6" t="n"/>
+      <c r="BT20" s="8" t="n"/>
+      <c r="BU20" s="11" t="inlineStr"/>
+      <c r="BV20" s="6" t="n"/>
+      <c r="BW20" s="8" t="n"/>
+      <c r="BX20" s="12" t="n"/>
+      <c r="BY20" s="12" t="n"/>
+      <c r="BZ20" s="12" t="n"/>
+      <c r="CA20" s="12" t="n"/>
+      <c r="CB20" s="8" t="n"/>
+      <c r="CC20" s="12" t="n"/>
+      <c r="CD20" s="12" t="n"/>
+      <c r="CE20" s="12" t="n"/>
+      <c r="CF20" s="12" t="n"/>
+      <c r="CG20" s="8" t="n"/>
+      <c r="CH20" s="12" t="n"/>
+      <c r="CI20" s="12" t="n"/>
+      <c r="CJ20" s="12" t="n"/>
+      <c r="CK20" s="12" t="n"/>
+      <c r="CL20" s="8" t="n"/>
+      <c r="CM20" s="12" t="n"/>
+      <c r="CN20" s="12" t="n"/>
+      <c r="CO20" s="12" t="n"/>
+      <c r="CP20" s="12" t="n"/>
+      <c r="CQ20" s="8" t="n"/>
+      <c r="CR20" s="12" t="n"/>
+      <c r="CS20" s="12" t="n"/>
+      <c r="CT20" s="12" t="n"/>
+      <c r="CU20" s="12" t="n"/>
+      <c r="CV20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="4" t="n"/>
@@ -1889,6 +3543,68 @@
       <c r="AD21" s="12" t="n"/>
       <c r="AE21" s="12" t="n"/>
       <c r="AF21" s="7" t="n"/>
+      <c r="AJ21" s="4" t="n"/>
+      <c r="AK21" s="6" t="n"/>
+      <c r="AL21" s="8" t="n"/>
+      <c r="AM21" s="11" t="inlineStr"/>
+      <c r="AN21" s="6" t="n"/>
+      <c r="AO21" s="8" t="n"/>
+      <c r="AP21" s="12" t="n"/>
+      <c r="AQ21" s="12" t="n"/>
+      <c r="AR21" s="12" t="n"/>
+      <c r="AS21" s="12" t="n"/>
+      <c r="AT21" s="8" t="n"/>
+      <c r="AU21" s="12" t="n"/>
+      <c r="AV21" s="12" t="n"/>
+      <c r="AW21" s="12" t="n"/>
+      <c r="AX21" s="12" t="n"/>
+      <c r="AY21" s="8" t="n"/>
+      <c r="AZ21" s="12" t="n"/>
+      <c r="BA21" s="12" t="n"/>
+      <c r="BB21" s="12" t="n"/>
+      <c r="BC21" s="12" t="n"/>
+      <c r="BD21" s="8" t="n"/>
+      <c r="BE21" s="12" t="n"/>
+      <c r="BF21" s="12" t="n"/>
+      <c r="BG21" s="12" t="n"/>
+      <c r="BH21" s="12" t="n"/>
+      <c r="BI21" s="8" t="n"/>
+      <c r="BJ21" s="12" t="n"/>
+      <c r="BK21" s="12" t="n"/>
+      <c r="BL21" s="12" t="n"/>
+      <c r="BM21" s="12" t="n"/>
+      <c r="BN21" s="7" t="n"/>
+      <c r="BR21" s="4" t="n"/>
+      <c r="BS21" s="6" t="n"/>
+      <c r="BT21" s="8" t="n"/>
+      <c r="BU21" s="11" t="inlineStr"/>
+      <c r="BV21" s="6" t="n"/>
+      <c r="BW21" s="8" t="n"/>
+      <c r="BX21" s="12" t="n"/>
+      <c r="BY21" s="12" t="n"/>
+      <c r="BZ21" s="12" t="n"/>
+      <c r="CA21" s="12" t="n"/>
+      <c r="CB21" s="8" t="n"/>
+      <c r="CC21" s="12" t="n"/>
+      <c r="CD21" s="12" t="n"/>
+      <c r="CE21" s="12" t="n"/>
+      <c r="CF21" s="12" t="n"/>
+      <c r="CG21" s="8" t="n"/>
+      <c r="CH21" s="12" t="n"/>
+      <c r="CI21" s="12" t="n"/>
+      <c r="CJ21" s="12" t="n"/>
+      <c r="CK21" s="12" t="n"/>
+      <c r="CL21" s="8" t="n"/>
+      <c r="CM21" s="12" t="n"/>
+      <c r="CN21" s="12" t="n"/>
+      <c r="CO21" s="12" t="n"/>
+      <c r="CP21" s="12" t="n"/>
+      <c r="CQ21" s="8" t="n"/>
+      <c r="CR21" s="12" t="n"/>
+      <c r="CS21" s="12" t="n"/>
+      <c r="CT21" s="12" t="n"/>
+      <c r="CU21" s="12" t="n"/>
+      <c r="CV21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="B22" s="4" t="n"/>
@@ -1922,6 +3638,68 @@
       <c r="AD22" s="12" t="n"/>
       <c r="AE22" s="12" t="n"/>
       <c r="AF22" s="7" t="n"/>
+      <c r="AJ22" s="4" t="n"/>
+      <c r="AK22" s="6" t="n"/>
+      <c r="AL22" s="8" t="n"/>
+      <c r="AM22" s="11" t="inlineStr"/>
+      <c r="AN22" s="6" t="n"/>
+      <c r="AO22" s="8" t="n"/>
+      <c r="AP22" s="12" t="n"/>
+      <c r="AQ22" s="12" t="n"/>
+      <c r="AR22" s="12" t="n"/>
+      <c r="AS22" s="12" t="n"/>
+      <c r="AT22" s="8" t="n"/>
+      <c r="AU22" s="12" t="n"/>
+      <c r="AV22" s="12" t="n"/>
+      <c r="AW22" s="12" t="n"/>
+      <c r="AX22" s="12" t="n"/>
+      <c r="AY22" s="8" t="n"/>
+      <c r="AZ22" s="12" t="n"/>
+      <c r="BA22" s="12" t="n"/>
+      <c r="BB22" s="12" t="n"/>
+      <c r="BC22" s="12" t="n"/>
+      <c r="BD22" s="8" t="n"/>
+      <c r="BE22" s="12" t="n"/>
+      <c r="BF22" s="12" t="n"/>
+      <c r="BG22" s="12" t="n"/>
+      <c r="BH22" s="12" t="n"/>
+      <c r="BI22" s="8" t="n"/>
+      <c r="BJ22" s="12" t="n"/>
+      <c r="BK22" s="12" t="n"/>
+      <c r="BL22" s="12" t="n"/>
+      <c r="BM22" s="12" t="n"/>
+      <c r="BN22" s="7" t="n"/>
+      <c r="BR22" s="4" t="n"/>
+      <c r="BS22" s="6" t="n"/>
+      <c r="BT22" s="8" t="n"/>
+      <c r="BU22" s="11" t="inlineStr"/>
+      <c r="BV22" s="6" t="n"/>
+      <c r="BW22" s="8" t="n"/>
+      <c r="BX22" s="12" t="n"/>
+      <c r="BY22" s="12" t="n"/>
+      <c r="BZ22" s="12" t="n"/>
+      <c r="CA22" s="12" t="n"/>
+      <c r="CB22" s="8" t="n"/>
+      <c r="CC22" s="12" t="n"/>
+      <c r="CD22" s="12" t="n"/>
+      <c r="CE22" s="12" t="n"/>
+      <c r="CF22" s="12" t="n"/>
+      <c r="CG22" s="8" t="n"/>
+      <c r="CH22" s="12" t="n"/>
+      <c r="CI22" s="12" t="n"/>
+      <c r="CJ22" s="12" t="n"/>
+      <c r="CK22" s="12" t="n"/>
+      <c r="CL22" s="8" t="n"/>
+      <c r="CM22" s="12" t="n"/>
+      <c r="CN22" s="12" t="n"/>
+      <c r="CO22" s="12" t="n"/>
+      <c r="CP22" s="12" t="n"/>
+      <c r="CQ22" s="8" t="n"/>
+      <c r="CR22" s="12" t="n"/>
+      <c r="CS22" s="12" t="n"/>
+      <c r="CT22" s="12" t="n"/>
+      <c r="CU22" s="12" t="n"/>
+      <c r="CV22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="B23" s="4" t="n"/>
@@ -1955,6 +3733,68 @@
       <c r="AD23" s="12" t="n"/>
       <c r="AE23" s="12" t="n"/>
       <c r="AF23" s="7" t="n"/>
+      <c r="AJ23" s="4" t="n"/>
+      <c r="AK23" s="6" t="n"/>
+      <c r="AL23" s="8" t="n"/>
+      <c r="AM23" s="11" t="inlineStr"/>
+      <c r="AN23" s="6" t="n"/>
+      <c r="AO23" s="8" t="n"/>
+      <c r="AP23" s="12" t="n"/>
+      <c r="AQ23" s="12" t="n"/>
+      <c r="AR23" s="12" t="n"/>
+      <c r="AS23" s="12" t="n"/>
+      <c r="AT23" s="8" t="n"/>
+      <c r="AU23" s="12" t="n"/>
+      <c r="AV23" s="12" t="n"/>
+      <c r="AW23" s="12" t="n"/>
+      <c r="AX23" s="12" t="n"/>
+      <c r="AY23" s="8" t="n"/>
+      <c r="AZ23" s="12" t="n"/>
+      <c r="BA23" s="12" t="n"/>
+      <c r="BB23" s="12" t="n"/>
+      <c r="BC23" s="12" t="n"/>
+      <c r="BD23" s="8" t="n"/>
+      <c r="BE23" s="12" t="n"/>
+      <c r="BF23" s="12" t="n"/>
+      <c r="BG23" s="12" t="n"/>
+      <c r="BH23" s="12" t="n"/>
+      <c r="BI23" s="8" t="n"/>
+      <c r="BJ23" s="12" t="n"/>
+      <c r="BK23" s="12" t="n"/>
+      <c r="BL23" s="12" t="n"/>
+      <c r="BM23" s="12" t="n"/>
+      <c r="BN23" s="7" t="n"/>
+      <c r="BR23" s="4" t="n"/>
+      <c r="BS23" s="6" t="n"/>
+      <c r="BT23" s="8" t="n"/>
+      <c r="BU23" s="11" t="inlineStr"/>
+      <c r="BV23" s="6" t="n"/>
+      <c r="BW23" s="8" t="n"/>
+      <c r="BX23" s="12" t="n"/>
+      <c r="BY23" s="12" t="n"/>
+      <c r="BZ23" s="12" t="n"/>
+      <c r="CA23" s="12" t="n"/>
+      <c r="CB23" s="8" t="n"/>
+      <c r="CC23" s="12" t="n"/>
+      <c r="CD23" s="12" t="n"/>
+      <c r="CE23" s="12" t="n"/>
+      <c r="CF23" s="12" t="n"/>
+      <c r="CG23" s="8" t="n"/>
+      <c r="CH23" s="12" t="n"/>
+      <c r="CI23" s="12" t="n"/>
+      <c r="CJ23" s="12" t="n"/>
+      <c r="CK23" s="12" t="n"/>
+      <c r="CL23" s="8" t="n"/>
+      <c r="CM23" s="12" t="n"/>
+      <c r="CN23" s="12" t="n"/>
+      <c r="CO23" s="12" t="n"/>
+      <c r="CP23" s="12" t="n"/>
+      <c r="CQ23" s="8" t="n"/>
+      <c r="CR23" s="12" t="n"/>
+      <c r="CS23" s="12" t="n"/>
+      <c r="CT23" s="12" t="n"/>
+      <c r="CU23" s="12" t="n"/>
+      <c r="CV23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="B24" s="4" t="n"/>
@@ -1988,6 +3828,68 @@
       <c r="AD24" s="12" t="n"/>
       <c r="AE24" s="12" t="n"/>
       <c r="AF24" s="7" t="n"/>
+      <c r="AJ24" s="4" t="n"/>
+      <c r="AK24" s="6" t="n"/>
+      <c r="AL24" s="8" t="n"/>
+      <c r="AM24" s="11" t="inlineStr"/>
+      <c r="AN24" s="6" t="n"/>
+      <c r="AO24" s="8" t="n"/>
+      <c r="AP24" s="12" t="n"/>
+      <c r="AQ24" s="12" t="n"/>
+      <c r="AR24" s="12" t="n"/>
+      <c r="AS24" s="12" t="n"/>
+      <c r="AT24" s="8" t="n"/>
+      <c r="AU24" s="12" t="n"/>
+      <c r="AV24" s="12" t="n"/>
+      <c r="AW24" s="12" t="n"/>
+      <c r="AX24" s="12" t="n"/>
+      <c r="AY24" s="8" t="n"/>
+      <c r="AZ24" s="12" t="n"/>
+      <c r="BA24" s="12" t="n"/>
+      <c r="BB24" s="12" t="n"/>
+      <c r="BC24" s="12" t="n"/>
+      <c r="BD24" s="8" t="n"/>
+      <c r="BE24" s="12" t="n"/>
+      <c r="BF24" s="12" t="n"/>
+      <c r="BG24" s="12" t="n"/>
+      <c r="BH24" s="12" t="n"/>
+      <c r="BI24" s="8" t="n"/>
+      <c r="BJ24" s="12" t="n"/>
+      <c r="BK24" s="12" t="n"/>
+      <c r="BL24" s="12" t="n"/>
+      <c r="BM24" s="12" t="n"/>
+      <c r="BN24" s="7" t="n"/>
+      <c r="BR24" s="4" t="n"/>
+      <c r="BS24" s="6" t="n"/>
+      <c r="BT24" s="8" t="n"/>
+      <c r="BU24" s="11" t="inlineStr"/>
+      <c r="BV24" s="6" t="n"/>
+      <c r="BW24" s="8" t="n"/>
+      <c r="BX24" s="12" t="n"/>
+      <c r="BY24" s="12" t="n"/>
+      <c r="BZ24" s="12" t="n"/>
+      <c r="CA24" s="12" t="n"/>
+      <c r="CB24" s="8" t="n"/>
+      <c r="CC24" s="12" t="n"/>
+      <c r="CD24" s="12" t="n"/>
+      <c r="CE24" s="12" t="n"/>
+      <c r="CF24" s="12" t="n"/>
+      <c r="CG24" s="8" t="n"/>
+      <c r="CH24" s="12" t="n"/>
+      <c r="CI24" s="12" t="n"/>
+      <c r="CJ24" s="12" t="n"/>
+      <c r="CK24" s="12" t="n"/>
+      <c r="CL24" s="8" t="n"/>
+      <c r="CM24" s="12" t="n"/>
+      <c r="CN24" s="12" t="n"/>
+      <c r="CO24" s="12" t="n"/>
+      <c r="CP24" s="12" t="n"/>
+      <c r="CQ24" s="8" t="n"/>
+      <c r="CR24" s="12" t="n"/>
+      <c r="CS24" s="12" t="n"/>
+      <c r="CT24" s="12" t="n"/>
+      <c r="CU24" s="12" t="n"/>
+      <c r="CV24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="4" t="n"/>
@@ -2021,6 +3923,68 @@
       <c r="AD25" s="12" t="n"/>
       <c r="AE25" s="12" t="n"/>
       <c r="AF25" s="7" t="n"/>
+      <c r="AJ25" s="4" t="n"/>
+      <c r="AK25" s="6" t="n"/>
+      <c r="AL25" s="8" t="n"/>
+      <c r="AM25" s="11" t="inlineStr"/>
+      <c r="AN25" s="6" t="n"/>
+      <c r="AO25" s="8" t="n"/>
+      <c r="AP25" s="12" t="n"/>
+      <c r="AQ25" s="12" t="n"/>
+      <c r="AR25" s="12" t="n"/>
+      <c r="AS25" s="12" t="n"/>
+      <c r="AT25" s="8" t="n"/>
+      <c r="AU25" s="12" t="n"/>
+      <c r="AV25" s="12" t="n"/>
+      <c r="AW25" s="12" t="n"/>
+      <c r="AX25" s="12" t="n"/>
+      <c r="AY25" s="8" t="n"/>
+      <c r="AZ25" s="12" t="n"/>
+      <c r="BA25" s="12" t="n"/>
+      <c r="BB25" s="12" t="n"/>
+      <c r="BC25" s="12" t="n"/>
+      <c r="BD25" s="8" t="n"/>
+      <c r="BE25" s="12" t="n"/>
+      <c r="BF25" s="12" t="n"/>
+      <c r="BG25" s="12" t="n"/>
+      <c r="BH25" s="12" t="n"/>
+      <c r="BI25" s="8" t="n"/>
+      <c r="BJ25" s="12" t="n"/>
+      <c r="BK25" s="12" t="n"/>
+      <c r="BL25" s="12" t="n"/>
+      <c r="BM25" s="12" t="n"/>
+      <c r="BN25" s="7" t="n"/>
+      <c r="BR25" s="4" t="n"/>
+      <c r="BS25" s="6" t="n"/>
+      <c r="BT25" s="8" t="n"/>
+      <c r="BU25" s="11" t="inlineStr"/>
+      <c r="BV25" s="6" t="n"/>
+      <c r="BW25" s="8" t="n"/>
+      <c r="BX25" s="12" t="n"/>
+      <c r="BY25" s="12" t="n"/>
+      <c r="BZ25" s="12" t="n"/>
+      <c r="CA25" s="12" t="n"/>
+      <c r="CB25" s="8" t="n"/>
+      <c r="CC25" s="12" t="n"/>
+      <c r="CD25" s="12" t="n"/>
+      <c r="CE25" s="12" t="n"/>
+      <c r="CF25" s="12" t="n"/>
+      <c r="CG25" s="8" t="n"/>
+      <c r="CH25" s="12" t="n"/>
+      <c r="CI25" s="12" t="n"/>
+      <c r="CJ25" s="12" t="n"/>
+      <c r="CK25" s="12" t="n"/>
+      <c r="CL25" s="8" t="n"/>
+      <c r="CM25" s="12" t="n"/>
+      <c r="CN25" s="12" t="n"/>
+      <c r="CO25" s="12" t="n"/>
+      <c r="CP25" s="12" t="n"/>
+      <c r="CQ25" s="8" t="n"/>
+      <c r="CR25" s="12" t="n"/>
+      <c r="CS25" s="12" t="n"/>
+      <c r="CT25" s="12" t="n"/>
+      <c r="CU25" s="12" t="n"/>
+      <c r="CV25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="B26" s="4" t="n"/>
@@ -2054,6 +4018,68 @@
       <c r="AD26" s="8" t="n"/>
       <c r="AE26" s="8" t="n"/>
       <c r="AF26" s="7" t="n"/>
+      <c r="AJ26" s="4" t="n"/>
+      <c r="AK26" s="8" t="n"/>
+      <c r="AL26" s="8" t="n"/>
+      <c r="AM26" s="8" t="n"/>
+      <c r="AN26" s="8" t="n"/>
+      <c r="AO26" s="8" t="n"/>
+      <c r="AP26" s="8" t="n"/>
+      <c r="AQ26" s="8" t="n"/>
+      <c r="AR26" s="8" t="n"/>
+      <c r="AS26" s="8" t="n"/>
+      <c r="AT26" s="8" t="n"/>
+      <c r="AU26" s="8" t="n"/>
+      <c r="AV26" s="8" t="n"/>
+      <c r="AW26" s="8" t="n"/>
+      <c r="AX26" s="8" t="n"/>
+      <c r="AY26" s="8" t="n"/>
+      <c r="AZ26" s="8" t="n"/>
+      <c r="BA26" s="8" t="n"/>
+      <c r="BB26" s="8" t="n"/>
+      <c r="BC26" s="8" t="n"/>
+      <c r="BD26" s="8" t="n"/>
+      <c r="BE26" s="8" t="n"/>
+      <c r="BF26" s="8" t="n"/>
+      <c r="BG26" s="8" t="n"/>
+      <c r="BH26" s="8" t="n"/>
+      <c r="BI26" s="8" t="n"/>
+      <c r="BJ26" s="8" t="n"/>
+      <c r="BK26" s="8" t="n"/>
+      <c r="BL26" s="8" t="n"/>
+      <c r="BM26" s="8" t="n"/>
+      <c r="BN26" s="7" t="n"/>
+      <c r="BR26" s="4" t="n"/>
+      <c r="BS26" s="8" t="n"/>
+      <c r="BT26" s="8" t="n"/>
+      <c r="BU26" s="8" t="n"/>
+      <c r="BV26" s="8" t="n"/>
+      <c r="BW26" s="8" t="n"/>
+      <c r="BX26" s="8" t="n"/>
+      <c r="BY26" s="8" t="n"/>
+      <c r="BZ26" s="8" t="n"/>
+      <c r="CA26" s="8" t="n"/>
+      <c r="CB26" s="8" t="n"/>
+      <c r="CC26" s="8" t="n"/>
+      <c r="CD26" s="8" t="n"/>
+      <c r="CE26" s="8" t="n"/>
+      <c r="CF26" s="8" t="n"/>
+      <c r="CG26" s="8" t="n"/>
+      <c r="CH26" s="8" t="n"/>
+      <c r="CI26" s="8" t="n"/>
+      <c r="CJ26" s="8" t="n"/>
+      <c r="CK26" s="8" t="n"/>
+      <c r="CL26" s="8" t="n"/>
+      <c r="CM26" s="8" t="n"/>
+      <c r="CN26" s="8" t="n"/>
+      <c r="CO26" s="8" t="n"/>
+      <c r="CP26" s="8" t="n"/>
+      <c r="CQ26" s="8" t="n"/>
+      <c r="CR26" s="8" t="n"/>
+      <c r="CS26" s="8" t="n"/>
+      <c r="CT26" s="8" t="n"/>
+      <c r="CU26" s="8" t="n"/>
+      <c r="CV26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="B27" s="4" t="n"/>
@@ -2091,6 +4117,76 @@
       <c r="AD27" s="12" t="n"/>
       <c r="AE27" s="12" t="n"/>
       <c r="AF27" s="7" t="n"/>
+      <c r="AJ27" s="4" t="n"/>
+      <c r="AK27" s="10" t="inlineStr">
+        <is>
+          <t>Day 3</t>
+        </is>
+      </c>
+      <c r="AL27" s="8" t="n"/>
+      <c r="AM27" s="11" t="inlineStr"/>
+      <c r="AN27" s="6" t="n"/>
+      <c r="AO27" s="8" t="n"/>
+      <c r="AP27" s="12" t="n"/>
+      <c r="AQ27" s="12" t="n"/>
+      <c r="AR27" s="12" t="n"/>
+      <c r="AS27" s="12" t="n"/>
+      <c r="AT27" s="8" t="n"/>
+      <c r="AU27" s="12" t="n"/>
+      <c r="AV27" s="12" t="n"/>
+      <c r="AW27" s="12" t="n"/>
+      <c r="AX27" s="12" t="n"/>
+      <c r="AY27" s="8" t="n"/>
+      <c r="AZ27" s="12" t="n"/>
+      <c r="BA27" s="12" t="n"/>
+      <c r="BB27" s="12" t="n"/>
+      <c r="BC27" s="12" t="n"/>
+      <c r="BD27" s="8" t="n"/>
+      <c r="BE27" s="12" t="n"/>
+      <c r="BF27" s="12" t="n"/>
+      <c r="BG27" s="12" t="n"/>
+      <c r="BH27" s="12" t="n"/>
+      <c r="BI27" s="8" t="n"/>
+      <c r="BJ27" s="12" t="n"/>
+      <c r="BK27" s="12" t="n"/>
+      <c r="BL27" s="12" t="n"/>
+      <c r="BM27" s="12" t="n"/>
+      <c r="BN27" s="7" t="n"/>
+      <c r="BR27" s="4" t="n"/>
+      <c r="BS27" s="10" t="inlineStr">
+        <is>
+          <t>Day 3</t>
+        </is>
+      </c>
+      <c r="BT27" s="8" t="n"/>
+      <c r="BU27" s="11" t="inlineStr"/>
+      <c r="BV27" s="6" t="n"/>
+      <c r="BW27" s="8" t="n"/>
+      <c r="BX27" s="12" t="n"/>
+      <c r="BY27" s="12" t="n"/>
+      <c r="BZ27" s="12" t="n"/>
+      <c r="CA27" s="12" t="n"/>
+      <c r="CB27" s="8" t="n"/>
+      <c r="CC27" s="12" t="n"/>
+      <c r="CD27" s="12" t="n"/>
+      <c r="CE27" s="12" t="n"/>
+      <c r="CF27" s="12" t="n"/>
+      <c r="CG27" s="8" t="n"/>
+      <c r="CH27" s="12" t="n"/>
+      <c r="CI27" s="12" t="n"/>
+      <c r="CJ27" s="12" t="n"/>
+      <c r="CK27" s="12" t="n"/>
+      <c r="CL27" s="8" t="n"/>
+      <c r="CM27" s="12" t="n"/>
+      <c r="CN27" s="12" t="n"/>
+      <c r="CO27" s="12" t="n"/>
+      <c r="CP27" s="12" t="n"/>
+      <c r="CQ27" s="8" t="n"/>
+      <c r="CR27" s="12" t="n"/>
+      <c r="CS27" s="12" t="n"/>
+      <c r="CT27" s="12" t="n"/>
+      <c r="CU27" s="12" t="n"/>
+      <c r="CV27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="B28" s="4" t="n"/>
@@ -2124,6 +4220,68 @@
       <c r="AD28" s="12" t="n"/>
       <c r="AE28" s="12" t="n"/>
       <c r="AF28" s="7" t="n"/>
+      <c r="AJ28" s="4" t="n"/>
+      <c r="AK28" s="6" t="n"/>
+      <c r="AL28" s="8" t="n"/>
+      <c r="AM28" s="11" t="inlineStr"/>
+      <c r="AN28" s="6" t="n"/>
+      <c r="AO28" s="8" t="n"/>
+      <c r="AP28" s="12" t="n"/>
+      <c r="AQ28" s="12" t="n"/>
+      <c r="AR28" s="12" t="n"/>
+      <c r="AS28" s="12" t="n"/>
+      <c r="AT28" s="8" t="n"/>
+      <c r="AU28" s="12" t="n"/>
+      <c r="AV28" s="12" t="n"/>
+      <c r="AW28" s="12" t="n"/>
+      <c r="AX28" s="12" t="n"/>
+      <c r="AY28" s="8" t="n"/>
+      <c r="AZ28" s="12" t="n"/>
+      <c r="BA28" s="12" t="n"/>
+      <c r="BB28" s="12" t="n"/>
+      <c r="BC28" s="12" t="n"/>
+      <c r="BD28" s="8" t="n"/>
+      <c r="BE28" s="12" t="n"/>
+      <c r="BF28" s="12" t="n"/>
+      <c r="BG28" s="12" t="n"/>
+      <c r="BH28" s="12" t="n"/>
+      <c r="BI28" s="8" t="n"/>
+      <c r="BJ28" s="12" t="n"/>
+      <c r="BK28" s="12" t="n"/>
+      <c r="BL28" s="12" t="n"/>
+      <c r="BM28" s="12" t="n"/>
+      <c r="BN28" s="7" t="n"/>
+      <c r="BR28" s="4" t="n"/>
+      <c r="BS28" s="6" t="n"/>
+      <c r="BT28" s="8" t="n"/>
+      <c r="BU28" s="11" t="inlineStr"/>
+      <c r="BV28" s="6" t="n"/>
+      <c r="BW28" s="8" t="n"/>
+      <c r="BX28" s="12" t="n"/>
+      <c r="BY28" s="12" t="n"/>
+      <c r="BZ28" s="12" t="n"/>
+      <c r="CA28" s="12" t="n"/>
+      <c r="CB28" s="8" t="n"/>
+      <c r="CC28" s="12" t="n"/>
+      <c r="CD28" s="12" t="n"/>
+      <c r="CE28" s="12" t="n"/>
+      <c r="CF28" s="12" t="n"/>
+      <c r="CG28" s="8" t="n"/>
+      <c r="CH28" s="12" t="n"/>
+      <c r="CI28" s="12" t="n"/>
+      <c r="CJ28" s="12" t="n"/>
+      <c r="CK28" s="12" t="n"/>
+      <c r="CL28" s="8" t="n"/>
+      <c r="CM28" s="12" t="n"/>
+      <c r="CN28" s="12" t="n"/>
+      <c r="CO28" s="12" t="n"/>
+      <c r="CP28" s="12" t="n"/>
+      <c r="CQ28" s="8" t="n"/>
+      <c r="CR28" s="12" t="n"/>
+      <c r="CS28" s="12" t="n"/>
+      <c r="CT28" s="12" t="n"/>
+      <c r="CU28" s="12" t="n"/>
+      <c r="CV28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="4" t="n"/>
@@ -2157,6 +4315,68 @@
       <c r="AD29" s="12" t="n"/>
       <c r="AE29" s="12" t="n"/>
       <c r="AF29" s="7" t="n"/>
+      <c r="AJ29" s="4" t="n"/>
+      <c r="AK29" s="6" t="n"/>
+      <c r="AL29" s="8" t="n"/>
+      <c r="AM29" s="11" t="inlineStr"/>
+      <c r="AN29" s="6" t="n"/>
+      <c r="AO29" s="8" t="n"/>
+      <c r="AP29" s="12" t="n"/>
+      <c r="AQ29" s="12" t="n"/>
+      <c r="AR29" s="12" t="n"/>
+      <c r="AS29" s="12" t="n"/>
+      <c r="AT29" s="8" t="n"/>
+      <c r="AU29" s="12" t="n"/>
+      <c r="AV29" s="12" t="n"/>
+      <c r="AW29" s="12" t="n"/>
+      <c r="AX29" s="12" t="n"/>
+      <c r="AY29" s="8" t="n"/>
+      <c r="AZ29" s="12" t="n"/>
+      <c r="BA29" s="12" t="n"/>
+      <c r="BB29" s="12" t="n"/>
+      <c r="BC29" s="12" t="n"/>
+      <c r="BD29" s="8" t="n"/>
+      <c r="BE29" s="12" t="n"/>
+      <c r="BF29" s="12" t="n"/>
+      <c r="BG29" s="12" t="n"/>
+      <c r="BH29" s="12" t="n"/>
+      <c r="BI29" s="8" t="n"/>
+      <c r="BJ29" s="12" t="n"/>
+      <c r="BK29" s="12" t="n"/>
+      <c r="BL29" s="12" t="n"/>
+      <c r="BM29" s="12" t="n"/>
+      <c r="BN29" s="7" t="n"/>
+      <c r="BR29" s="4" t="n"/>
+      <c r="BS29" s="6" t="n"/>
+      <c r="BT29" s="8" t="n"/>
+      <c r="BU29" s="11" t="inlineStr"/>
+      <c r="BV29" s="6" t="n"/>
+      <c r="BW29" s="8" t="n"/>
+      <c r="BX29" s="12" t="n"/>
+      <c r="BY29" s="12" t="n"/>
+      <c r="BZ29" s="12" t="n"/>
+      <c r="CA29" s="12" t="n"/>
+      <c r="CB29" s="8" t="n"/>
+      <c r="CC29" s="12" t="n"/>
+      <c r="CD29" s="12" t="n"/>
+      <c r="CE29" s="12" t="n"/>
+      <c r="CF29" s="12" t="n"/>
+      <c r="CG29" s="8" t="n"/>
+      <c r="CH29" s="12" t="n"/>
+      <c r="CI29" s="12" t="n"/>
+      <c r="CJ29" s="12" t="n"/>
+      <c r="CK29" s="12" t="n"/>
+      <c r="CL29" s="8" t="n"/>
+      <c r="CM29" s="12" t="n"/>
+      <c r="CN29" s="12" t="n"/>
+      <c r="CO29" s="12" t="n"/>
+      <c r="CP29" s="12" t="n"/>
+      <c r="CQ29" s="8" t="n"/>
+      <c r="CR29" s="12" t="n"/>
+      <c r="CS29" s="12" t="n"/>
+      <c r="CT29" s="12" t="n"/>
+      <c r="CU29" s="12" t="n"/>
+      <c r="CV29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="B30" s="4" t="n"/>
@@ -2190,6 +4410,68 @@
       <c r="AD30" s="12" t="n"/>
       <c r="AE30" s="12" t="n"/>
       <c r="AF30" s="7" t="n"/>
+      <c r="AJ30" s="4" t="n"/>
+      <c r="AK30" s="6" t="n"/>
+      <c r="AL30" s="8" t="n"/>
+      <c r="AM30" s="11" t="inlineStr"/>
+      <c r="AN30" s="6" t="n"/>
+      <c r="AO30" s="8" t="n"/>
+      <c r="AP30" s="12" t="n"/>
+      <c r="AQ30" s="12" t="n"/>
+      <c r="AR30" s="12" t="n"/>
+      <c r="AS30" s="12" t="n"/>
+      <c r="AT30" s="8" t="n"/>
+      <c r="AU30" s="12" t="n"/>
+      <c r="AV30" s="12" t="n"/>
+      <c r="AW30" s="12" t="n"/>
+      <c r="AX30" s="12" t="n"/>
+      <c r="AY30" s="8" t="n"/>
+      <c r="AZ30" s="12" t="n"/>
+      <c r="BA30" s="12" t="n"/>
+      <c r="BB30" s="12" t="n"/>
+      <c r="BC30" s="12" t="n"/>
+      <c r="BD30" s="8" t="n"/>
+      <c r="BE30" s="12" t="n"/>
+      <c r="BF30" s="12" t="n"/>
+      <c r="BG30" s="12" t="n"/>
+      <c r="BH30" s="12" t="n"/>
+      <c r="BI30" s="8" t="n"/>
+      <c r="BJ30" s="12" t="n"/>
+      <c r="BK30" s="12" t="n"/>
+      <c r="BL30" s="12" t="n"/>
+      <c r="BM30" s="12" t="n"/>
+      <c r="BN30" s="7" t="n"/>
+      <c r="BR30" s="4" t="n"/>
+      <c r="BS30" s="6" t="n"/>
+      <c r="BT30" s="8" t="n"/>
+      <c r="BU30" s="11" t="inlineStr"/>
+      <c r="BV30" s="6" t="n"/>
+      <c r="BW30" s="8" t="n"/>
+      <c r="BX30" s="12" t="n"/>
+      <c r="BY30" s="12" t="n"/>
+      <c r="BZ30" s="12" t="n"/>
+      <c r="CA30" s="12" t="n"/>
+      <c r="CB30" s="8" t="n"/>
+      <c r="CC30" s="12" t="n"/>
+      <c r="CD30" s="12" t="n"/>
+      <c r="CE30" s="12" t="n"/>
+      <c r="CF30" s="12" t="n"/>
+      <c r="CG30" s="8" t="n"/>
+      <c r="CH30" s="12" t="n"/>
+      <c r="CI30" s="12" t="n"/>
+      <c r="CJ30" s="12" t="n"/>
+      <c r="CK30" s="12" t="n"/>
+      <c r="CL30" s="8" t="n"/>
+      <c r="CM30" s="12" t="n"/>
+      <c r="CN30" s="12" t="n"/>
+      <c r="CO30" s="12" t="n"/>
+      <c r="CP30" s="12" t="n"/>
+      <c r="CQ30" s="8" t="n"/>
+      <c r="CR30" s="12" t="n"/>
+      <c r="CS30" s="12" t="n"/>
+      <c r="CT30" s="12" t="n"/>
+      <c r="CU30" s="12" t="n"/>
+      <c r="CV30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="B31" s="4" t="n"/>
@@ -2223,6 +4505,68 @@
       <c r="AD31" s="12" t="n"/>
       <c r="AE31" s="12" t="n"/>
       <c r="AF31" s="7" t="n"/>
+      <c r="AJ31" s="4" t="n"/>
+      <c r="AK31" s="6" t="n"/>
+      <c r="AL31" s="8" t="n"/>
+      <c r="AM31" s="11" t="inlineStr"/>
+      <c r="AN31" s="6" t="n"/>
+      <c r="AO31" s="8" t="n"/>
+      <c r="AP31" s="12" t="n"/>
+      <c r="AQ31" s="12" t="n"/>
+      <c r="AR31" s="12" t="n"/>
+      <c r="AS31" s="12" t="n"/>
+      <c r="AT31" s="8" t="n"/>
+      <c r="AU31" s="12" t="n"/>
+      <c r="AV31" s="12" t="n"/>
+      <c r="AW31" s="12" t="n"/>
+      <c r="AX31" s="12" t="n"/>
+      <c r="AY31" s="8" t="n"/>
+      <c r="AZ31" s="12" t="n"/>
+      <c r="BA31" s="12" t="n"/>
+      <c r="BB31" s="12" t="n"/>
+      <c r="BC31" s="12" t="n"/>
+      <c r="BD31" s="8" t="n"/>
+      <c r="BE31" s="12" t="n"/>
+      <c r="BF31" s="12" t="n"/>
+      <c r="BG31" s="12" t="n"/>
+      <c r="BH31" s="12" t="n"/>
+      <c r="BI31" s="8" t="n"/>
+      <c r="BJ31" s="12" t="n"/>
+      <c r="BK31" s="12" t="n"/>
+      <c r="BL31" s="12" t="n"/>
+      <c r="BM31" s="12" t="n"/>
+      <c r="BN31" s="7" t="n"/>
+      <c r="BR31" s="4" t="n"/>
+      <c r="BS31" s="6" t="n"/>
+      <c r="BT31" s="8" t="n"/>
+      <c r="BU31" s="11" t="inlineStr"/>
+      <c r="BV31" s="6" t="n"/>
+      <c r="BW31" s="8" t="n"/>
+      <c r="BX31" s="12" t="n"/>
+      <c r="BY31" s="12" t="n"/>
+      <c r="BZ31" s="12" t="n"/>
+      <c r="CA31" s="12" t="n"/>
+      <c r="CB31" s="8" t="n"/>
+      <c r="CC31" s="12" t="n"/>
+      <c r="CD31" s="12" t="n"/>
+      <c r="CE31" s="12" t="n"/>
+      <c r="CF31" s="12" t="n"/>
+      <c r="CG31" s="8" t="n"/>
+      <c r="CH31" s="12" t="n"/>
+      <c r="CI31" s="12" t="n"/>
+      <c r="CJ31" s="12" t="n"/>
+      <c r="CK31" s="12" t="n"/>
+      <c r="CL31" s="8" t="n"/>
+      <c r="CM31" s="12" t="n"/>
+      <c r="CN31" s="12" t="n"/>
+      <c r="CO31" s="12" t="n"/>
+      <c r="CP31" s="12" t="n"/>
+      <c r="CQ31" s="8" t="n"/>
+      <c r="CR31" s="12" t="n"/>
+      <c r="CS31" s="12" t="n"/>
+      <c r="CT31" s="12" t="n"/>
+      <c r="CU31" s="12" t="n"/>
+      <c r="CV31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="B32" s="4" t="n"/>
@@ -2256,6 +4600,68 @@
       <c r="AD32" s="12" t="n"/>
       <c r="AE32" s="12" t="n"/>
       <c r="AF32" s="7" t="n"/>
+      <c r="AJ32" s="4" t="n"/>
+      <c r="AK32" s="6" t="n"/>
+      <c r="AL32" s="8" t="n"/>
+      <c r="AM32" s="11" t="inlineStr"/>
+      <c r="AN32" s="6" t="n"/>
+      <c r="AO32" s="8" t="n"/>
+      <c r="AP32" s="12" t="n"/>
+      <c r="AQ32" s="12" t="n"/>
+      <c r="AR32" s="12" t="n"/>
+      <c r="AS32" s="12" t="n"/>
+      <c r="AT32" s="8" t="n"/>
+      <c r="AU32" s="12" t="n"/>
+      <c r="AV32" s="12" t="n"/>
+      <c r="AW32" s="12" t="n"/>
+      <c r="AX32" s="12" t="n"/>
+      <c r="AY32" s="8" t="n"/>
+      <c r="AZ32" s="12" t="n"/>
+      <c r="BA32" s="12" t="n"/>
+      <c r="BB32" s="12" t="n"/>
+      <c r="BC32" s="12" t="n"/>
+      <c r="BD32" s="8" t="n"/>
+      <c r="BE32" s="12" t="n"/>
+      <c r="BF32" s="12" t="n"/>
+      <c r="BG32" s="12" t="n"/>
+      <c r="BH32" s="12" t="n"/>
+      <c r="BI32" s="8" t="n"/>
+      <c r="BJ32" s="12" t="n"/>
+      <c r="BK32" s="12" t="n"/>
+      <c r="BL32" s="12" t="n"/>
+      <c r="BM32" s="12" t="n"/>
+      <c r="BN32" s="7" t="n"/>
+      <c r="BR32" s="4" t="n"/>
+      <c r="BS32" s="6" t="n"/>
+      <c r="BT32" s="8" t="n"/>
+      <c r="BU32" s="11" t="inlineStr"/>
+      <c r="BV32" s="6" t="n"/>
+      <c r="BW32" s="8" t="n"/>
+      <c r="BX32" s="12" t="n"/>
+      <c r="BY32" s="12" t="n"/>
+      <c r="BZ32" s="12" t="n"/>
+      <c r="CA32" s="12" t="n"/>
+      <c r="CB32" s="8" t="n"/>
+      <c r="CC32" s="12" t="n"/>
+      <c r="CD32" s="12" t="n"/>
+      <c r="CE32" s="12" t="n"/>
+      <c r="CF32" s="12" t="n"/>
+      <c r="CG32" s="8" t="n"/>
+      <c r="CH32" s="12" t="n"/>
+      <c r="CI32" s="12" t="n"/>
+      <c r="CJ32" s="12" t="n"/>
+      <c r="CK32" s="12" t="n"/>
+      <c r="CL32" s="8" t="n"/>
+      <c r="CM32" s="12" t="n"/>
+      <c r="CN32" s="12" t="n"/>
+      <c r="CO32" s="12" t="n"/>
+      <c r="CP32" s="12" t="n"/>
+      <c r="CQ32" s="8" t="n"/>
+      <c r="CR32" s="12" t="n"/>
+      <c r="CS32" s="12" t="n"/>
+      <c r="CT32" s="12" t="n"/>
+      <c r="CU32" s="12" t="n"/>
+      <c r="CV32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="B33" s="4" t="n"/>
@@ -2289,6 +4695,68 @@
       <c r="AD33" s="12" t="n"/>
       <c r="AE33" s="12" t="n"/>
       <c r="AF33" s="7" t="n"/>
+      <c r="AJ33" s="4" t="n"/>
+      <c r="AK33" s="6" t="n"/>
+      <c r="AL33" s="8" t="n"/>
+      <c r="AM33" s="11" t="inlineStr"/>
+      <c r="AN33" s="6" t="n"/>
+      <c r="AO33" s="8" t="n"/>
+      <c r="AP33" s="12" t="n"/>
+      <c r="AQ33" s="12" t="n"/>
+      <c r="AR33" s="12" t="n"/>
+      <c r="AS33" s="12" t="n"/>
+      <c r="AT33" s="8" t="n"/>
+      <c r="AU33" s="12" t="n"/>
+      <c r="AV33" s="12" t="n"/>
+      <c r="AW33" s="12" t="n"/>
+      <c r="AX33" s="12" t="n"/>
+      <c r="AY33" s="8" t="n"/>
+      <c r="AZ33" s="12" t="n"/>
+      <c r="BA33" s="12" t="n"/>
+      <c r="BB33" s="12" t="n"/>
+      <c r="BC33" s="12" t="n"/>
+      <c r="BD33" s="8" t="n"/>
+      <c r="BE33" s="12" t="n"/>
+      <c r="BF33" s="12" t="n"/>
+      <c r="BG33" s="12" t="n"/>
+      <c r="BH33" s="12" t="n"/>
+      <c r="BI33" s="8" t="n"/>
+      <c r="BJ33" s="12" t="n"/>
+      <c r="BK33" s="12" t="n"/>
+      <c r="BL33" s="12" t="n"/>
+      <c r="BM33" s="12" t="n"/>
+      <c r="BN33" s="7" t="n"/>
+      <c r="BR33" s="4" t="n"/>
+      <c r="BS33" s="6" t="n"/>
+      <c r="BT33" s="8" t="n"/>
+      <c r="BU33" s="11" t="inlineStr"/>
+      <c r="BV33" s="6" t="n"/>
+      <c r="BW33" s="8" t="n"/>
+      <c r="BX33" s="12" t="n"/>
+      <c r="BY33" s="12" t="n"/>
+      <c r="BZ33" s="12" t="n"/>
+      <c r="CA33" s="12" t="n"/>
+      <c r="CB33" s="8" t="n"/>
+      <c r="CC33" s="12" t="n"/>
+      <c r="CD33" s="12" t="n"/>
+      <c r="CE33" s="12" t="n"/>
+      <c r="CF33" s="12" t="n"/>
+      <c r="CG33" s="8" t="n"/>
+      <c r="CH33" s="12" t="n"/>
+      <c r="CI33" s="12" t="n"/>
+      <c r="CJ33" s="12" t="n"/>
+      <c r="CK33" s="12" t="n"/>
+      <c r="CL33" s="8" t="n"/>
+      <c r="CM33" s="12" t="n"/>
+      <c r="CN33" s="12" t="n"/>
+      <c r="CO33" s="12" t="n"/>
+      <c r="CP33" s="12" t="n"/>
+      <c r="CQ33" s="8" t="n"/>
+      <c r="CR33" s="12" t="n"/>
+      <c r="CS33" s="12" t="n"/>
+      <c r="CT33" s="12" t="n"/>
+      <c r="CU33" s="12" t="n"/>
+      <c r="CV33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="B34" s="4" t="n"/>
@@ -2322,6 +4790,68 @@
       <c r="AD34" s="12" t="n"/>
       <c r="AE34" s="12" t="n"/>
       <c r="AF34" s="7" t="n"/>
+      <c r="AJ34" s="4" t="n"/>
+      <c r="AK34" s="6" t="n"/>
+      <c r="AL34" s="8" t="n"/>
+      <c r="AM34" s="11" t="inlineStr"/>
+      <c r="AN34" s="6" t="n"/>
+      <c r="AO34" s="8" t="n"/>
+      <c r="AP34" s="12" t="n"/>
+      <c r="AQ34" s="12" t="n"/>
+      <c r="AR34" s="12" t="n"/>
+      <c r="AS34" s="12" t="n"/>
+      <c r="AT34" s="8" t="n"/>
+      <c r="AU34" s="12" t="n"/>
+      <c r="AV34" s="12" t="n"/>
+      <c r="AW34" s="12" t="n"/>
+      <c r="AX34" s="12" t="n"/>
+      <c r="AY34" s="8" t="n"/>
+      <c r="AZ34" s="12" t="n"/>
+      <c r="BA34" s="12" t="n"/>
+      <c r="BB34" s="12" t="n"/>
+      <c r="BC34" s="12" t="n"/>
+      <c r="BD34" s="8" t="n"/>
+      <c r="BE34" s="12" t="n"/>
+      <c r="BF34" s="12" t="n"/>
+      <c r="BG34" s="12" t="n"/>
+      <c r="BH34" s="12" t="n"/>
+      <c r="BI34" s="8" t="n"/>
+      <c r="BJ34" s="12" t="n"/>
+      <c r="BK34" s="12" t="n"/>
+      <c r="BL34" s="12" t="n"/>
+      <c r="BM34" s="12" t="n"/>
+      <c r="BN34" s="7" t="n"/>
+      <c r="BR34" s="4" t="n"/>
+      <c r="BS34" s="6" t="n"/>
+      <c r="BT34" s="8" t="n"/>
+      <c r="BU34" s="11" t="inlineStr"/>
+      <c r="BV34" s="6" t="n"/>
+      <c r="BW34" s="8" t="n"/>
+      <c r="BX34" s="12" t="n"/>
+      <c r="BY34" s="12" t="n"/>
+      <c r="BZ34" s="12" t="n"/>
+      <c r="CA34" s="12" t="n"/>
+      <c r="CB34" s="8" t="n"/>
+      <c r="CC34" s="12" t="n"/>
+      <c r="CD34" s="12" t="n"/>
+      <c r="CE34" s="12" t="n"/>
+      <c r="CF34" s="12" t="n"/>
+      <c r="CG34" s="8" t="n"/>
+      <c r="CH34" s="12" t="n"/>
+      <c r="CI34" s="12" t="n"/>
+      <c r="CJ34" s="12" t="n"/>
+      <c r="CK34" s="12" t="n"/>
+      <c r="CL34" s="8" t="n"/>
+      <c r="CM34" s="12" t="n"/>
+      <c r="CN34" s="12" t="n"/>
+      <c r="CO34" s="12" t="n"/>
+      <c r="CP34" s="12" t="n"/>
+      <c r="CQ34" s="8" t="n"/>
+      <c r="CR34" s="12" t="n"/>
+      <c r="CS34" s="12" t="n"/>
+      <c r="CT34" s="12" t="n"/>
+      <c r="CU34" s="12" t="n"/>
+      <c r="CV34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="B35" s="4" t="n"/>
@@ -2355,6 +4885,68 @@
       <c r="AD35" s="8" t="n"/>
       <c r="AE35" s="8" t="n"/>
       <c r="AF35" s="7" t="n"/>
+      <c r="AJ35" s="4" t="n"/>
+      <c r="AK35" s="8" t="n"/>
+      <c r="AL35" s="8" t="n"/>
+      <c r="AM35" s="8" t="n"/>
+      <c r="AN35" s="8" t="n"/>
+      <c r="AO35" s="8" t="n"/>
+      <c r="AP35" s="8" t="n"/>
+      <c r="AQ35" s="8" t="n"/>
+      <c r="AR35" s="8" t="n"/>
+      <c r="AS35" s="8" t="n"/>
+      <c r="AT35" s="8" t="n"/>
+      <c r="AU35" s="8" t="n"/>
+      <c r="AV35" s="8" t="n"/>
+      <c r="AW35" s="8" t="n"/>
+      <c r="AX35" s="8" t="n"/>
+      <c r="AY35" s="8" t="n"/>
+      <c r="AZ35" s="8" t="n"/>
+      <c r="BA35" s="8" t="n"/>
+      <c r="BB35" s="8" t="n"/>
+      <c r="BC35" s="8" t="n"/>
+      <c r="BD35" s="8" t="n"/>
+      <c r="BE35" s="8" t="n"/>
+      <c r="BF35" s="8" t="n"/>
+      <c r="BG35" s="8" t="n"/>
+      <c r="BH35" s="8" t="n"/>
+      <c r="BI35" s="8" t="n"/>
+      <c r="BJ35" s="8" t="n"/>
+      <c r="BK35" s="8" t="n"/>
+      <c r="BL35" s="8" t="n"/>
+      <c r="BM35" s="8" t="n"/>
+      <c r="BN35" s="7" t="n"/>
+      <c r="BR35" s="4" t="n"/>
+      <c r="BS35" s="8" t="n"/>
+      <c r="BT35" s="8" t="n"/>
+      <c r="BU35" s="8" t="n"/>
+      <c r="BV35" s="8" t="n"/>
+      <c r="BW35" s="8" t="n"/>
+      <c r="BX35" s="8" t="n"/>
+      <c r="BY35" s="8" t="n"/>
+      <c r="BZ35" s="8" t="n"/>
+      <c r="CA35" s="8" t="n"/>
+      <c r="CB35" s="8" t="n"/>
+      <c r="CC35" s="8" t="n"/>
+      <c r="CD35" s="8" t="n"/>
+      <c r="CE35" s="8" t="n"/>
+      <c r="CF35" s="8" t="n"/>
+      <c r="CG35" s="8" t="n"/>
+      <c r="CH35" s="8" t="n"/>
+      <c r="CI35" s="8" t="n"/>
+      <c r="CJ35" s="8" t="n"/>
+      <c r="CK35" s="8" t="n"/>
+      <c r="CL35" s="8" t="n"/>
+      <c r="CM35" s="8" t="n"/>
+      <c r="CN35" s="8" t="n"/>
+      <c r="CO35" s="8" t="n"/>
+      <c r="CP35" s="8" t="n"/>
+      <c r="CQ35" s="8" t="n"/>
+      <c r="CR35" s="8" t="n"/>
+      <c r="CS35" s="8" t="n"/>
+      <c r="CT35" s="8" t="n"/>
+      <c r="CU35" s="8" t="n"/>
+      <c r="CV35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="B36" s="4" t="n"/>
@@ -2376,7 +4968,7 @@
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>142.5kg</t>
+          <t>147.5kg</t>
         </is>
       </c>
       <c r="J36" s="15" t="n">
@@ -2393,7 +4985,7 @@
       </c>
       <c r="N36" s="14" t="inlineStr">
         <is>
-          <t>152.5kg</t>
+          <t>157.5kg</t>
         </is>
       </c>
       <c r="O36" s="15" t="n">
@@ -2410,7 +5002,7 @@
       </c>
       <c r="S36" s="14" t="inlineStr">
         <is>
-          <t>162.5kg</t>
+          <t>165kg</t>
         </is>
       </c>
       <c r="T36" s="15" t="n">
@@ -2427,7 +5019,7 @@
       </c>
       <c r="X36" s="14" t="inlineStr">
         <is>
-          <t>157.5kg</t>
+          <t>160kg</t>
         </is>
       </c>
       <c r="Y36" s="15" t="n">
@@ -2444,7 +5036,7 @@
       </c>
       <c r="AC36" s="14" t="inlineStr">
         <is>
-          <t>165kg</t>
+          <t>170kg</t>
         </is>
       </c>
       <c r="AD36" s="15" t="n">
@@ -2456,6 +5048,204 @@
         </is>
       </c>
       <c r="AF36" s="7" t="n"/>
+      <c r="AJ36" s="4" t="n"/>
+      <c r="AK36" s="10" t="inlineStr">
+        <is>
+          <t>Day 4</t>
+        </is>
+      </c>
+      <c r="AL36" s="8" t="n"/>
+      <c r="AM36" s="13" t="inlineStr">
+        <is>
+          <t>Squat</t>
+        </is>
+      </c>
+      <c r="AN36" s="6" t="n"/>
+      <c r="AO36" s="8" t="n"/>
+      <c r="AP36" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ36" s="14" t="inlineStr">
+        <is>
+          <t>150kg</t>
+        </is>
+      </c>
+      <c r="AR36" s="15" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AS36" s="16" t="inlineStr">
+        <is>
+          <t>Wave 1 – Controlled reps at slightly higher load.</t>
+        </is>
+      </c>
+      <c r="AT36" s="8" t="n"/>
+      <c r="AU36" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV36" s="14" t="inlineStr">
+        <is>
+          <t>165kg</t>
+        </is>
+      </c>
+      <c r="AW36" s="15" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AX36" s="16" t="inlineStr">
+        <is>
+          <t>Wave 1 – Drive from the hole, maintain upright posture.</t>
+        </is>
+      </c>
+      <c r="AY36" s="8" t="n"/>
+      <c r="AZ36" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA36" s="14" t="inlineStr">
+        <is>
+          <t>179.5kg</t>
+        </is>
+      </c>
+      <c r="BB36" s="15" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="BC36" s="16" t="inlineStr">
+        <is>
+          <t>Wave 1 – Top single; aggressive but clean.</t>
+        </is>
+      </c>
+      <c r="BD36" s="8" t="n"/>
+      <c r="BE36" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF36" s="14" t="inlineStr">
+        <is>
+          <t>165kg</t>
+        </is>
+      </c>
+      <c r="BG36" s="15" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BH36" s="16" t="inlineStr">
+        <is>
+          <t>Wave 2 – Stay tight, avoid fatigue breakdown.</t>
+        </is>
+      </c>
+      <c r="BI36" s="8" t="n"/>
+      <c r="BJ36" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK36" s="14" t="inlineStr">
+        <is>
+          <t>179.5kg</t>
+        </is>
+      </c>
+      <c r="BL36" s="15" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="BM36" s="16" t="inlineStr">
+        <is>
+          <t>Wave 2 – Final single with intent.</t>
+        </is>
+      </c>
+      <c r="BN36" s="7" t="n"/>
+      <c r="BR36" s="4" t="n"/>
+      <c r="BS36" s="10" t="inlineStr">
+        <is>
+          <t>Day 4</t>
+        </is>
+      </c>
+      <c r="BT36" s="8" t="n"/>
+      <c r="BU36" s="13" t="inlineStr">
+        <is>
+          <t>Squat</t>
+        </is>
+      </c>
+      <c r="BV36" s="6" t="n"/>
+      <c r="BW36" s="8" t="n"/>
+      <c r="BX36" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BY36" s="14" t="inlineStr">
+        <is>
+          <t>157.5kg</t>
+        </is>
+      </c>
+      <c r="BZ36" s="15" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="CA36" s="16" t="inlineStr">
+        <is>
+          <t>Wave 1 – Strong triples, maintain bracing.</t>
+        </is>
+      </c>
+      <c r="CB36" s="8" t="n"/>
+      <c r="CC36" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD36" s="14" t="inlineStr">
+        <is>
+          <t>170kg</t>
+        </is>
+      </c>
+      <c r="CE36" s="15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CF36" s="16" t="inlineStr">
+        <is>
+          <t>Wave 1 – Push into heavier intensity with power.</t>
+        </is>
+      </c>
+      <c r="CG36" s="8" t="n"/>
+      <c r="CH36" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI36" s="14" t="inlineStr">
+        <is>
+          <t>185.2kg</t>
+        </is>
+      </c>
+      <c r="CJ36" s="15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CK36" s="16" t="inlineStr">
+        <is>
+          <t>Wave 1 – Top single; clean and confident.</t>
+        </is>
+      </c>
+      <c r="CL36" s="8" t="n"/>
+      <c r="CM36" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN36" s="14" t="inlineStr">
+        <is>
+          <t>170kg</t>
+        </is>
+      </c>
+      <c r="CO36" s="15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CP36" s="16" t="inlineStr">
+        <is>
+          <t>Wave 2 – Repeat with same focus and precision.</t>
+        </is>
+      </c>
+      <c r="CQ36" s="8" t="n"/>
+      <c r="CR36" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS36" s="14" t="inlineStr">
+        <is>
+          <t>185.2kg</t>
+        </is>
+      </c>
+      <c r="CT36" s="15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CU36" s="16" t="inlineStr">
+        <is>
+          <t>Wave 2 – Final heavy single with intent.</t>
+        </is>
+      </c>
+      <c r="CV36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="B37" s="4" t="n"/>
@@ -2541,6 +5331,172 @@
       <c r="AD37" s="12" t="n"/>
       <c r="AE37" s="12" t="n"/>
       <c r="AF37" s="7" t="n"/>
+      <c r="AJ37" s="4" t="n"/>
+      <c r="AK37" s="6" t="n"/>
+      <c r="AL37" s="8" t="n"/>
+      <c r="AM37" s="13" t="inlineStr">
+        <is>
+          <t>Weighted Muscle-Ups</t>
+        </is>
+      </c>
+      <c r="AN37" s="6" t="n"/>
+      <c r="AO37" s="8" t="n"/>
+      <c r="AP37" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ37" s="14" t="inlineStr">
+        <is>
+          <t>17.5kg</t>
+        </is>
+      </c>
+      <c r="AR37" s="15" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AS37" s="16" t="inlineStr">
+        <is>
+          <t>Keep transition smooth under higher load.</t>
+        </is>
+      </c>
+      <c r="AT37" s="8" t="n"/>
+      <c r="AU37" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV37" s="14" t="inlineStr">
+        <is>
+          <t>17.5kg</t>
+        </is>
+      </c>
+      <c r="AW37" s="15" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AX37" s="16" t="inlineStr">
+        <is>
+          <t>Keep transition smooth under higher load.</t>
+        </is>
+      </c>
+      <c r="AY37" s="8" t="n"/>
+      <c r="AZ37" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA37" s="14" t="inlineStr">
+        <is>
+          <t>23kg</t>
+        </is>
+      </c>
+      <c r="BB37" s="15" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="BC37" s="16" t="inlineStr">
+        <is>
+          <t>Strong pull with full lockout.</t>
+        </is>
+      </c>
+      <c r="BD37" s="8" t="n"/>
+      <c r="BE37" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF37" s="14" t="inlineStr">
+        <is>
+          <t>23kg</t>
+        </is>
+      </c>
+      <c r="BG37" s="15" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="BH37" s="16" t="inlineStr">
+        <is>
+          <t>Strong pull with full lockout.</t>
+        </is>
+      </c>
+      <c r="BI37" s="8" t="n"/>
+      <c r="BJ37" s="12" t="n"/>
+      <c r="BK37" s="12" t="n"/>
+      <c r="BL37" s="12" t="n"/>
+      <c r="BM37" s="12" t="n"/>
+      <c r="BN37" s="7" t="n"/>
+      <c r="BR37" s="4" t="n"/>
+      <c r="BS37" s="6" t="n"/>
+      <c r="BT37" s="8" t="n"/>
+      <c r="BU37" s="13" t="inlineStr">
+        <is>
+          <t>Weighted Muscle-Ups</t>
+        </is>
+      </c>
+      <c r="BV37" s="6" t="n"/>
+      <c r="BW37" s="8" t="n"/>
+      <c r="BX37" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BY37" s="14" t="inlineStr">
+        <is>
+          <t>20kg</t>
+        </is>
+      </c>
+      <c r="BZ37" s="15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CA37" s="16" t="inlineStr">
+        <is>
+          <t>Tight kip, clean over-bar transition.</t>
+        </is>
+      </c>
+      <c r="CB37" s="8" t="n"/>
+      <c r="CC37" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD37" s="14" t="inlineStr">
+        <is>
+          <t>20kg</t>
+        </is>
+      </c>
+      <c r="CE37" s="15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CF37" s="16" t="inlineStr">
+        <is>
+          <t>Tight kip, clean over-bar transition.</t>
+        </is>
+      </c>
+      <c r="CG37" s="8" t="n"/>
+      <c r="CH37" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI37" s="14" t="inlineStr">
+        <is>
+          <t>23.8kg</t>
+        </is>
+      </c>
+      <c r="CJ37" s="15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CK37" s="16" t="inlineStr">
+        <is>
+          <t>Top singles – explosive but clean.</t>
+        </is>
+      </c>
+      <c r="CL37" s="8" t="n"/>
+      <c r="CM37" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN37" s="14" t="inlineStr">
+        <is>
+          <t>23.8kg</t>
+        </is>
+      </c>
+      <c r="CO37" s="15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CP37" s="16" t="inlineStr">
+        <is>
+          <t>Top singles – explosive but clean.</t>
+        </is>
+      </c>
+      <c r="CQ37" s="8" t="n"/>
+      <c r="CR37" s="12" t="n"/>
+      <c r="CS37" s="12" t="n"/>
+      <c r="CT37" s="12" t="n"/>
+      <c r="CU37" s="12" t="n"/>
+      <c r="CV37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="B38" s="4" t="n"/>
@@ -2574,6 +5530,68 @@
       <c r="AD38" s="12" t="n"/>
       <c r="AE38" s="12" t="n"/>
       <c r="AF38" s="7" t="n"/>
+      <c r="AJ38" s="4" t="n"/>
+      <c r="AK38" s="6" t="n"/>
+      <c r="AL38" s="8" t="n"/>
+      <c r="AM38" s="11" t="inlineStr"/>
+      <c r="AN38" s="6" t="n"/>
+      <c r="AO38" s="8" t="n"/>
+      <c r="AP38" s="12" t="n"/>
+      <c r="AQ38" s="12" t="n"/>
+      <c r="AR38" s="12" t="n"/>
+      <c r="AS38" s="12" t="n"/>
+      <c r="AT38" s="8" t="n"/>
+      <c r="AU38" s="12" t="n"/>
+      <c r="AV38" s="12" t="n"/>
+      <c r="AW38" s="12" t="n"/>
+      <c r="AX38" s="12" t="n"/>
+      <c r="AY38" s="8" t="n"/>
+      <c r="AZ38" s="12" t="n"/>
+      <c r="BA38" s="12" t="n"/>
+      <c r="BB38" s="12" t="n"/>
+      <c r="BC38" s="12" t="n"/>
+      <c r="BD38" s="8" t="n"/>
+      <c r="BE38" s="12" t="n"/>
+      <c r="BF38" s="12" t="n"/>
+      <c r="BG38" s="12" t="n"/>
+      <c r="BH38" s="12" t="n"/>
+      <c r="BI38" s="8" t="n"/>
+      <c r="BJ38" s="12" t="n"/>
+      <c r="BK38" s="12" t="n"/>
+      <c r="BL38" s="12" t="n"/>
+      <c r="BM38" s="12" t="n"/>
+      <c r="BN38" s="7" t="n"/>
+      <c r="BR38" s="4" t="n"/>
+      <c r="BS38" s="6" t="n"/>
+      <c r="BT38" s="8" t="n"/>
+      <c r="BU38" s="11" t="inlineStr"/>
+      <c r="BV38" s="6" t="n"/>
+      <c r="BW38" s="8" t="n"/>
+      <c r="BX38" s="12" t="n"/>
+      <c r="BY38" s="12" t="n"/>
+      <c r="BZ38" s="12" t="n"/>
+      <c r="CA38" s="12" t="n"/>
+      <c r="CB38" s="8" t="n"/>
+      <c r="CC38" s="12" t="n"/>
+      <c r="CD38" s="12" t="n"/>
+      <c r="CE38" s="12" t="n"/>
+      <c r="CF38" s="12" t="n"/>
+      <c r="CG38" s="8" t="n"/>
+      <c r="CH38" s="12" t="n"/>
+      <c r="CI38" s="12" t="n"/>
+      <c r="CJ38" s="12" t="n"/>
+      <c r="CK38" s="12" t="n"/>
+      <c r="CL38" s="8" t="n"/>
+      <c r="CM38" s="12" t="n"/>
+      <c r="CN38" s="12" t="n"/>
+      <c r="CO38" s="12" t="n"/>
+      <c r="CP38" s="12" t="n"/>
+      <c r="CQ38" s="8" t="n"/>
+      <c r="CR38" s="12" t="n"/>
+      <c r="CS38" s="12" t="n"/>
+      <c r="CT38" s="12" t="n"/>
+      <c r="CU38" s="12" t="n"/>
+      <c r="CV38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="B39" s="4" t="n"/>
@@ -2607,6 +5625,68 @@
       <c r="AD39" s="12" t="n"/>
       <c r="AE39" s="12" t="n"/>
       <c r="AF39" s="7" t="n"/>
+      <c r="AJ39" s="4" t="n"/>
+      <c r="AK39" s="6" t="n"/>
+      <c r="AL39" s="8" t="n"/>
+      <c r="AM39" s="11" t="inlineStr"/>
+      <c r="AN39" s="6" t="n"/>
+      <c r="AO39" s="8" t="n"/>
+      <c r="AP39" s="12" t="n"/>
+      <c r="AQ39" s="12" t="n"/>
+      <c r="AR39" s="12" t="n"/>
+      <c r="AS39" s="12" t="n"/>
+      <c r="AT39" s="8" t="n"/>
+      <c r="AU39" s="12" t="n"/>
+      <c r="AV39" s="12" t="n"/>
+      <c r="AW39" s="12" t="n"/>
+      <c r="AX39" s="12" t="n"/>
+      <c r="AY39" s="8" t="n"/>
+      <c r="AZ39" s="12" t="n"/>
+      <c r="BA39" s="12" t="n"/>
+      <c r="BB39" s="12" t="n"/>
+      <c r="BC39" s="12" t="n"/>
+      <c r="BD39" s="8" t="n"/>
+      <c r="BE39" s="12" t="n"/>
+      <c r="BF39" s="12" t="n"/>
+      <c r="BG39" s="12" t="n"/>
+      <c r="BH39" s="12" t="n"/>
+      <c r="BI39" s="8" t="n"/>
+      <c r="BJ39" s="12" t="n"/>
+      <c r="BK39" s="12" t="n"/>
+      <c r="BL39" s="12" t="n"/>
+      <c r="BM39" s="12" t="n"/>
+      <c r="BN39" s="7" t="n"/>
+      <c r="BR39" s="4" t="n"/>
+      <c r="BS39" s="6" t="n"/>
+      <c r="BT39" s="8" t="n"/>
+      <c r="BU39" s="11" t="inlineStr"/>
+      <c r="BV39" s="6" t="n"/>
+      <c r="BW39" s="8" t="n"/>
+      <c r="BX39" s="12" t="n"/>
+      <c r="BY39" s="12" t="n"/>
+      <c r="BZ39" s="12" t="n"/>
+      <c r="CA39" s="12" t="n"/>
+      <c r="CB39" s="8" t="n"/>
+      <c r="CC39" s="12" t="n"/>
+      <c r="CD39" s="12" t="n"/>
+      <c r="CE39" s="12" t="n"/>
+      <c r="CF39" s="12" t="n"/>
+      <c r="CG39" s="8" t="n"/>
+      <c r="CH39" s="12" t="n"/>
+      <c r="CI39" s="12" t="n"/>
+      <c r="CJ39" s="12" t="n"/>
+      <c r="CK39" s="12" t="n"/>
+      <c r="CL39" s="8" t="n"/>
+      <c r="CM39" s="12" t="n"/>
+      <c r="CN39" s="12" t="n"/>
+      <c r="CO39" s="12" t="n"/>
+      <c r="CP39" s="12" t="n"/>
+      <c r="CQ39" s="8" t="n"/>
+      <c r="CR39" s="12" t="n"/>
+      <c r="CS39" s="12" t="n"/>
+      <c r="CT39" s="12" t="n"/>
+      <c r="CU39" s="12" t="n"/>
+      <c r="CV39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="B40" s="4" t="n"/>
@@ -2640,6 +5720,68 @@
       <c r="AD40" s="12" t="n"/>
       <c r="AE40" s="12" t="n"/>
       <c r="AF40" s="7" t="n"/>
+      <c r="AJ40" s="4" t="n"/>
+      <c r="AK40" s="6" t="n"/>
+      <c r="AL40" s="8" t="n"/>
+      <c r="AM40" s="11" t="inlineStr"/>
+      <c r="AN40" s="6" t="n"/>
+      <c r="AO40" s="8" t="n"/>
+      <c r="AP40" s="12" t="n"/>
+      <c r="AQ40" s="12" t="n"/>
+      <c r="AR40" s="12" t="n"/>
+      <c r="AS40" s="12" t="n"/>
+      <c r="AT40" s="8" t="n"/>
+      <c r="AU40" s="12" t="n"/>
+      <c r="AV40" s="12" t="n"/>
+      <c r="AW40" s="12" t="n"/>
+      <c r="AX40" s="12" t="n"/>
+      <c r="AY40" s="8" t="n"/>
+      <c r="AZ40" s="12" t="n"/>
+      <c r="BA40" s="12" t="n"/>
+      <c r="BB40" s="12" t="n"/>
+      <c r="BC40" s="12" t="n"/>
+      <c r="BD40" s="8" t="n"/>
+      <c r="BE40" s="12" t="n"/>
+      <c r="BF40" s="12" t="n"/>
+      <c r="BG40" s="12" t="n"/>
+      <c r="BH40" s="12" t="n"/>
+      <c r="BI40" s="8" t="n"/>
+      <c r="BJ40" s="12" t="n"/>
+      <c r="BK40" s="12" t="n"/>
+      <c r="BL40" s="12" t="n"/>
+      <c r="BM40" s="12" t="n"/>
+      <c r="BN40" s="7" t="n"/>
+      <c r="BR40" s="4" t="n"/>
+      <c r="BS40" s="6" t="n"/>
+      <c r="BT40" s="8" t="n"/>
+      <c r="BU40" s="11" t="inlineStr"/>
+      <c r="BV40" s="6" t="n"/>
+      <c r="BW40" s="8" t="n"/>
+      <c r="BX40" s="12" t="n"/>
+      <c r="BY40" s="12" t="n"/>
+      <c r="BZ40" s="12" t="n"/>
+      <c r="CA40" s="12" t="n"/>
+      <c r="CB40" s="8" t="n"/>
+      <c r="CC40" s="12" t="n"/>
+      <c r="CD40" s="12" t="n"/>
+      <c r="CE40" s="12" t="n"/>
+      <c r="CF40" s="12" t="n"/>
+      <c r="CG40" s="8" t="n"/>
+      <c r="CH40" s="12" t="n"/>
+      <c r="CI40" s="12" t="n"/>
+      <c r="CJ40" s="12" t="n"/>
+      <c r="CK40" s="12" t="n"/>
+      <c r="CL40" s="8" t="n"/>
+      <c r="CM40" s="12" t="n"/>
+      <c r="CN40" s="12" t="n"/>
+      <c r="CO40" s="12" t="n"/>
+      <c r="CP40" s="12" t="n"/>
+      <c r="CQ40" s="8" t="n"/>
+      <c r="CR40" s="12" t="n"/>
+      <c r="CS40" s="12" t="n"/>
+      <c r="CT40" s="12" t="n"/>
+      <c r="CU40" s="12" t="n"/>
+      <c r="CV40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="B41" s="4" t="n"/>
@@ -2673,6 +5815,68 @@
       <c r="AD41" s="12" t="n"/>
       <c r="AE41" s="12" t="n"/>
       <c r="AF41" s="7" t="n"/>
+      <c r="AJ41" s="4" t="n"/>
+      <c r="AK41" s="6" t="n"/>
+      <c r="AL41" s="8" t="n"/>
+      <c r="AM41" s="11" t="inlineStr"/>
+      <c r="AN41" s="6" t="n"/>
+      <c r="AO41" s="8" t="n"/>
+      <c r="AP41" s="12" t="n"/>
+      <c r="AQ41" s="12" t="n"/>
+      <c r="AR41" s="12" t="n"/>
+      <c r="AS41" s="12" t="n"/>
+      <c r="AT41" s="8" t="n"/>
+      <c r="AU41" s="12" t="n"/>
+      <c r="AV41" s="12" t="n"/>
+      <c r="AW41" s="12" t="n"/>
+      <c r="AX41" s="12" t="n"/>
+      <c r="AY41" s="8" t="n"/>
+      <c r="AZ41" s="12" t="n"/>
+      <c r="BA41" s="12" t="n"/>
+      <c r="BB41" s="12" t="n"/>
+      <c r="BC41" s="12" t="n"/>
+      <c r="BD41" s="8" t="n"/>
+      <c r="BE41" s="12" t="n"/>
+      <c r="BF41" s="12" t="n"/>
+      <c r="BG41" s="12" t="n"/>
+      <c r="BH41" s="12" t="n"/>
+      <c r="BI41" s="8" t="n"/>
+      <c r="BJ41" s="12" t="n"/>
+      <c r="BK41" s="12" t="n"/>
+      <c r="BL41" s="12" t="n"/>
+      <c r="BM41" s="12" t="n"/>
+      <c r="BN41" s="7" t="n"/>
+      <c r="BR41" s="4" t="n"/>
+      <c r="BS41" s="6" t="n"/>
+      <c r="BT41" s="8" t="n"/>
+      <c r="BU41" s="11" t="inlineStr"/>
+      <c r="BV41" s="6" t="n"/>
+      <c r="BW41" s="8" t="n"/>
+      <c r="BX41" s="12" t="n"/>
+      <c r="BY41" s="12" t="n"/>
+      <c r="BZ41" s="12" t="n"/>
+      <c r="CA41" s="12" t="n"/>
+      <c r="CB41" s="8" t="n"/>
+      <c r="CC41" s="12" t="n"/>
+      <c r="CD41" s="12" t="n"/>
+      <c r="CE41" s="12" t="n"/>
+      <c r="CF41" s="12" t="n"/>
+      <c r="CG41" s="8" t="n"/>
+      <c r="CH41" s="12" t="n"/>
+      <c r="CI41" s="12" t="n"/>
+      <c r="CJ41" s="12" t="n"/>
+      <c r="CK41" s="12" t="n"/>
+      <c r="CL41" s="8" t="n"/>
+      <c r="CM41" s="12" t="n"/>
+      <c r="CN41" s="12" t="n"/>
+      <c r="CO41" s="12" t="n"/>
+      <c r="CP41" s="12" t="n"/>
+      <c r="CQ41" s="8" t="n"/>
+      <c r="CR41" s="12" t="n"/>
+      <c r="CS41" s="12" t="n"/>
+      <c r="CT41" s="12" t="n"/>
+      <c r="CU41" s="12" t="n"/>
+      <c r="CV41" s="7" t="n"/>
     </row>
     <row r="42">
       <c r="B42" s="4" t="n"/>
@@ -2706,6 +5910,68 @@
       <c r="AD42" s="12" t="n"/>
       <c r="AE42" s="12" t="n"/>
       <c r="AF42" s="7" t="n"/>
+      <c r="AJ42" s="4" t="n"/>
+      <c r="AK42" s="6" t="n"/>
+      <c r="AL42" s="8" t="n"/>
+      <c r="AM42" s="11" t="inlineStr"/>
+      <c r="AN42" s="6" t="n"/>
+      <c r="AO42" s="8" t="n"/>
+      <c r="AP42" s="12" t="n"/>
+      <c r="AQ42" s="12" t="n"/>
+      <c r="AR42" s="12" t="n"/>
+      <c r="AS42" s="12" t="n"/>
+      <c r="AT42" s="8" t="n"/>
+      <c r="AU42" s="12" t="n"/>
+      <c r="AV42" s="12" t="n"/>
+      <c r="AW42" s="12" t="n"/>
+      <c r="AX42" s="12" t="n"/>
+      <c r="AY42" s="8" t="n"/>
+      <c r="AZ42" s="12" t="n"/>
+      <c r="BA42" s="12" t="n"/>
+      <c r="BB42" s="12" t="n"/>
+      <c r="BC42" s="12" t="n"/>
+      <c r="BD42" s="8" t="n"/>
+      <c r="BE42" s="12" t="n"/>
+      <c r="BF42" s="12" t="n"/>
+      <c r="BG42" s="12" t="n"/>
+      <c r="BH42" s="12" t="n"/>
+      <c r="BI42" s="8" t="n"/>
+      <c r="BJ42" s="12" t="n"/>
+      <c r="BK42" s="12" t="n"/>
+      <c r="BL42" s="12" t="n"/>
+      <c r="BM42" s="12" t="n"/>
+      <c r="BN42" s="7" t="n"/>
+      <c r="BR42" s="4" t="n"/>
+      <c r="BS42" s="6" t="n"/>
+      <c r="BT42" s="8" t="n"/>
+      <c r="BU42" s="11" t="inlineStr"/>
+      <c r="BV42" s="6" t="n"/>
+      <c r="BW42" s="8" t="n"/>
+      <c r="BX42" s="12" t="n"/>
+      <c r="BY42" s="12" t="n"/>
+      <c r="BZ42" s="12" t="n"/>
+      <c r="CA42" s="12" t="n"/>
+      <c r="CB42" s="8" t="n"/>
+      <c r="CC42" s="12" t="n"/>
+      <c r="CD42" s="12" t="n"/>
+      <c r="CE42" s="12" t="n"/>
+      <c r="CF42" s="12" t="n"/>
+      <c r="CG42" s="8" t="n"/>
+      <c r="CH42" s="12" t="n"/>
+      <c r="CI42" s="12" t="n"/>
+      <c r="CJ42" s="12" t="n"/>
+      <c r="CK42" s="12" t="n"/>
+      <c r="CL42" s="8" t="n"/>
+      <c r="CM42" s="12" t="n"/>
+      <c r="CN42" s="12" t="n"/>
+      <c r="CO42" s="12" t="n"/>
+      <c r="CP42" s="12" t="n"/>
+      <c r="CQ42" s="8" t="n"/>
+      <c r="CR42" s="12" t="n"/>
+      <c r="CS42" s="12" t="n"/>
+      <c r="CT42" s="12" t="n"/>
+      <c r="CU42" s="12" t="n"/>
+      <c r="CV42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="B43" s="4" t="n"/>
@@ -2739,6 +6005,68 @@
       <c r="AD43" s="12" t="n"/>
       <c r="AE43" s="12" t="n"/>
       <c r="AF43" s="7" t="n"/>
+      <c r="AJ43" s="4" t="n"/>
+      <c r="AK43" s="6" t="n"/>
+      <c r="AL43" s="8" t="n"/>
+      <c r="AM43" s="11" t="inlineStr"/>
+      <c r="AN43" s="6" t="n"/>
+      <c r="AO43" s="8" t="n"/>
+      <c r="AP43" s="12" t="n"/>
+      <c r="AQ43" s="12" t="n"/>
+      <c r="AR43" s="12" t="n"/>
+      <c r="AS43" s="12" t="n"/>
+      <c r="AT43" s="8" t="n"/>
+      <c r="AU43" s="12" t="n"/>
+      <c r="AV43" s="12" t="n"/>
+      <c r="AW43" s="12" t="n"/>
+      <c r="AX43" s="12" t="n"/>
+      <c r="AY43" s="8" t="n"/>
+      <c r="AZ43" s="12" t="n"/>
+      <c r="BA43" s="12" t="n"/>
+      <c r="BB43" s="12" t="n"/>
+      <c r="BC43" s="12" t="n"/>
+      <c r="BD43" s="8" t="n"/>
+      <c r="BE43" s="12" t="n"/>
+      <c r="BF43" s="12" t="n"/>
+      <c r="BG43" s="12" t="n"/>
+      <c r="BH43" s="12" t="n"/>
+      <c r="BI43" s="8" t="n"/>
+      <c r="BJ43" s="12" t="n"/>
+      <c r="BK43" s="12" t="n"/>
+      <c r="BL43" s="12" t="n"/>
+      <c r="BM43" s="12" t="n"/>
+      <c r="BN43" s="7" t="n"/>
+      <c r="BR43" s="4" t="n"/>
+      <c r="BS43" s="6" t="n"/>
+      <c r="BT43" s="8" t="n"/>
+      <c r="BU43" s="11" t="inlineStr"/>
+      <c r="BV43" s="6" t="n"/>
+      <c r="BW43" s="8" t="n"/>
+      <c r="BX43" s="12" t="n"/>
+      <c r="BY43" s="12" t="n"/>
+      <c r="BZ43" s="12" t="n"/>
+      <c r="CA43" s="12" t="n"/>
+      <c r="CB43" s="8" t="n"/>
+      <c r="CC43" s="12" t="n"/>
+      <c r="CD43" s="12" t="n"/>
+      <c r="CE43" s="12" t="n"/>
+      <c r="CF43" s="12" t="n"/>
+      <c r="CG43" s="8" t="n"/>
+      <c r="CH43" s="12" t="n"/>
+      <c r="CI43" s="12" t="n"/>
+      <c r="CJ43" s="12" t="n"/>
+      <c r="CK43" s="12" t="n"/>
+      <c r="CL43" s="8" t="n"/>
+      <c r="CM43" s="12" t="n"/>
+      <c r="CN43" s="12" t="n"/>
+      <c r="CO43" s="12" t="n"/>
+      <c r="CP43" s="12" t="n"/>
+      <c r="CQ43" s="8" t="n"/>
+      <c r="CR43" s="12" t="n"/>
+      <c r="CS43" s="12" t="n"/>
+      <c r="CT43" s="12" t="n"/>
+      <c r="CU43" s="12" t="n"/>
+      <c r="CV43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="B44" s="4" t="n"/>
@@ -2772,6 +6100,68 @@
       <c r="AD44" s="8" t="n"/>
       <c r="AE44" s="8" t="n"/>
       <c r="AF44" s="7" t="n"/>
+      <c r="AJ44" s="4" t="n"/>
+      <c r="AK44" s="8" t="n"/>
+      <c r="AL44" s="8" t="n"/>
+      <c r="AM44" s="8" t="n"/>
+      <c r="AN44" s="8" t="n"/>
+      <c r="AO44" s="8" t="n"/>
+      <c r="AP44" s="8" t="n"/>
+      <c r="AQ44" s="8" t="n"/>
+      <c r="AR44" s="8" t="n"/>
+      <c r="AS44" s="8" t="n"/>
+      <c r="AT44" s="8" t="n"/>
+      <c r="AU44" s="8" t="n"/>
+      <c r="AV44" s="8" t="n"/>
+      <c r="AW44" s="8" t="n"/>
+      <c r="AX44" s="8" t="n"/>
+      <c r="AY44" s="8" t="n"/>
+      <c r="AZ44" s="8" t="n"/>
+      <c r="BA44" s="8" t="n"/>
+      <c r="BB44" s="8" t="n"/>
+      <c r="BC44" s="8" t="n"/>
+      <c r="BD44" s="8" t="n"/>
+      <c r="BE44" s="8" t="n"/>
+      <c r="BF44" s="8" t="n"/>
+      <c r="BG44" s="8" t="n"/>
+      <c r="BH44" s="8" t="n"/>
+      <c r="BI44" s="8" t="n"/>
+      <c r="BJ44" s="8" t="n"/>
+      <c r="BK44" s="8" t="n"/>
+      <c r="BL44" s="8" t="n"/>
+      <c r="BM44" s="8" t="n"/>
+      <c r="BN44" s="7" t="n"/>
+      <c r="BR44" s="4" t="n"/>
+      <c r="BS44" s="8" t="n"/>
+      <c r="BT44" s="8" t="n"/>
+      <c r="BU44" s="8" t="n"/>
+      <c r="BV44" s="8" t="n"/>
+      <c r="BW44" s="8" t="n"/>
+      <c r="BX44" s="8" t="n"/>
+      <c r="BY44" s="8" t="n"/>
+      <c r="BZ44" s="8" t="n"/>
+      <c r="CA44" s="8" t="n"/>
+      <c r="CB44" s="8" t="n"/>
+      <c r="CC44" s="8" t="n"/>
+      <c r="CD44" s="8" t="n"/>
+      <c r="CE44" s="8" t="n"/>
+      <c r="CF44" s="8" t="n"/>
+      <c r="CG44" s="8" t="n"/>
+      <c r="CH44" s="8" t="n"/>
+      <c r="CI44" s="8" t="n"/>
+      <c r="CJ44" s="8" t="n"/>
+      <c r="CK44" s="8" t="n"/>
+      <c r="CL44" s="8" t="n"/>
+      <c r="CM44" s="8" t="n"/>
+      <c r="CN44" s="8" t="n"/>
+      <c r="CO44" s="8" t="n"/>
+      <c r="CP44" s="8" t="n"/>
+      <c r="CQ44" s="8" t="n"/>
+      <c r="CR44" s="8" t="n"/>
+      <c r="CS44" s="8" t="n"/>
+      <c r="CT44" s="8" t="n"/>
+      <c r="CU44" s="8" t="n"/>
+      <c r="CV44" s="7" t="n"/>
     </row>
     <row r="45">
       <c r="B45" s="4" t="n"/>
@@ -2861,6 +6251,180 @@
       <c r="AD45" s="12" t="n"/>
       <c r="AE45" s="12" t="n"/>
       <c r="AF45" s="7" t="n"/>
+      <c r="AJ45" s="4" t="n"/>
+      <c r="AK45" s="10" t="inlineStr">
+        <is>
+          <t>Day 5</t>
+        </is>
+      </c>
+      <c r="AL45" s="8" t="n"/>
+      <c r="AM45" s="13" t="inlineStr">
+        <is>
+          <t>Weighted Pull-Ups</t>
+        </is>
+      </c>
+      <c r="AN45" s="6" t="n"/>
+      <c r="AO45" s="8" t="n"/>
+      <c r="AP45" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ45" s="14" t="inlineStr">
+        <is>
+          <t>55kg</t>
+        </is>
+      </c>
+      <c r="AR45" s="15" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AS45" s="16" t="inlineStr">
+        <is>
+          <t>Reinforce bar path and consistency.</t>
+        </is>
+      </c>
+      <c r="AT45" s="8" t="n"/>
+      <c r="AU45" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV45" s="14" t="inlineStr">
+        <is>
+          <t>55kg</t>
+        </is>
+      </c>
+      <c r="AW45" s="15" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AX45" s="16" t="inlineStr">
+        <is>
+          <t>Reinforce bar path and consistency.</t>
+        </is>
+      </c>
+      <c r="AY45" s="8" t="n"/>
+      <c r="AZ45" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA45" s="14" t="inlineStr">
+        <is>
+          <t>55kg</t>
+        </is>
+      </c>
+      <c r="BB45" s="15" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="BC45" s="16" t="inlineStr">
+        <is>
+          <t>Reinforce bar path and consistency.</t>
+        </is>
+      </c>
+      <c r="BD45" s="8" t="n"/>
+      <c r="BE45" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF45" s="14" t="inlineStr">
+        <is>
+          <t>55kg</t>
+        </is>
+      </c>
+      <c r="BG45" s="15" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="BH45" s="16" t="inlineStr">
+        <is>
+          <t>Reinforce bar path and consistency.</t>
+        </is>
+      </c>
+      <c r="BI45" s="8" t="n"/>
+      <c r="BJ45" s="12" t="n"/>
+      <c r="BK45" s="12" t="n"/>
+      <c r="BL45" s="12" t="n"/>
+      <c r="BM45" s="12" t="n"/>
+      <c r="BN45" s="7" t="n"/>
+      <c r="BR45" s="4" t="n"/>
+      <c r="BS45" s="10" t="inlineStr">
+        <is>
+          <t>Day 5</t>
+        </is>
+      </c>
+      <c r="BT45" s="8" t="n"/>
+      <c r="BU45" s="13" t="inlineStr">
+        <is>
+          <t>Weighted Pull-Ups</t>
+        </is>
+      </c>
+      <c r="BV45" s="6" t="n"/>
+      <c r="BW45" s="8" t="n"/>
+      <c r="BX45" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BY45" s="14" t="inlineStr">
+        <is>
+          <t>55kg</t>
+        </is>
+      </c>
+      <c r="BZ45" s="15" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="CA45" s="16" t="inlineStr">
+        <is>
+          <t>Hold volume steady; bar speed is priority.</t>
+        </is>
+      </c>
+      <c r="CB45" s="8" t="n"/>
+      <c r="CC45" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="CD45" s="14" t="inlineStr">
+        <is>
+          <t>55kg</t>
+        </is>
+      </c>
+      <c r="CE45" s="15" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="CF45" s="16" t="inlineStr">
+        <is>
+          <t>Hold volume steady; bar speed is priority.</t>
+        </is>
+      </c>
+      <c r="CG45" s="8" t="n"/>
+      <c r="CH45" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI45" s="14" t="inlineStr">
+        <is>
+          <t>55kg</t>
+        </is>
+      </c>
+      <c r="CJ45" s="15" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="CK45" s="16" t="inlineStr">
+        <is>
+          <t>Hold volume steady; bar speed is priority.</t>
+        </is>
+      </c>
+      <c r="CL45" s="8" t="n"/>
+      <c r="CM45" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="CN45" s="14" t="inlineStr">
+        <is>
+          <t>55kg</t>
+        </is>
+      </c>
+      <c r="CO45" s="15" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="CP45" s="16" t="inlineStr">
+        <is>
+          <t>Hold volume steady; bar speed is priority.</t>
+        </is>
+      </c>
+      <c r="CQ45" s="8" t="n"/>
+      <c r="CR45" s="12" t="n"/>
+      <c r="CS45" s="12" t="n"/>
+      <c r="CT45" s="12" t="n"/>
+      <c r="CU45" s="12" t="n"/>
+      <c r="CV45" s="7" t="n"/>
     </row>
     <row r="46">
       <c r="B46" s="4" t="n"/>
@@ -2958,6 +6522,196 @@
         </is>
       </c>
       <c r="AF46" s="7" t="n"/>
+      <c r="AJ46" s="4" t="n"/>
+      <c r="AK46" s="6" t="n"/>
+      <c r="AL46" s="8" t="n"/>
+      <c r="AM46" s="13" t="inlineStr">
+        <is>
+          <t>Weighted Dips</t>
+        </is>
+      </c>
+      <c r="AN46" s="6" t="n"/>
+      <c r="AO46" s="8" t="n"/>
+      <c r="AP46" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ46" s="14" t="inlineStr">
+        <is>
+          <t>57.5kg</t>
+        </is>
+      </c>
+      <c r="AR46" s="15" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AS46" s="16" t="inlineStr">
+        <is>
+          <t>Heavier triples; maintain technique and tightness.</t>
+        </is>
+      </c>
+      <c r="AT46" s="8" t="n"/>
+      <c r="AU46" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV46" s="14" t="inlineStr">
+        <is>
+          <t>57.5kg</t>
+        </is>
+      </c>
+      <c r="AW46" s="15" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AX46" s="16" t="inlineStr">
+        <is>
+          <t>Heavier triples; maintain technique and tightness.</t>
+        </is>
+      </c>
+      <c r="AY46" s="8" t="n"/>
+      <c r="AZ46" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA46" s="14" t="inlineStr">
+        <is>
+          <t>57.5kg</t>
+        </is>
+      </c>
+      <c r="BB46" s="15" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="BC46" s="16" t="inlineStr">
+        <is>
+          <t>Heavier triples; maintain technique and tightness.</t>
+        </is>
+      </c>
+      <c r="BD46" s="8" t="n"/>
+      <c r="BE46" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF46" s="14" t="inlineStr">
+        <is>
+          <t>57.5kg</t>
+        </is>
+      </c>
+      <c r="BG46" s="15" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="BH46" s="16" t="inlineStr">
+        <is>
+          <t>Heavier triples; maintain technique and tightness.</t>
+        </is>
+      </c>
+      <c r="BI46" s="8" t="n"/>
+      <c r="BJ46" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK46" s="14" t="inlineStr">
+        <is>
+          <t>57.5kg</t>
+        </is>
+      </c>
+      <c r="BL46" s="15" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="BM46" s="16" t="inlineStr">
+        <is>
+          <t>Heavier triples; maintain technique and tightness.</t>
+        </is>
+      </c>
+      <c r="BN46" s="7" t="n"/>
+      <c r="BR46" s="4" t="n"/>
+      <c r="BS46" s="6" t="n"/>
+      <c r="BT46" s="8" t="n"/>
+      <c r="BU46" s="13" t="inlineStr">
+        <is>
+          <t>Weighted Dips</t>
+        </is>
+      </c>
+      <c r="BV46" s="6" t="n"/>
+      <c r="BW46" s="8" t="n"/>
+      <c r="BX46" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BY46" s="14" t="inlineStr">
+        <is>
+          <t>57.5kg</t>
+        </is>
+      </c>
+      <c r="BZ46" s="15" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="CA46" s="16" t="inlineStr">
+        <is>
+          <t>Maintain control and joint stability.</t>
+        </is>
+      </c>
+      <c r="CB46" s="8" t="n"/>
+      <c r="CC46" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="CD46" s="14" t="inlineStr">
+        <is>
+          <t>57.5kg</t>
+        </is>
+      </c>
+      <c r="CE46" s="15" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="CF46" s="16" t="inlineStr">
+        <is>
+          <t>Maintain control and joint stability.</t>
+        </is>
+      </c>
+      <c r="CG46" s="8" t="n"/>
+      <c r="CH46" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI46" s="14" t="inlineStr">
+        <is>
+          <t>57.5kg</t>
+        </is>
+      </c>
+      <c r="CJ46" s="15" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="CK46" s="16" t="inlineStr">
+        <is>
+          <t>Maintain control and joint stability.</t>
+        </is>
+      </c>
+      <c r="CL46" s="8" t="n"/>
+      <c r="CM46" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN46" s="14" t="inlineStr">
+        <is>
+          <t>57.5kg</t>
+        </is>
+      </c>
+      <c r="CO46" s="15" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="CP46" s="16" t="inlineStr">
+        <is>
+          <t>Maintain control and joint stability.</t>
+        </is>
+      </c>
+      <c r="CQ46" s="8" t="n"/>
+      <c r="CR46" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="CS46" s="14" t="inlineStr">
+        <is>
+          <t>57.5kg</t>
+        </is>
+      </c>
+      <c r="CT46" s="15" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="CU46" s="16" t="inlineStr">
+        <is>
+          <t>Maintain control and joint stability.</t>
+        </is>
+      </c>
+      <c r="CV46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="B47" s="4" t="n"/>
@@ -2991,6 +6745,68 @@
       <c r="AD47" s="12" t="n"/>
       <c r="AE47" s="12" t="n"/>
       <c r="AF47" s="7" t="n"/>
+      <c r="AJ47" s="4" t="n"/>
+      <c r="AK47" s="6" t="n"/>
+      <c r="AL47" s="8" t="n"/>
+      <c r="AM47" s="11" t="inlineStr"/>
+      <c r="AN47" s="6" t="n"/>
+      <c r="AO47" s="8" t="n"/>
+      <c r="AP47" s="12" t="n"/>
+      <c r="AQ47" s="12" t="n"/>
+      <c r="AR47" s="12" t="n"/>
+      <c r="AS47" s="12" t="n"/>
+      <c r="AT47" s="8" t="n"/>
+      <c r="AU47" s="12" t="n"/>
+      <c r="AV47" s="12" t="n"/>
+      <c r="AW47" s="12" t="n"/>
+      <c r="AX47" s="12" t="n"/>
+      <c r="AY47" s="8" t="n"/>
+      <c r="AZ47" s="12" t="n"/>
+      <c r="BA47" s="12" t="n"/>
+      <c r="BB47" s="12" t="n"/>
+      <c r="BC47" s="12" t="n"/>
+      <c r="BD47" s="8" t="n"/>
+      <c r="BE47" s="12" t="n"/>
+      <c r="BF47" s="12" t="n"/>
+      <c r="BG47" s="12" t="n"/>
+      <c r="BH47" s="12" t="n"/>
+      <c r="BI47" s="8" t="n"/>
+      <c r="BJ47" s="12" t="n"/>
+      <c r="BK47" s="12" t="n"/>
+      <c r="BL47" s="12" t="n"/>
+      <c r="BM47" s="12" t="n"/>
+      <c r="BN47" s="7" t="n"/>
+      <c r="BR47" s="4" t="n"/>
+      <c r="BS47" s="6" t="n"/>
+      <c r="BT47" s="8" t="n"/>
+      <c r="BU47" s="11" t="inlineStr"/>
+      <c r="BV47" s="6" t="n"/>
+      <c r="BW47" s="8" t="n"/>
+      <c r="BX47" s="12" t="n"/>
+      <c r="BY47" s="12" t="n"/>
+      <c r="BZ47" s="12" t="n"/>
+      <c r="CA47" s="12" t="n"/>
+      <c r="CB47" s="8" t="n"/>
+      <c r="CC47" s="12" t="n"/>
+      <c r="CD47" s="12" t="n"/>
+      <c r="CE47" s="12" t="n"/>
+      <c r="CF47" s="12" t="n"/>
+      <c r="CG47" s="8" t="n"/>
+      <c r="CH47" s="12" t="n"/>
+      <c r="CI47" s="12" t="n"/>
+      <c r="CJ47" s="12" t="n"/>
+      <c r="CK47" s="12" t="n"/>
+      <c r="CL47" s="8" t="n"/>
+      <c r="CM47" s="12" t="n"/>
+      <c r="CN47" s="12" t="n"/>
+      <c r="CO47" s="12" t="n"/>
+      <c r="CP47" s="12" t="n"/>
+      <c r="CQ47" s="8" t="n"/>
+      <c r="CR47" s="12" t="n"/>
+      <c r="CS47" s="12" t="n"/>
+      <c r="CT47" s="12" t="n"/>
+      <c r="CU47" s="12" t="n"/>
+      <c r="CV47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="B48" s="4" t="n"/>
@@ -3024,6 +6840,68 @@
       <c r="AD48" s="12" t="n"/>
       <c r="AE48" s="12" t="n"/>
       <c r="AF48" s="7" t="n"/>
+      <c r="AJ48" s="4" t="n"/>
+      <c r="AK48" s="6" t="n"/>
+      <c r="AL48" s="8" t="n"/>
+      <c r="AM48" s="11" t="inlineStr"/>
+      <c r="AN48" s="6" t="n"/>
+      <c r="AO48" s="8" t="n"/>
+      <c r="AP48" s="12" t="n"/>
+      <c r="AQ48" s="12" t="n"/>
+      <c r="AR48" s="12" t="n"/>
+      <c r="AS48" s="12" t="n"/>
+      <c r="AT48" s="8" t="n"/>
+      <c r="AU48" s="12" t="n"/>
+      <c r="AV48" s="12" t="n"/>
+      <c r="AW48" s="12" t="n"/>
+      <c r="AX48" s="12" t="n"/>
+      <c r="AY48" s="8" t="n"/>
+      <c r="AZ48" s="12" t="n"/>
+      <c r="BA48" s="12" t="n"/>
+      <c r="BB48" s="12" t="n"/>
+      <c r="BC48" s="12" t="n"/>
+      <c r="BD48" s="8" t="n"/>
+      <c r="BE48" s="12" t="n"/>
+      <c r="BF48" s="12" t="n"/>
+      <c r="BG48" s="12" t="n"/>
+      <c r="BH48" s="12" t="n"/>
+      <c r="BI48" s="8" t="n"/>
+      <c r="BJ48" s="12" t="n"/>
+      <c r="BK48" s="12" t="n"/>
+      <c r="BL48" s="12" t="n"/>
+      <c r="BM48" s="12" t="n"/>
+      <c r="BN48" s="7" t="n"/>
+      <c r="BR48" s="4" t="n"/>
+      <c r="BS48" s="6" t="n"/>
+      <c r="BT48" s="8" t="n"/>
+      <c r="BU48" s="11" t="inlineStr"/>
+      <c r="BV48" s="6" t="n"/>
+      <c r="BW48" s="8" t="n"/>
+      <c r="BX48" s="12" t="n"/>
+      <c r="BY48" s="12" t="n"/>
+      <c r="BZ48" s="12" t="n"/>
+      <c r="CA48" s="12" t="n"/>
+      <c r="CB48" s="8" t="n"/>
+      <c r="CC48" s="12" t="n"/>
+      <c r="CD48" s="12" t="n"/>
+      <c r="CE48" s="12" t="n"/>
+      <c r="CF48" s="12" t="n"/>
+      <c r="CG48" s="8" t="n"/>
+      <c r="CH48" s="12" t="n"/>
+      <c r="CI48" s="12" t="n"/>
+      <c r="CJ48" s="12" t="n"/>
+      <c r="CK48" s="12" t="n"/>
+      <c r="CL48" s="8" t="n"/>
+      <c r="CM48" s="12" t="n"/>
+      <c r="CN48" s="12" t="n"/>
+      <c r="CO48" s="12" t="n"/>
+      <c r="CP48" s="12" t="n"/>
+      <c r="CQ48" s="8" t="n"/>
+      <c r="CR48" s="12" t="n"/>
+      <c r="CS48" s="12" t="n"/>
+      <c r="CT48" s="12" t="n"/>
+      <c r="CU48" s="12" t="n"/>
+      <c r="CV48" s="7" t="n"/>
     </row>
     <row r="49">
       <c r="B49" s="4" t="n"/>
@@ -3057,6 +6935,68 @@
       <c r="AD49" s="12" t="n"/>
       <c r="AE49" s="12" t="n"/>
       <c r="AF49" s="7" t="n"/>
+      <c r="AJ49" s="4" t="n"/>
+      <c r="AK49" s="6" t="n"/>
+      <c r="AL49" s="8" t="n"/>
+      <c r="AM49" s="11" t="inlineStr"/>
+      <c r="AN49" s="6" t="n"/>
+      <c r="AO49" s="8" t="n"/>
+      <c r="AP49" s="12" t="n"/>
+      <c r="AQ49" s="12" t="n"/>
+      <c r="AR49" s="12" t="n"/>
+      <c r="AS49" s="12" t="n"/>
+      <c r="AT49" s="8" t="n"/>
+      <c r="AU49" s="12" t="n"/>
+      <c r="AV49" s="12" t="n"/>
+      <c r="AW49" s="12" t="n"/>
+      <c r="AX49" s="12" t="n"/>
+      <c r="AY49" s="8" t="n"/>
+      <c r="AZ49" s="12" t="n"/>
+      <c r="BA49" s="12" t="n"/>
+      <c r="BB49" s="12" t="n"/>
+      <c r="BC49" s="12" t="n"/>
+      <c r="BD49" s="8" t="n"/>
+      <c r="BE49" s="12" t="n"/>
+      <c r="BF49" s="12" t="n"/>
+      <c r="BG49" s="12" t="n"/>
+      <c r="BH49" s="12" t="n"/>
+      <c r="BI49" s="8" t="n"/>
+      <c r="BJ49" s="12" t="n"/>
+      <c r="BK49" s="12" t="n"/>
+      <c r="BL49" s="12" t="n"/>
+      <c r="BM49" s="12" t="n"/>
+      <c r="BN49" s="7" t="n"/>
+      <c r="BR49" s="4" t="n"/>
+      <c r="BS49" s="6" t="n"/>
+      <c r="BT49" s="8" t="n"/>
+      <c r="BU49" s="11" t="inlineStr"/>
+      <c r="BV49" s="6" t="n"/>
+      <c r="BW49" s="8" t="n"/>
+      <c r="BX49" s="12" t="n"/>
+      <c r="BY49" s="12" t="n"/>
+      <c r="BZ49" s="12" t="n"/>
+      <c r="CA49" s="12" t="n"/>
+      <c r="CB49" s="8" t="n"/>
+      <c r="CC49" s="12" t="n"/>
+      <c r="CD49" s="12" t="n"/>
+      <c r="CE49" s="12" t="n"/>
+      <c r="CF49" s="12" t="n"/>
+      <c r="CG49" s="8" t="n"/>
+      <c r="CH49" s="12" t="n"/>
+      <c r="CI49" s="12" t="n"/>
+      <c r="CJ49" s="12" t="n"/>
+      <c r="CK49" s="12" t="n"/>
+      <c r="CL49" s="8" t="n"/>
+      <c r="CM49" s="12" t="n"/>
+      <c r="CN49" s="12" t="n"/>
+      <c r="CO49" s="12" t="n"/>
+      <c r="CP49" s="12" t="n"/>
+      <c r="CQ49" s="8" t="n"/>
+      <c r="CR49" s="12" t="n"/>
+      <c r="CS49" s="12" t="n"/>
+      <c r="CT49" s="12" t="n"/>
+      <c r="CU49" s="12" t="n"/>
+      <c r="CV49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="B50" s="4" t="n"/>
@@ -3090,6 +7030,68 @@
       <c r="AD50" s="12" t="n"/>
       <c r="AE50" s="12" t="n"/>
       <c r="AF50" s="7" t="n"/>
+      <c r="AJ50" s="4" t="n"/>
+      <c r="AK50" s="6" t="n"/>
+      <c r="AL50" s="8" t="n"/>
+      <c r="AM50" s="11" t="inlineStr"/>
+      <c r="AN50" s="6" t="n"/>
+      <c r="AO50" s="8" t="n"/>
+      <c r="AP50" s="12" t="n"/>
+      <c r="AQ50" s="12" t="n"/>
+      <c r="AR50" s="12" t="n"/>
+      <c r="AS50" s="12" t="n"/>
+      <c r="AT50" s="8" t="n"/>
+      <c r="AU50" s="12" t="n"/>
+      <c r="AV50" s="12" t="n"/>
+      <c r="AW50" s="12" t="n"/>
+      <c r="AX50" s="12" t="n"/>
+      <c r="AY50" s="8" t="n"/>
+      <c r="AZ50" s="12" t="n"/>
+      <c r="BA50" s="12" t="n"/>
+      <c r="BB50" s="12" t="n"/>
+      <c r="BC50" s="12" t="n"/>
+      <c r="BD50" s="8" t="n"/>
+      <c r="BE50" s="12" t="n"/>
+      <c r="BF50" s="12" t="n"/>
+      <c r="BG50" s="12" t="n"/>
+      <c r="BH50" s="12" t="n"/>
+      <c r="BI50" s="8" t="n"/>
+      <c r="BJ50" s="12" t="n"/>
+      <c r="BK50" s="12" t="n"/>
+      <c r="BL50" s="12" t="n"/>
+      <c r="BM50" s="12" t="n"/>
+      <c r="BN50" s="7" t="n"/>
+      <c r="BR50" s="4" t="n"/>
+      <c r="BS50" s="6" t="n"/>
+      <c r="BT50" s="8" t="n"/>
+      <c r="BU50" s="11" t="inlineStr"/>
+      <c r="BV50" s="6" t="n"/>
+      <c r="BW50" s="8" t="n"/>
+      <c r="BX50" s="12" t="n"/>
+      <c r="BY50" s="12" t="n"/>
+      <c r="BZ50" s="12" t="n"/>
+      <c r="CA50" s="12" t="n"/>
+      <c r="CB50" s="8" t="n"/>
+      <c r="CC50" s="12" t="n"/>
+      <c r="CD50" s="12" t="n"/>
+      <c r="CE50" s="12" t="n"/>
+      <c r="CF50" s="12" t="n"/>
+      <c r="CG50" s="8" t="n"/>
+      <c r="CH50" s="12" t="n"/>
+      <c r="CI50" s="12" t="n"/>
+      <c r="CJ50" s="12" t="n"/>
+      <c r="CK50" s="12" t="n"/>
+      <c r="CL50" s="8" t="n"/>
+      <c r="CM50" s="12" t="n"/>
+      <c r="CN50" s="12" t="n"/>
+      <c r="CO50" s="12" t="n"/>
+      <c r="CP50" s="12" t="n"/>
+      <c r="CQ50" s="8" t="n"/>
+      <c r="CR50" s="12" t="n"/>
+      <c r="CS50" s="12" t="n"/>
+      <c r="CT50" s="12" t="n"/>
+      <c r="CU50" s="12" t="n"/>
+      <c r="CV50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="B51" s="4" t="n"/>
@@ -3123,6 +7125,68 @@
       <c r="AD51" s="12" t="n"/>
       <c r="AE51" s="12" t="n"/>
       <c r="AF51" s="7" t="n"/>
+      <c r="AJ51" s="4" t="n"/>
+      <c r="AK51" s="6" t="n"/>
+      <c r="AL51" s="8" t="n"/>
+      <c r="AM51" s="11" t="inlineStr"/>
+      <c r="AN51" s="6" t="n"/>
+      <c r="AO51" s="8" t="n"/>
+      <c r="AP51" s="12" t="n"/>
+      <c r="AQ51" s="12" t="n"/>
+      <c r="AR51" s="12" t="n"/>
+      <c r="AS51" s="12" t="n"/>
+      <c r="AT51" s="8" t="n"/>
+      <c r="AU51" s="12" t="n"/>
+      <c r="AV51" s="12" t="n"/>
+      <c r="AW51" s="12" t="n"/>
+      <c r="AX51" s="12" t="n"/>
+      <c r="AY51" s="8" t="n"/>
+      <c r="AZ51" s="12" t="n"/>
+      <c r="BA51" s="12" t="n"/>
+      <c r="BB51" s="12" t="n"/>
+      <c r="BC51" s="12" t="n"/>
+      <c r="BD51" s="8" t="n"/>
+      <c r="BE51" s="12" t="n"/>
+      <c r="BF51" s="12" t="n"/>
+      <c r="BG51" s="12" t="n"/>
+      <c r="BH51" s="12" t="n"/>
+      <c r="BI51" s="8" t="n"/>
+      <c r="BJ51" s="12" t="n"/>
+      <c r="BK51" s="12" t="n"/>
+      <c r="BL51" s="12" t="n"/>
+      <c r="BM51" s="12" t="n"/>
+      <c r="BN51" s="7" t="n"/>
+      <c r="BR51" s="4" t="n"/>
+      <c r="BS51" s="6" t="n"/>
+      <c r="BT51" s="8" t="n"/>
+      <c r="BU51" s="11" t="inlineStr"/>
+      <c r="BV51" s="6" t="n"/>
+      <c r="BW51" s="8" t="n"/>
+      <c r="BX51" s="12" t="n"/>
+      <c r="BY51" s="12" t="n"/>
+      <c r="BZ51" s="12" t="n"/>
+      <c r="CA51" s="12" t="n"/>
+      <c r="CB51" s="8" t="n"/>
+      <c r="CC51" s="12" t="n"/>
+      <c r="CD51" s="12" t="n"/>
+      <c r="CE51" s="12" t="n"/>
+      <c r="CF51" s="12" t="n"/>
+      <c r="CG51" s="8" t="n"/>
+      <c r="CH51" s="12" t="n"/>
+      <c r="CI51" s="12" t="n"/>
+      <c r="CJ51" s="12" t="n"/>
+      <c r="CK51" s="12" t="n"/>
+      <c r="CL51" s="8" t="n"/>
+      <c r="CM51" s="12" t="n"/>
+      <c r="CN51" s="12" t="n"/>
+      <c r="CO51" s="12" t="n"/>
+      <c r="CP51" s="12" t="n"/>
+      <c r="CQ51" s="8" t="n"/>
+      <c r="CR51" s="12" t="n"/>
+      <c r="CS51" s="12" t="n"/>
+      <c r="CT51" s="12" t="n"/>
+      <c r="CU51" s="12" t="n"/>
+      <c r="CV51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="B52" s="4" t="n"/>
@@ -3156,6 +7220,68 @@
       <c r="AD52" s="12" t="n"/>
       <c r="AE52" s="12" t="n"/>
       <c r="AF52" s="7" t="n"/>
+      <c r="AJ52" s="4" t="n"/>
+      <c r="AK52" s="6" t="n"/>
+      <c r="AL52" s="8" t="n"/>
+      <c r="AM52" s="11" t="inlineStr"/>
+      <c r="AN52" s="6" t="n"/>
+      <c r="AO52" s="8" t="n"/>
+      <c r="AP52" s="12" t="n"/>
+      <c r="AQ52" s="12" t="n"/>
+      <c r="AR52" s="12" t="n"/>
+      <c r="AS52" s="12" t="n"/>
+      <c r="AT52" s="8" t="n"/>
+      <c r="AU52" s="12" t="n"/>
+      <c r="AV52" s="12" t="n"/>
+      <c r="AW52" s="12" t="n"/>
+      <c r="AX52" s="12" t="n"/>
+      <c r="AY52" s="8" t="n"/>
+      <c r="AZ52" s="12" t="n"/>
+      <c r="BA52" s="12" t="n"/>
+      <c r="BB52" s="12" t="n"/>
+      <c r="BC52" s="12" t="n"/>
+      <c r="BD52" s="8" t="n"/>
+      <c r="BE52" s="12" t="n"/>
+      <c r="BF52" s="12" t="n"/>
+      <c r="BG52" s="12" t="n"/>
+      <c r="BH52" s="12" t="n"/>
+      <c r="BI52" s="8" t="n"/>
+      <c r="BJ52" s="12" t="n"/>
+      <c r="BK52" s="12" t="n"/>
+      <c r="BL52" s="12" t="n"/>
+      <c r="BM52" s="12" t="n"/>
+      <c r="BN52" s="7" t="n"/>
+      <c r="BR52" s="4" t="n"/>
+      <c r="BS52" s="6" t="n"/>
+      <c r="BT52" s="8" t="n"/>
+      <c r="BU52" s="11" t="inlineStr"/>
+      <c r="BV52" s="6" t="n"/>
+      <c r="BW52" s="8" t="n"/>
+      <c r="BX52" s="12" t="n"/>
+      <c r="BY52" s="12" t="n"/>
+      <c r="BZ52" s="12" t="n"/>
+      <c r="CA52" s="12" t="n"/>
+      <c r="CB52" s="8" t="n"/>
+      <c r="CC52" s="12" t="n"/>
+      <c r="CD52" s="12" t="n"/>
+      <c r="CE52" s="12" t="n"/>
+      <c r="CF52" s="12" t="n"/>
+      <c r="CG52" s="8" t="n"/>
+      <c r="CH52" s="12" t="n"/>
+      <c r="CI52" s="12" t="n"/>
+      <c r="CJ52" s="12" t="n"/>
+      <c r="CK52" s="12" t="n"/>
+      <c r="CL52" s="8" t="n"/>
+      <c r="CM52" s="12" t="n"/>
+      <c r="CN52" s="12" t="n"/>
+      <c r="CO52" s="12" t="n"/>
+      <c r="CP52" s="12" t="n"/>
+      <c r="CQ52" s="8" t="n"/>
+      <c r="CR52" s="12" t="n"/>
+      <c r="CS52" s="12" t="n"/>
+      <c r="CT52" s="12" t="n"/>
+      <c r="CU52" s="12" t="n"/>
+      <c r="CV52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="B53" s="4" t="n"/>
@@ -3189,6 +7315,68 @@
       <c r="AD53" s="8" t="n"/>
       <c r="AE53" s="8" t="n"/>
       <c r="AF53" s="7" t="n"/>
+      <c r="AJ53" s="4" t="n"/>
+      <c r="AK53" s="8" t="n"/>
+      <c r="AL53" s="8" t="n"/>
+      <c r="AM53" s="8" t="n"/>
+      <c r="AN53" s="8" t="n"/>
+      <c r="AO53" s="8" t="n"/>
+      <c r="AP53" s="8" t="n"/>
+      <c r="AQ53" s="8" t="n"/>
+      <c r="AR53" s="8" t="n"/>
+      <c r="AS53" s="8" t="n"/>
+      <c r="AT53" s="8" t="n"/>
+      <c r="AU53" s="8" t="n"/>
+      <c r="AV53" s="8" t="n"/>
+      <c r="AW53" s="8" t="n"/>
+      <c r="AX53" s="8" t="n"/>
+      <c r="AY53" s="8" t="n"/>
+      <c r="AZ53" s="8" t="n"/>
+      <c r="BA53" s="8" t="n"/>
+      <c r="BB53" s="8" t="n"/>
+      <c r="BC53" s="8" t="n"/>
+      <c r="BD53" s="8" t="n"/>
+      <c r="BE53" s="8" t="n"/>
+      <c r="BF53" s="8" t="n"/>
+      <c r="BG53" s="8" t="n"/>
+      <c r="BH53" s="8" t="n"/>
+      <c r="BI53" s="8" t="n"/>
+      <c r="BJ53" s="8" t="n"/>
+      <c r="BK53" s="8" t="n"/>
+      <c r="BL53" s="8" t="n"/>
+      <c r="BM53" s="8" t="n"/>
+      <c r="BN53" s="7" t="n"/>
+      <c r="BR53" s="4" t="n"/>
+      <c r="BS53" s="8" t="n"/>
+      <c r="BT53" s="8" t="n"/>
+      <c r="BU53" s="8" t="n"/>
+      <c r="BV53" s="8" t="n"/>
+      <c r="BW53" s="8" t="n"/>
+      <c r="BX53" s="8" t="n"/>
+      <c r="BY53" s="8" t="n"/>
+      <c r="BZ53" s="8" t="n"/>
+      <c r="CA53" s="8" t="n"/>
+      <c r="CB53" s="8" t="n"/>
+      <c r="CC53" s="8" t="n"/>
+      <c r="CD53" s="8" t="n"/>
+      <c r="CE53" s="8" t="n"/>
+      <c r="CF53" s="8" t="n"/>
+      <c r="CG53" s="8" t="n"/>
+      <c r="CH53" s="8" t="n"/>
+      <c r="CI53" s="8" t="n"/>
+      <c r="CJ53" s="8" t="n"/>
+      <c r="CK53" s="8" t="n"/>
+      <c r="CL53" s="8" t="n"/>
+      <c r="CM53" s="8" t="n"/>
+      <c r="CN53" s="8" t="n"/>
+      <c r="CO53" s="8" t="n"/>
+      <c r="CP53" s="8" t="n"/>
+      <c r="CQ53" s="8" t="n"/>
+      <c r="CR53" s="8" t="n"/>
+      <c r="CS53" s="8" t="n"/>
+      <c r="CT53" s="8" t="n"/>
+      <c r="CU53" s="8" t="n"/>
+      <c r="CV53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="B54" s="4" t="n"/>
@@ -3226,6 +7414,76 @@
       <c r="AD54" s="12" t="n"/>
       <c r="AE54" s="12" t="n"/>
       <c r="AF54" s="7" t="n"/>
+      <c r="AJ54" s="4" t="n"/>
+      <c r="AK54" s="10" t="inlineStr">
+        <is>
+          <t>Day 6</t>
+        </is>
+      </c>
+      <c r="AL54" s="8" t="n"/>
+      <c r="AM54" s="11" t="inlineStr"/>
+      <c r="AN54" s="6" t="n"/>
+      <c r="AO54" s="8" t="n"/>
+      <c r="AP54" s="12" t="n"/>
+      <c r="AQ54" s="12" t="n"/>
+      <c r="AR54" s="12" t="n"/>
+      <c r="AS54" s="12" t="n"/>
+      <c r="AT54" s="8" t="n"/>
+      <c r="AU54" s="12" t="n"/>
+      <c r="AV54" s="12" t="n"/>
+      <c r="AW54" s="12" t="n"/>
+      <c r="AX54" s="12" t="n"/>
+      <c r="AY54" s="8" t="n"/>
+      <c r="AZ54" s="12" t="n"/>
+      <c r="BA54" s="12" t="n"/>
+      <c r="BB54" s="12" t="n"/>
+      <c r="BC54" s="12" t="n"/>
+      <c r="BD54" s="8" t="n"/>
+      <c r="BE54" s="12" t="n"/>
+      <c r="BF54" s="12" t="n"/>
+      <c r="BG54" s="12" t="n"/>
+      <c r="BH54" s="12" t="n"/>
+      <c r="BI54" s="8" t="n"/>
+      <c r="BJ54" s="12" t="n"/>
+      <c r="BK54" s="12" t="n"/>
+      <c r="BL54" s="12" t="n"/>
+      <c r="BM54" s="12" t="n"/>
+      <c r="BN54" s="7" t="n"/>
+      <c r="BR54" s="4" t="n"/>
+      <c r="BS54" s="10" t="inlineStr">
+        <is>
+          <t>Day 6</t>
+        </is>
+      </c>
+      <c r="BT54" s="8" t="n"/>
+      <c r="BU54" s="11" t="inlineStr"/>
+      <c r="BV54" s="6" t="n"/>
+      <c r="BW54" s="8" t="n"/>
+      <c r="BX54" s="12" t="n"/>
+      <c r="BY54" s="12" t="n"/>
+      <c r="BZ54" s="12" t="n"/>
+      <c r="CA54" s="12" t="n"/>
+      <c r="CB54" s="8" t="n"/>
+      <c r="CC54" s="12" t="n"/>
+      <c r="CD54" s="12" t="n"/>
+      <c r="CE54" s="12" t="n"/>
+      <c r="CF54" s="12" t="n"/>
+      <c r="CG54" s="8" t="n"/>
+      <c r="CH54" s="12" t="n"/>
+      <c r="CI54" s="12" t="n"/>
+      <c r="CJ54" s="12" t="n"/>
+      <c r="CK54" s="12" t="n"/>
+      <c r="CL54" s="8" t="n"/>
+      <c r="CM54" s="12" t="n"/>
+      <c r="CN54" s="12" t="n"/>
+      <c r="CO54" s="12" t="n"/>
+      <c r="CP54" s="12" t="n"/>
+      <c r="CQ54" s="8" t="n"/>
+      <c r="CR54" s="12" t="n"/>
+      <c r="CS54" s="12" t="n"/>
+      <c r="CT54" s="12" t="n"/>
+      <c r="CU54" s="12" t="n"/>
+      <c r="CV54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="B55" s="4" t="n"/>
@@ -3259,6 +7517,68 @@
       <c r="AD55" s="12" t="n"/>
       <c r="AE55" s="12" t="n"/>
       <c r="AF55" s="7" t="n"/>
+      <c r="AJ55" s="4" t="n"/>
+      <c r="AK55" s="6" t="n"/>
+      <c r="AL55" s="8" t="n"/>
+      <c r="AM55" s="11" t="inlineStr"/>
+      <c r="AN55" s="6" t="n"/>
+      <c r="AO55" s="8" t="n"/>
+      <c r="AP55" s="12" t="n"/>
+      <c r="AQ55" s="12" t="n"/>
+      <c r="AR55" s="12" t="n"/>
+      <c r="AS55" s="12" t="n"/>
+      <c r="AT55" s="8" t="n"/>
+      <c r="AU55" s="12" t="n"/>
+      <c r="AV55" s="12" t="n"/>
+      <c r="AW55" s="12" t="n"/>
+      <c r="AX55" s="12" t="n"/>
+      <c r="AY55" s="8" t="n"/>
+      <c r="AZ55" s="12" t="n"/>
+      <c r="BA55" s="12" t="n"/>
+      <c r="BB55" s="12" t="n"/>
+      <c r="BC55" s="12" t="n"/>
+      <c r="BD55" s="8" t="n"/>
+      <c r="BE55" s="12" t="n"/>
+      <c r="BF55" s="12" t="n"/>
+      <c r="BG55" s="12" t="n"/>
+      <c r="BH55" s="12" t="n"/>
+      <c r="BI55" s="8" t="n"/>
+      <c r="BJ55" s="12" t="n"/>
+      <c r="BK55" s="12" t="n"/>
+      <c r="BL55" s="12" t="n"/>
+      <c r="BM55" s="12" t="n"/>
+      <c r="BN55" s="7" t="n"/>
+      <c r="BR55" s="4" t="n"/>
+      <c r="BS55" s="6" t="n"/>
+      <c r="BT55" s="8" t="n"/>
+      <c r="BU55" s="11" t="inlineStr"/>
+      <c r="BV55" s="6" t="n"/>
+      <c r="BW55" s="8" t="n"/>
+      <c r="BX55" s="12" t="n"/>
+      <c r="BY55" s="12" t="n"/>
+      <c r="BZ55" s="12" t="n"/>
+      <c r="CA55" s="12" t="n"/>
+      <c r="CB55" s="8" t="n"/>
+      <c r="CC55" s="12" t="n"/>
+      <c r="CD55" s="12" t="n"/>
+      <c r="CE55" s="12" t="n"/>
+      <c r="CF55" s="12" t="n"/>
+      <c r="CG55" s="8" t="n"/>
+      <c r="CH55" s="12" t="n"/>
+      <c r="CI55" s="12" t="n"/>
+      <c r="CJ55" s="12" t="n"/>
+      <c r="CK55" s="12" t="n"/>
+      <c r="CL55" s="8" t="n"/>
+      <c r="CM55" s="12" t="n"/>
+      <c r="CN55" s="12" t="n"/>
+      <c r="CO55" s="12" t="n"/>
+      <c r="CP55" s="12" t="n"/>
+      <c r="CQ55" s="8" t="n"/>
+      <c r="CR55" s="12" t="n"/>
+      <c r="CS55" s="12" t="n"/>
+      <c r="CT55" s="12" t="n"/>
+      <c r="CU55" s="12" t="n"/>
+      <c r="CV55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="B56" s="4" t="n"/>
@@ -3292,6 +7612,68 @@
       <c r="AD56" s="12" t="n"/>
       <c r="AE56" s="12" t="n"/>
       <c r="AF56" s="7" t="n"/>
+      <c r="AJ56" s="4" t="n"/>
+      <c r="AK56" s="6" t="n"/>
+      <c r="AL56" s="8" t="n"/>
+      <c r="AM56" s="11" t="inlineStr"/>
+      <c r="AN56" s="6" t="n"/>
+      <c r="AO56" s="8" t="n"/>
+      <c r="AP56" s="12" t="n"/>
+      <c r="AQ56" s="12" t="n"/>
+      <c r="AR56" s="12" t="n"/>
+      <c r="AS56" s="12" t="n"/>
+      <c r="AT56" s="8" t="n"/>
+      <c r="AU56" s="12" t="n"/>
+      <c r="AV56" s="12" t="n"/>
+      <c r="AW56" s="12" t="n"/>
+      <c r="AX56" s="12" t="n"/>
+      <c r="AY56" s="8" t="n"/>
+      <c r="AZ56" s="12" t="n"/>
+      <c r="BA56" s="12" t="n"/>
+      <c r="BB56" s="12" t="n"/>
+      <c r="BC56" s="12" t="n"/>
+      <c r="BD56" s="8" t="n"/>
+      <c r="BE56" s="12" t="n"/>
+      <c r="BF56" s="12" t="n"/>
+      <c r="BG56" s="12" t="n"/>
+      <c r="BH56" s="12" t="n"/>
+      <c r="BI56" s="8" t="n"/>
+      <c r="BJ56" s="12" t="n"/>
+      <c r="BK56" s="12" t="n"/>
+      <c r="BL56" s="12" t="n"/>
+      <c r="BM56" s="12" t="n"/>
+      <c r="BN56" s="7" t="n"/>
+      <c r="BR56" s="4" t="n"/>
+      <c r="BS56" s="6" t="n"/>
+      <c r="BT56" s="8" t="n"/>
+      <c r="BU56" s="11" t="inlineStr"/>
+      <c r="BV56" s="6" t="n"/>
+      <c r="BW56" s="8" t="n"/>
+      <c r="BX56" s="12" t="n"/>
+      <c r="BY56" s="12" t="n"/>
+      <c r="BZ56" s="12" t="n"/>
+      <c r="CA56" s="12" t="n"/>
+      <c r="CB56" s="8" t="n"/>
+      <c r="CC56" s="12" t="n"/>
+      <c r="CD56" s="12" t="n"/>
+      <c r="CE56" s="12" t="n"/>
+      <c r="CF56" s="12" t="n"/>
+      <c r="CG56" s="8" t="n"/>
+      <c r="CH56" s="12" t="n"/>
+      <c r="CI56" s="12" t="n"/>
+      <c r="CJ56" s="12" t="n"/>
+      <c r="CK56" s="12" t="n"/>
+      <c r="CL56" s="8" t="n"/>
+      <c r="CM56" s="12" t="n"/>
+      <c r="CN56" s="12" t="n"/>
+      <c r="CO56" s="12" t="n"/>
+      <c r="CP56" s="12" t="n"/>
+      <c r="CQ56" s="8" t="n"/>
+      <c r="CR56" s="12" t="n"/>
+      <c r="CS56" s="12" t="n"/>
+      <c r="CT56" s="12" t="n"/>
+      <c r="CU56" s="12" t="n"/>
+      <c r="CV56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="B57" s="4" t="n"/>
@@ -3325,6 +7707,68 @@
       <c r="AD57" s="12" t="n"/>
       <c r="AE57" s="12" t="n"/>
       <c r="AF57" s="7" t="n"/>
+      <c r="AJ57" s="4" t="n"/>
+      <c r="AK57" s="6" t="n"/>
+      <c r="AL57" s="8" t="n"/>
+      <c r="AM57" s="11" t="inlineStr"/>
+      <c r="AN57" s="6" t="n"/>
+      <c r="AO57" s="8" t="n"/>
+      <c r="AP57" s="12" t="n"/>
+      <c r="AQ57" s="12" t="n"/>
+      <c r="AR57" s="12" t="n"/>
+      <c r="AS57" s="12" t="n"/>
+      <c r="AT57" s="8" t="n"/>
+      <c r="AU57" s="12" t="n"/>
+      <c r="AV57" s="12" t="n"/>
+      <c r="AW57" s="12" t="n"/>
+      <c r="AX57" s="12" t="n"/>
+      <c r="AY57" s="8" t="n"/>
+      <c r="AZ57" s="12" t="n"/>
+      <c r="BA57" s="12" t="n"/>
+      <c r="BB57" s="12" t="n"/>
+      <c r="BC57" s="12" t="n"/>
+      <c r="BD57" s="8" t="n"/>
+      <c r="BE57" s="12" t="n"/>
+      <c r="BF57" s="12" t="n"/>
+      <c r="BG57" s="12" t="n"/>
+      <c r="BH57" s="12" t="n"/>
+      <c r="BI57" s="8" t="n"/>
+      <c r="BJ57" s="12" t="n"/>
+      <c r="BK57" s="12" t="n"/>
+      <c r="BL57" s="12" t="n"/>
+      <c r="BM57" s="12" t="n"/>
+      <c r="BN57" s="7" t="n"/>
+      <c r="BR57" s="4" t="n"/>
+      <c r="BS57" s="6" t="n"/>
+      <c r="BT57" s="8" t="n"/>
+      <c r="BU57" s="11" t="inlineStr"/>
+      <c r="BV57" s="6" t="n"/>
+      <c r="BW57" s="8" t="n"/>
+      <c r="BX57" s="12" t="n"/>
+      <c r="BY57" s="12" t="n"/>
+      <c r="BZ57" s="12" t="n"/>
+      <c r="CA57" s="12" t="n"/>
+      <c r="CB57" s="8" t="n"/>
+      <c r="CC57" s="12" t="n"/>
+      <c r="CD57" s="12" t="n"/>
+      <c r="CE57" s="12" t="n"/>
+      <c r="CF57" s="12" t="n"/>
+      <c r="CG57" s="8" t="n"/>
+      <c r="CH57" s="12" t="n"/>
+      <c r="CI57" s="12" t="n"/>
+      <c r="CJ57" s="12" t="n"/>
+      <c r="CK57" s="12" t="n"/>
+      <c r="CL57" s="8" t="n"/>
+      <c r="CM57" s="12" t="n"/>
+      <c r="CN57" s="12" t="n"/>
+      <c r="CO57" s="12" t="n"/>
+      <c r="CP57" s="12" t="n"/>
+      <c r="CQ57" s="8" t="n"/>
+      <c r="CR57" s="12" t="n"/>
+      <c r="CS57" s="12" t="n"/>
+      <c r="CT57" s="12" t="n"/>
+      <c r="CU57" s="12" t="n"/>
+      <c r="CV57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="B58" s="4" t="n"/>
@@ -3358,6 +7802,68 @@
       <c r="AD58" s="12" t="n"/>
       <c r="AE58" s="12" t="n"/>
       <c r="AF58" s="7" t="n"/>
+      <c r="AJ58" s="4" t="n"/>
+      <c r="AK58" s="6" t="n"/>
+      <c r="AL58" s="8" t="n"/>
+      <c r="AM58" s="11" t="inlineStr"/>
+      <c r="AN58" s="6" t="n"/>
+      <c r="AO58" s="8" t="n"/>
+      <c r="AP58" s="12" t="n"/>
+      <c r="AQ58" s="12" t="n"/>
+      <c r="AR58" s="12" t="n"/>
+      <c r="AS58" s="12" t="n"/>
+      <c r="AT58" s="8" t="n"/>
+      <c r="AU58" s="12" t="n"/>
+      <c r="AV58" s="12" t="n"/>
+      <c r="AW58" s="12" t="n"/>
+      <c r="AX58" s="12" t="n"/>
+      <c r="AY58" s="8" t="n"/>
+      <c r="AZ58" s="12" t="n"/>
+      <c r="BA58" s="12" t="n"/>
+      <c r="BB58" s="12" t="n"/>
+      <c r="BC58" s="12" t="n"/>
+      <c r="BD58" s="8" t="n"/>
+      <c r="BE58" s="12" t="n"/>
+      <c r="BF58" s="12" t="n"/>
+      <c r="BG58" s="12" t="n"/>
+      <c r="BH58" s="12" t="n"/>
+      <c r="BI58" s="8" t="n"/>
+      <c r="BJ58" s="12" t="n"/>
+      <c r="BK58" s="12" t="n"/>
+      <c r="BL58" s="12" t="n"/>
+      <c r="BM58" s="12" t="n"/>
+      <c r="BN58" s="7" t="n"/>
+      <c r="BR58" s="4" t="n"/>
+      <c r="BS58" s="6" t="n"/>
+      <c r="BT58" s="8" t="n"/>
+      <c r="BU58" s="11" t="inlineStr"/>
+      <c r="BV58" s="6" t="n"/>
+      <c r="BW58" s="8" t="n"/>
+      <c r="BX58" s="12" t="n"/>
+      <c r="BY58" s="12" t="n"/>
+      <c r="BZ58" s="12" t="n"/>
+      <c r="CA58" s="12" t="n"/>
+      <c r="CB58" s="8" t="n"/>
+      <c r="CC58" s="12" t="n"/>
+      <c r="CD58" s="12" t="n"/>
+      <c r="CE58" s="12" t="n"/>
+      <c r="CF58" s="12" t="n"/>
+      <c r="CG58" s="8" t="n"/>
+      <c r="CH58" s="12" t="n"/>
+      <c r="CI58" s="12" t="n"/>
+      <c r="CJ58" s="12" t="n"/>
+      <c r="CK58" s="12" t="n"/>
+      <c r="CL58" s="8" t="n"/>
+      <c r="CM58" s="12" t="n"/>
+      <c r="CN58" s="12" t="n"/>
+      <c r="CO58" s="12" t="n"/>
+      <c r="CP58" s="12" t="n"/>
+      <c r="CQ58" s="8" t="n"/>
+      <c r="CR58" s="12" t="n"/>
+      <c r="CS58" s="12" t="n"/>
+      <c r="CT58" s="12" t="n"/>
+      <c r="CU58" s="12" t="n"/>
+      <c r="CV58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="B59" s="4" t="n"/>
@@ -3391,6 +7897,68 @@
       <c r="AD59" s="12" t="n"/>
       <c r="AE59" s="12" t="n"/>
       <c r="AF59" s="7" t="n"/>
+      <c r="AJ59" s="4" t="n"/>
+      <c r="AK59" s="6" t="n"/>
+      <c r="AL59" s="8" t="n"/>
+      <c r="AM59" s="11" t="inlineStr"/>
+      <c r="AN59" s="6" t="n"/>
+      <c r="AO59" s="8" t="n"/>
+      <c r="AP59" s="12" t="n"/>
+      <c r="AQ59" s="12" t="n"/>
+      <c r="AR59" s="12" t="n"/>
+      <c r="AS59" s="12" t="n"/>
+      <c r="AT59" s="8" t="n"/>
+      <c r="AU59" s="12" t="n"/>
+      <c r="AV59" s="12" t="n"/>
+      <c r="AW59" s="12" t="n"/>
+      <c r="AX59" s="12" t="n"/>
+      <c r="AY59" s="8" t="n"/>
+      <c r="AZ59" s="12" t="n"/>
+      <c r="BA59" s="12" t="n"/>
+      <c r="BB59" s="12" t="n"/>
+      <c r="BC59" s="12" t="n"/>
+      <c r="BD59" s="8" t="n"/>
+      <c r="BE59" s="12" t="n"/>
+      <c r="BF59" s="12" t="n"/>
+      <c r="BG59" s="12" t="n"/>
+      <c r="BH59" s="12" t="n"/>
+      <c r="BI59" s="8" t="n"/>
+      <c r="BJ59" s="12" t="n"/>
+      <c r="BK59" s="12" t="n"/>
+      <c r="BL59" s="12" t="n"/>
+      <c r="BM59" s="12" t="n"/>
+      <c r="BN59" s="7" t="n"/>
+      <c r="BR59" s="4" t="n"/>
+      <c r="BS59" s="6" t="n"/>
+      <c r="BT59" s="8" t="n"/>
+      <c r="BU59" s="11" t="inlineStr"/>
+      <c r="BV59" s="6" t="n"/>
+      <c r="BW59" s="8" t="n"/>
+      <c r="BX59" s="12" t="n"/>
+      <c r="BY59" s="12" t="n"/>
+      <c r="BZ59" s="12" t="n"/>
+      <c r="CA59" s="12" t="n"/>
+      <c r="CB59" s="8" t="n"/>
+      <c r="CC59" s="12" t="n"/>
+      <c r="CD59" s="12" t="n"/>
+      <c r="CE59" s="12" t="n"/>
+      <c r="CF59" s="12" t="n"/>
+      <c r="CG59" s="8" t="n"/>
+      <c r="CH59" s="12" t="n"/>
+      <c r="CI59" s="12" t="n"/>
+      <c r="CJ59" s="12" t="n"/>
+      <c r="CK59" s="12" t="n"/>
+      <c r="CL59" s="8" t="n"/>
+      <c r="CM59" s="12" t="n"/>
+      <c r="CN59" s="12" t="n"/>
+      <c r="CO59" s="12" t="n"/>
+      <c r="CP59" s="12" t="n"/>
+      <c r="CQ59" s="8" t="n"/>
+      <c r="CR59" s="12" t="n"/>
+      <c r="CS59" s="12" t="n"/>
+      <c r="CT59" s="12" t="n"/>
+      <c r="CU59" s="12" t="n"/>
+      <c r="CV59" s="7" t="n"/>
     </row>
     <row r="60">
       <c r="B60" s="4" t="n"/>
@@ -3424,6 +7992,68 @@
       <c r="AD60" s="12" t="n"/>
       <c r="AE60" s="12" t="n"/>
       <c r="AF60" s="7" t="n"/>
+      <c r="AJ60" s="4" t="n"/>
+      <c r="AK60" s="6" t="n"/>
+      <c r="AL60" s="8" t="n"/>
+      <c r="AM60" s="11" t="inlineStr"/>
+      <c r="AN60" s="6" t="n"/>
+      <c r="AO60" s="8" t="n"/>
+      <c r="AP60" s="12" t="n"/>
+      <c r="AQ60" s="12" t="n"/>
+      <c r="AR60" s="12" t="n"/>
+      <c r="AS60" s="12" t="n"/>
+      <c r="AT60" s="8" t="n"/>
+      <c r="AU60" s="12" t="n"/>
+      <c r="AV60" s="12" t="n"/>
+      <c r="AW60" s="12" t="n"/>
+      <c r="AX60" s="12" t="n"/>
+      <c r="AY60" s="8" t="n"/>
+      <c r="AZ60" s="12" t="n"/>
+      <c r="BA60" s="12" t="n"/>
+      <c r="BB60" s="12" t="n"/>
+      <c r="BC60" s="12" t="n"/>
+      <c r="BD60" s="8" t="n"/>
+      <c r="BE60" s="12" t="n"/>
+      <c r="BF60" s="12" t="n"/>
+      <c r="BG60" s="12" t="n"/>
+      <c r="BH60" s="12" t="n"/>
+      <c r="BI60" s="8" t="n"/>
+      <c r="BJ60" s="12" t="n"/>
+      <c r="BK60" s="12" t="n"/>
+      <c r="BL60" s="12" t="n"/>
+      <c r="BM60" s="12" t="n"/>
+      <c r="BN60" s="7" t="n"/>
+      <c r="BR60" s="4" t="n"/>
+      <c r="BS60" s="6" t="n"/>
+      <c r="BT60" s="8" t="n"/>
+      <c r="BU60" s="11" t="inlineStr"/>
+      <c r="BV60" s="6" t="n"/>
+      <c r="BW60" s="8" t="n"/>
+      <c r="BX60" s="12" t="n"/>
+      <c r="BY60" s="12" t="n"/>
+      <c r="BZ60" s="12" t="n"/>
+      <c r="CA60" s="12" t="n"/>
+      <c r="CB60" s="8" t="n"/>
+      <c r="CC60" s="12" t="n"/>
+      <c r="CD60" s="12" t="n"/>
+      <c r="CE60" s="12" t="n"/>
+      <c r="CF60" s="12" t="n"/>
+      <c r="CG60" s="8" t="n"/>
+      <c r="CH60" s="12" t="n"/>
+      <c r="CI60" s="12" t="n"/>
+      <c r="CJ60" s="12" t="n"/>
+      <c r="CK60" s="12" t="n"/>
+      <c r="CL60" s="8" t="n"/>
+      <c r="CM60" s="12" t="n"/>
+      <c r="CN60" s="12" t="n"/>
+      <c r="CO60" s="12" t="n"/>
+      <c r="CP60" s="12" t="n"/>
+      <c r="CQ60" s="8" t="n"/>
+      <c r="CR60" s="12" t="n"/>
+      <c r="CS60" s="12" t="n"/>
+      <c r="CT60" s="12" t="n"/>
+      <c r="CU60" s="12" t="n"/>
+      <c r="CV60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="B61" s="4" t="n"/>
@@ -3457,6 +8087,68 @@
       <c r="AD61" s="12" t="n"/>
       <c r="AE61" s="12" t="n"/>
       <c r="AF61" s="7" t="n"/>
+      <c r="AJ61" s="4" t="n"/>
+      <c r="AK61" s="6" t="n"/>
+      <c r="AL61" s="8" t="n"/>
+      <c r="AM61" s="11" t="inlineStr"/>
+      <c r="AN61" s="6" t="n"/>
+      <c r="AO61" s="8" t="n"/>
+      <c r="AP61" s="12" t="n"/>
+      <c r="AQ61" s="12" t="n"/>
+      <c r="AR61" s="12" t="n"/>
+      <c r="AS61" s="12" t="n"/>
+      <c r="AT61" s="8" t="n"/>
+      <c r="AU61" s="12" t="n"/>
+      <c r="AV61" s="12" t="n"/>
+      <c r="AW61" s="12" t="n"/>
+      <c r="AX61" s="12" t="n"/>
+      <c r="AY61" s="8" t="n"/>
+      <c r="AZ61" s="12" t="n"/>
+      <c r="BA61" s="12" t="n"/>
+      <c r="BB61" s="12" t="n"/>
+      <c r="BC61" s="12" t="n"/>
+      <c r="BD61" s="8" t="n"/>
+      <c r="BE61" s="12" t="n"/>
+      <c r="BF61" s="12" t="n"/>
+      <c r="BG61" s="12" t="n"/>
+      <c r="BH61" s="12" t="n"/>
+      <c r="BI61" s="8" t="n"/>
+      <c r="BJ61" s="12" t="n"/>
+      <c r="BK61" s="12" t="n"/>
+      <c r="BL61" s="12" t="n"/>
+      <c r="BM61" s="12" t="n"/>
+      <c r="BN61" s="7" t="n"/>
+      <c r="BR61" s="4" t="n"/>
+      <c r="BS61" s="6" t="n"/>
+      <c r="BT61" s="8" t="n"/>
+      <c r="BU61" s="11" t="inlineStr"/>
+      <c r="BV61" s="6" t="n"/>
+      <c r="BW61" s="8" t="n"/>
+      <c r="BX61" s="12" t="n"/>
+      <c r="BY61" s="12" t="n"/>
+      <c r="BZ61" s="12" t="n"/>
+      <c r="CA61" s="12" t="n"/>
+      <c r="CB61" s="8" t="n"/>
+      <c r="CC61" s="12" t="n"/>
+      <c r="CD61" s="12" t="n"/>
+      <c r="CE61" s="12" t="n"/>
+      <c r="CF61" s="12" t="n"/>
+      <c r="CG61" s="8" t="n"/>
+      <c r="CH61" s="12" t="n"/>
+      <c r="CI61" s="12" t="n"/>
+      <c r="CJ61" s="12" t="n"/>
+      <c r="CK61" s="12" t="n"/>
+      <c r="CL61" s="8" t="n"/>
+      <c r="CM61" s="12" t="n"/>
+      <c r="CN61" s="12" t="n"/>
+      <c r="CO61" s="12" t="n"/>
+      <c r="CP61" s="12" t="n"/>
+      <c r="CQ61" s="8" t="n"/>
+      <c r="CR61" s="12" t="n"/>
+      <c r="CS61" s="12" t="n"/>
+      <c r="CT61" s="12" t="n"/>
+      <c r="CU61" s="12" t="n"/>
+      <c r="CV61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="B62" s="4" t="n"/>
@@ -3490,6 +8182,68 @@
       <c r="AD62" s="8" t="n"/>
       <c r="AE62" s="8" t="n"/>
       <c r="AF62" s="7" t="n"/>
+      <c r="AJ62" s="4" t="n"/>
+      <c r="AK62" s="8" t="n"/>
+      <c r="AL62" s="8" t="n"/>
+      <c r="AM62" s="8" t="n"/>
+      <c r="AN62" s="8" t="n"/>
+      <c r="AO62" s="8" t="n"/>
+      <c r="AP62" s="8" t="n"/>
+      <c r="AQ62" s="8" t="n"/>
+      <c r="AR62" s="8" t="n"/>
+      <c r="AS62" s="8" t="n"/>
+      <c r="AT62" s="8" t="n"/>
+      <c r="AU62" s="8" t="n"/>
+      <c r="AV62" s="8" t="n"/>
+      <c r="AW62" s="8" t="n"/>
+      <c r="AX62" s="8" t="n"/>
+      <c r="AY62" s="8" t="n"/>
+      <c r="AZ62" s="8" t="n"/>
+      <c r="BA62" s="8" t="n"/>
+      <c r="BB62" s="8" t="n"/>
+      <c r="BC62" s="8" t="n"/>
+      <c r="BD62" s="8" t="n"/>
+      <c r="BE62" s="8" t="n"/>
+      <c r="BF62" s="8" t="n"/>
+      <c r="BG62" s="8" t="n"/>
+      <c r="BH62" s="8" t="n"/>
+      <c r="BI62" s="8" t="n"/>
+      <c r="BJ62" s="8" t="n"/>
+      <c r="BK62" s="8" t="n"/>
+      <c r="BL62" s="8" t="n"/>
+      <c r="BM62" s="8" t="n"/>
+      <c r="BN62" s="7" t="n"/>
+      <c r="BR62" s="4" t="n"/>
+      <c r="BS62" s="8" t="n"/>
+      <c r="BT62" s="8" t="n"/>
+      <c r="BU62" s="8" t="n"/>
+      <c r="BV62" s="8" t="n"/>
+      <c r="BW62" s="8" t="n"/>
+      <c r="BX62" s="8" t="n"/>
+      <c r="BY62" s="8" t="n"/>
+      <c r="BZ62" s="8" t="n"/>
+      <c r="CA62" s="8" t="n"/>
+      <c r="CB62" s="8" t="n"/>
+      <c r="CC62" s="8" t="n"/>
+      <c r="CD62" s="8" t="n"/>
+      <c r="CE62" s="8" t="n"/>
+      <c r="CF62" s="8" t="n"/>
+      <c r="CG62" s="8" t="n"/>
+      <c r="CH62" s="8" t="n"/>
+      <c r="CI62" s="8" t="n"/>
+      <c r="CJ62" s="8" t="n"/>
+      <c r="CK62" s="8" t="n"/>
+      <c r="CL62" s="8" t="n"/>
+      <c r="CM62" s="8" t="n"/>
+      <c r="CN62" s="8" t="n"/>
+      <c r="CO62" s="8" t="n"/>
+      <c r="CP62" s="8" t="n"/>
+      <c r="CQ62" s="8" t="n"/>
+      <c r="CR62" s="8" t="n"/>
+      <c r="CS62" s="8" t="n"/>
+      <c r="CT62" s="8" t="n"/>
+      <c r="CU62" s="8" t="n"/>
+      <c r="CV62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="B63" s="4" t="n"/>
@@ -3511,7 +8265,7 @@
       </c>
       <c r="I63" s="14" t="inlineStr">
         <is>
-          <t>102.5kg</t>
+          <t>105kg</t>
         </is>
       </c>
       <c r="J63" s="15" t="n">
@@ -3528,7 +8282,7 @@
       </c>
       <c r="N63" s="14" t="inlineStr">
         <is>
-          <t>102.5kg</t>
+          <t>105kg</t>
         </is>
       </c>
       <c r="O63" s="15" t="n">
@@ -3545,7 +8299,7 @@
       </c>
       <c r="S63" s="14" t="inlineStr">
         <is>
-          <t>102.5kg</t>
+          <t>105kg</t>
         </is>
       </c>
       <c r="T63" s="15" t="n">
@@ -3567,6 +8321,156 @@
       <c r="AD63" s="12" t="n"/>
       <c r="AE63" s="12" t="n"/>
       <c r="AF63" s="7" t="n"/>
+      <c r="AJ63" s="4" t="n"/>
+      <c r="AK63" s="10" t="inlineStr">
+        <is>
+          <t>Day 7</t>
+        </is>
+      </c>
+      <c r="AL63" s="8" t="n"/>
+      <c r="AM63" s="13" t="inlineStr">
+        <is>
+          <t>Squat</t>
+        </is>
+      </c>
+      <c r="AN63" s="6" t="n"/>
+      <c r="AO63" s="8" t="n"/>
+      <c r="AP63" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ63" s="14" t="inlineStr">
+        <is>
+          <t>107.5kg</t>
+        </is>
+      </c>
+      <c r="AR63" s="15" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AS63" s="16" t="inlineStr">
+        <is>
+          <t>Tempo or pause squats; slightly heavier than Week 1.</t>
+        </is>
+      </c>
+      <c r="AT63" s="8" t="n"/>
+      <c r="AU63" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV63" s="14" t="inlineStr">
+        <is>
+          <t>107.5kg</t>
+        </is>
+      </c>
+      <c r="AW63" s="15" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AX63" s="16" t="inlineStr">
+        <is>
+          <t>Tempo or pause squats; slightly heavier than Week 1.</t>
+        </is>
+      </c>
+      <c r="AY63" s="8" t="n"/>
+      <c r="AZ63" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA63" s="14" t="inlineStr">
+        <is>
+          <t>107.5kg</t>
+        </is>
+      </c>
+      <c r="BB63" s="15" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BC63" s="16" t="inlineStr">
+        <is>
+          <t>Tempo or pause squats; slightly heavier than Week 1.</t>
+        </is>
+      </c>
+      <c r="BD63" s="8" t="n"/>
+      <c r="BE63" s="12" t="n"/>
+      <c r="BF63" s="12" t="n"/>
+      <c r="BG63" s="12" t="n"/>
+      <c r="BH63" s="12" t="n"/>
+      <c r="BI63" s="8" t="n"/>
+      <c r="BJ63" s="12" t="n"/>
+      <c r="BK63" s="12" t="n"/>
+      <c r="BL63" s="12" t="n"/>
+      <c r="BM63" s="12" t="n"/>
+      <c r="BN63" s="7" t="n"/>
+      <c r="BR63" s="4" t="n"/>
+      <c r="BS63" s="10" t="inlineStr">
+        <is>
+          <t>Day 7</t>
+        </is>
+      </c>
+      <c r="BT63" s="8" t="n"/>
+      <c r="BU63" s="13" t="inlineStr">
+        <is>
+          <t>Squat</t>
+        </is>
+      </c>
+      <c r="BV63" s="6" t="n"/>
+      <c r="BW63" s="8" t="n"/>
+      <c r="BX63" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="BY63" s="14" t="inlineStr">
+        <is>
+          <t>112.5kg</t>
+        </is>
+      </c>
+      <c r="BZ63" s="15" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="CA63" s="16" t="inlineStr">
+        <is>
+          <t>Pause squats or tempo reps; maintain fluid motion.</t>
+        </is>
+      </c>
+      <c r="CB63" s="8" t="n"/>
+      <c r="CC63" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="CD63" s="14" t="inlineStr">
+        <is>
+          <t>112.5kg</t>
+        </is>
+      </c>
+      <c r="CE63" s="15" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="CF63" s="16" t="inlineStr">
+        <is>
+          <t>Pause squats or tempo reps; maintain fluid motion.</t>
+        </is>
+      </c>
+      <c r="CG63" s="8" t="n"/>
+      <c r="CH63" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="CI63" s="14" t="inlineStr">
+        <is>
+          <t>112.5kg</t>
+        </is>
+      </c>
+      <c r="CJ63" s="15" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="CK63" s="16" t="inlineStr">
+        <is>
+          <t>Pause squats or tempo reps; maintain fluid motion.</t>
+        </is>
+      </c>
+      <c r="CL63" s="8" t="n"/>
+      <c r="CM63" s="12" t="n"/>
+      <c r="CN63" s="12" t="n"/>
+      <c r="CO63" s="12" t="n"/>
+      <c r="CP63" s="12" t="n"/>
+      <c r="CQ63" s="8" t="n"/>
+      <c r="CR63" s="12" t="n"/>
+      <c r="CS63" s="12" t="n"/>
+      <c r="CT63" s="12" t="n"/>
+      <c r="CU63" s="12" t="n"/>
+      <c r="CV63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="B64" s="4" t="n"/>
@@ -3664,6 +8568,196 @@
         </is>
       </c>
       <c r="AF64" s="7" t="n"/>
+      <c r="AJ64" s="4" t="n"/>
+      <c r="AK64" s="6" t="n"/>
+      <c r="AL64" s="8" t="n"/>
+      <c r="AM64" s="13" t="inlineStr">
+        <is>
+          <t>Weighted Muscle-Ups</t>
+        </is>
+      </c>
+      <c r="AN64" s="6" t="n"/>
+      <c r="AO64" s="8" t="n"/>
+      <c r="AP64" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ64" s="14" t="inlineStr">
+        <is>
+          <t>16.8kg</t>
+        </is>
+      </c>
+      <c r="AR64" s="15" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AS64" s="16" t="inlineStr">
+        <is>
+          <t>EMOM – Crisp explosive reps, no form breakdown.</t>
+        </is>
+      </c>
+      <c r="AT64" s="8" t="n"/>
+      <c r="AU64" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV64" s="14" t="inlineStr">
+        <is>
+          <t>16.8kg</t>
+        </is>
+      </c>
+      <c r="AW64" s="15" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AX64" s="16" t="inlineStr">
+        <is>
+          <t>EMOM – Crisp explosive reps, no form breakdown.</t>
+        </is>
+      </c>
+      <c r="AY64" s="8" t="n"/>
+      <c r="AZ64" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA64" s="14" t="inlineStr">
+        <is>
+          <t>16.8kg</t>
+        </is>
+      </c>
+      <c r="BB64" s="15" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BC64" s="16" t="inlineStr">
+        <is>
+          <t>EMOM – Crisp explosive reps, no form breakdown.</t>
+        </is>
+      </c>
+      <c r="BD64" s="8" t="n"/>
+      <c r="BE64" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF64" s="14" t="inlineStr">
+        <is>
+          <t>16.8kg</t>
+        </is>
+      </c>
+      <c r="BG64" s="15" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BH64" s="16" t="inlineStr">
+        <is>
+          <t>EMOM – Crisp explosive reps, no form breakdown.</t>
+        </is>
+      </c>
+      <c r="BI64" s="8" t="n"/>
+      <c r="BJ64" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK64" s="14" t="inlineStr">
+        <is>
+          <t>16.8kg</t>
+        </is>
+      </c>
+      <c r="BL64" s="15" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BM64" s="16" t="inlineStr">
+        <is>
+          <t>EMOM – Crisp explosive reps, no form breakdown.</t>
+        </is>
+      </c>
+      <c r="BN64" s="7" t="n"/>
+      <c r="BR64" s="4" t="n"/>
+      <c r="BS64" s="6" t="n"/>
+      <c r="BT64" s="8" t="n"/>
+      <c r="BU64" s="13" t="inlineStr">
+        <is>
+          <t>Weighted Muscle-Ups</t>
+        </is>
+      </c>
+      <c r="BV64" s="6" t="n"/>
+      <c r="BW64" s="8" t="n"/>
+      <c r="BX64" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY64" s="14" t="inlineStr">
+        <is>
+          <t>17.5kg</t>
+        </is>
+      </c>
+      <c r="BZ64" s="15" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CA64" s="16" t="inlineStr">
+        <is>
+          <t>EMOM — crisp reps, short range of fatigue.</t>
+        </is>
+      </c>
+      <c r="CB64" s="8" t="n"/>
+      <c r="CC64" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD64" s="14" t="inlineStr">
+        <is>
+          <t>17.5kg</t>
+        </is>
+      </c>
+      <c r="CE64" s="15" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CF64" s="16" t="inlineStr">
+        <is>
+          <t>EMOM — crisp reps, short range of fatigue.</t>
+        </is>
+      </c>
+      <c r="CG64" s="8" t="n"/>
+      <c r="CH64" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI64" s="14" t="inlineStr">
+        <is>
+          <t>17.5kg</t>
+        </is>
+      </c>
+      <c r="CJ64" s="15" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CK64" s="16" t="inlineStr">
+        <is>
+          <t>EMOM — crisp reps, short range of fatigue.</t>
+        </is>
+      </c>
+      <c r="CL64" s="8" t="n"/>
+      <c r="CM64" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN64" s="14" t="inlineStr">
+        <is>
+          <t>17.5kg</t>
+        </is>
+      </c>
+      <c r="CO64" s="15" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CP64" s="16" t="inlineStr">
+        <is>
+          <t>EMOM — crisp reps, short range of fatigue.</t>
+        </is>
+      </c>
+      <c r="CQ64" s="8" t="n"/>
+      <c r="CR64" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS64" s="14" t="inlineStr">
+        <is>
+          <t>17.5kg</t>
+        </is>
+      </c>
+      <c r="CT64" s="15" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CU64" s="16" t="inlineStr">
+        <is>
+          <t>EMOM — crisp reps, short range of fatigue.</t>
+        </is>
+      </c>
+      <c r="CV64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="B65" s="4" t="n"/>
@@ -3697,6 +8791,68 @@
       <c r="AD65" s="12" t="n"/>
       <c r="AE65" s="12" t="n"/>
       <c r="AF65" s="7" t="n"/>
+      <c r="AJ65" s="4" t="n"/>
+      <c r="AK65" s="6" t="n"/>
+      <c r="AL65" s="8" t="n"/>
+      <c r="AM65" s="11" t="inlineStr"/>
+      <c r="AN65" s="6" t="n"/>
+      <c r="AO65" s="8" t="n"/>
+      <c r="AP65" s="12" t="n"/>
+      <c r="AQ65" s="12" t="n"/>
+      <c r="AR65" s="12" t="n"/>
+      <c r="AS65" s="12" t="n"/>
+      <c r="AT65" s="8" t="n"/>
+      <c r="AU65" s="12" t="n"/>
+      <c r="AV65" s="12" t="n"/>
+      <c r="AW65" s="12" t="n"/>
+      <c r="AX65" s="12" t="n"/>
+      <c r="AY65" s="8" t="n"/>
+      <c r="AZ65" s="12" t="n"/>
+      <c r="BA65" s="12" t="n"/>
+      <c r="BB65" s="12" t="n"/>
+      <c r="BC65" s="12" t="n"/>
+      <c r="BD65" s="8" t="n"/>
+      <c r="BE65" s="12" t="n"/>
+      <c r="BF65" s="12" t="n"/>
+      <c r="BG65" s="12" t="n"/>
+      <c r="BH65" s="12" t="n"/>
+      <c r="BI65" s="8" t="n"/>
+      <c r="BJ65" s="12" t="n"/>
+      <c r="BK65" s="12" t="n"/>
+      <c r="BL65" s="12" t="n"/>
+      <c r="BM65" s="12" t="n"/>
+      <c r="BN65" s="7" t="n"/>
+      <c r="BR65" s="4" t="n"/>
+      <c r="BS65" s="6" t="n"/>
+      <c r="BT65" s="8" t="n"/>
+      <c r="BU65" s="11" t="inlineStr"/>
+      <c r="BV65" s="6" t="n"/>
+      <c r="BW65" s="8" t="n"/>
+      <c r="BX65" s="12" t="n"/>
+      <c r="BY65" s="12" t="n"/>
+      <c r="BZ65" s="12" t="n"/>
+      <c r="CA65" s="12" t="n"/>
+      <c r="CB65" s="8" t="n"/>
+      <c r="CC65" s="12" t="n"/>
+      <c r="CD65" s="12" t="n"/>
+      <c r="CE65" s="12" t="n"/>
+      <c r="CF65" s="12" t="n"/>
+      <c r="CG65" s="8" t="n"/>
+      <c r="CH65" s="12" t="n"/>
+      <c r="CI65" s="12" t="n"/>
+      <c r="CJ65" s="12" t="n"/>
+      <c r="CK65" s="12" t="n"/>
+      <c r="CL65" s="8" t="n"/>
+      <c r="CM65" s="12" t="n"/>
+      <c r="CN65" s="12" t="n"/>
+      <c r="CO65" s="12" t="n"/>
+      <c r="CP65" s="12" t="n"/>
+      <c r="CQ65" s="8" t="n"/>
+      <c r="CR65" s="12" t="n"/>
+      <c r="CS65" s="12" t="n"/>
+      <c r="CT65" s="12" t="n"/>
+      <c r="CU65" s="12" t="n"/>
+      <c r="CV65" s="7" t="n"/>
     </row>
     <row r="66">
       <c r="B66" s="4" t="n"/>
@@ -3730,6 +8886,68 @@
       <c r="AD66" s="12" t="n"/>
       <c r="AE66" s="12" t="n"/>
       <c r="AF66" s="7" t="n"/>
+      <c r="AJ66" s="4" t="n"/>
+      <c r="AK66" s="6" t="n"/>
+      <c r="AL66" s="8" t="n"/>
+      <c r="AM66" s="11" t="inlineStr"/>
+      <c r="AN66" s="6" t="n"/>
+      <c r="AO66" s="8" t="n"/>
+      <c r="AP66" s="12" t="n"/>
+      <c r="AQ66" s="12" t="n"/>
+      <c r="AR66" s="12" t="n"/>
+      <c r="AS66" s="12" t="n"/>
+      <c r="AT66" s="8" t="n"/>
+      <c r="AU66" s="12" t="n"/>
+      <c r="AV66" s="12" t="n"/>
+      <c r="AW66" s="12" t="n"/>
+      <c r="AX66" s="12" t="n"/>
+      <c r="AY66" s="8" t="n"/>
+      <c r="AZ66" s="12" t="n"/>
+      <c r="BA66" s="12" t="n"/>
+      <c r="BB66" s="12" t="n"/>
+      <c r="BC66" s="12" t="n"/>
+      <c r="BD66" s="8" t="n"/>
+      <c r="BE66" s="12" t="n"/>
+      <c r="BF66" s="12" t="n"/>
+      <c r="BG66" s="12" t="n"/>
+      <c r="BH66" s="12" t="n"/>
+      <c r="BI66" s="8" t="n"/>
+      <c r="BJ66" s="12" t="n"/>
+      <c r="BK66" s="12" t="n"/>
+      <c r="BL66" s="12" t="n"/>
+      <c r="BM66" s="12" t="n"/>
+      <c r="BN66" s="7" t="n"/>
+      <c r="BR66" s="4" t="n"/>
+      <c r="BS66" s="6" t="n"/>
+      <c r="BT66" s="8" t="n"/>
+      <c r="BU66" s="11" t="inlineStr"/>
+      <c r="BV66" s="6" t="n"/>
+      <c r="BW66" s="8" t="n"/>
+      <c r="BX66" s="12" t="n"/>
+      <c r="BY66" s="12" t="n"/>
+      <c r="BZ66" s="12" t="n"/>
+      <c r="CA66" s="12" t="n"/>
+      <c r="CB66" s="8" t="n"/>
+      <c r="CC66" s="12" t="n"/>
+      <c r="CD66" s="12" t="n"/>
+      <c r="CE66" s="12" t="n"/>
+      <c r="CF66" s="12" t="n"/>
+      <c r="CG66" s="8" t="n"/>
+      <c r="CH66" s="12" t="n"/>
+      <c r="CI66" s="12" t="n"/>
+      <c r="CJ66" s="12" t="n"/>
+      <c r="CK66" s="12" t="n"/>
+      <c r="CL66" s="8" t="n"/>
+      <c r="CM66" s="12" t="n"/>
+      <c r="CN66" s="12" t="n"/>
+      <c r="CO66" s="12" t="n"/>
+      <c r="CP66" s="12" t="n"/>
+      <c r="CQ66" s="8" t="n"/>
+      <c r="CR66" s="12" t="n"/>
+      <c r="CS66" s="12" t="n"/>
+      <c r="CT66" s="12" t="n"/>
+      <c r="CU66" s="12" t="n"/>
+      <c r="CV66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="B67" s="4" t="n"/>
@@ -3763,6 +8981,68 @@
       <c r="AD67" s="12" t="n"/>
       <c r="AE67" s="12" t="n"/>
       <c r="AF67" s="7" t="n"/>
+      <c r="AJ67" s="4" t="n"/>
+      <c r="AK67" s="6" t="n"/>
+      <c r="AL67" s="8" t="n"/>
+      <c r="AM67" s="11" t="inlineStr"/>
+      <c r="AN67" s="6" t="n"/>
+      <c r="AO67" s="8" t="n"/>
+      <c r="AP67" s="12" t="n"/>
+      <c r="AQ67" s="12" t="n"/>
+      <c r="AR67" s="12" t="n"/>
+      <c r="AS67" s="12" t="n"/>
+      <c r="AT67" s="8" t="n"/>
+      <c r="AU67" s="12" t="n"/>
+      <c r="AV67" s="12" t="n"/>
+      <c r="AW67" s="12" t="n"/>
+      <c r="AX67" s="12" t="n"/>
+      <c r="AY67" s="8" t="n"/>
+      <c r="AZ67" s="12" t="n"/>
+      <c r="BA67" s="12" t="n"/>
+      <c r="BB67" s="12" t="n"/>
+      <c r="BC67" s="12" t="n"/>
+      <c r="BD67" s="8" t="n"/>
+      <c r="BE67" s="12" t="n"/>
+      <c r="BF67" s="12" t="n"/>
+      <c r="BG67" s="12" t="n"/>
+      <c r="BH67" s="12" t="n"/>
+      <c r="BI67" s="8" t="n"/>
+      <c r="BJ67" s="12" t="n"/>
+      <c r="BK67" s="12" t="n"/>
+      <c r="BL67" s="12" t="n"/>
+      <c r="BM67" s="12" t="n"/>
+      <c r="BN67" s="7" t="n"/>
+      <c r="BR67" s="4" t="n"/>
+      <c r="BS67" s="6" t="n"/>
+      <c r="BT67" s="8" t="n"/>
+      <c r="BU67" s="11" t="inlineStr"/>
+      <c r="BV67" s="6" t="n"/>
+      <c r="BW67" s="8" t="n"/>
+      <c r="BX67" s="12" t="n"/>
+      <c r="BY67" s="12" t="n"/>
+      <c r="BZ67" s="12" t="n"/>
+      <c r="CA67" s="12" t="n"/>
+      <c r="CB67" s="8" t="n"/>
+      <c r="CC67" s="12" t="n"/>
+      <c r="CD67" s="12" t="n"/>
+      <c r="CE67" s="12" t="n"/>
+      <c r="CF67" s="12" t="n"/>
+      <c r="CG67" s="8" t="n"/>
+      <c r="CH67" s="12" t="n"/>
+      <c r="CI67" s="12" t="n"/>
+      <c r="CJ67" s="12" t="n"/>
+      <c r="CK67" s="12" t="n"/>
+      <c r="CL67" s="8" t="n"/>
+      <c r="CM67" s="12" t="n"/>
+      <c r="CN67" s="12" t="n"/>
+      <c r="CO67" s="12" t="n"/>
+      <c r="CP67" s="12" t="n"/>
+      <c r="CQ67" s="8" t="n"/>
+      <c r="CR67" s="12" t="n"/>
+      <c r="CS67" s="12" t="n"/>
+      <c r="CT67" s="12" t="n"/>
+      <c r="CU67" s="12" t="n"/>
+      <c r="CV67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="B68" s="4" t="n"/>
@@ -3796,6 +9076,68 @@
       <c r="AD68" s="12" t="n"/>
       <c r="AE68" s="12" t="n"/>
       <c r="AF68" s="7" t="n"/>
+      <c r="AJ68" s="4" t="n"/>
+      <c r="AK68" s="6" t="n"/>
+      <c r="AL68" s="8" t="n"/>
+      <c r="AM68" s="11" t="inlineStr"/>
+      <c r="AN68" s="6" t="n"/>
+      <c r="AO68" s="8" t="n"/>
+      <c r="AP68" s="12" t="n"/>
+      <c r="AQ68" s="12" t="n"/>
+      <c r="AR68" s="12" t="n"/>
+      <c r="AS68" s="12" t="n"/>
+      <c r="AT68" s="8" t="n"/>
+      <c r="AU68" s="12" t="n"/>
+      <c r="AV68" s="12" t="n"/>
+      <c r="AW68" s="12" t="n"/>
+      <c r="AX68" s="12" t="n"/>
+      <c r="AY68" s="8" t="n"/>
+      <c r="AZ68" s="12" t="n"/>
+      <c r="BA68" s="12" t="n"/>
+      <c r="BB68" s="12" t="n"/>
+      <c r="BC68" s="12" t="n"/>
+      <c r="BD68" s="8" t="n"/>
+      <c r="BE68" s="12" t="n"/>
+      <c r="BF68" s="12" t="n"/>
+      <c r="BG68" s="12" t="n"/>
+      <c r="BH68" s="12" t="n"/>
+      <c r="BI68" s="8" t="n"/>
+      <c r="BJ68" s="12" t="n"/>
+      <c r="BK68" s="12" t="n"/>
+      <c r="BL68" s="12" t="n"/>
+      <c r="BM68" s="12" t="n"/>
+      <c r="BN68" s="7" t="n"/>
+      <c r="BR68" s="4" t="n"/>
+      <c r="BS68" s="6" t="n"/>
+      <c r="BT68" s="8" t="n"/>
+      <c r="BU68" s="11" t="inlineStr"/>
+      <c r="BV68" s="6" t="n"/>
+      <c r="BW68" s="8" t="n"/>
+      <c r="BX68" s="12" t="n"/>
+      <c r="BY68" s="12" t="n"/>
+      <c r="BZ68" s="12" t="n"/>
+      <c r="CA68" s="12" t="n"/>
+      <c r="CB68" s="8" t="n"/>
+      <c r="CC68" s="12" t="n"/>
+      <c r="CD68" s="12" t="n"/>
+      <c r="CE68" s="12" t="n"/>
+      <c r="CF68" s="12" t="n"/>
+      <c r="CG68" s="8" t="n"/>
+      <c r="CH68" s="12" t="n"/>
+      <c r="CI68" s="12" t="n"/>
+      <c r="CJ68" s="12" t="n"/>
+      <c r="CK68" s="12" t="n"/>
+      <c r="CL68" s="8" t="n"/>
+      <c r="CM68" s="12" t="n"/>
+      <c r="CN68" s="12" t="n"/>
+      <c r="CO68" s="12" t="n"/>
+      <c r="CP68" s="12" t="n"/>
+      <c r="CQ68" s="8" t="n"/>
+      <c r="CR68" s="12" t="n"/>
+      <c r="CS68" s="12" t="n"/>
+      <c r="CT68" s="12" t="n"/>
+      <c r="CU68" s="12" t="n"/>
+      <c r="CV68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="B69" s="4" t="n"/>
@@ -3829,6 +9171,68 @@
       <c r="AD69" s="12" t="n"/>
       <c r="AE69" s="12" t="n"/>
       <c r="AF69" s="7" t="n"/>
+      <c r="AJ69" s="4" t="n"/>
+      <c r="AK69" s="6" t="n"/>
+      <c r="AL69" s="8" t="n"/>
+      <c r="AM69" s="11" t="inlineStr"/>
+      <c r="AN69" s="6" t="n"/>
+      <c r="AO69" s="8" t="n"/>
+      <c r="AP69" s="12" t="n"/>
+      <c r="AQ69" s="12" t="n"/>
+      <c r="AR69" s="12" t="n"/>
+      <c r="AS69" s="12" t="n"/>
+      <c r="AT69" s="8" t="n"/>
+      <c r="AU69" s="12" t="n"/>
+      <c r="AV69" s="12" t="n"/>
+      <c r="AW69" s="12" t="n"/>
+      <c r="AX69" s="12" t="n"/>
+      <c r="AY69" s="8" t="n"/>
+      <c r="AZ69" s="12" t="n"/>
+      <c r="BA69" s="12" t="n"/>
+      <c r="BB69" s="12" t="n"/>
+      <c r="BC69" s="12" t="n"/>
+      <c r="BD69" s="8" t="n"/>
+      <c r="BE69" s="12" t="n"/>
+      <c r="BF69" s="12" t="n"/>
+      <c r="BG69" s="12" t="n"/>
+      <c r="BH69" s="12" t="n"/>
+      <c r="BI69" s="8" t="n"/>
+      <c r="BJ69" s="12" t="n"/>
+      <c r="BK69" s="12" t="n"/>
+      <c r="BL69" s="12" t="n"/>
+      <c r="BM69" s="12" t="n"/>
+      <c r="BN69" s="7" t="n"/>
+      <c r="BR69" s="4" t="n"/>
+      <c r="BS69" s="6" t="n"/>
+      <c r="BT69" s="8" t="n"/>
+      <c r="BU69" s="11" t="inlineStr"/>
+      <c r="BV69" s="6" t="n"/>
+      <c r="BW69" s="8" t="n"/>
+      <c r="BX69" s="12" t="n"/>
+      <c r="BY69" s="12" t="n"/>
+      <c r="BZ69" s="12" t="n"/>
+      <c r="CA69" s="12" t="n"/>
+      <c r="CB69" s="8" t="n"/>
+      <c r="CC69" s="12" t="n"/>
+      <c r="CD69" s="12" t="n"/>
+      <c r="CE69" s="12" t="n"/>
+      <c r="CF69" s="12" t="n"/>
+      <c r="CG69" s="8" t="n"/>
+      <c r="CH69" s="12" t="n"/>
+      <c r="CI69" s="12" t="n"/>
+      <c r="CJ69" s="12" t="n"/>
+      <c r="CK69" s="12" t="n"/>
+      <c r="CL69" s="8" t="n"/>
+      <c r="CM69" s="12" t="n"/>
+      <c r="CN69" s="12" t="n"/>
+      <c r="CO69" s="12" t="n"/>
+      <c r="CP69" s="12" t="n"/>
+      <c r="CQ69" s="8" t="n"/>
+      <c r="CR69" s="12" t="n"/>
+      <c r="CS69" s="12" t="n"/>
+      <c r="CT69" s="12" t="n"/>
+      <c r="CU69" s="12" t="n"/>
+      <c r="CV69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="B70" s="4" t="n"/>
@@ -3862,6 +9266,68 @@
       <c r="AD70" s="12" t="n"/>
       <c r="AE70" s="12" t="n"/>
       <c r="AF70" s="7" t="n"/>
+      <c r="AJ70" s="4" t="n"/>
+      <c r="AK70" s="6" t="n"/>
+      <c r="AL70" s="8" t="n"/>
+      <c r="AM70" s="11" t="inlineStr"/>
+      <c r="AN70" s="6" t="n"/>
+      <c r="AO70" s="8" t="n"/>
+      <c r="AP70" s="12" t="n"/>
+      <c r="AQ70" s="12" t="n"/>
+      <c r="AR70" s="12" t="n"/>
+      <c r="AS70" s="12" t="n"/>
+      <c r="AT70" s="8" t="n"/>
+      <c r="AU70" s="12" t="n"/>
+      <c r="AV70" s="12" t="n"/>
+      <c r="AW70" s="12" t="n"/>
+      <c r="AX70" s="12" t="n"/>
+      <c r="AY70" s="8" t="n"/>
+      <c r="AZ70" s="12" t="n"/>
+      <c r="BA70" s="12" t="n"/>
+      <c r="BB70" s="12" t="n"/>
+      <c r="BC70" s="12" t="n"/>
+      <c r="BD70" s="8" t="n"/>
+      <c r="BE70" s="12" t="n"/>
+      <c r="BF70" s="12" t="n"/>
+      <c r="BG70" s="12" t="n"/>
+      <c r="BH70" s="12" t="n"/>
+      <c r="BI70" s="8" t="n"/>
+      <c r="BJ70" s="12" t="n"/>
+      <c r="BK70" s="12" t="n"/>
+      <c r="BL70" s="12" t="n"/>
+      <c r="BM70" s="12" t="n"/>
+      <c r="BN70" s="7" t="n"/>
+      <c r="BR70" s="4" t="n"/>
+      <c r="BS70" s="6" t="n"/>
+      <c r="BT70" s="8" t="n"/>
+      <c r="BU70" s="11" t="inlineStr"/>
+      <c r="BV70" s="6" t="n"/>
+      <c r="BW70" s="8" t="n"/>
+      <c r="BX70" s="12" t="n"/>
+      <c r="BY70" s="12" t="n"/>
+      <c r="BZ70" s="12" t="n"/>
+      <c r="CA70" s="12" t="n"/>
+      <c r="CB70" s="8" t="n"/>
+      <c r="CC70" s="12" t="n"/>
+      <c r="CD70" s="12" t="n"/>
+      <c r="CE70" s="12" t="n"/>
+      <c r="CF70" s="12" t="n"/>
+      <c r="CG70" s="8" t="n"/>
+      <c r="CH70" s="12" t="n"/>
+      <c r="CI70" s="12" t="n"/>
+      <c r="CJ70" s="12" t="n"/>
+      <c r="CK70" s="12" t="n"/>
+      <c r="CL70" s="8" t="n"/>
+      <c r="CM70" s="12" t="n"/>
+      <c r="CN70" s="12" t="n"/>
+      <c r="CO70" s="12" t="n"/>
+      <c r="CP70" s="12" t="n"/>
+      <c r="CQ70" s="8" t="n"/>
+      <c r="CR70" s="12" t="n"/>
+      <c r="CS70" s="12" t="n"/>
+      <c r="CT70" s="12" t="n"/>
+      <c r="CU70" s="12" t="n"/>
+      <c r="CV70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="B71" s="17" t="n"/>
@@ -3895,76 +9361,276 @@
       <c r="AD71" s="18" t="n"/>
       <c r="AE71" s="18" t="n"/>
       <c r="AF71" s="19" t="n"/>
+      <c r="AJ71" s="17" t="n"/>
+      <c r="AK71" s="18" t="n"/>
+      <c r="AL71" s="18" t="n"/>
+      <c r="AM71" s="18" t="n"/>
+      <c r="AN71" s="18" t="n"/>
+      <c r="AO71" s="18" t="n"/>
+      <c r="AP71" s="18" t="n"/>
+      <c r="AQ71" s="18" t="n"/>
+      <c r="AR71" s="18" t="n"/>
+      <c r="AS71" s="18" t="n"/>
+      <c r="AT71" s="18" t="n"/>
+      <c r="AU71" s="18" t="n"/>
+      <c r="AV71" s="18" t="n"/>
+      <c r="AW71" s="18" t="n"/>
+      <c r="AX71" s="18" t="n"/>
+      <c r="AY71" s="18" t="n"/>
+      <c r="AZ71" s="18" t="n"/>
+      <c r="BA71" s="18" t="n"/>
+      <c r="BB71" s="18" t="n"/>
+      <c r="BC71" s="18" t="n"/>
+      <c r="BD71" s="18" t="n"/>
+      <c r="BE71" s="18" t="n"/>
+      <c r="BF71" s="18" t="n"/>
+      <c r="BG71" s="18" t="n"/>
+      <c r="BH71" s="18" t="n"/>
+      <c r="BI71" s="18" t="n"/>
+      <c r="BJ71" s="18" t="n"/>
+      <c r="BK71" s="18" t="n"/>
+      <c r="BL71" s="18" t="n"/>
+      <c r="BM71" s="18" t="n"/>
+      <c r="BN71" s="19" t="n"/>
+      <c r="BR71" s="17" t="n"/>
+      <c r="BS71" s="18" t="n"/>
+      <c r="BT71" s="18" t="n"/>
+      <c r="BU71" s="18" t="n"/>
+      <c r="BV71" s="18" t="n"/>
+      <c r="BW71" s="18" t="n"/>
+      <c r="BX71" s="18" t="n"/>
+      <c r="BY71" s="18" t="n"/>
+      <c r="BZ71" s="18" t="n"/>
+      <c r="CA71" s="18" t="n"/>
+      <c r="CB71" s="18" t="n"/>
+      <c r="CC71" s="18" t="n"/>
+      <c r="CD71" s="18" t="n"/>
+      <c r="CE71" s="18" t="n"/>
+      <c r="CF71" s="18" t="n"/>
+      <c r="CG71" s="18" t="n"/>
+      <c r="CH71" s="18" t="n"/>
+      <c r="CI71" s="18" t="n"/>
+      <c r="CJ71" s="18" t="n"/>
+      <c r="CK71" s="18" t="n"/>
+      <c r="CL71" s="18" t="n"/>
+      <c r="CM71" s="18" t="n"/>
+      <c r="CN71" s="18" t="n"/>
+      <c r="CO71" s="18" t="n"/>
+      <c r="CP71" s="18" t="n"/>
+      <c r="CQ71" s="18" t="n"/>
+      <c r="CR71" s="18" t="n"/>
+      <c r="CS71" s="18" t="n"/>
+      <c r="CT71" s="18" t="n"/>
+      <c r="CU71" s="18" t="n"/>
+      <c r="CV71" s="19" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="69">
-    <mergeCell ref="E43:F43"/>
+  <mergeCells count="207">
+    <mergeCell ref="AK36:AK43"/>
+    <mergeCell ref="BU31:BV31"/>
+    <mergeCell ref="AM42:AN42"/>
+    <mergeCell ref="AM29:AN29"/>
+    <mergeCell ref="BU21:BV21"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="AM23:AN23"/>
+    <mergeCell ref="AM38:AN38"/>
+    <mergeCell ref="AM13:AN13"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="AM56:AN56"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="C45:C52"/>
+    <mergeCell ref="AM43:AN43"/>
+    <mergeCell ref="AM58:AN58"/>
+    <mergeCell ref="AM40:AN40"/>
+    <mergeCell ref="BU23:BV23"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="AM24:AN24"/>
+    <mergeCell ref="BE6:BH6"/>
+    <mergeCell ref="AM60:AN60"/>
+    <mergeCell ref="BU48:BV48"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="AM57:AN57"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="AM70:AN70"/>
+    <mergeCell ref="BU57:BV57"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="AM63:AN63"/>
+    <mergeCell ref="BU34:BV34"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="R6:U6"/>
+    <mergeCell ref="BU49:BV49"/>
+    <mergeCell ref="AK63:AK70"/>
+    <mergeCell ref="AM25:AN25"/>
+    <mergeCell ref="BU36:BV36"/>
+    <mergeCell ref="BU20:BV20"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="AM33:AN33"/>
+    <mergeCell ref="BU66:BV66"/>
     <mergeCell ref="E12:F12"/>
+    <mergeCell ref="AK27:AK34"/>
+    <mergeCell ref="BU22:BV22"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="BU59:BV59"/>
+    <mergeCell ref="BU12:BV12"/>
+    <mergeCell ref="AM19:AN19"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="AM14:AN14"/>
+    <mergeCell ref="AM46:AN46"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="AM28:AN28"/>
+    <mergeCell ref="BU46:BV46"/>
+    <mergeCell ref="BU61:BV61"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="BU39:BV39"/>
+    <mergeCell ref="BU14:BV14"/>
+    <mergeCell ref="BU70:BV70"/>
+    <mergeCell ref="AM48:AN48"/>
+    <mergeCell ref="AM59:AN59"/>
+    <mergeCell ref="BU29:BV29"/>
+    <mergeCell ref="BU38:BV38"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="W6:Z6"/>
+    <mergeCell ref="BU13:BV13"/>
+    <mergeCell ref="C9:C16"/>
+    <mergeCell ref="AK9:AK16"/>
+    <mergeCell ref="AK45:AK52"/>
+    <mergeCell ref="BU40:BV40"/>
+    <mergeCell ref="AK54:AK61"/>
+    <mergeCell ref="AM30:AN30"/>
+    <mergeCell ref="AM45:AN45"/>
+    <mergeCell ref="BU37:BV37"/>
+    <mergeCell ref="BU15:BV15"/>
+    <mergeCell ref="AM10:AN10"/>
+    <mergeCell ref="AM54:AN54"/>
+    <mergeCell ref="BU24:BV24"/>
+    <mergeCell ref="AU6:AX6"/>
+    <mergeCell ref="CC6:CF6"/>
+    <mergeCell ref="BU33:BV33"/>
+    <mergeCell ref="AM65:AN65"/>
+    <mergeCell ref="BU65:BV65"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="AM16:AN16"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="BU63:BV63"/>
+    <mergeCell ref="AM36:AN36"/>
+    <mergeCell ref="BU16:BV16"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="AP6:AS6"/>
+    <mergeCell ref="AM18:AN18"/>
+    <mergeCell ref="BU25:BV25"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="AM51:AN51"/>
+    <mergeCell ref="CR6:CU6"/>
+    <mergeCell ref="BS45:BS52"/>
+    <mergeCell ref="BU51:BV51"/>
     <mergeCell ref="E68:F68"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="E67:F67"/>
     <mergeCell ref="C3:AE3"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="AM47:AN47"/>
+    <mergeCell ref="BU50:BV50"/>
     <mergeCell ref="E52:F52"/>
-    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="AM22:AN22"/>
     <mergeCell ref="C18:C25"/>
     <mergeCell ref="E39:F39"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="BU11:BV11"/>
+    <mergeCell ref="BU42:BV42"/>
+    <mergeCell ref="BS3:CU3"/>
     <mergeCell ref="E20:F20"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="C45:C52"/>
+    <mergeCell ref="AM34:AN34"/>
     <mergeCell ref="E29:F29"/>
+    <mergeCell ref="BU52:BV52"/>
+    <mergeCell ref="AK18:AK25"/>
+    <mergeCell ref="BS18:BS25"/>
+    <mergeCell ref="BU67:BV67"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="C63:C70"/>
+    <mergeCell ref="AM49:AN49"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="BU28:BV28"/>
+    <mergeCell ref="AZ6:BC6"/>
+    <mergeCell ref="CH6:CK6"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="BS54:BS61"/>
+    <mergeCell ref="AM20:AN20"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="AM64:AN64"/>
+    <mergeCell ref="BS63:BS70"/>
+    <mergeCell ref="BU69:BV69"/>
+    <mergeCell ref="BU30:BV30"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="C36:C43"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="BS9:BS16"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="AM12:AN12"/>
+    <mergeCell ref="BS27:BS34"/>
+    <mergeCell ref="BU55:BV55"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="AM21:AN21"/>
+    <mergeCell ref="BS36:BS43"/>
+    <mergeCell ref="BU64:BV64"/>
+    <mergeCell ref="BU45:BV45"/>
+    <mergeCell ref="BU54:BV54"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="AM27:AN27"/>
+    <mergeCell ref="AM32:AN32"/>
+    <mergeCell ref="BU32:BV32"/>
+    <mergeCell ref="AM41:AN41"/>
+    <mergeCell ref="BU41:BV41"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="CM6:CP6"/>
+    <mergeCell ref="BU47:BV47"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="BU56:BV56"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="BU43:BV43"/>
+    <mergeCell ref="AM66:AN66"/>
+    <mergeCell ref="BU18:BV18"/>
+    <mergeCell ref="BU27:BV27"/>
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="E19:F19"/>
-    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="AM68:AN68"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="AB6:AE6"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="C63:C70"/>
-    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="AK3:BM3"/>
+    <mergeCell ref="BU58:BV58"/>
     <mergeCell ref="E60:F60"/>
-    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="C54:C61"/>
     <mergeCell ref="E9:F9"/>
-    <mergeCell ref="C54:C61"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="W6:Z6"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="C9:C16"/>
-    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="AM9:AN9"/>
+    <mergeCell ref="AM52:AN52"/>
+    <mergeCell ref="AM61:AN61"/>
+    <mergeCell ref="AM67:AN67"/>
+    <mergeCell ref="AM39:AN39"/>
+    <mergeCell ref="BU10:BV10"/>
+    <mergeCell ref="BU19:BV19"/>
     <mergeCell ref="E30:F30"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="BU60:BV60"/>
+    <mergeCell ref="BU9:BV9"/>
     <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="AM11:AN11"/>
+    <mergeCell ref="AM69:AN69"/>
     <mergeCell ref="H6:K6"/>
     <mergeCell ref="E45:F45"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="R6:U6"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="C36:C43"/>
+    <mergeCell ref="BU68:BV68"/>
+    <mergeCell ref="BJ6:BM6"/>
     <mergeCell ref="C27:C34"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="AM31:AN31"/>
+    <mergeCell ref="BX6:CA6"/>
+    <mergeCell ref="AM50:AN50"/>
+    <mergeCell ref="AM15:AN15"/>
+    <mergeCell ref="AM55:AN55"/>
     <mergeCell ref="E37:F37"/>
     <mergeCell ref="M6:P6"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="AM37:AN37"/>
     <mergeCell ref="E47:F47"/>
     <mergeCell ref="E21:F21"/>
   </mergeCells>
@@ -3978,7 +9644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4015,6 +9681,34 @@
       </c>
       <c r="D2" t="n">
         <v>81.17647058823529</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>83.17647058823529</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>83.17647058823529</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>85.70588235294117</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>85.70588235294117</v>
       </c>
     </row>
   </sheetData>

--- a/workout_plan_new.xlsx
+++ b/workout_plan_new.xlsx
@@ -48,38 +48,38 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="005297C5"/>
-        <bgColor rgb="005297C5"/>
+        <fgColor rgb="005279C5"/>
+        <bgColor rgb="005279C5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0065A3CC"/>
-        <bgColor rgb="0065A3CC"/>
+        <fgColor rgb="006587CC"/>
+        <bgColor rgb="006587CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0079AED2"/>
-        <bgColor rgb="0079AED2"/>
+        <fgColor rgb="007996D2"/>
+        <bgColor rgb="007996D2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="008CBAD8"/>
-        <bgColor rgb="008CBAD8"/>
+        <fgColor rgb="008CA5D8"/>
+        <bgColor rgb="008CA5D8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="009FC5DF"/>
-        <bgColor rgb="009FC5DF"/>
+        <fgColor rgb="009FB4DF"/>
+        <bgColor rgb="009FB4DF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00B2D1E5"/>
-        <bgColor rgb="00B2D1E5"/>
+        <fgColor rgb="00B2C3E5"/>
+        <bgColor rgb="00B2C3E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -321,12 +321,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Charts'!$A$2:$A$8</f>
+              <f>'Charts'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Charts'!$B$2:$B$8</f>
+              <f>'Charts'!$B$2:$B$9</f>
             </numRef>
           </val>
         </ser>
@@ -439,12 +439,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Charts'!$A$2:$A$8</f>
+              <f>'Charts'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Charts'!$C$2:$C$8</f>
+              <f>'Charts'!$C$2:$C$9</f>
             </numRef>
           </val>
         </ser>
@@ -557,12 +557,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Charts'!$A$2:$A$8</f>
+              <f>'Charts'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Charts'!$D$2:$D$8</f>
+              <f>'Charts'!$D$2:$D$9</f>
             </numRef>
           </val>
         </ser>
@@ -991,7 +991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:KT71"/>
+  <dimension ref="B1:ML71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="9" max="9"/>
@@ -1061,14 +1061,23 @@
     <col width="24.5" customWidth="1" min="241" max="241"/>
     <col width="13" customWidth="1" min="244" max="244"/>
     <col width="24.5" customWidth="1" min="246" max="246"/>
+    <col width="13" customWidth="1" min="272" max="272"/>
     <col width="13" customWidth="1" min="273" max="273"/>
-    <col width="48.3" customWidth="1" min="275" max="275"/>
+    <col width="63.7" customWidth="1" min="275" max="275"/>
     <col width="13" customWidth="1" min="278" max="278"/>
     <col width="16.1" customWidth="1" min="280" max="280"/>
     <col width="13" customWidth="1" min="283" max="283"/>
     <col width="16.1" customWidth="1" min="285" max="285"/>
     <col width="13" customWidth="1" min="288" max="288"/>
     <col width="16.1" customWidth="1" min="290" max="290"/>
+    <col width="13" customWidth="1" min="317" max="317"/>
+    <col width="27.3" customWidth="1" min="319" max="319"/>
+    <col width="13" customWidth="1" min="322" max="322"/>
+    <col width="13" customWidth="1" min="324" max="324"/>
+    <col width="13" customWidth="1" min="327" max="327"/>
+    <col width="11.9" customWidth="1" min="329" max="329"/>
+    <col width="13" customWidth="1" min="332" max="332"/>
+    <col width="54.59999999999999" customWidth="1" min="334" max="334"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -1360,12 +1369,53 @@
       <c r="KR2" s="2" t="n"/>
       <c r="KS2" s="2" t="n"/>
       <c r="KT2" s="3" t="n"/>
+      <c r="KX2" s="1" t="n"/>
+      <c r="KY2" s="2" t="n"/>
+      <c r="KZ2" s="2" t="n"/>
+      <c r="LA2" s="2" t="n"/>
+      <c r="LB2" s="2" t="n"/>
+      <c r="LC2" s="2" t="n"/>
+      <c r="LD2" s="2" t="n"/>
+      <c r="LE2" s="2" t="n"/>
+      <c r="LF2" s="2" t="n"/>
+      <c r="LG2" s="2" t="n"/>
+      <c r="LH2" s="2" t="n"/>
+      <c r="LI2" s="2" t="n"/>
+      <c r="LJ2" s="2" t="n"/>
+      <c r="LK2" s="2" t="n"/>
+      <c r="LL2" s="2" t="n"/>
+      <c r="LM2" s="2" t="n"/>
+      <c r="LN2" s="2" t="n"/>
+      <c r="LO2" s="2" t="n"/>
+      <c r="LP2" s="2" t="n"/>
+      <c r="LQ2" s="2" t="n"/>
+      <c r="LR2" s="2" t="n"/>
+      <c r="LS2" s="2" t="n"/>
+      <c r="LT2" s="2" t="n"/>
+      <c r="LU2" s="2" t="n"/>
+      <c r="LV2" s="2" t="n"/>
+      <c r="LW2" s="2" t="n"/>
+      <c r="LX2" s="2" t="n"/>
+      <c r="LY2" s="2" t="n"/>
+      <c r="LZ2" s="2" t="n"/>
+      <c r="MA2" s="2" t="n"/>
+      <c r="MB2" s="2" t="n"/>
+      <c r="MC2" s="2" t="n"/>
+      <c r="MD2" s="2" t="n"/>
+      <c r="ME2" s="2" t="n"/>
+      <c r="MF2" s="2" t="n"/>
+      <c r="MG2" s="2" t="n"/>
+      <c r="MH2" s="2" t="n"/>
+      <c r="MI2" s="2" t="n"/>
+      <c r="MJ2" s="2" t="n"/>
+      <c r="MK2" s="2" t="n"/>
+      <c r="ML2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="B3" s="4" t="n"/>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Week 1 - Week Commencing 28-07-2025</t>
+          <t>Week 1 - Week Commencing 01-09-2025</t>
         </is>
       </c>
       <c r="D3" s="6" t="n"/>
@@ -1410,7 +1460,7 @@
       <c r="AT3" s="4" t="n"/>
       <c r="AU3" s="5" t="inlineStr">
         <is>
-          <t>Week 2 - Week Commencing 04-08-2025</t>
+          <t>Week 2 - Week Commencing 08-09-2025</t>
         </is>
       </c>
       <c r="AV3" s="6" t="n"/>
@@ -1455,7 +1505,7 @@
       <c r="CL3" s="4" t="n"/>
       <c r="CM3" s="5" t="inlineStr">
         <is>
-          <t>Week 3 - Week Commencing 11-08-2025</t>
+          <t>Week 3 - Week Commencing 15-09-2025</t>
         </is>
       </c>
       <c r="CN3" s="6" t="n"/>
@@ -1500,7 +1550,7 @@
       <c r="ED3" s="4" t="n"/>
       <c r="EE3" s="5" t="inlineStr">
         <is>
-          <t>Week 4 - Week Commencing 18-08-2025</t>
+          <t>Week 4 - Week Commencing 22-09-2025</t>
         </is>
       </c>
       <c r="EF3" s="6" t="n"/>
@@ -1545,7 +1595,7 @@
       <c r="FV3" s="4" t="n"/>
       <c r="FW3" s="5" t="inlineStr">
         <is>
-          <t>Week 5 - Week Commencing 25-08-2025</t>
+          <t>Week 5 - Week Commencing 29-09-2025</t>
         </is>
       </c>
       <c r="FX3" s="6" t="n"/>
@@ -1590,7 +1640,7 @@
       <c r="HN3" s="4" t="n"/>
       <c r="HO3" s="5" t="inlineStr">
         <is>
-          <t>Week 6 - Week Commencing 01-09-2025</t>
+          <t>Week 6 - Week Commencing 06-10-2025</t>
         </is>
       </c>
       <c r="HP3" s="6" t="n"/>
@@ -1635,7 +1685,7 @@
       <c r="JF3" s="4" t="n"/>
       <c r="JG3" s="5" t="inlineStr">
         <is>
-          <t>Week 7 - Week Commencing 08-09-2025</t>
+          <t>Week 7 - Week Commencing 13-10-2025</t>
         </is>
       </c>
       <c r="JH3" s="6" t="n"/>
@@ -1677,6 +1727,51 @@
       <c r="KR3" s="6" t="n"/>
       <c r="KS3" s="6" t="n"/>
       <c r="KT3" s="7" t="n"/>
+      <c r="KX3" s="4" t="n"/>
+      <c r="KY3" s="5" t="inlineStr">
+        <is>
+          <t>Week 8 - Week Commencing 20-10-2025</t>
+        </is>
+      </c>
+      <c r="KZ3" s="6" t="n"/>
+      <c r="LA3" s="6" t="n"/>
+      <c r="LB3" s="6" t="n"/>
+      <c r="LC3" s="6" t="n"/>
+      <c r="LD3" s="6" t="n"/>
+      <c r="LE3" s="6" t="n"/>
+      <c r="LF3" s="6" t="n"/>
+      <c r="LG3" s="6" t="n"/>
+      <c r="LH3" s="6" t="n"/>
+      <c r="LI3" s="6" t="n"/>
+      <c r="LJ3" s="6" t="n"/>
+      <c r="LK3" s="6" t="n"/>
+      <c r="LL3" s="6" t="n"/>
+      <c r="LM3" s="6" t="n"/>
+      <c r="LN3" s="6" t="n"/>
+      <c r="LO3" s="6" t="n"/>
+      <c r="LP3" s="6" t="n"/>
+      <c r="LQ3" s="6" t="n"/>
+      <c r="LR3" s="6" t="n"/>
+      <c r="LS3" s="6" t="n"/>
+      <c r="LT3" s="6" t="n"/>
+      <c r="LU3" s="6" t="n"/>
+      <c r="LV3" s="6" t="n"/>
+      <c r="LW3" s="6" t="n"/>
+      <c r="LX3" s="6" t="n"/>
+      <c r="LY3" s="6" t="n"/>
+      <c r="LZ3" s="6" t="n"/>
+      <c r="MA3" s="6" t="n"/>
+      <c r="MB3" s="6" t="n"/>
+      <c r="MC3" s="6" t="n"/>
+      <c r="MD3" s="6" t="n"/>
+      <c r="ME3" s="6" t="n"/>
+      <c r="MF3" s="6" t="n"/>
+      <c r="MG3" s="6" t="n"/>
+      <c r="MH3" s="6" t="n"/>
+      <c r="MI3" s="6" t="n"/>
+      <c r="MJ3" s="6" t="n"/>
+      <c r="MK3" s="6" t="n"/>
+      <c r="ML3" s="7" t="n"/>
     </row>
     <row r="4">
       <c r="B4" s="4" t="n"/>
@@ -1966,6 +2061,47 @@
       <c r="KR4" s="8" t="n"/>
       <c r="KS4" s="8" t="n"/>
       <c r="KT4" s="7" t="n"/>
+      <c r="KX4" s="4" t="n"/>
+      <c r="KY4" s="8" t="n"/>
+      <c r="KZ4" s="8" t="n"/>
+      <c r="LA4" s="8" t="n"/>
+      <c r="LB4" s="8" t="n"/>
+      <c r="LC4" s="8" t="n"/>
+      <c r="LD4" s="8" t="n"/>
+      <c r="LE4" s="8" t="n"/>
+      <c r="LF4" s="8" t="n"/>
+      <c r="LG4" s="8" t="n"/>
+      <c r="LH4" s="8" t="n"/>
+      <c r="LI4" s="8" t="n"/>
+      <c r="LJ4" s="8" t="n"/>
+      <c r="LK4" s="8" t="n"/>
+      <c r="LL4" s="8" t="n"/>
+      <c r="LM4" s="8" t="n"/>
+      <c r="LN4" s="8" t="n"/>
+      <c r="LO4" s="8" t="n"/>
+      <c r="LP4" s="8" t="n"/>
+      <c r="LQ4" s="8" t="n"/>
+      <c r="LR4" s="8" t="n"/>
+      <c r="LS4" s="8" t="n"/>
+      <c r="LT4" s="8" t="n"/>
+      <c r="LU4" s="8" t="n"/>
+      <c r="LV4" s="8" t="n"/>
+      <c r="LW4" s="8" t="n"/>
+      <c r="LX4" s="8" t="n"/>
+      <c r="LY4" s="8" t="n"/>
+      <c r="LZ4" s="8" t="n"/>
+      <c r="MA4" s="8" t="n"/>
+      <c r="MB4" s="8" t="n"/>
+      <c r="MC4" s="8" t="n"/>
+      <c r="MD4" s="8" t="n"/>
+      <c r="ME4" s="8" t="n"/>
+      <c r="MF4" s="8" t="n"/>
+      <c r="MG4" s="8" t="n"/>
+      <c r="MH4" s="8" t="n"/>
+      <c r="MI4" s="8" t="n"/>
+      <c r="MJ4" s="8" t="n"/>
+      <c r="MK4" s="8" t="n"/>
+      <c r="ML4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="B5" s="4" t="n"/>
@@ -2255,6 +2391,47 @@
       <c r="KR5" s="8" t="n"/>
       <c r="KS5" s="8" t="n"/>
       <c r="KT5" s="7" t="n"/>
+      <c r="KX5" s="4" t="n"/>
+      <c r="KY5" s="8" t="n"/>
+      <c r="KZ5" s="8" t="n"/>
+      <c r="LA5" s="8" t="n"/>
+      <c r="LB5" s="8" t="n"/>
+      <c r="LC5" s="8" t="n"/>
+      <c r="LD5" s="8" t="n"/>
+      <c r="LE5" s="8" t="n"/>
+      <c r="LF5" s="8" t="n"/>
+      <c r="LG5" s="8" t="n"/>
+      <c r="LH5" s="8" t="n"/>
+      <c r="LI5" s="8" t="n"/>
+      <c r="LJ5" s="8" t="n"/>
+      <c r="LK5" s="8" t="n"/>
+      <c r="LL5" s="8" t="n"/>
+      <c r="LM5" s="8" t="n"/>
+      <c r="LN5" s="8" t="n"/>
+      <c r="LO5" s="8" t="n"/>
+      <c r="LP5" s="8" t="n"/>
+      <c r="LQ5" s="8" t="n"/>
+      <c r="LR5" s="8" t="n"/>
+      <c r="LS5" s="8" t="n"/>
+      <c r="LT5" s="8" t="n"/>
+      <c r="LU5" s="8" t="n"/>
+      <c r="LV5" s="8" t="n"/>
+      <c r="LW5" s="8" t="n"/>
+      <c r="LX5" s="8" t="n"/>
+      <c r="LY5" s="8" t="n"/>
+      <c r="LZ5" s="8" t="n"/>
+      <c r="MA5" s="8" t="n"/>
+      <c r="MB5" s="8" t="n"/>
+      <c r="MC5" s="8" t="n"/>
+      <c r="MD5" s="8" t="n"/>
+      <c r="ME5" s="8" t="n"/>
+      <c r="MF5" s="8" t="n"/>
+      <c r="MG5" s="8" t="n"/>
+      <c r="MH5" s="8" t="n"/>
+      <c r="MI5" s="8" t="n"/>
+      <c r="MJ5" s="8" t="n"/>
+      <c r="MK5" s="8" t="n"/>
+      <c r="ML5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="4" t="n"/>
@@ -2740,6 +2917,75 @@
       <c r="KR6" s="6" t="n"/>
       <c r="KS6" s="6" t="n"/>
       <c r="KT6" s="7" t="n"/>
+      <c r="KX6" s="4" t="n"/>
+      <c r="KY6" s="8" t="n"/>
+      <c r="KZ6" s="8" t="n"/>
+      <c r="LA6" s="8" t="n"/>
+      <c r="LB6" s="8" t="n"/>
+      <c r="LC6" s="8" t="n"/>
+      <c r="LD6" s="9" t="inlineStr">
+        <is>
+          <t>Set 1</t>
+        </is>
+      </c>
+      <c r="LE6" s="6" t="n"/>
+      <c r="LF6" s="6" t="n"/>
+      <c r="LG6" s="6" t="n"/>
+      <c r="LH6" s="8" t="n"/>
+      <c r="LI6" s="9" t="inlineStr">
+        <is>
+          <t>Set 2</t>
+        </is>
+      </c>
+      <c r="LJ6" s="6" t="n"/>
+      <c r="LK6" s="6" t="n"/>
+      <c r="LL6" s="6" t="n"/>
+      <c r="LM6" s="8" t="n"/>
+      <c r="LN6" s="9" t="inlineStr">
+        <is>
+          <t>Set 3</t>
+        </is>
+      </c>
+      <c r="LO6" s="6" t="n"/>
+      <c r="LP6" s="6" t="n"/>
+      <c r="LQ6" s="6" t="n"/>
+      <c r="LR6" s="8" t="n"/>
+      <c r="LS6" s="9" t="inlineStr">
+        <is>
+          <t>Set 4</t>
+        </is>
+      </c>
+      <c r="LT6" s="6" t="n"/>
+      <c r="LU6" s="6" t="n"/>
+      <c r="LV6" s="6" t="n"/>
+      <c r="LW6" s="8" t="n"/>
+      <c r="LX6" s="9" t="inlineStr">
+        <is>
+          <t>Set 5</t>
+        </is>
+      </c>
+      <c r="LY6" s="6" t="n"/>
+      <c r="LZ6" s="6" t="n"/>
+      <c r="MA6" s="6" t="n"/>
+      <c r="MB6" s="8" t="n"/>
+      <c r="MC6" s="9" t="inlineStr">
+        <is>
+          <t>Set 6</t>
+        </is>
+      </c>
+      <c r="MD6" s="6" t="n"/>
+      <c r="ME6" s="6" t="n"/>
+      <c r="MF6" s="6" t="n"/>
+      <c r="MG6" s="8" t="n"/>
+      <c r="MH6" s="9" t="inlineStr">
+        <is>
+          <t>Set 7</t>
+        </is>
+      </c>
+      <c r="MI6" s="6" t="n"/>
+      <c r="MJ6" s="6" t="n"/>
+      <c r="MK6" s="6" t="n"/>
+      <c r="ML6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="4" t="n"/>
@@ -3813,6 +4059,159 @@
         </is>
       </c>
       <c r="KT7" s="7" t="n"/>
+      <c r="KX7" s="4" t="n"/>
+      <c r="KY7" s="8" t="n"/>
+      <c r="KZ7" s="8" t="n"/>
+      <c r="LA7" s="8" t="n"/>
+      <c r="LB7" s="8" t="n"/>
+      <c r="LC7" s="8" t="n"/>
+      <c r="LD7" s="9" t="inlineStr">
+        <is>
+          <t>Reps</t>
+        </is>
+      </c>
+      <c r="LE7" s="9" t="inlineStr">
+        <is>
+          <t>Weights</t>
+        </is>
+      </c>
+      <c r="LF7" s="9" t="inlineStr">
+        <is>
+          <t>%1RM</t>
+        </is>
+      </c>
+      <c r="LG7" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="LH7" s="8" t="n"/>
+      <c r="LI7" s="9" t="inlineStr">
+        <is>
+          <t>Reps</t>
+        </is>
+      </c>
+      <c r="LJ7" s="9" t="inlineStr">
+        <is>
+          <t>Weights</t>
+        </is>
+      </c>
+      <c r="LK7" s="9" t="inlineStr">
+        <is>
+          <t>%1RM</t>
+        </is>
+      </c>
+      <c r="LL7" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="LM7" s="8" t="n"/>
+      <c r="LN7" s="9" t="inlineStr">
+        <is>
+          <t>Reps</t>
+        </is>
+      </c>
+      <c r="LO7" s="9" t="inlineStr">
+        <is>
+          <t>Weights</t>
+        </is>
+      </c>
+      <c r="LP7" s="9" t="inlineStr">
+        <is>
+          <t>%1RM</t>
+        </is>
+      </c>
+      <c r="LQ7" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="LR7" s="8" t="n"/>
+      <c r="LS7" s="9" t="inlineStr">
+        <is>
+          <t>Reps</t>
+        </is>
+      </c>
+      <c r="LT7" s="9" t="inlineStr">
+        <is>
+          <t>Weights</t>
+        </is>
+      </c>
+      <c r="LU7" s="9" t="inlineStr">
+        <is>
+          <t>%1RM</t>
+        </is>
+      </c>
+      <c r="LV7" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="LW7" s="8" t="n"/>
+      <c r="LX7" s="9" t="inlineStr">
+        <is>
+          <t>Reps</t>
+        </is>
+      </c>
+      <c r="LY7" s="9" t="inlineStr">
+        <is>
+          <t>Weights</t>
+        </is>
+      </c>
+      <c r="LZ7" s="9" t="inlineStr">
+        <is>
+          <t>%1RM</t>
+        </is>
+      </c>
+      <c r="MA7" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="MB7" s="8" t="n"/>
+      <c r="MC7" s="9" t="inlineStr">
+        <is>
+          <t>Reps</t>
+        </is>
+      </c>
+      <c r="MD7" s="9" t="inlineStr">
+        <is>
+          <t>Weights</t>
+        </is>
+      </c>
+      <c r="ME7" s="9" t="inlineStr">
+        <is>
+          <t>%1RM</t>
+        </is>
+      </c>
+      <c r="MF7" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="MG7" s="8" t="n"/>
+      <c r="MH7" s="9" t="inlineStr">
+        <is>
+          <t>Reps</t>
+        </is>
+      </c>
+      <c r="MI7" s="9" t="inlineStr">
+        <is>
+          <t>Weights</t>
+        </is>
+      </c>
+      <c r="MJ7" s="9" t="inlineStr">
+        <is>
+          <t>%1RM</t>
+        </is>
+      </c>
+      <c r="MK7" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="ML7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="4" t="n"/>
@@ -4102,6 +4501,47 @@
       <c r="KR8" s="8" t="n"/>
       <c r="KS8" s="8" t="n"/>
       <c r="KT8" s="7" t="n"/>
+      <c r="KX8" s="4" t="n"/>
+      <c r="KY8" s="8" t="n"/>
+      <c r="KZ8" s="8" t="n"/>
+      <c r="LA8" s="8" t="n"/>
+      <c r="LB8" s="8" t="n"/>
+      <c r="LC8" s="8" t="n"/>
+      <c r="LD8" s="8" t="n"/>
+      <c r="LE8" s="8" t="n"/>
+      <c r="LF8" s="8" t="n"/>
+      <c r="LG8" s="8" t="n"/>
+      <c r="LH8" s="8" t="n"/>
+      <c r="LI8" s="8" t="n"/>
+      <c r="LJ8" s="8" t="n"/>
+      <c r="LK8" s="8" t="n"/>
+      <c r="LL8" s="8" t="n"/>
+      <c r="LM8" s="8" t="n"/>
+      <c r="LN8" s="8" t="n"/>
+      <c r="LO8" s="8" t="n"/>
+      <c r="LP8" s="8" t="n"/>
+      <c r="LQ8" s="8" t="n"/>
+      <c r="LR8" s="8" t="n"/>
+      <c r="LS8" s="8" t="n"/>
+      <c r="LT8" s="8" t="n"/>
+      <c r="LU8" s="8" t="n"/>
+      <c r="LV8" s="8" t="n"/>
+      <c r="LW8" s="8" t="n"/>
+      <c r="LX8" s="8" t="n"/>
+      <c r="LY8" s="8" t="n"/>
+      <c r="LZ8" s="8" t="n"/>
+      <c r="MA8" s="8" t="n"/>
+      <c r="MB8" s="8" t="n"/>
+      <c r="MC8" s="8" t="n"/>
+      <c r="MD8" s="8" t="n"/>
+      <c r="ME8" s="8" t="n"/>
+      <c r="MF8" s="8" t="n"/>
+      <c r="MG8" s="8" t="n"/>
+      <c r="MH8" s="8" t="n"/>
+      <c r="MI8" s="8" t="n"/>
+      <c r="MJ8" s="8" t="n"/>
+      <c r="MK8" s="8" t="n"/>
+      <c r="ML8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="4" t="n"/>
@@ -4685,7 +5125,7 @@
       </c>
       <c r="JO9" s="16" t="inlineStr">
         <is>
-          <t>Bump +1-2.5% from W5 single if it was &lt;= RPE 8. Otherwise, repeat W5.</t>
+          <t>Bump +1–2.5% from W5 single if it was &lt;= RPE 8. Otherwise, repeat W5.</t>
         </is>
       </c>
       <c r="JP9" s="8" t="n"/>
@@ -4755,6 +5195,103 @@
       <c r="KR9" s="12" t="n"/>
       <c r="KS9" s="12" t="n"/>
       <c r="KT9" s="7" t="n"/>
+      <c r="KX9" s="4" t="n"/>
+      <c r="KY9" s="10" t="inlineStr">
+        <is>
+          <t>Day 1</t>
+        </is>
+      </c>
+      <c r="KZ9" s="8" t="n"/>
+      <c r="LA9" s="13" t="inlineStr">
+        <is>
+          <t>Squat</t>
+        </is>
+      </c>
+      <c r="LB9" s="6" t="n"/>
+      <c r="LC9" s="8" t="n"/>
+      <c r="LD9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="LE9" s="14" t="inlineStr">
+        <is>
+          <t>136.2kg</t>
+        </is>
+      </c>
+      <c r="LF9" s="15" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="LG9" s="16" t="inlineStr">
+        <is>
+          <t>Warm-up</t>
+        </is>
+      </c>
+      <c r="LH9" s="8" t="n"/>
+      <c r="LI9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="LJ9" s="14" t="inlineStr">
+        <is>
+          <t>155kg</t>
+        </is>
+      </c>
+      <c r="LK9" s="15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="LL9" s="16" t="inlineStr">
+        <is>
+          <t>Warm-up</t>
+        </is>
+      </c>
+      <c r="LM9" s="8" t="n"/>
+      <c r="LN9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="LO9" s="14" t="inlineStr">
+        <is>
+          <t>175kg</t>
+        </is>
+      </c>
+      <c r="LP9" s="15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="LQ9" s="16" t="inlineStr">
+        <is>
+          <t>Warm-up</t>
+        </is>
+      </c>
+      <c r="LR9" s="8" t="n"/>
+      <c r="LS9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="LT9" s="14" t="inlineStr">
+        <is>
+          <t>180kg</t>
+        </is>
+      </c>
+      <c r="LU9" s="17" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="LV9" s="16" t="inlineStr">
+        <is>
+          <t>Confidence single (92.5–95%). Stop here—no maxing to save recovery for WP/Dip.</t>
+        </is>
+      </c>
+      <c r="LW9" s="8" t="n"/>
+      <c r="LX9" s="12" t="n"/>
+      <c r="LY9" s="12" t="n"/>
+      <c r="LZ9" s="12" t="n"/>
+      <c r="MA9" s="12" t="n"/>
+      <c r="MB9" s="8" t="n"/>
+      <c r="MC9" s="12" t="n"/>
+      <c r="MD9" s="12" t="n"/>
+      <c r="ME9" s="12" t="n"/>
+      <c r="MF9" s="12" t="n"/>
+      <c r="MG9" s="8" t="n"/>
+      <c r="MH9" s="12" t="n"/>
+      <c r="MI9" s="12" t="n"/>
+      <c r="MJ9" s="12" t="n"/>
+      <c r="MK9" s="12" t="n"/>
+      <c r="ML9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="4" t="n"/>
@@ -5132,6 +5669,47 @@
       <c r="KR10" s="12" t="n"/>
       <c r="KS10" s="12" t="n"/>
       <c r="KT10" s="7" t="n"/>
+      <c r="KX10" s="4" t="n"/>
+      <c r="KY10" s="6" t="n"/>
+      <c r="KZ10" s="8" t="n"/>
+      <c r="LA10" s="11" t="inlineStr"/>
+      <c r="LB10" s="6" t="n"/>
+      <c r="LC10" s="8" t="n"/>
+      <c r="LD10" s="12" t="n"/>
+      <c r="LE10" s="12" t="n"/>
+      <c r="LF10" s="12" t="n"/>
+      <c r="LG10" s="12" t="n"/>
+      <c r="LH10" s="8" t="n"/>
+      <c r="LI10" s="12" t="n"/>
+      <c r="LJ10" s="12" t="n"/>
+      <c r="LK10" s="12" t="n"/>
+      <c r="LL10" s="12" t="n"/>
+      <c r="LM10" s="8" t="n"/>
+      <c r="LN10" s="12" t="n"/>
+      <c r="LO10" s="12" t="n"/>
+      <c r="LP10" s="12" t="n"/>
+      <c r="LQ10" s="12" t="n"/>
+      <c r="LR10" s="8" t="n"/>
+      <c r="LS10" s="12" t="n"/>
+      <c r="LT10" s="12" t="n"/>
+      <c r="LU10" s="12" t="n"/>
+      <c r="LV10" s="12" t="n"/>
+      <c r="LW10" s="8" t="n"/>
+      <c r="LX10" s="12" t="n"/>
+      <c r="LY10" s="12" t="n"/>
+      <c r="LZ10" s="12" t="n"/>
+      <c r="MA10" s="12" t="n"/>
+      <c r="MB10" s="8" t="n"/>
+      <c r="MC10" s="12" t="n"/>
+      <c r="MD10" s="12" t="n"/>
+      <c r="ME10" s="12" t="n"/>
+      <c r="MF10" s="12" t="n"/>
+      <c r="MG10" s="8" t="n"/>
+      <c r="MH10" s="12" t="n"/>
+      <c r="MI10" s="12" t="n"/>
+      <c r="MJ10" s="12" t="n"/>
+      <c r="MK10" s="12" t="n"/>
+      <c r="ML10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="4" t="n"/>
@@ -5421,6 +5999,47 @@
       <c r="KR11" s="12" t="n"/>
       <c r="KS11" s="12" t="n"/>
       <c r="KT11" s="7" t="n"/>
+      <c r="KX11" s="4" t="n"/>
+      <c r="KY11" s="6" t="n"/>
+      <c r="KZ11" s="8" t="n"/>
+      <c r="LA11" s="11" t="inlineStr"/>
+      <c r="LB11" s="6" t="n"/>
+      <c r="LC11" s="8" t="n"/>
+      <c r="LD11" s="12" t="n"/>
+      <c r="LE11" s="12" t="n"/>
+      <c r="LF11" s="12" t="n"/>
+      <c r="LG11" s="12" t="n"/>
+      <c r="LH11" s="8" t="n"/>
+      <c r="LI11" s="12" t="n"/>
+      <c r="LJ11" s="12" t="n"/>
+      <c r="LK11" s="12" t="n"/>
+      <c r="LL11" s="12" t="n"/>
+      <c r="LM11" s="8" t="n"/>
+      <c r="LN11" s="12" t="n"/>
+      <c r="LO11" s="12" t="n"/>
+      <c r="LP11" s="12" t="n"/>
+      <c r="LQ11" s="12" t="n"/>
+      <c r="LR11" s="8" t="n"/>
+      <c r="LS11" s="12" t="n"/>
+      <c r="LT11" s="12" t="n"/>
+      <c r="LU11" s="12" t="n"/>
+      <c r="LV11" s="12" t="n"/>
+      <c r="LW11" s="8" t="n"/>
+      <c r="LX11" s="12" t="n"/>
+      <c r="LY11" s="12" t="n"/>
+      <c r="LZ11" s="12" t="n"/>
+      <c r="MA11" s="12" t="n"/>
+      <c r="MB11" s="8" t="n"/>
+      <c r="MC11" s="12" t="n"/>
+      <c r="MD11" s="12" t="n"/>
+      <c r="ME11" s="12" t="n"/>
+      <c r="MF11" s="12" t="n"/>
+      <c r="MG11" s="8" t="n"/>
+      <c r="MH11" s="12" t="n"/>
+      <c r="MI11" s="12" t="n"/>
+      <c r="MJ11" s="12" t="n"/>
+      <c r="MK11" s="12" t="n"/>
+      <c r="ML11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="4" t="n"/>
@@ -5710,6 +6329,47 @@
       <c r="KR12" s="12" t="n"/>
       <c r="KS12" s="12" t="n"/>
       <c r="KT12" s="7" t="n"/>
+      <c r="KX12" s="4" t="n"/>
+      <c r="KY12" s="6" t="n"/>
+      <c r="KZ12" s="8" t="n"/>
+      <c r="LA12" s="11" t="inlineStr"/>
+      <c r="LB12" s="6" t="n"/>
+      <c r="LC12" s="8" t="n"/>
+      <c r="LD12" s="12" t="n"/>
+      <c r="LE12" s="12" t="n"/>
+      <c r="LF12" s="12" t="n"/>
+      <c r="LG12" s="12" t="n"/>
+      <c r="LH12" s="8" t="n"/>
+      <c r="LI12" s="12" t="n"/>
+      <c r="LJ12" s="12" t="n"/>
+      <c r="LK12" s="12" t="n"/>
+      <c r="LL12" s="12" t="n"/>
+      <c r="LM12" s="8" t="n"/>
+      <c r="LN12" s="12" t="n"/>
+      <c r="LO12" s="12" t="n"/>
+      <c r="LP12" s="12" t="n"/>
+      <c r="LQ12" s="12" t="n"/>
+      <c r="LR12" s="8" t="n"/>
+      <c r="LS12" s="12" t="n"/>
+      <c r="LT12" s="12" t="n"/>
+      <c r="LU12" s="12" t="n"/>
+      <c r="LV12" s="12" t="n"/>
+      <c r="LW12" s="8" t="n"/>
+      <c r="LX12" s="12" t="n"/>
+      <c r="LY12" s="12" t="n"/>
+      <c r="LZ12" s="12" t="n"/>
+      <c r="MA12" s="12" t="n"/>
+      <c r="MB12" s="8" t="n"/>
+      <c r="MC12" s="12" t="n"/>
+      <c r="MD12" s="12" t="n"/>
+      <c r="ME12" s="12" t="n"/>
+      <c r="MF12" s="12" t="n"/>
+      <c r="MG12" s="8" t="n"/>
+      <c r="MH12" s="12" t="n"/>
+      <c r="MI12" s="12" t="n"/>
+      <c r="MJ12" s="12" t="n"/>
+      <c r="MK12" s="12" t="n"/>
+      <c r="ML12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="4" t="n"/>
@@ -5999,6 +6659,47 @@
       <c r="KR13" s="12" t="n"/>
       <c r="KS13" s="12" t="n"/>
       <c r="KT13" s="7" t="n"/>
+      <c r="KX13" s="4" t="n"/>
+      <c r="KY13" s="6" t="n"/>
+      <c r="KZ13" s="8" t="n"/>
+      <c r="LA13" s="11" t="inlineStr"/>
+      <c r="LB13" s="6" t="n"/>
+      <c r="LC13" s="8" t="n"/>
+      <c r="LD13" s="12" t="n"/>
+      <c r="LE13" s="12" t="n"/>
+      <c r="LF13" s="12" t="n"/>
+      <c r="LG13" s="12" t="n"/>
+      <c r="LH13" s="8" t="n"/>
+      <c r="LI13" s="12" t="n"/>
+      <c r="LJ13" s="12" t="n"/>
+      <c r="LK13" s="12" t="n"/>
+      <c r="LL13" s="12" t="n"/>
+      <c r="LM13" s="8" t="n"/>
+      <c r="LN13" s="12" t="n"/>
+      <c r="LO13" s="12" t="n"/>
+      <c r="LP13" s="12" t="n"/>
+      <c r="LQ13" s="12" t="n"/>
+      <c r="LR13" s="8" t="n"/>
+      <c r="LS13" s="12" t="n"/>
+      <c r="LT13" s="12" t="n"/>
+      <c r="LU13" s="12" t="n"/>
+      <c r="LV13" s="12" t="n"/>
+      <c r="LW13" s="8" t="n"/>
+      <c r="LX13" s="12" t="n"/>
+      <c r="LY13" s="12" t="n"/>
+      <c r="LZ13" s="12" t="n"/>
+      <c r="MA13" s="12" t="n"/>
+      <c r="MB13" s="8" t="n"/>
+      <c r="MC13" s="12" t="n"/>
+      <c r="MD13" s="12" t="n"/>
+      <c r="ME13" s="12" t="n"/>
+      <c r="MF13" s="12" t="n"/>
+      <c r="MG13" s="8" t="n"/>
+      <c r="MH13" s="12" t="n"/>
+      <c r="MI13" s="12" t="n"/>
+      <c r="MJ13" s="12" t="n"/>
+      <c r="MK13" s="12" t="n"/>
+      <c r="ML13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="4" t="n"/>
@@ -6288,6 +6989,47 @@
       <c r="KR14" s="12" t="n"/>
       <c r="KS14" s="12" t="n"/>
       <c r="KT14" s="7" t="n"/>
+      <c r="KX14" s="4" t="n"/>
+      <c r="KY14" s="6" t="n"/>
+      <c r="KZ14" s="8" t="n"/>
+      <c r="LA14" s="11" t="inlineStr"/>
+      <c r="LB14" s="6" t="n"/>
+      <c r="LC14" s="8" t="n"/>
+      <c r="LD14" s="12" t="n"/>
+      <c r="LE14" s="12" t="n"/>
+      <c r="LF14" s="12" t="n"/>
+      <c r="LG14" s="12" t="n"/>
+      <c r="LH14" s="8" t="n"/>
+      <c r="LI14" s="12" t="n"/>
+      <c r="LJ14" s="12" t="n"/>
+      <c r="LK14" s="12" t="n"/>
+      <c r="LL14" s="12" t="n"/>
+      <c r="LM14" s="8" t="n"/>
+      <c r="LN14" s="12" t="n"/>
+      <c r="LO14" s="12" t="n"/>
+      <c r="LP14" s="12" t="n"/>
+      <c r="LQ14" s="12" t="n"/>
+      <c r="LR14" s="8" t="n"/>
+      <c r="LS14" s="12" t="n"/>
+      <c r="LT14" s="12" t="n"/>
+      <c r="LU14" s="12" t="n"/>
+      <c r="LV14" s="12" t="n"/>
+      <c r="LW14" s="8" t="n"/>
+      <c r="LX14" s="12" t="n"/>
+      <c r="LY14" s="12" t="n"/>
+      <c r="LZ14" s="12" t="n"/>
+      <c r="MA14" s="12" t="n"/>
+      <c r="MB14" s="8" t="n"/>
+      <c r="MC14" s="12" t="n"/>
+      <c r="MD14" s="12" t="n"/>
+      <c r="ME14" s="12" t="n"/>
+      <c r="MF14" s="12" t="n"/>
+      <c r="MG14" s="8" t="n"/>
+      <c r="MH14" s="12" t="n"/>
+      <c r="MI14" s="12" t="n"/>
+      <c r="MJ14" s="12" t="n"/>
+      <c r="MK14" s="12" t="n"/>
+      <c r="ML14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="B15" s="4" t="n"/>
@@ -6577,6 +7319,47 @@
       <c r="KR15" s="12" t="n"/>
       <c r="KS15" s="12" t="n"/>
       <c r="KT15" s="7" t="n"/>
+      <c r="KX15" s="4" t="n"/>
+      <c r="KY15" s="6" t="n"/>
+      <c r="KZ15" s="8" t="n"/>
+      <c r="LA15" s="11" t="inlineStr"/>
+      <c r="LB15" s="6" t="n"/>
+      <c r="LC15" s="8" t="n"/>
+      <c r="LD15" s="12" t="n"/>
+      <c r="LE15" s="12" t="n"/>
+      <c r="LF15" s="12" t="n"/>
+      <c r="LG15" s="12" t="n"/>
+      <c r="LH15" s="8" t="n"/>
+      <c r="LI15" s="12" t="n"/>
+      <c r="LJ15" s="12" t="n"/>
+      <c r="LK15" s="12" t="n"/>
+      <c r="LL15" s="12" t="n"/>
+      <c r="LM15" s="8" t="n"/>
+      <c r="LN15" s="12" t="n"/>
+      <c r="LO15" s="12" t="n"/>
+      <c r="LP15" s="12" t="n"/>
+      <c r="LQ15" s="12" t="n"/>
+      <c r="LR15" s="8" t="n"/>
+      <c r="LS15" s="12" t="n"/>
+      <c r="LT15" s="12" t="n"/>
+      <c r="LU15" s="12" t="n"/>
+      <c r="LV15" s="12" t="n"/>
+      <c r="LW15" s="8" t="n"/>
+      <c r="LX15" s="12" t="n"/>
+      <c r="LY15" s="12" t="n"/>
+      <c r="LZ15" s="12" t="n"/>
+      <c r="MA15" s="12" t="n"/>
+      <c r="MB15" s="8" t="n"/>
+      <c r="MC15" s="12" t="n"/>
+      <c r="MD15" s="12" t="n"/>
+      <c r="ME15" s="12" t="n"/>
+      <c r="MF15" s="12" t="n"/>
+      <c r="MG15" s="8" t="n"/>
+      <c r="MH15" s="12" t="n"/>
+      <c r="MI15" s="12" t="n"/>
+      <c r="MJ15" s="12" t="n"/>
+      <c r="MK15" s="12" t="n"/>
+      <c r="ML15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="B16" s="4" t="n"/>
@@ -6866,6 +7649,47 @@
       <c r="KR16" s="12" t="n"/>
       <c r="KS16" s="12" t="n"/>
       <c r="KT16" s="7" t="n"/>
+      <c r="KX16" s="4" t="n"/>
+      <c r="KY16" s="6" t="n"/>
+      <c r="KZ16" s="8" t="n"/>
+      <c r="LA16" s="11" t="inlineStr"/>
+      <c r="LB16" s="6" t="n"/>
+      <c r="LC16" s="8" t="n"/>
+      <c r="LD16" s="12" t="n"/>
+      <c r="LE16" s="12" t="n"/>
+      <c r="LF16" s="12" t="n"/>
+      <c r="LG16" s="12" t="n"/>
+      <c r="LH16" s="8" t="n"/>
+      <c r="LI16" s="12" t="n"/>
+      <c r="LJ16" s="12" t="n"/>
+      <c r="LK16" s="12" t="n"/>
+      <c r="LL16" s="12" t="n"/>
+      <c r="LM16" s="8" t="n"/>
+      <c r="LN16" s="12" t="n"/>
+      <c r="LO16" s="12" t="n"/>
+      <c r="LP16" s="12" t="n"/>
+      <c r="LQ16" s="12" t="n"/>
+      <c r="LR16" s="8" t="n"/>
+      <c r="LS16" s="12" t="n"/>
+      <c r="LT16" s="12" t="n"/>
+      <c r="LU16" s="12" t="n"/>
+      <c r="LV16" s="12" t="n"/>
+      <c r="LW16" s="8" t="n"/>
+      <c r="LX16" s="12" t="n"/>
+      <c r="LY16" s="12" t="n"/>
+      <c r="LZ16" s="12" t="n"/>
+      <c r="MA16" s="12" t="n"/>
+      <c r="MB16" s="8" t="n"/>
+      <c r="MC16" s="12" t="n"/>
+      <c r="MD16" s="12" t="n"/>
+      <c r="ME16" s="12" t="n"/>
+      <c r="MF16" s="12" t="n"/>
+      <c r="MG16" s="8" t="n"/>
+      <c r="MH16" s="12" t="n"/>
+      <c r="MI16" s="12" t="n"/>
+      <c r="MJ16" s="12" t="n"/>
+      <c r="MK16" s="12" t="n"/>
+      <c r="ML16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="4" t="n"/>
@@ -7155,6 +7979,47 @@
       <c r="KR17" s="8" t="n"/>
       <c r="KS17" s="8" t="n"/>
       <c r="KT17" s="7" t="n"/>
+      <c r="KX17" s="4" t="n"/>
+      <c r="KY17" s="8" t="n"/>
+      <c r="KZ17" s="8" t="n"/>
+      <c r="LA17" s="8" t="n"/>
+      <c r="LB17" s="8" t="n"/>
+      <c r="LC17" s="8" t="n"/>
+      <c r="LD17" s="8" t="n"/>
+      <c r="LE17" s="8" t="n"/>
+      <c r="LF17" s="8" t="n"/>
+      <c r="LG17" s="8" t="n"/>
+      <c r="LH17" s="8" t="n"/>
+      <c r="LI17" s="8" t="n"/>
+      <c r="LJ17" s="8" t="n"/>
+      <c r="LK17" s="8" t="n"/>
+      <c r="LL17" s="8" t="n"/>
+      <c r="LM17" s="8" t="n"/>
+      <c r="LN17" s="8" t="n"/>
+      <c r="LO17" s="8" t="n"/>
+      <c r="LP17" s="8" t="n"/>
+      <c r="LQ17" s="8" t="n"/>
+      <c r="LR17" s="8" t="n"/>
+      <c r="LS17" s="8" t="n"/>
+      <c r="LT17" s="8" t="n"/>
+      <c r="LU17" s="8" t="n"/>
+      <c r="LV17" s="8" t="n"/>
+      <c r="LW17" s="8" t="n"/>
+      <c r="LX17" s="8" t="n"/>
+      <c r="LY17" s="8" t="n"/>
+      <c r="LZ17" s="8" t="n"/>
+      <c r="MA17" s="8" t="n"/>
+      <c r="MB17" s="8" t="n"/>
+      <c r="MC17" s="8" t="n"/>
+      <c r="MD17" s="8" t="n"/>
+      <c r="ME17" s="8" t="n"/>
+      <c r="MF17" s="8" t="n"/>
+      <c r="MG17" s="8" t="n"/>
+      <c r="MH17" s="8" t="n"/>
+      <c r="MI17" s="8" t="n"/>
+      <c r="MJ17" s="8" t="n"/>
+      <c r="MK17" s="8" t="n"/>
+      <c r="ML17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="4" t="n"/>
@@ -7472,6 +8337,51 @@
       <c r="KR18" s="12" t="n"/>
       <c r="KS18" s="12" t="n"/>
       <c r="KT18" s="7" t="n"/>
+      <c r="KX18" s="4" t="n"/>
+      <c r="KY18" s="10" t="inlineStr">
+        <is>
+          <t>Day 2</t>
+        </is>
+      </c>
+      <c r="KZ18" s="8" t="n"/>
+      <c r="LA18" s="11" t="inlineStr"/>
+      <c r="LB18" s="6" t="n"/>
+      <c r="LC18" s="8" t="n"/>
+      <c r="LD18" s="12" t="n"/>
+      <c r="LE18" s="12" t="n"/>
+      <c r="LF18" s="12" t="n"/>
+      <c r="LG18" s="12" t="n"/>
+      <c r="LH18" s="8" t="n"/>
+      <c r="LI18" s="12" t="n"/>
+      <c r="LJ18" s="12" t="n"/>
+      <c r="LK18" s="12" t="n"/>
+      <c r="LL18" s="12" t="n"/>
+      <c r="LM18" s="8" t="n"/>
+      <c r="LN18" s="12" t="n"/>
+      <c r="LO18" s="12" t="n"/>
+      <c r="LP18" s="12" t="n"/>
+      <c r="LQ18" s="12" t="n"/>
+      <c r="LR18" s="8" t="n"/>
+      <c r="LS18" s="12" t="n"/>
+      <c r="LT18" s="12" t="n"/>
+      <c r="LU18" s="12" t="n"/>
+      <c r="LV18" s="12" t="n"/>
+      <c r="LW18" s="8" t="n"/>
+      <c r="LX18" s="12" t="n"/>
+      <c r="LY18" s="12" t="n"/>
+      <c r="LZ18" s="12" t="n"/>
+      <c r="MA18" s="12" t="n"/>
+      <c r="MB18" s="8" t="n"/>
+      <c r="MC18" s="12" t="n"/>
+      <c r="MD18" s="12" t="n"/>
+      <c r="ME18" s="12" t="n"/>
+      <c r="MF18" s="12" t="n"/>
+      <c r="MG18" s="8" t="n"/>
+      <c r="MH18" s="12" t="n"/>
+      <c r="MI18" s="12" t="n"/>
+      <c r="MJ18" s="12" t="n"/>
+      <c r="MK18" s="12" t="n"/>
+      <c r="ML18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="B19" s="4" t="n"/>
@@ -7761,6 +8671,47 @@
       <c r="KR19" s="12" t="n"/>
       <c r="KS19" s="12" t="n"/>
       <c r="KT19" s="7" t="n"/>
+      <c r="KX19" s="4" t="n"/>
+      <c r="KY19" s="6" t="n"/>
+      <c r="KZ19" s="8" t="n"/>
+      <c r="LA19" s="11" t="inlineStr"/>
+      <c r="LB19" s="6" t="n"/>
+      <c r="LC19" s="8" t="n"/>
+      <c r="LD19" s="12" t="n"/>
+      <c r="LE19" s="12" t="n"/>
+      <c r="LF19" s="12" t="n"/>
+      <c r="LG19" s="12" t="n"/>
+      <c r="LH19" s="8" t="n"/>
+      <c r="LI19" s="12" t="n"/>
+      <c r="LJ19" s="12" t="n"/>
+      <c r="LK19" s="12" t="n"/>
+      <c r="LL19" s="12" t="n"/>
+      <c r="LM19" s="8" t="n"/>
+      <c r="LN19" s="12" t="n"/>
+      <c r="LO19" s="12" t="n"/>
+      <c r="LP19" s="12" t="n"/>
+      <c r="LQ19" s="12" t="n"/>
+      <c r="LR19" s="8" t="n"/>
+      <c r="LS19" s="12" t="n"/>
+      <c r="LT19" s="12" t="n"/>
+      <c r="LU19" s="12" t="n"/>
+      <c r="LV19" s="12" t="n"/>
+      <c r="LW19" s="8" t="n"/>
+      <c r="LX19" s="12" t="n"/>
+      <c r="LY19" s="12" t="n"/>
+      <c r="LZ19" s="12" t="n"/>
+      <c r="MA19" s="12" t="n"/>
+      <c r="MB19" s="8" t="n"/>
+      <c r="MC19" s="12" t="n"/>
+      <c r="MD19" s="12" t="n"/>
+      <c r="ME19" s="12" t="n"/>
+      <c r="MF19" s="12" t="n"/>
+      <c r="MG19" s="8" t="n"/>
+      <c r="MH19" s="12" t="n"/>
+      <c r="MI19" s="12" t="n"/>
+      <c r="MJ19" s="12" t="n"/>
+      <c r="MK19" s="12" t="n"/>
+      <c r="ML19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="B20" s="4" t="n"/>
@@ -8050,6 +9001,47 @@
       <c r="KR20" s="12" t="n"/>
       <c r="KS20" s="12" t="n"/>
       <c r="KT20" s="7" t="n"/>
+      <c r="KX20" s="4" t="n"/>
+      <c r="KY20" s="6" t="n"/>
+      <c r="KZ20" s="8" t="n"/>
+      <c r="LA20" s="11" t="inlineStr"/>
+      <c r="LB20" s="6" t="n"/>
+      <c r="LC20" s="8" t="n"/>
+      <c r="LD20" s="12" t="n"/>
+      <c r="LE20" s="12" t="n"/>
+      <c r="LF20" s="12" t="n"/>
+      <c r="LG20" s="12" t="n"/>
+      <c r="LH20" s="8" t="n"/>
+      <c r="LI20" s="12" t="n"/>
+      <c r="LJ20" s="12" t="n"/>
+      <c r="LK20" s="12" t="n"/>
+      <c r="LL20" s="12" t="n"/>
+      <c r="LM20" s="8" t="n"/>
+      <c r="LN20" s="12" t="n"/>
+      <c r="LO20" s="12" t="n"/>
+      <c r="LP20" s="12" t="n"/>
+      <c r="LQ20" s="12" t="n"/>
+      <c r="LR20" s="8" t="n"/>
+      <c r="LS20" s="12" t="n"/>
+      <c r="LT20" s="12" t="n"/>
+      <c r="LU20" s="12" t="n"/>
+      <c r="LV20" s="12" t="n"/>
+      <c r="LW20" s="8" t="n"/>
+      <c r="LX20" s="12" t="n"/>
+      <c r="LY20" s="12" t="n"/>
+      <c r="LZ20" s="12" t="n"/>
+      <c r="MA20" s="12" t="n"/>
+      <c r="MB20" s="8" t="n"/>
+      <c r="MC20" s="12" t="n"/>
+      <c r="MD20" s="12" t="n"/>
+      <c r="ME20" s="12" t="n"/>
+      <c r="MF20" s="12" t="n"/>
+      <c r="MG20" s="8" t="n"/>
+      <c r="MH20" s="12" t="n"/>
+      <c r="MI20" s="12" t="n"/>
+      <c r="MJ20" s="12" t="n"/>
+      <c r="MK20" s="12" t="n"/>
+      <c r="ML20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="4" t="n"/>
@@ -8339,6 +9331,47 @@
       <c r="KR21" s="12" t="n"/>
       <c r="KS21" s="12" t="n"/>
       <c r="KT21" s="7" t="n"/>
+      <c r="KX21" s="4" t="n"/>
+      <c r="KY21" s="6" t="n"/>
+      <c r="KZ21" s="8" t="n"/>
+      <c r="LA21" s="11" t="inlineStr"/>
+      <c r="LB21" s="6" t="n"/>
+      <c r="LC21" s="8" t="n"/>
+      <c r="LD21" s="12" t="n"/>
+      <c r="LE21" s="12" t="n"/>
+      <c r="LF21" s="12" t="n"/>
+      <c r="LG21" s="12" t="n"/>
+      <c r="LH21" s="8" t="n"/>
+      <c r="LI21" s="12" t="n"/>
+      <c r="LJ21" s="12" t="n"/>
+      <c r="LK21" s="12" t="n"/>
+      <c r="LL21" s="12" t="n"/>
+      <c r="LM21" s="8" t="n"/>
+      <c r="LN21" s="12" t="n"/>
+      <c r="LO21" s="12" t="n"/>
+      <c r="LP21" s="12" t="n"/>
+      <c r="LQ21" s="12" t="n"/>
+      <c r="LR21" s="8" t="n"/>
+      <c r="LS21" s="12" t="n"/>
+      <c r="LT21" s="12" t="n"/>
+      <c r="LU21" s="12" t="n"/>
+      <c r="LV21" s="12" t="n"/>
+      <c r="LW21" s="8" t="n"/>
+      <c r="LX21" s="12" t="n"/>
+      <c r="LY21" s="12" t="n"/>
+      <c r="LZ21" s="12" t="n"/>
+      <c r="MA21" s="12" t="n"/>
+      <c r="MB21" s="8" t="n"/>
+      <c r="MC21" s="12" t="n"/>
+      <c r="MD21" s="12" t="n"/>
+      <c r="ME21" s="12" t="n"/>
+      <c r="MF21" s="12" t="n"/>
+      <c r="MG21" s="8" t="n"/>
+      <c r="MH21" s="12" t="n"/>
+      <c r="MI21" s="12" t="n"/>
+      <c r="MJ21" s="12" t="n"/>
+      <c r="MK21" s="12" t="n"/>
+      <c r="ML21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="B22" s="4" t="n"/>
@@ -8628,6 +9661,47 @@
       <c r="KR22" s="12" t="n"/>
       <c r="KS22" s="12" t="n"/>
       <c r="KT22" s="7" t="n"/>
+      <c r="KX22" s="4" t="n"/>
+      <c r="KY22" s="6" t="n"/>
+      <c r="KZ22" s="8" t="n"/>
+      <c r="LA22" s="11" t="inlineStr"/>
+      <c r="LB22" s="6" t="n"/>
+      <c r="LC22" s="8" t="n"/>
+      <c r="LD22" s="12" t="n"/>
+      <c r="LE22" s="12" t="n"/>
+      <c r="LF22" s="12" t="n"/>
+      <c r="LG22" s="12" t="n"/>
+      <c r="LH22" s="8" t="n"/>
+      <c r="LI22" s="12" t="n"/>
+      <c r="LJ22" s="12" t="n"/>
+      <c r="LK22" s="12" t="n"/>
+      <c r="LL22" s="12" t="n"/>
+      <c r="LM22" s="8" t="n"/>
+      <c r="LN22" s="12" t="n"/>
+      <c r="LO22" s="12" t="n"/>
+      <c r="LP22" s="12" t="n"/>
+      <c r="LQ22" s="12" t="n"/>
+      <c r="LR22" s="8" t="n"/>
+      <c r="LS22" s="12" t="n"/>
+      <c r="LT22" s="12" t="n"/>
+      <c r="LU22" s="12" t="n"/>
+      <c r="LV22" s="12" t="n"/>
+      <c r="LW22" s="8" t="n"/>
+      <c r="LX22" s="12" t="n"/>
+      <c r="LY22" s="12" t="n"/>
+      <c r="LZ22" s="12" t="n"/>
+      <c r="MA22" s="12" t="n"/>
+      <c r="MB22" s="8" t="n"/>
+      <c r="MC22" s="12" t="n"/>
+      <c r="MD22" s="12" t="n"/>
+      <c r="ME22" s="12" t="n"/>
+      <c r="MF22" s="12" t="n"/>
+      <c r="MG22" s="8" t="n"/>
+      <c r="MH22" s="12" t="n"/>
+      <c r="MI22" s="12" t="n"/>
+      <c r="MJ22" s="12" t="n"/>
+      <c r="MK22" s="12" t="n"/>
+      <c r="ML22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="B23" s="4" t="n"/>
@@ -8917,6 +9991,47 @@
       <c r="KR23" s="12" t="n"/>
       <c r="KS23" s="12" t="n"/>
       <c r="KT23" s="7" t="n"/>
+      <c r="KX23" s="4" t="n"/>
+      <c r="KY23" s="6" t="n"/>
+      <c r="KZ23" s="8" t="n"/>
+      <c r="LA23" s="11" t="inlineStr"/>
+      <c r="LB23" s="6" t="n"/>
+      <c r="LC23" s="8" t="n"/>
+      <c r="LD23" s="12" t="n"/>
+      <c r="LE23" s="12" t="n"/>
+      <c r="LF23" s="12" t="n"/>
+      <c r="LG23" s="12" t="n"/>
+      <c r="LH23" s="8" t="n"/>
+      <c r="LI23" s="12" t="n"/>
+      <c r="LJ23" s="12" t="n"/>
+      <c r="LK23" s="12" t="n"/>
+      <c r="LL23" s="12" t="n"/>
+      <c r="LM23" s="8" t="n"/>
+      <c r="LN23" s="12" t="n"/>
+      <c r="LO23" s="12" t="n"/>
+      <c r="LP23" s="12" t="n"/>
+      <c r="LQ23" s="12" t="n"/>
+      <c r="LR23" s="8" t="n"/>
+      <c r="LS23" s="12" t="n"/>
+      <c r="LT23" s="12" t="n"/>
+      <c r="LU23" s="12" t="n"/>
+      <c r="LV23" s="12" t="n"/>
+      <c r="LW23" s="8" t="n"/>
+      <c r="LX23" s="12" t="n"/>
+      <c r="LY23" s="12" t="n"/>
+      <c r="LZ23" s="12" t="n"/>
+      <c r="MA23" s="12" t="n"/>
+      <c r="MB23" s="8" t="n"/>
+      <c r="MC23" s="12" t="n"/>
+      <c r="MD23" s="12" t="n"/>
+      <c r="ME23" s="12" t="n"/>
+      <c r="MF23" s="12" t="n"/>
+      <c r="MG23" s="8" t="n"/>
+      <c r="MH23" s="12" t="n"/>
+      <c r="MI23" s="12" t="n"/>
+      <c r="MJ23" s="12" t="n"/>
+      <c r="MK23" s="12" t="n"/>
+      <c r="ML23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="B24" s="4" t="n"/>
@@ -9206,6 +10321,47 @@
       <c r="KR24" s="12" t="n"/>
       <c r="KS24" s="12" t="n"/>
       <c r="KT24" s="7" t="n"/>
+      <c r="KX24" s="4" t="n"/>
+      <c r="KY24" s="6" t="n"/>
+      <c r="KZ24" s="8" t="n"/>
+      <c r="LA24" s="11" t="inlineStr"/>
+      <c r="LB24" s="6" t="n"/>
+      <c r="LC24" s="8" t="n"/>
+      <c r="LD24" s="12" t="n"/>
+      <c r="LE24" s="12" t="n"/>
+      <c r="LF24" s="12" t="n"/>
+      <c r="LG24" s="12" t="n"/>
+      <c r="LH24" s="8" t="n"/>
+      <c r="LI24" s="12" t="n"/>
+      <c r="LJ24" s="12" t="n"/>
+      <c r="LK24" s="12" t="n"/>
+      <c r="LL24" s="12" t="n"/>
+      <c r="LM24" s="8" t="n"/>
+      <c r="LN24" s="12" t="n"/>
+      <c r="LO24" s="12" t="n"/>
+      <c r="LP24" s="12" t="n"/>
+      <c r="LQ24" s="12" t="n"/>
+      <c r="LR24" s="8" t="n"/>
+      <c r="LS24" s="12" t="n"/>
+      <c r="LT24" s="12" t="n"/>
+      <c r="LU24" s="12" t="n"/>
+      <c r="LV24" s="12" t="n"/>
+      <c r="LW24" s="8" t="n"/>
+      <c r="LX24" s="12" t="n"/>
+      <c r="LY24" s="12" t="n"/>
+      <c r="LZ24" s="12" t="n"/>
+      <c r="MA24" s="12" t="n"/>
+      <c r="MB24" s="8" t="n"/>
+      <c r="MC24" s="12" t="n"/>
+      <c r="MD24" s="12" t="n"/>
+      <c r="ME24" s="12" t="n"/>
+      <c r="MF24" s="12" t="n"/>
+      <c r="MG24" s="8" t="n"/>
+      <c r="MH24" s="12" t="n"/>
+      <c r="MI24" s="12" t="n"/>
+      <c r="MJ24" s="12" t="n"/>
+      <c r="MK24" s="12" t="n"/>
+      <c r="ML24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="4" t="n"/>
@@ -9495,6 +10651,47 @@
       <c r="KR25" s="12" t="n"/>
       <c r="KS25" s="12" t="n"/>
       <c r="KT25" s="7" t="n"/>
+      <c r="KX25" s="4" t="n"/>
+      <c r="KY25" s="6" t="n"/>
+      <c r="KZ25" s="8" t="n"/>
+      <c r="LA25" s="11" t="inlineStr"/>
+      <c r="LB25" s="6" t="n"/>
+      <c r="LC25" s="8" t="n"/>
+      <c r="LD25" s="12" t="n"/>
+      <c r="LE25" s="12" t="n"/>
+      <c r="LF25" s="12" t="n"/>
+      <c r="LG25" s="12" t="n"/>
+      <c r="LH25" s="8" t="n"/>
+      <c r="LI25" s="12" t="n"/>
+      <c r="LJ25" s="12" t="n"/>
+      <c r="LK25" s="12" t="n"/>
+      <c r="LL25" s="12" t="n"/>
+      <c r="LM25" s="8" t="n"/>
+      <c r="LN25" s="12" t="n"/>
+      <c r="LO25" s="12" t="n"/>
+      <c r="LP25" s="12" t="n"/>
+      <c r="LQ25" s="12" t="n"/>
+      <c r="LR25" s="8" t="n"/>
+      <c r="LS25" s="12" t="n"/>
+      <c r="LT25" s="12" t="n"/>
+      <c r="LU25" s="12" t="n"/>
+      <c r="LV25" s="12" t="n"/>
+      <c r="LW25" s="8" t="n"/>
+      <c r="LX25" s="12" t="n"/>
+      <c r="LY25" s="12" t="n"/>
+      <c r="LZ25" s="12" t="n"/>
+      <c r="MA25" s="12" t="n"/>
+      <c r="MB25" s="8" t="n"/>
+      <c r="MC25" s="12" t="n"/>
+      <c r="MD25" s="12" t="n"/>
+      <c r="ME25" s="12" t="n"/>
+      <c r="MF25" s="12" t="n"/>
+      <c r="MG25" s="8" t="n"/>
+      <c r="MH25" s="12" t="n"/>
+      <c r="MI25" s="12" t="n"/>
+      <c r="MJ25" s="12" t="n"/>
+      <c r="MK25" s="12" t="n"/>
+      <c r="ML25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="B26" s="4" t="n"/>
@@ -9784,6 +10981,47 @@
       <c r="KR26" s="8" t="n"/>
       <c r="KS26" s="8" t="n"/>
       <c r="KT26" s="7" t="n"/>
+      <c r="KX26" s="4" t="n"/>
+      <c r="KY26" s="8" t="n"/>
+      <c r="KZ26" s="8" t="n"/>
+      <c r="LA26" s="8" t="n"/>
+      <c r="LB26" s="8" t="n"/>
+      <c r="LC26" s="8" t="n"/>
+      <c r="LD26" s="8" t="n"/>
+      <c r="LE26" s="8" t="n"/>
+      <c r="LF26" s="8" t="n"/>
+      <c r="LG26" s="8" t="n"/>
+      <c r="LH26" s="8" t="n"/>
+      <c r="LI26" s="8" t="n"/>
+      <c r="LJ26" s="8" t="n"/>
+      <c r="LK26" s="8" t="n"/>
+      <c r="LL26" s="8" t="n"/>
+      <c r="LM26" s="8" t="n"/>
+      <c r="LN26" s="8" t="n"/>
+      <c r="LO26" s="8" t="n"/>
+      <c r="LP26" s="8" t="n"/>
+      <c r="LQ26" s="8" t="n"/>
+      <c r="LR26" s="8" t="n"/>
+      <c r="LS26" s="8" t="n"/>
+      <c r="LT26" s="8" t="n"/>
+      <c r="LU26" s="8" t="n"/>
+      <c r="LV26" s="8" t="n"/>
+      <c r="LW26" s="8" t="n"/>
+      <c r="LX26" s="8" t="n"/>
+      <c r="LY26" s="8" t="n"/>
+      <c r="LZ26" s="8" t="n"/>
+      <c r="MA26" s="8" t="n"/>
+      <c r="MB26" s="8" t="n"/>
+      <c r="MC26" s="8" t="n"/>
+      <c r="MD26" s="8" t="n"/>
+      <c r="ME26" s="8" t="n"/>
+      <c r="MF26" s="8" t="n"/>
+      <c r="MG26" s="8" t="n"/>
+      <c r="MH26" s="8" t="n"/>
+      <c r="MI26" s="8" t="n"/>
+      <c r="MJ26" s="8" t="n"/>
+      <c r="MK26" s="8" t="n"/>
+      <c r="ML26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="B27" s="4" t="n"/>
@@ -10101,6 +11339,103 @@
       <c r="KR27" s="12" t="n"/>
       <c r="KS27" s="12" t="n"/>
       <c r="KT27" s="7" t="n"/>
+      <c r="KX27" s="4" t="n"/>
+      <c r="KY27" s="10" t="inlineStr">
+        <is>
+          <t>Day 3</t>
+        </is>
+      </c>
+      <c r="KZ27" s="8" t="n"/>
+      <c r="LA27" s="13" t="inlineStr">
+        <is>
+          <t>Weighted Pull-Ups</t>
+        </is>
+      </c>
+      <c r="LB27" s="6" t="n"/>
+      <c r="LC27" s="8" t="n"/>
+      <c r="LD27" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="LE27" s="14" t="inlineStr">
+        <is>
+          <t>73.8kg</t>
+        </is>
+      </c>
+      <c r="LF27" s="15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="LG27" s="16" t="inlineStr">
+        <is>
+          <t>Warm-up single</t>
+        </is>
+      </c>
+      <c r="LH27" s="8" t="n"/>
+      <c r="LI27" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="LJ27" s="14" t="inlineStr">
+        <is>
+          <t>77.5kg</t>
+        </is>
+      </c>
+      <c r="LK27" s="15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="LL27" s="16" t="inlineStr">
+        <is>
+          <t>Opener</t>
+        </is>
+      </c>
+      <c r="LM27" s="8" t="n"/>
+      <c r="LN27" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="LO27" s="14" t="inlineStr">
+        <is>
+          <t>82.5kg</t>
+        </is>
+      </c>
+      <c r="LP27" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="LQ27" s="16" t="inlineStr">
+        <is>
+          <t>Second (match PB)</t>
+        </is>
+      </c>
+      <c r="LR27" s="8" t="n"/>
+      <c r="LS27" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="LT27" s="14" t="inlineStr">
+        <is>
+          <t>83.8kg</t>
+        </is>
+      </c>
+      <c r="LU27" s="15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="LV27" s="16" t="inlineStr">
+        <is>
+          <t>Third (102–103% only if second was clean)</t>
+        </is>
+      </c>
+      <c r="LW27" s="8" t="n"/>
+      <c r="LX27" s="12" t="n"/>
+      <c r="LY27" s="12" t="n"/>
+      <c r="LZ27" s="12" t="n"/>
+      <c r="MA27" s="12" t="n"/>
+      <c r="MB27" s="8" t="n"/>
+      <c r="MC27" s="12" t="n"/>
+      <c r="MD27" s="12" t="n"/>
+      <c r="ME27" s="12" t="n"/>
+      <c r="MF27" s="12" t="n"/>
+      <c r="MG27" s="8" t="n"/>
+      <c r="MH27" s="12" t="n"/>
+      <c r="MI27" s="12" t="n"/>
+      <c r="MJ27" s="12" t="n"/>
+      <c r="MK27" s="12" t="n"/>
+      <c r="ML27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="B28" s="4" t="n"/>
@@ -10390,6 +11725,47 @@
       <c r="KR28" s="12" t="n"/>
       <c r="KS28" s="12" t="n"/>
       <c r="KT28" s="7" t="n"/>
+      <c r="KX28" s="4" t="n"/>
+      <c r="KY28" s="6" t="n"/>
+      <c r="KZ28" s="8" t="n"/>
+      <c r="LA28" s="11" t="inlineStr"/>
+      <c r="LB28" s="6" t="n"/>
+      <c r="LC28" s="8" t="n"/>
+      <c r="LD28" s="12" t="n"/>
+      <c r="LE28" s="12" t="n"/>
+      <c r="LF28" s="12" t="n"/>
+      <c r="LG28" s="12" t="n"/>
+      <c r="LH28" s="8" t="n"/>
+      <c r="LI28" s="12" t="n"/>
+      <c r="LJ28" s="12" t="n"/>
+      <c r="LK28" s="12" t="n"/>
+      <c r="LL28" s="12" t="n"/>
+      <c r="LM28" s="8" t="n"/>
+      <c r="LN28" s="12" t="n"/>
+      <c r="LO28" s="12" t="n"/>
+      <c r="LP28" s="12" t="n"/>
+      <c r="LQ28" s="12" t="n"/>
+      <c r="LR28" s="8" t="n"/>
+      <c r="LS28" s="12" t="n"/>
+      <c r="LT28" s="12" t="n"/>
+      <c r="LU28" s="12" t="n"/>
+      <c r="LV28" s="12" t="n"/>
+      <c r="LW28" s="8" t="n"/>
+      <c r="LX28" s="12" t="n"/>
+      <c r="LY28" s="12" t="n"/>
+      <c r="LZ28" s="12" t="n"/>
+      <c r="MA28" s="12" t="n"/>
+      <c r="MB28" s="8" t="n"/>
+      <c r="MC28" s="12" t="n"/>
+      <c r="MD28" s="12" t="n"/>
+      <c r="ME28" s="12" t="n"/>
+      <c r="MF28" s="12" t="n"/>
+      <c r="MG28" s="8" t="n"/>
+      <c r="MH28" s="12" t="n"/>
+      <c r="MI28" s="12" t="n"/>
+      <c r="MJ28" s="12" t="n"/>
+      <c r="MK28" s="12" t="n"/>
+      <c r="ML28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="4" t="n"/>
@@ -10679,6 +12055,47 @@
       <c r="KR29" s="12" t="n"/>
       <c r="KS29" s="12" t="n"/>
       <c r="KT29" s="7" t="n"/>
+      <c r="KX29" s="4" t="n"/>
+      <c r="KY29" s="6" t="n"/>
+      <c r="KZ29" s="8" t="n"/>
+      <c r="LA29" s="11" t="inlineStr"/>
+      <c r="LB29" s="6" t="n"/>
+      <c r="LC29" s="8" t="n"/>
+      <c r="LD29" s="12" t="n"/>
+      <c r="LE29" s="12" t="n"/>
+      <c r="LF29" s="12" t="n"/>
+      <c r="LG29" s="12" t="n"/>
+      <c r="LH29" s="8" t="n"/>
+      <c r="LI29" s="12" t="n"/>
+      <c r="LJ29" s="12" t="n"/>
+      <c r="LK29" s="12" t="n"/>
+      <c r="LL29" s="12" t="n"/>
+      <c r="LM29" s="8" t="n"/>
+      <c r="LN29" s="12" t="n"/>
+      <c r="LO29" s="12" t="n"/>
+      <c r="LP29" s="12" t="n"/>
+      <c r="LQ29" s="12" t="n"/>
+      <c r="LR29" s="8" t="n"/>
+      <c r="LS29" s="12" t="n"/>
+      <c r="LT29" s="12" t="n"/>
+      <c r="LU29" s="12" t="n"/>
+      <c r="LV29" s="12" t="n"/>
+      <c r="LW29" s="8" t="n"/>
+      <c r="LX29" s="12" t="n"/>
+      <c r="LY29" s="12" t="n"/>
+      <c r="LZ29" s="12" t="n"/>
+      <c r="MA29" s="12" t="n"/>
+      <c r="MB29" s="8" t="n"/>
+      <c r="MC29" s="12" t="n"/>
+      <c r="MD29" s="12" t="n"/>
+      <c r="ME29" s="12" t="n"/>
+      <c r="MF29" s="12" t="n"/>
+      <c r="MG29" s="8" t="n"/>
+      <c r="MH29" s="12" t="n"/>
+      <c r="MI29" s="12" t="n"/>
+      <c r="MJ29" s="12" t="n"/>
+      <c r="MK29" s="12" t="n"/>
+      <c r="ML29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="B30" s="4" t="n"/>
@@ -10968,6 +12385,47 @@
       <c r="KR30" s="12" t="n"/>
       <c r="KS30" s="12" t="n"/>
       <c r="KT30" s="7" t="n"/>
+      <c r="KX30" s="4" t="n"/>
+      <c r="KY30" s="6" t="n"/>
+      <c r="KZ30" s="8" t="n"/>
+      <c r="LA30" s="11" t="inlineStr"/>
+      <c r="LB30" s="6" t="n"/>
+      <c r="LC30" s="8" t="n"/>
+      <c r="LD30" s="12" t="n"/>
+      <c r="LE30" s="12" t="n"/>
+      <c r="LF30" s="12" t="n"/>
+      <c r="LG30" s="12" t="n"/>
+      <c r="LH30" s="8" t="n"/>
+      <c r="LI30" s="12" t="n"/>
+      <c r="LJ30" s="12" t="n"/>
+      <c r="LK30" s="12" t="n"/>
+      <c r="LL30" s="12" t="n"/>
+      <c r="LM30" s="8" t="n"/>
+      <c r="LN30" s="12" t="n"/>
+      <c r="LO30" s="12" t="n"/>
+      <c r="LP30" s="12" t="n"/>
+      <c r="LQ30" s="12" t="n"/>
+      <c r="LR30" s="8" t="n"/>
+      <c r="LS30" s="12" t="n"/>
+      <c r="LT30" s="12" t="n"/>
+      <c r="LU30" s="12" t="n"/>
+      <c r="LV30" s="12" t="n"/>
+      <c r="LW30" s="8" t="n"/>
+      <c r="LX30" s="12" t="n"/>
+      <c r="LY30" s="12" t="n"/>
+      <c r="LZ30" s="12" t="n"/>
+      <c r="MA30" s="12" t="n"/>
+      <c r="MB30" s="8" t="n"/>
+      <c r="MC30" s="12" t="n"/>
+      <c r="MD30" s="12" t="n"/>
+      <c r="ME30" s="12" t="n"/>
+      <c r="MF30" s="12" t="n"/>
+      <c r="MG30" s="8" t="n"/>
+      <c r="MH30" s="12" t="n"/>
+      <c r="MI30" s="12" t="n"/>
+      <c r="MJ30" s="12" t="n"/>
+      <c r="MK30" s="12" t="n"/>
+      <c r="ML30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="B31" s="4" t="n"/>
@@ -11257,6 +12715,47 @@
       <c r="KR31" s="12" t="n"/>
       <c r="KS31" s="12" t="n"/>
       <c r="KT31" s="7" t="n"/>
+      <c r="KX31" s="4" t="n"/>
+      <c r="KY31" s="6" t="n"/>
+      <c r="KZ31" s="8" t="n"/>
+      <c r="LA31" s="11" t="inlineStr"/>
+      <c r="LB31" s="6" t="n"/>
+      <c r="LC31" s="8" t="n"/>
+      <c r="LD31" s="12" t="n"/>
+      <c r="LE31" s="12" t="n"/>
+      <c r="LF31" s="12" t="n"/>
+      <c r="LG31" s="12" t="n"/>
+      <c r="LH31" s="8" t="n"/>
+      <c r="LI31" s="12" t="n"/>
+      <c r="LJ31" s="12" t="n"/>
+      <c r="LK31" s="12" t="n"/>
+      <c r="LL31" s="12" t="n"/>
+      <c r="LM31" s="8" t="n"/>
+      <c r="LN31" s="12" t="n"/>
+      <c r="LO31" s="12" t="n"/>
+      <c r="LP31" s="12" t="n"/>
+      <c r="LQ31" s="12" t="n"/>
+      <c r="LR31" s="8" t="n"/>
+      <c r="LS31" s="12" t="n"/>
+      <c r="LT31" s="12" t="n"/>
+      <c r="LU31" s="12" t="n"/>
+      <c r="LV31" s="12" t="n"/>
+      <c r="LW31" s="8" t="n"/>
+      <c r="LX31" s="12" t="n"/>
+      <c r="LY31" s="12" t="n"/>
+      <c r="LZ31" s="12" t="n"/>
+      <c r="MA31" s="12" t="n"/>
+      <c r="MB31" s="8" t="n"/>
+      <c r="MC31" s="12" t="n"/>
+      <c r="MD31" s="12" t="n"/>
+      <c r="ME31" s="12" t="n"/>
+      <c r="MF31" s="12" t="n"/>
+      <c r="MG31" s="8" t="n"/>
+      <c r="MH31" s="12" t="n"/>
+      <c r="MI31" s="12" t="n"/>
+      <c r="MJ31" s="12" t="n"/>
+      <c r="MK31" s="12" t="n"/>
+      <c r="ML31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="B32" s="4" t="n"/>
@@ -11546,6 +13045,47 @@
       <c r="KR32" s="12" t="n"/>
       <c r="KS32" s="12" t="n"/>
       <c r="KT32" s="7" t="n"/>
+      <c r="KX32" s="4" t="n"/>
+      <c r="KY32" s="6" t="n"/>
+      <c r="KZ32" s="8" t="n"/>
+      <c r="LA32" s="11" t="inlineStr"/>
+      <c r="LB32" s="6" t="n"/>
+      <c r="LC32" s="8" t="n"/>
+      <c r="LD32" s="12" t="n"/>
+      <c r="LE32" s="12" t="n"/>
+      <c r="LF32" s="12" t="n"/>
+      <c r="LG32" s="12" t="n"/>
+      <c r="LH32" s="8" t="n"/>
+      <c r="LI32" s="12" t="n"/>
+      <c r="LJ32" s="12" t="n"/>
+      <c r="LK32" s="12" t="n"/>
+      <c r="LL32" s="12" t="n"/>
+      <c r="LM32" s="8" t="n"/>
+      <c r="LN32" s="12" t="n"/>
+      <c r="LO32" s="12" t="n"/>
+      <c r="LP32" s="12" t="n"/>
+      <c r="LQ32" s="12" t="n"/>
+      <c r="LR32" s="8" t="n"/>
+      <c r="LS32" s="12" t="n"/>
+      <c r="LT32" s="12" t="n"/>
+      <c r="LU32" s="12" t="n"/>
+      <c r="LV32" s="12" t="n"/>
+      <c r="LW32" s="8" t="n"/>
+      <c r="LX32" s="12" t="n"/>
+      <c r="LY32" s="12" t="n"/>
+      <c r="LZ32" s="12" t="n"/>
+      <c r="MA32" s="12" t="n"/>
+      <c r="MB32" s="8" t="n"/>
+      <c r="MC32" s="12" t="n"/>
+      <c r="MD32" s="12" t="n"/>
+      <c r="ME32" s="12" t="n"/>
+      <c r="MF32" s="12" t="n"/>
+      <c r="MG32" s="8" t="n"/>
+      <c r="MH32" s="12" t="n"/>
+      <c r="MI32" s="12" t="n"/>
+      <c r="MJ32" s="12" t="n"/>
+      <c r="MK32" s="12" t="n"/>
+      <c r="ML32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="B33" s="4" t="n"/>
@@ -11835,6 +13375,47 @@
       <c r="KR33" s="12" t="n"/>
       <c r="KS33" s="12" t="n"/>
       <c r="KT33" s="7" t="n"/>
+      <c r="KX33" s="4" t="n"/>
+      <c r="KY33" s="6" t="n"/>
+      <c r="KZ33" s="8" t="n"/>
+      <c r="LA33" s="11" t="inlineStr"/>
+      <c r="LB33" s="6" t="n"/>
+      <c r="LC33" s="8" t="n"/>
+      <c r="LD33" s="12" t="n"/>
+      <c r="LE33" s="12" t="n"/>
+      <c r="LF33" s="12" t="n"/>
+      <c r="LG33" s="12" t="n"/>
+      <c r="LH33" s="8" t="n"/>
+      <c r="LI33" s="12" t="n"/>
+      <c r="LJ33" s="12" t="n"/>
+      <c r="LK33" s="12" t="n"/>
+      <c r="LL33" s="12" t="n"/>
+      <c r="LM33" s="8" t="n"/>
+      <c r="LN33" s="12" t="n"/>
+      <c r="LO33" s="12" t="n"/>
+      <c r="LP33" s="12" t="n"/>
+      <c r="LQ33" s="12" t="n"/>
+      <c r="LR33" s="8" t="n"/>
+      <c r="LS33" s="12" t="n"/>
+      <c r="LT33" s="12" t="n"/>
+      <c r="LU33" s="12" t="n"/>
+      <c r="LV33" s="12" t="n"/>
+      <c r="LW33" s="8" t="n"/>
+      <c r="LX33" s="12" t="n"/>
+      <c r="LY33" s="12" t="n"/>
+      <c r="LZ33" s="12" t="n"/>
+      <c r="MA33" s="12" t="n"/>
+      <c r="MB33" s="8" t="n"/>
+      <c r="MC33" s="12" t="n"/>
+      <c r="MD33" s="12" t="n"/>
+      <c r="ME33" s="12" t="n"/>
+      <c r="MF33" s="12" t="n"/>
+      <c r="MG33" s="8" t="n"/>
+      <c r="MH33" s="12" t="n"/>
+      <c r="MI33" s="12" t="n"/>
+      <c r="MJ33" s="12" t="n"/>
+      <c r="MK33" s="12" t="n"/>
+      <c r="ML33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="B34" s="4" t="n"/>
@@ -12124,6 +13705,47 @@
       <c r="KR34" s="12" t="n"/>
       <c r="KS34" s="12" t="n"/>
       <c r="KT34" s="7" t="n"/>
+      <c r="KX34" s="4" t="n"/>
+      <c r="KY34" s="6" t="n"/>
+      <c r="KZ34" s="8" t="n"/>
+      <c r="LA34" s="11" t="inlineStr"/>
+      <c r="LB34" s="6" t="n"/>
+      <c r="LC34" s="8" t="n"/>
+      <c r="LD34" s="12" t="n"/>
+      <c r="LE34" s="12" t="n"/>
+      <c r="LF34" s="12" t="n"/>
+      <c r="LG34" s="12" t="n"/>
+      <c r="LH34" s="8" t="n"/>
+      <c r="LI34" s="12" t="n"/>
+      <c r="LJ34" s="12" t="n"/>
+      <c r="LK34" s="12" t="n"/>
+      <c r="LL34" s="12" t="n"/>
+      <c r="LM34" s="8" t="n"/>
+      <c r="LN34" s="12" t="n"/>
+      <c r="LO34" s="12" t="n"/>
+      <c r="LP34" s="12" t="n"/>
+      <c r="LQ34" s="12" t="n"/>
+      <c r="LR34" s="8" t="n"/>
+      <c r="LS34" s="12" t="n"/>
+      <c r="LT34" s="12" t="n"/>
+      <c r="LU34" s="12" t="n"/>
+      <c r="LV34" s="12" t="n"/>
+      <c r="LW34" s="8" t="n"/>
+      <c r="LX34" s="12" t="n"/>
+      <c r="LY34" s="12" t="n"/>
+      <c r="LZ34" s="12" t="n"/>
+      <c r="MA34" s="12" t="n"/>
+      <c r="MB34" s="8" t="n"/>
+      <c r="MC34" s="12" t="n"/>
+      <c r="MD34" s="12" t="n"/>
+      <c r="ME34" s="12" t="n"/>
+      <c r="MF34" s="12" t="n"/>
+      <c r="MG34" s="8" t="n"/>
+      <c r="MH34" s="12" t="n"/>
+      <c r="MI34" s="12" t="n"/>
+      <c r="MJ34" s="12" t="n"/>
+      <c r="MK34" s="12" t="n"/>
+      <c r="ML34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="B35" s="4" t="n"/>
@@ -12413,6 +14035,47 @@
       <c r="KR35" s="8" t="n"/>
       <c r="KS35" s="8" t="n"/>
       <c r="KT35" s="7" t="n"/>
+      <c r="KX35" s="4" t="n"/>
+      <c r="KY35" s="8" t="n"/>
+      <c r="KZ35" s="8" t="n"/>
+      <c r="LA35" s="8" t="n"/>
+      <c r="LB35" s="8" t="n"/>
+      <c r="LC35" s="8" t="n"/>
+      <c r="LD35" s="8" t="n"/>
+      <c r="LE35" s="8" t="n"/>
+      <c r="LF35" s="8" t="n"/>
+      <c r="LG35" s="8" t="n"/>
+      <c r="LH35" s="8" t="n"/>
+      <c r="LI35" s="8" t="n"/>
+      <c r="LJ35" s="8" t="n"/>
+      <c r="LK35" s="8" t="n"/>
+      <c r="LL35" s="8" t="n"/>
+      <c r="LM35" s="8" t="n"/>
+      <c r="LN35" s="8" t="n"/>
+      <c r="LO35" s="8" t="n"/>
+      <c r="LP35" s="8" t="n"/>
+      <c r="LQ35" s="8" t="n"/>
+      <c r="LR35" s="8" t="n"/>
+      <c r="LS35" s="8" t="n"/>
+      <c r="LT35" s="8" t="n"/>
+      <c r="LU35" s="8" t="n"/>
+      <c r="LV35" s="8" t="n"/>
+      <c r="LW35" s="8" t="n"/>
+      <c r="LX35" s="8" t="n"/>
+      <c r="LY35" s="8" t="n"/>
+      <c r="LZ35" s="8" t="n"/>
+      <c r="MA35" s="8" t="n"/>
+      <c r="MB35" s="8" t="n"/>
+      <c r="MC35" s="8" t="n"/>
+      <c r="MD35" s="8" t="n"/>
+      <c r="ME35" s="8" t="n"/>
+      <c r="MF35" s="8" t="n"/>
+      <c r="MG35" s="8" t="n"/>
+      <c r="MH35" s="8" t="n"/>
+      <c r="MI35" s="8" t="n"/>
+      <c r="MJ35" s="8" t="n"/>
+      <c r="MK35" s="8" t="n"/>
+      <c r="ML35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="B36" s="4" t="n"/>
@@ -12434,7 +14097,7 @@
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>63.8kg</t>
+          <t>70kg</t>
         </is>
       </c>
       <c r="J36" s="15" t="n">
@@ -12451,7 +14114,7 @@
       </c>
       <c r="N36" s="14" t="inlineStr">
         <is>
-          <t>60kg</t>
+          <t>65kg</t>
         </is>
       </c>
       <c r="O36" s="15" t="n">
@@ -12468,7 +14131,7 @@
       </c>
       <c r="S36" s="14" t="inlineStr">
         <is>
-          <t>60kg</t>
+          <t>65kg</t>
         </is>
       </c>
       <c r="T36" s="15" t="n">
@@ -12485,7 +14148,7 @@
       </c>
       <c r="X36" s="14" t="inlineStr">
         <is>
-          <t>60kg</t>
+          <t>65kg</t>
         </is>
       </c>
       <c r="Y36" s="15" t="n">
@@ -12502,7 +14165,7 @@
       </c>
       <c r="AC36" s="14" t="inlineStr">
         <is>
-          <t>60kg</t>
+          <t>65kg</t>
         </is>
       </c>
       <c r="AD36" s="15" t="n">
@@ -12543,7 +14206,7 @@
       </c>
       <c r="BA36" s="14" t="inlineStr">
         <is>
-          <t>65kg</t>
+          <t>71.2kg</t>
         </is>
       </c>
       <c r="BB36" s="17" t="n">
@@ -12560,7 +14223,7 @@
       </c>
       <c r="BF36" s="14" t="inlineStr">
         <is>
-          <t>61.2kg</t>
+          <t>67.5kg</t>
         </is>
       </c>
       <c r="BG36" s="17" t="n">
@@ -12577,7 +14240,7 @@
       </c>
       <c r="BK36" s="14" t="inlineStr">
         <is>
-          <t>61.2kg</t>
+          <t>67.5kg</t>
         </is>
       </c>
       <c r="BL36" s="17" t="n">
@@ -12594,7 +14257,7 @@
       </c>
       <c r="BP36" s="14" t="inlineStr">
         <is>
-          <t>61.2kg</t>
+          <t>67.5kg</t>
         </is>
       </c>
       <c r="BQ36" s="17" t="n">
@@ -12611,7 +14274,7 @@
       </c>
       <c r="BU36" s="14" t="inlineStr">
         <is>
-          <t>61.2kg</t>
+          <t>67.5kg</t>
         </is>
       </c>
       <c r="BV36" s="17" t="n">
@@ -12652,7 +14315,7 @@
       </c>
       <c r="CS36" s="14" t="inlineStr">
         <is>
-          <t>67.5kg</t>
+          <t>73.8kg</t>
         </is>
       </c>
       <c r="CT36" s="15" t="n">
@@ -12671,7 +14334,7 @@
       </c>
       <c r="CX36" s="14" t="inlineStr">
         <is>
-          <t>61.2kg</t>
+          <t>67.5kg</t>
         </is>
       </c>
       <c r="CY36" s="17" t="n">
@@ -12727,7 +14390,7 @@
       </c>
       <c r="EK36" s="14" t="inlineStr">
         <is>
-          <t>60kg</t>
+          <t>65kg</t>
         </is>
       </c>
       <c r="EL36" s="15" t="n">
@@ -12744,7 +14407,7 @@
       </c>
       <c r="EP36" s="14" t="inlineStr">
         <is>
-          <t>56.2kg</t>
+          <t>61.2kg</t>
         </is>
       </c>
       <c r="EQ36" s="15" t="n">
@@ -12761,7 +14424,7 @@
       </c>
       <c r="EU36" s="14" t="inlineStr">
         <is>
-          <t>56.2kg</t>
+          <t>61.2kg</t>
         </is>
       </c>
       <c r="EV36" s="15" t="n">
@@ -12812,7 +14475,7 @@
       </c>
       <c r="GC36" s="14" t="inlineStr">
         <is>
-          <t>68.8kg</t>
+          <t>76.2kg</t>
         </is>
       </c>
       <c r="GD36" s="17" t="n">
@@ -12831,7 +14494,7 @@
       </c>
       <c r="GH36" s="14" t="inlineStr">
         <is>
-          <t>63.8kg</t>
+          <t>70kg</t>
         </is>
       </c>
       <c r="GI36" s="15" t="n">
@@ -12887,7 +14550,7 @@
       </c>
       <c r="HU36" s="14" t="inlineStr">
         <is>
-          <t>71.2kg</t>
+          <t>77.5kg</t>
         </is>
       </c>
       <c r="HV36" s="15" t="n">
@@ -12904,7 +14567,7 @@
       </c>
       <c r="HZ36" s="14" t="inlineStr">
         <is>
-          <t>65kg</t>
+          <t>71.2kg</t>
         </is>
       </c>
       <c r="IA36" s="17" t="n">
@@ -12921,7 +14584,7 @@
       </c>
       <c r="IE36" s="14" t="inlineStr">
         <is>
-          <t>65kg</t>
+          <t>71.2kg</t>
         </is>
       </c>
       <c r="IF36" s="17" t="n">
@@ -12938,7 +14601,7 @@
       </c>
       <c r="IJ36" s="14" t="inlineStr">
         <is>
-          <t>65kg</t>
+          <t>71.2kg</t>
         </is>
       </c>
       <c r="IK36" s="17" t="n">
@@ -12972,13 +14635,29 @@
         </is>
       </c>
       <c r="JH36" s="8" t="n"/>
-      <c r="JI36" s="11" t="inlineStr"/>
+      <c r="JI36" s="13" t="inlineStr">
+        <is>
+          <t>Weighted Pull-Ups</t>
+        </is>
+      </c>
       <c r="JJ36" s="6" t="n"/>
       <c r="JK36" s="8" t="n"/>
-      <c r="JL36" s="12" t="n"/>
-      <c r="JM36" s="12" t="n"/>
-      <c r="JN36" s="12" t="n"/>
-      <c r="JO36" s="12" t="n"/>
+      <c r="JL36" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="JM36" s="14" t="inlineStr">
+        <is>
+          <t>71.2kg</t>
+        </is>
+      </c>
+      <c r="JN36" s="17" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="JO36" s="16" t="inlineStr">
+        <is>
+          <t>Heavy-ish speed single (≤RPE7). If bar speed is great, you may go up to ~90%. No back-offs.</t>
+        </is>
+      </c>
       <c r="JP36" s="8" t="n"/>
       <c r="JQ36" s="12" t="n"/>
       <c r="JR36" s="12" t="n"/>
@@ -13010,6 +14689,51 @@
       <c r="KR36" s="12" t="n"/>
       <c r="KS36" s="12" t="n"/>
       <c r="KT36" s="7" t="n"/>
+      <c r="KX36" s="4" t="n"/>
+      <c r="KY36" s="10" t="inlineStr">
+        <is>
+          <t>Day 4</t>
+        </is>
+      </c>
+      <c r="KZ36" s="8" t="n"/>
+      <c r="LA36" s="11" t="inlineStr"/>
+      <c r="LB36" s="6" t="n"/>
+      <c r="LC36" s="8" t="n"/>
+      <c r="LD36" s="12" t="n"/>
+      <c r="LE36" s="12" t="n"/>
+      <c r="LF36" s="12" t="n"/>
+      <c r="LG36" s="12" t="n"/>
+      <c r="LH36" s="8" t="n"/>
+      <c r="LI36" s="12" t="n"/>
+      <c r="LJ36" s="12" t="n"/>
+      <c r="LK36" s="12" t="n"/>
+      <c r="LL36" s="12" t="n"/>
+      <c r="LM36" s="8" t="n"/>
+      <c r="LN36" s="12" t="n"/>
+      <c r="LO36" s="12" t="n"/>
+      <c r="LP36" s="12" t="n"/>
+      <c r="LQ36" s="12" t="n"/>
+      <c r="LR36" s="8" t="n"/>
+      <c r="LS36" s="12" t="n"/>
+      <c r="LT36" s="12" t="n"/>
+      <c r="LU36" s="12" t="n"/>
+      <c r="LV36" s="12" t="n"/>
+      <c r="LW36" s="8" t="n"/>
+      <c r="LX36" s="12" t="n"/>
+      <c r="LY36" s="12" t="n"/>
+      <c r="LZ36" s="12" t="n"/>
+      <c r="MA36" s="12" t="n"/>
+      <c r="MB36" s="8" t="n"/>
+      <c r="MC36" s="12" t="n"/>
+      <c r="MD36" s="12" t="n"/>
+      <c r="ME36" s="12" t="n"/>
+      <c r="MF36" s="12" t="n"/>
+      <c r="MG36" s="8" t="n"/>
+      <c r="MH36" s="12" t="n"/>
+      <c r="MI36" s="12" t="n"/>
+      <c r="MJ36" s="12" t="n"/>
+      <c r="MK36" s="12" t="n"/>
+      <c r="ML36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="B37" s="4" t="n"/>
@@ -13027,7 +14751,7 @@
       </c>
       <c r="I37" s="14" t="inlineStr">
         <is>
-          <t>58.8kg</t>
+          <t>63.8kg</t>
         </is>
       </c>
       <c r="J37" s="15" t="n">
@@ -13044,7 +14768,7 @@
       </c>
       <c r="N37" s="14" t="inlineStr">
         <is>
-          <t>58.8kg</t>
+          <t>63.8kg</t>
         </is>
       </c>
       <c r="O37" s="15" t="n">
@@ -13061,7 +14785,7 @@
       </c>
       <c r="S37" s="14" t="inlineStr">
         <is>
-          <t>58.8kg</t>
+          <t>63.8kg</t>
         </is>
       </c>
       <c r="T37" s="15" t="n">
@@ -13078,7 +14802,7 @@
       </c>
       <c r="X37" s="14" t="inlineStr">
         <is>
-          <t>58.8kg</t>
+          <t>63.8kg</t>
         </is>
       </c>
       <c r="Y37" s="15" t="n">
@@ -13120,7 +14844,7 @@
       </c>
       <c r="BA37" s="14" t="inlineStr">
         <is>
-          <t>61.2kg</t>
+          <t>66.2kg</t>
         </is>
       </c>
       <c r="BB37" s="17" t="n">
@@ -13137,7 +14861,7 @@
       </c>
       <c r="BF37" s="14" t="inlineStr">
         <is>
-          <t>61.2kg</t>
+          <t>66.2kg</t>
         </is>
       </c>
       <c r="BG37" s="17" t="n">
@@ -13154,7 +14878,7 @@
       </c>
       <c r="BK37" s="14" t="inlineStr">
         <is>
-          <t>61.2kg</t>
+          <t>66.2kg</t>
         </is>
       </c>
       <c r="BL37" s="17" t="n">
@@ -13171,7 +14895,7 @@
       </c>
       <c r="BP37" s="14" t="inlineStr">
         <is>
-          <t>61.2kg</t>
+          <t>66.2kg</t>
         </is>
       </c>
       <c r="BQ37" s="17" t="n">
@@ -13213,7 +14937,7 @@
       </c>
       <c r="CS37" s="14" t="inlineStr">
         <is>
-          <t>63.8kg</t>
+          <t>68.8kg</t>
         </is>
       </c>
       <c r="CT37" s="15" t="n">
@@ -13230,7 +14954,7 @@
       </c>
       <c r="CX37" s="14" t="inlineStr">
         <is>
-          <t>63.8kg</t>
+          <t>68.8kg</t>
         </is>
       </c>
       <c r="CY37" s="15" t="n">
@@ -13247,7 +14971,7 @@
       </c>
       <c r="DC37" s="14" t="inlineStr">
         <is>
-          <t>63.8kg</t>
+          <t>68.8kg</t>
         </is>
       </c>
       <c r="DD37" s="15" t="n">
@@ -13264,7 +14988,7 @@
       </c>
       <c r="DH37" s="14" t="inlineStr">
         <is>
-          <t>63.8kg</t>
+          <t>68.8kg</t>
         </is>
       </c>
       <c r="DI37" s="15" t="n">
@@ -13306,7 +15030,7 @@
       </c>
       <c r="EK37" s="14" t="inlineStr">
         <is>
-          <t>55kg</t>
+          <t>60kg</t>
         </is>
       </c>
       <c r="EL37" s="15" t="n">
@@ -13323,7 +15047,7 @@
       </c>
       <c r="EP37" s="14" t="inlineStr">
         <is>
-          <t>55kg</t>
+          <t>60kg</t>
         </is>
       </c>
       <c r="EQ37" s="15" t="n">
@@ -13375,7 +15099,7 @@
       </c>
       <c r="GC37" s="14" t="inlineStr">
         <is>
-          <t>58.8kg</t>
+          <t>63.8kg</t>
         </is>
       </c>
       <c r="GD37" s="15" t="n">
@@ -13392,7 +15116,7 @@
       </c>
       <c r="GH37" s="14" t="inlineStr">
         <is>
-          <t>58.8kg</t>
+          <t>63.8kg</t>
         </is>
       </c>
       <c r="GI37" s="15" t="n">
@@ -13409,7 +15133,7 @@
       </c>
       <c r="GM37" s="14" t="inlineStr">
         <is>
-          <t>58.8kg</t>
+          <t>63.8kg</t>
         </is>
       </c>
       <c r="GN37" s="15" t="n">
@@ -13456,7 +15180,7 @@
       </c>
       <c r="HU37" s="14" t="inlineStr">
         <is>
-          <t>58.8kg</t>
+          <t>63.8kg</t>
         </is>
       </c>
       <c r="HV37" s="15" t="n">
@@ -13473,7 +15197,7 @@
       </c>
       <c r="HZ37" s="14" t="inlineStr">
         <is>
-          <t>58.8kg</t>
+          <t>63.8kg</t>
         </is>
       </c>
       <c r="IA37" s="15" t="n">
@@ -13490,7 +15214,7 @@
       </c>
       <c r="IE37" s="14" t="inlineStr">
         <is>
-          <t>58.8kg</t>
+          <t>63.8kg</t>
         </is>
       </c>
       <c r="IF37" s="15" t="n">
@@ -13525,13 +15249,29 @@
       <c r="JF37" s="4" t="n"/>
       <c r="JG37" s="6" t="n"/>
       <c r="JH37" s="8" t="n"/>
-      <c r="JI37" s="11" t="inlineStr"/>
+      <c r="JI37" s="13" t="inlineStr">
+        <is>
+          <t>Weighted Dips</t>
+        </is>
+      </c>
       <c r="JJ37" s="6" t="n"/>
       <c r="JK37" s="8" t="n"/>
-      <c r="JL37" s="12" t="n"/>
-      <c r="JM37" s="12" t="n"/>
-      <c r="JN37" s="12" t="n"/>
-      <c r="JO37" s="12" t="n"/>
+      <c r="JL37" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="JM37" s="14" t="inlineStr">
+        <is>
+          <t>80kg</t>
+        </is>
+      </c>
+      <c r="JN37" s="17" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="JO37" s="16" t="inlineStr">
+        <is>
+          <t>Heavy-ish speed single (≤RPE7). If bar speed is great, you may go up to ~90%. No back-offs.</t>
+        </is>
+      </c>
       <c r="JP37" s="8" t="n"/>
       <c r="JQ37" s="12" t="n"/>
       <c r="JR37" s="12" t="n"/>
@@ -13563,6 +15303,47 @@
       <c r="KR37" s="12" t="n"/>
       <c r="KS37" s="12" t="n"/>
       <c r="KT37" s="7" t="n"/>
+      <c r="KX37" s="4" t="n"/>
+      <c r="KY37" s="6" t="n"/>
+      <c r="KZ37" s="8" t="n"/>
+      <c r="LA37" s="11" t="inlineStr"/>
+      <c r="LB37" s="6" t="n"/>
+      <c r="LC37" s="8" t="n"/>
+      <c r="LD37" s="12" t="n"/>
+      <c r="LE37" s="12" t="n"/>
+      <c r="LF37" s="12" t="n"/>
+      <c r="LG37" s="12" t="n"/>
+      <c r="LH37" s="8" t="n"/>
+      <c r="LI37" s="12" t="n"/>
+      <c r="LJ37" s="12" t="n"/>
+      <c r="LK37" s="12" t="n"/>
+      <c r="LL37" s="12" t="n"/>
+      <c r="LM37" s="8" t="n"/>
+      <c r="LN37" s="12" t="n"/>
+      <c r="LO37" s="12" t="n"/>
+      <c r="LP37" s="12" t="n"/>
+      <c r="LQ37" s="12" t="n"/>
+      <c r="LR37" s="8" t="n"/>
+      <c r="LS37" s="12" t="n"/>
+      <c r="LT37" s="12" t="n"/>
+      <c r="LU37" s="12" t="n"/>
+      <c r="LV37" s="12" t="n"/>
+      <c r="LW37" s="8" t="n"/>
+      <c r="LX37" s="12" t="n"/>
+      <c r="LY37" s="12" t="n"/>
+      <c r="LZ37" s="12" t="n"/>
+      <c r="MA37" s="12" t="n"/>
+      <c r="MB37" s="8" t="n"/>
+      <c r="MC37" s="12" t="n"/>
+      <c r="MD37" s="12" t="n"/>
+      <c r="ME37" s="12" t="n"/>
+      <c r="MF37" s="12" t="n"/>
+      <c r="MG37" s="8" t="n"/>
+      <c r="MH37" s="12" t="n"/>
+      <c r="MI37" s="12" t="n"/>
+      <c r="MJ37" s="12" t="n"/>
+      <c r="MK37" s="12" t="n"/>
+      <c r="ML37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="B38" s="4" t="n"/>
@@ -13900,6 +15681,47 @@
       <c r="KR38" s="12" t="n"/>
       <c r="KS38" s="12" t="n"/>
       <c r="KT38" s="7" t="n"/>
+      <c r="KX38" s="4" t="n"/>
+      <c r="KY38" s="6" t="n"/>
+      <c r="KZ38" s="8" t="n"/>
+      <c r="LA38" s="11" t="inlineStr"/>
+      <c r="LB38" s="6" t="n"/>
+      <c r="LC38" s="8" t="n"/>
+      <c r="LD38" s="12" t="n"/>
+      <c r="LE38" s="12" t="n"/>
+      <c r="LF38" s="12" t="n"/>
+      <c r="LG38" s="12" t="n"/>
+      <c r="LH38" s="8" t="n"/>
+      <c r="LI38" s="12" t="n"/>
+      <c r="LJ38" s="12" t="n"/>
+      <c r="LK38" s="12" t="n"/>
+      <c r="LL38" s="12" t="n"/>
+      <c r="LM38" s="8" t="n"/>
+      <c r="LN38" s="12" t="n"/>
+      <c r="LO38" s="12" t="n"/>
+      <c r="LP38" s="12" t="n"/>
+      <c r="LQ38" s="12" t="n"/>
+      <c r="LR38" s="8" t="n"/>
+      <c r="LS38" s="12" t="n"/>
+      <c r="LT38" s="12" t="n"/>
+      <c r="LU38" s="12" t="n"/>
+      <c r="LV38" s="12" t="n"/>
+      <c r="LW38" s="8" t="n"/>
+      <c r="LX38" s="12" t="n"/>
+      <c r="LY38" s="12" t="n"/>
+      <c r="LZ38" s="12" t="n"/>
+      <c r="MA38" s="12" t="n"/>
+      <c r="MB38" s="8" t="n"/>
+      <c r="MC38" s="12" t="n"/>
+      <c r="MD38" s="12" t="n"/>
+      <c r="ME38" s="12" t="n"/>
+      <c r="MF38" s="12" t="n"/>
+      <c r="MG38" s="8" t="n"/>
+      <c r="MH38" s="12" t="n"/>
+      <c r="MI38" s="12" t="n"/>
+      <c r="MJ38" s="12" t="n"/>
+      <c r="MK38" s="12" t="n"/>
+      <c r="ML38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="B39" s="4" t="n"/>
@@ -14189,6 +16011,47 @@
       <c r="KR39" s="12" t="n"/>
       <c r="KS39" s="12" t="n"/>
       <c r="KT39" s="7" t="n"/>
+      <c r="KX39" s="4" t="n"/>
+      <c r="KY39" s="6" t="n"/>
+      <c r="KZ39" s="8" t="n"/>
+      <c r="LA39" s="11" t="inlineStr"/>
+      <c r="LB39" s="6" t="n"/>
+      <c r="LC39" s="8" t="n"/>
+      <c r="LD39" s="12" t="n"/>
+      <c r="LE39" s="12" t="n"/>
+      <c r="LF39" s="12" t="n"/>
+      <c r="LG39" s="12" t="n"/>
+      <c r="LH39" s="8" t="n"/>
+      <c r="LI39" s="12" t="n"/>
+      <c r="LJ39" s="12" t="n"/>
+      <c r="LK39" s="12" t="n"/>
+      <c r="LL39" s="12" t="n"/>
+      <c r="LM39" s="8" t="n"/>
+      <c r="LN39" s="12" t="n"/>
+      <c r="LO39" s="12" t="n"/>
+      <c r="LP39" s="12" t="n"/>
+      <c r="LQ39" s="12" t="n"/>
+      <c r="LR39" s="8" t="n"/>
+      <c r="LS39" s="12" t="n"/>
+      <c r="LT39" s="12" t="n"/>
+      <c r="LU39" s="12" t="n"/>
+      <c r="LV39" s="12" t="n"/>
+      <c r="LW39" s="8" t="n"/>
+      <c r="LX39" s="12" t="n"/>
+      <c r="LY39" s="12" t="n"/>
+      <c r="LZ39" s="12" t="n"/>
+      <c r="MA39" s="12" t="n"/>
+      <c r="MB39" s="8" t="n"/>
+      <c r="MC39" s="12" t="n"/>
+      <c r="MD39" s="12" t="n"/>
+      <c r="ME39" s="12" t="n"/>
+      <c r="MF39" s="12" t="n"/>
+      <c r="MG39" s="8" t="n"/>
+      <c r="MH39" s="12" t="n"/>
+      <c r="MI39" s="12" t="n"/>
+      <c r="MJ39" s="12" t="n"/>
+      <c r="MK39" s="12" t="n"/>
+      <c r="ML39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="B40" s="4" t="n"/>
@@ -14478,6 +16341,47 @@
       <c r="KR40" s="12" t="n"/>
       <c r="KS40" s="12" t="n"/>
       <c r="KT40" s="7" t="n"/>
+      <c r="KX40" s="4" t="n"/>
+      <c r="KY40" s="6" t="n"/>
+      <c r="KZ40" s="8" t="n"/>
+      <c r="LA40" s="11" t="inlineStr"/>
+      <c r="LB40" s="6" t="n"/>
+      <c r="LC40" s="8" t="n"/>
+      <c r="LD40" s="12" t="n"/>
+      <c r="LE40" s="12" t="n"/>
+      <c r="LF40" s="12" t="n"/>
+      <c r="LG40" s="12" t="n"/>
+      <c r="LH40" s="8" t="n"/>
+      <c r="LI40" s="12" t="n"/>
+      <c r="LJ40" s="12" t="n"/>
+      <c r="LK40" s="12" t="n"/>
+      <c r="LL40" s="12" t="n"/>
+      <c r="LM40" s="8" t="n"/>
+      <c r="LN40" s="12" t="n"/>
+      <c r="LO40" s="12" t="n"/>
+      <c r="LP40" s="12" t="n"/>
+      <c r="LQ40" s="12" t="n"/>
+      <c r="LR40" s="8" t="n"/>
+      <c r="LS40" s="12" t="n"/>
+      <c r="LT40" s="12" t="n"/>
+      <c r="LU40" s="12" t="n"/>
+      <c r="LV40" s="12" t="n"/>
+      <c r="LW40" s="8" t="n"/>
+      <c r="LX40" s="12" t="n"/>
+      <c r="LY40" s="12" t="n"/>
+      <c r="LZ40" s="12" t="n"/>
+      <c r="MA40" s="12" t="n"/>
+      <c r="MB40" s="8" t="n"/>
+      <c r="MC40" s="12" t="n"/>
+      <c r="MD40" s="12" t="n"/>
+      <c r="ME40" s="12" t="n"/>
+      <c r="MF40" s="12" t="n"/>
+      <c r="MG40" s="8" t="n"/>
+      <c r="MH40" s="12" t="n"/>
+      <c r="MI40" s="12" t="n"/>
+      <c r="MJ40" s="12" t="n"/>
+      <c r="MK40" s="12" t="n"/>
+      <c r="ML40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="B41" s="4" t="n"/>
@@ -14767,6 +16671,47 @@
       <c r="KR41" s="12" t="n"/>
       <c r="KS41" s="12" t="n"/>
       <c r="KT41" s="7" t="n"/>
+      <c r="KX41" s="4" t="n"/>
+      <c r="KY41" s="6" t="n"/>
+      <c r="KZ41" s="8" t="n"/>
+      <c r="LA41" s="11" t="inlineStr"/>
+      <c r="LB41" s="6" t="n"/>
+      <c r="LC41" s="8" t="n"/>
+      <c r="LD41" s="12" t="n"/>
+      <c r="LE41" s="12" t="n"/>
+      <c r="LF41" s="12" t="n"/>
+      <c r="LG41" s="12" t="n"/>
+      <c r="LH41" s="8" t="n"/>
+      <c r="LI41" s="12" t="n"/>
+      <c r="LJ41" s="12" t="n"/>
+      <c r="LK41" s="12" t="n"/>
+      <c r="LL41" s="12" t="n"/>
+      <c r="LM41" s="8" t="n"/>
+      <c r="LN41" s="12" t="n"/>
+      <c r="LO41" s="12" t="n"/>
+      <c r="LP41" s="12" t="n"/>
+      <c r="LQ41" s="12" t="n"/>
+      <c r="LR41" s="8" t="n"/>
+      <c r="LS41" s="12" t="n"/>
+      <c r="LT41" s="12" t="n"/>
+      <c r="LU41" s="12" t="n"/>
+      <c r="LV41" s="12" t="n"/>
+      <c r="LW41" s="8" t="n"/>
+      <c r="LX41" s="12" t="n"/>
+      <c r="LY41" s="12" t="n"/>
+      <c r="LZ41" s="12" t="n"/>
+      <c r="MA41" s="12" t="n"/>
+      <c r="MB41" s="8" t="n"/>
+      <c r="MC41" s="12" t="n"/>
+      <c r="MD41" s="12" t="n"/>
+      <c r="ME41" s="12" t="n"/>
+      <c r="MF41" s="12" t="n"/>
+      <c r="MG41" s="8" t="n"/>
+      <c r="MH41" s="12" t="n"/>
+      <c r="MI41" s="12" t="n"/>
+      <c r="MJ41" s="12" t="n"/>
+      <c r="MK41" s="12" t="n"/>
+      <c r="ML41" s="7" t="n"/>
     </row>
     <row r="42">
       <c r="B42" s="4" t="n"/>
@@ -15056,6 +17001,47 @@
       <c r="KR42" s="12" t="n"/>
       <c r="KS42" s="12" t="n"/>
       <c r="KT42" s="7" t="n"/>
+      <c r="KX42" s="4" t="n"/>
+      <c r="KY42" s="6" t="n"/>
+      <c r="KZ42" s="8" t="n"/>
+      <c r="LA42" s="11" t="inlineStr"/>
+      <c r="LB42" s="6" t="n"/>
+      <c r="LC42" s="8" t="n"/>
+      <c r="LD42" s="12" t="n"/>
+      <c r="LE42" s="12" t="n"/>
+      <c r="LF42" s="12" t="n"/>
+      <c r="LG42" s="12" t="n"/>
+      <c r="LH42" s="8" t="n"/>
+      <c r="LI42" s="12" t="n"/>
+      <c r="LJ42" s="12" t="n"/>
+      <c r="LK42" s="12" t="n"/>
+      <c r="LL42" s="12" t="n"/>
+      <c r="LM42" s="8" t="n"/>
+      <c r="LN42" s="12" t="n"/>
+      <c r="LO42" s="12" t="n"/>
+      <c r="LP42" s="12" t="n"/>
+      <c r="LQ42" s="12" t="n"/>
+      <c r="LR42" s="8" t="n"/>
+      <c r="LS42" s="12" t="n"/>
+      <c r="LT42" s="12" t="n"/>
+      <c r="LU42" s="12" t="n"/>
+      <c r="LV42" s="12" t="n"/>
+      <c r="LW42" s="8" t="n"/>
+      <c r="LX42" s="12" t="n"/>
+      <c r="LY42" s="12" t="n"/>
+      <c r="LZ42" s="12" t="n"/>
+      <c r="MA42" s="12" t="n"/>
+      <c r="MB42" s="8" t="n"/>
+      <c r="MC42" s="12" t="n"/>
+      <c r="MD42" s="12" t="n"/>
+      <c r="ME42" s="12" t="n"/>
+      <c r="MF42" s="12" t="n"/>
+      <c r="MG42" s="8" t="n"/>
+      <c r="MH42" s="12" t="n"/>
+      <c r="MI42" s="12" t="n"/>
+      <c r="MJ42" s="12" t="n"/>
+      <c r="MK42" s="12" t="n"/>
+      <c r="ML42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="B43" s="4" t="n"/>
@@ -15345,6 +17331,47 @@
       <c r="KR43" s="12" t="n"/>
       <c r="KS43" s="12" t="n"/>
       <c r="KT43" s="7" t="n"/>
+      <c r="KX43" s="4" t="n"/>
+      <c r="KY43" s="6" t="n"/>
+      <c r="KZ43" s="8" t="n"/>
+      <c r="LA43" s="11" t="inlineStr"/>
+      <c r="LB43" s="6" t="n"/>
+      <c r="LC43" s="8" t="n"/>
+      <c r="LD43" s="12" t="n"/>
+      <c r="LE43" s="12" t="n"/>
+      <c r="LF43" s="12" t="n"/>
+      <c r="LG43" s="12" t="n"/>
+      <c r="LH43" s="8" t="n"/>
+      <c r="LI43" s="12" t="n"/>
+      <c r="LJ43" s="12" t="n"/>
+      <c r="LK43" s="12" t="n"/>
+      <c r="LL43" s="12" t="n"/>
+      <c r="LM43" s="8" t="n"/>
+      <c r="LN43" s="12" t="n"/>
+      <c r="LO43" s="12" t="n"/>
+      <c r="LP43" s="12" t="n"/>
+      <c r="LQ43" s="12" t="n"/>
+      <c r="LR43" s="8" t="n"/>
+      <c r="LS43" s="12" t="n"/>
+      <c r="LT43" s="12" t="n"/>
+      <c r="LU43" s="12" t="n"/>
+      <c r="LV43" s="12" t="n"/>
+      <c r="LW43" s="8" t="n"/>
+      <c r="LX43" s="12" t="n"/>
+      <c r="LY43" s="12" t="n"/>
+      <c r="LZ43" s="12" t="n"/>
+      <c r="MA43" s="12" t="n"/>
+      <c r="MB43" s="8" t="n"/>
+      <c r="MC43" s="12" t="n"/>
+      <c r="MD43" s="12" t="n"/>
+      <c r="ME43" s="12" t="n"/>
+      <c r="MF43" s="12" t="n"/>
+      <c r="MG43" s="8" t="n"/>
+      <c r="MH43" s="12" t="n"/>
+      <c r="MI43" s="12" t="n"/>
+      <c r="MJ43" s="12" t="n"/>
+      <c r="MK43" s="12" t="n"/>
+      <c r="ML43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="B44" s="4" t="n"/>
@@ -15634,6 +17661,47 @@
       <c r="KR44" s="8" t="n"/>
       <c r="KS44" s="8" t="n"/>
       <c r="KT44" s="7" t="n"/>
+      <c r="KX44" s="4" t="n"/>
+      <c r="KY44" s="8" t="n"/>
+      <c r="KZ44" s="8" t="n"/>
+      <c r="LA44" s="8" t="n"/>
+      <c r="LB44" s="8" t="n"/>
+      <c r="LC44" s="8" t="n"/>
+      <c r="LD44" s="8" t="n"/>
+      <c r="LE44" s="8" t="n"/>
+      <c r="LF44" s="8" t="n"/>
+      <c r="LG44" s="8" t="n"/>
+      <c r="LH44" s="8" t="n"/>
+      <c r="LI44" s="8" t="n"/>
+      <c r="LJ44" s="8" t="n"/>
+      <c r="LK44" s="8" t="n"/>
+      <c r="LL44" s="8" t="n"/>
+      <c r="LM44" s="8" t="n"/>
+      <c r="LN44" s="8" t="n"/>
+      <c r="LO44" s="8" t="n"/>
+      <c r="LP44" s="8" t="n"/>
+      <c r="LQ44" s="8" t="n"/>
+      <c r="LR44" s="8" t="n"/>
+      <c r="LS44" s="8" t="n"/>
+      <c r="LT44" s="8" t="n"/>
+      <c r="LU44" s="8" t="n"/>
+      <c r="LV44" s="8" t="n"/>
+      <c r="LW44" s="8" t="n"/>
+      <c r="LX44" s="8" t="n"/>
+      <c r="LY44" s="8" t="n"/>
+      <c r="LZ44" s="8" t="n"/>
+      <c r="MA44" s="8" t="n"/>
+      <c r="MB44" s="8" t="n"/>
+      <c r="MC44" s="8" t="n"/>
+      <c r="MD44" s="8" t="n"/>
+      <c r="ME44" s="8" t="n"/>
+      <c r="MF44" s="8" t="n"/>
+      <c r="MG44" s="8" t="n"/>
+      <c r="MH44" s="8" t="n"/>
+      <c r="MI44" s="8" t="n"/>
+      <c r="MJ44" s="8" t="n"/>
+      <c r="MK44" s="8" t="n"/>
+      <c r="ML44" s="7" t="n"/>
     </row>
     <row r="45">
       <c r="B45" s="4" t="n"/>
@@ -15951,6 +18019,103 @@
       <c r="KR45" s="12" t="n"/>
       <c r="KS45" s="12" t="n"/>
       <c r="KT45" s="7" t="n"/>
+      <c r="KX45" s="4" t="n"/>
+      <c r="KY45" s="10" t="inlineStr">
+        <is>
+          <t>Day 5</t>
+        </is>
+      </c>
+      <c r="KZ45" s="8" t="n"/>
+      <c r="LA45" s="13" t="inlineStr">
+        <is>
+          <t>Weighted Dips</t>
+        </is>
+      </c>
+      <c r="LB45" s="6" t="n"/>
+      <c r="LC45" s="8" t="n"/>
+      <c r="LD45" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="LE45" s="14" t="inlineStr">
+        <is>
+          <t>82.5kg</t>
+        </is>
+      </c>
+      <c r="LF45" s="15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="LG45" s="16" t="inlineStr">
+        <is>
+          <t>Warm-up single</t>
+        </is>
+      </c>
+      <c r="LH45" s="8" t="n"/>
+      <c r="LI45" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="LJ45" s="14" t="inlineStr">
+        <is>
+          <t>87.5kg</t>
+        </is>
+      </c>
+      <c r="LK45" s="15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="LL45" s="16" t="inlineStr">
+        <is>
+          <t>Opener</t>
+        </is>
+      </c>
+      <c r="LM45" s="8" t="n"/>
+      <c r="LN45" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="LO45" s="14" t="inlineStr">
+        <is>
+          <t>92.5kg</t>
+        </is>
+      </c>
+      <c r="LP45" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="LQ45" s="16" t="inlineStr">
+        <is>
+          <t>Second (match PB)</t>
+        </is>
+      </c>
+      <c r="LR45" s="8" t="n"/>
+      <c r="LS45" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="LT45" s="14" t="inlineStr">
+        <is>
+          <t>93.8kg</t>
+        </is>
+      </c>
+      <c r="LU45" s="15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="LV45" s="16" t="inlineStr">
+        <is>
+          <t>Third (102–103% only if second was clean)</t>
+        </is>
+      </c>
+      <c r="LW45" s="8" t="n"/>
+      <c r="LX45" s="12" t="n"/>
+      <c r="LY45" s="12" t="n"/>
+      <c r="LZ45" s="12" t="n"/>
+      <c r="MA45" s="12" t="n"/>
+      <c r="MB45" s="8" t="n"/>
+      <c r="MC45" s="12" t="n"/>
+      <c r="MD45" s="12" t="n"/>
+      <c r="ME45" s="12" t="n"/>
+      <c r="MF45" s="12" t="n"/>
+      <c r="MG45" s="8" t="n"/>
+      <c r="MH45" s="12" t="n"/>
+      <c r="MI45" s="12" t="n"/>
+      <c r="MJ45" s="12" t="n"/>
+      <c r="MK45" s="12" t="n"/>
+      <c r="ML45" s="7" t="n"/>
     </row>
     <row r="46">
       <c r="B46" s="4" t="n"/>
@@ -16240,6 +18405,47 @@
       <c r="KR46" s="12" t="n"/>
       <c r="KS46" s="12" t="n"/>
       <c r="KT46" s="7" t="n"/>
+      <c r="KX46" s="4" t="n"/>
+      <c r="KY46" s="6" t="n"/>
+      <c r="KZ46" s="8" t="n"/>
+      <c r="LA46" s="11" t="inlineStr"/>
+      <c r="LB46" s="6" t="n"/>
+      <c r="LC46" s="8" t="n"/>
+      <c r="LD46" s="12" t="n"/>
+      <c r="LE46" s="12" t="n"/>
+      <c r="LF46" s="12" t="n"/>
+      <c r="LG46" s="12" t="n"/>
+      <c r="LH46" s="8" t="n"/>
+      <c r="LI46" s="12" t="n"/>
+      <c r="LJ46" s="12" t="n"/>
+      <c r="LK46" s="12" t="n"/>
+      <c r="LL46" s="12" t="n"/>
+      <c r="LM46" s="8" t="n"/>
+      <c r="LN46" s="12" t="n"/>
+      <c r="LO46" s="12" t="n"/>
+      <c r="LP46" s="12" t="n"/>
+      <c r="LQ46" s="12" t="n"/>
+      <c r="LR46" s="8" t="n"/>
+      <c r="LS46" s="12" t="n"/>
+      <c r="LT46" s="12" t="n"/>
+      <c r="LU46" s="12" t="n"/>
+      <c r="LV46" s="12" t="n"/>
+      <c r="LW46" s="8" t="n"/>
+      <c r="LX46" s="12" t="n"/>
+      <c r="LY46" s="12" t="n"/>
+      <c r="LZ46" s="12" t="n"/>
+      <c r="MA46" s="12" t="n"/>
+      <c r="MB46" s="8" t="n"/>
+      <c r="MC46" s="12" t="n"/>
+      <c r="MD46" s="12" t="n"/>
+      <c r="ME46" s="12" t="n"/>
+      <c r="MF46" s="12" t="n"/>
+      <c r="MG46" s="8" t="n"/>
+      <c r="MH46" s="12" t="n"/>
+      <c r="MI46" s="12" t="n"/>
+      <c r="MJ46" s="12" t="n"/>
+      <c r="MK46" s="12" t="n"/>
+      <c r="ML46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="B47" s="4" t="n"/>
@@ -16529,6 +18735,47 @@
       <c r="KR47" s="12" t="n"/>
       <c r="KS47" s="12" t="n"/>
       <c r="KT47" s="7" t="n"/>
+      <c r="KX47" s="4" t="n"/>
+      <c r="KY47" s="6" t="n"/>
+      <c r="KZ47" s="8" t="n"/>
+      <c r="LA47" s="11" t="inlineStr"/>
+      <c r="LB47" s="6" t="n"/>
+      <c r="LC47" s="8" t="n"/>
+      <c r="LD47" s="12" t="n"/>
+      <c r="LE47" s="12" t="n"/>
+      <c r="LF47" s="12" t="n"/>
+      <c r="LG47" s="12" t="n"/>
+      <c r="LH47" s="8" t="n"/>
+      <c r="LI47" s="12" t="n"/>
+      <c r="LJ47" s="12" t="n"/>
+      <c r="LK47" s="12" t="n"/>
+      <c r="LL47" s="12" t="n"/>
+      <c r="LM47" s="8" t="n"/>
+      <c r="LN47" s="12" t="n"/>
+      <c r="LO47" s="12" t="n"/>
+      <c r="LP47" s="12" t="n"/>
+      <c r="LQ47" s="12" t="n"/>
+      <c r="LR47" s="8" t="n"/>
+      <c r="LS47" s="12" t="n"/>
+      <c r="LT47" s="12" t="n"/>
+      <c r="LU47" s="12" t="n"/>
+      <c r="LV47" s="12" t="n"/>
+      <c r="LW47" s="8" t="n"/>
+      <c r="LX47" s="12" t="n"/>
+      <c r="LY47" s="12" t="n"/>
+      <c r="LZ47" s="12" t="n"/>
+      <c r="MA47" s="12" t="n"/>
+      <c r="MB47" s="8" t="n"/>
+      <c r="MC47" s="12" t="n"/>
+      <c r="MD47" s="12" t="n"/>
+      <c r="ME47" s="12" t="n"/>
+      <c r="MF47" s="12" t="n"/>
+      <c r="MG47" s="8" t="n"/>
+      <c r="MH47" s="12" t="n"/>
+      <c r="MI47" s="12" t="n"/>
+      <c r="MJ47" s="12" t="n"/>
+      <c r="MK47" s="12" t="n"/>
+      <c r="ML47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="B48" s="4" t="n"/>
@@ -16818,6 +19065,47 @@
       <c r="KR48" s="12" t="n"/>
       <c r="KS48" s="12" t="n"/>
       <c r="KT48" s="7" t="n"/>
+      <c r="KX48" s="4" t="n"/>
+      <c r="KY48" s="6" t="n"/>
+      <c r="KZ48" s="8" t="n"/>
+      <c r="LA48" s="11" t="inlineStr"/>
+      <c r="LB48" s="6" t="n"/>
+      <c r="LC48" s="8" t="n"/>
+      <c r="LD48" s="12" t="n"/>
+      <c r="LE48" s="12" t="n"/>
+      <c r="LF48" s="12" t="n"/>
+      <c r="LG48" s="12" t="n"/>
+      <c r="LH48" s="8" t="n"/>
+      <c r="LI48" s="12" t="n"/>
+      <c r="LJ48" s="12" t="n"/>
+      <c r="LK48" s="12" t="n"/>
+      <c r="LL48" s="12" t="n"/>
+      <c r="LM48" s="8" t="n"/>
+      <c r="LN48" s="12" t="n"/>
+      <c r="LO48" s="12" t="n"/>
+      <c r="LP48" s="12" t="n"/>
+      <c r="LQ48" s="12" t="n"/>
+      <c r="LR48" s="8" t="n"/>
+      <c r="LS48" s="12" t="n"/>
+      <c r="LT48" s="12" t="n"/>
+      <c r="LU48" s="12" t="n"/>
+      <c r="LV48" s="12" t="n"/>
+      <c r="LW48" s="8" t="n"/>
+      <c r="LX48" s="12" t="n"/>
+      <c r="LY48" s="12" t="n"/>
+      <c r="LZ48" s="12" t="n"/>
+      <c r="MA48" s="12" t="n"/>
+      <c r="MB48" s="8" t="n"/>
+      <c r="MC48" s="12" t="n"/>
+      <c r="MD48" s="12" t="n"/>
+      <c r="ME48" s="12" t="n"/>
+      <c r="MF48" s="12" t="n"/>
+      <c r="MG48" s="8" t="n"/>
+      <c r="MH48" s="12" t="n"/>
+      <c r="MI48" s="12" t="n"/>
+      <c r="MJ48" s="12" t="n"/>
+      <c r="MK48" s="12" t="n"/>
+      <c r="ML48" s="7" t="n"/>
     </row>
     <row r="49">
       <c r="B49" s="4" t="n"/>
@@ -17107,6 +19395,47 @@
       <c r="KR49" s="12" t="n"/>
       <c r="KS49" s="12" t="n"/>
       <c r="KT49" s="7" t="n"/>
+      <c r="KX49" s="4" t="n"/>
+      <c r="KY49" s="6" t="n"/>
+      <c r="KZ49" s="8" t="n"/>
+      <c r="LA49" s="11" t="inlineStr"/>
+      <c r="LB49" s="6" t="n"/>
+      <c r="LC49" s="8" t="n"/>
+      <c r="LD49" s="12" t="n"/>
+      <c r="LE49" s="12" t="n"/>
+      <c r="LF49" s="12" t="n"/>
+      <c r="LG49" s="12" t="n"/>
+      <c r="LH49" s="8" t="n"/>
+      <c r="LI49" s="12" t="n"/>
+      <c r="LJ49" s="12" t="n"/>
+      <c r="LK49" s="12" t="n"/>
+      <c r="LL49" s="12" t="n"/>
+      <c r="LM49" s="8" t="n"/>
+      <c r="LN49" s="12" t="n"/>
+      <c r="LO49" s="12" t="n"/>
+      <c r="LP49" s="12" t="n"/>
+      <c r="LQ49" s="12" t="n"/>
+      <c r="LR49" s="8" t="n"/>
+      <c r="LS49" s="12" t="n"/>
+      <c r="LT49" s="12" t="n"/>
+      <c r="LU49" s="12" t="n"/>
+      <c r="LV49" s="12" t="n"/>
+      <c r="LW49" s="8" t="n"/>
+      <c r="LX49" s="12" t="n"/>
+      <c r="LY49" s="12" t="n"/>
+      <c r="LZ49" s="12" t="n"/>
+      <c r="MA49" s="12" t="n"/>
+      <c r="MB49" s="8" t="n"/>
+      <c r="MC49" s="12" t="n"/>
+      <c r="MD49" s="12" t="n"/>
+      <c r="ME49" s="12" t="n"/>
+      <c r="MF49" s="12" t="n"/>
+      <c r="MG49" s="8" t="n"/>
+      <c r="MH49" s="12" t="n"/>
+      <c r="MI49" s="12" t="n"/>
+      <c r="MJ49" s="12" t="n"/>
+      <c r="MK49" s="12" t="n"/>
+      <c r="ML49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="B50" s="4" t="n"/>
@@ -17396,6 +19725,47 @@
       <c r="KR50" s="12" t="n"/>
       <c r="KS50" s="12" t="n"/>
       <c r="KT50" s="7" t="n"/>
+      <c r="KX50" s="4" t="n"/>
+      <c r="KY50" s="6" t="n"/>
+      <c r="KZ50" s="8" t="n"/>
+      <c r="LA50" s="11" t="inlineStr"/>
+      <c r="LB50" s="6" t="n"/>
+      <c r="LC50" s="8" t="n"/>
+      <c r="LD50" s="12" t="n"/>
+      <c r="LE50" s="12" t="n"/>
+      <c r="LF50" s="12" t="n"/>
+      <c r="LG50" s="12" t="n"/>
+      <c r="LH50" s="8" t="n"/>
+      <c r="LI50" s="12" t="n"/>
+      <c r="LJ50" s="12" t="n"/>
+      <c r="LK50" s="12" t="n"/>
+      <c r="LL50" s="12" t="n"/>
+      <c r="LM50" s="8" t="n"/>
+      <c r="LN50" s="12" t="n"/>
+      <c r="LO50" s="12" t="n"/>
+      <c r="LP50" s="12" t="n"/>
+      <c r="LQ50" s="12" t="n"/>
+      <c r="LR50" s="8" t="n"/>
+      <c r="LS50" s="12" t="n"/>
+      <c r="LT50" s="12" t="n"/>
+      <c r="LU50" s="12" t="n"/>
+      <c r="LV50" s="12" t="n"/>
+      <c r="LW50" s="8" t="n"/>
+      <c r="LX50" s="12" t="n"/>
+      <c r="LY50" s="12" t="n"/>
+      <c r="LZ50" s="12" t="n"/>
+      <c r="MA50" s="12" t="n"/>
+      <c r="MB50" s="8" t="n"/>
+      <c r="MC50" s="12" t="n"/>
+      <c r="MD50" s="12" t="n"/>
+      <c r="ME50" s="12" t="n"/>
+      <c r="MF50" s="12" t="n"/>
+      <c r="MG50" s="8" t="n"/>
+      <c r="MH50" s="12" t="n"/>
+      <c r="MI50" s="12" t="n"/>
+      <c r="MJ50" s="12" t="n"/>
+      <c r="MK50" s="12" t="n"/>
+      <c r="ML50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="B51" s="4" t="n"/>
@@ -17685,6 +20055,47 @@
       <c r="KR51" s="12" t="n"/>
       <c r="KS51" s="12" t="n"/>
       <c r="KT51" s="7" t="n"/>
+      <c r="KX51" s="4" t="n"/>
+      <c r="KY51" s="6" t="n"/>
+      <c r="KZ51" s="8" t="n"/>
+      <c r="LA51" s="11" t="inlineStr"/>
+      <c r="LB51" s="6" t="n"/>
+      <c r="LC51" s="8" t="n"/>
+      <c r="LD51" s="12" t="n"/>
+      <c r="LE51" s="12" t="n"/>
+      <c r="LF51" s="12" t="n"/>
+      <c r="LG51" s="12" t="n"/>
+      <c r="LH51" s="8" t="n"/>
+      <c r="LI51" s="12" t="n"/>
+      <c r="LJ51" s="12" t="n"/>
+      <c r="LK51" s="12" t="n"/>
+      <c r="LL51" s="12" t="n"/>
+      <c r="LM51" s="8" t="n"/>
+      <c r="LN51" s="12" t="n"/>
+      <c r="LO51" s="12" t="n"/>
+      <c r="LP51" s="12" t="n"/>
+      <c r="LQ51" s="12" t="n"/>
+      <c r="LR51" s="8" t="n"/>
+      <c r="LS51" s="12" t="n"/>
+      <c r="LT51" s="12" t="n"/>
+      <c r="LU51" s="12" t="n"/>
+      <c r="LV51" s="12" t="n"/>
+      <c r="LW51" s="8" t="n"/>
+      <c r="LX51" s="12" t="n"/>
+      <c r="LY51" s="12" t="n"/>
+      <c r="LZ51" s="12" t="n"/>
+      <c r="MA51" s="12" t="n"/>
+      <c r="MB51" s="8" t="n"/>
+      <c r="MC51" s="12" t="n"/>
+      <c r="MD51" s="12" t="n"/>
+      <c r="ME51" s="12" t="n"/>
+      <c r="MF51" s="12" t="n"/>
+      <c r="MG51" s="8" t="n"/>
+      <c r="MH51" s="12" t="n"/>
+      <c r="MI51" s="12" t="n"/>
+      <c r="MJ51" s="12" t="n"/>
+      <c r="MK51" s="12" t="n"/>
+      <c r="ML51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="B52" s="4" t="n"/>
@@ -17974,6 +20385,47 @@
       <c r="KR52" s="12" t="n"/>
       <c r="KS52" s="12" t="n"/>
       <c r="KT52" s="7" t="n"/>
+      <c r="KX52" s="4" t="n"/>
+      <c r="KY52" s="6" t="n"/>
+      <c r="KZ52" s="8" t="n"/>
+      <c r="LA52" s="11" t="inlineStr"/>
+      <c r="LB52" s="6" t="n"/>
+      <c r="LC52" s="8" t="n"/>
+      <c r="LD52" s="12" t="n"/>
+      <c r="LE52" s="12" t="n"/>
+      <c r="LF52" s="12" t="n"/>
+      <c r="LG52" s="12" t="n"/>
+      <c r="LH52" s="8" t="n"/>
+      <c r="LI52" s="12" t="n"/>
+      <c r="LJ52" s="12" t="n"/>
+      <c r="LK52" s="12" t="n"/>
+      <c r="LL52" s="12" t="n"/>
+      <c r="LM52" s="8" t="n"/>
+      <c r="LN52" s="12" t="n"/>
+      <c r="LO52" s="12" t="n"/>
+      <c r="LP52" s="12" t="n"/>
+      <c r="LQ52" s="12" t="n"/>
+      <c r="LR52" s="8" t="n"/>
+      <c r="LS52" s="12" t="n"/>
+      <c r="LT52" s="12" t="n"/>
+      <c r="LU52" s="12" t="n"/>
+      <c r="LV52" s="12" t="n"/>
+      <c r="LW52" s="8" t="n"/>
+      <c r="LX52" s="12" t="n"/>
+      <c r="LY52" s="12" t="n"/>
+      <c r="LZ52" s="12" t="n"/>
+      <c r="MA52" s="12" t="n"/>
+      <c r="MB52" s="8" t="n"/>
+      <c r="MC52" s="12" t="n"/>
+      <c r="MD52" s="12" t="n"/>
+      <c r="ME52" s="12" t="n"/>
+      <c r="MF52" s="12" t="n"/>
+      <c r="MG52" s="8" t="n"/>
+      <c r="MH52" s="12" t="n"/>
+      <c r="MI52" s="12" t="n"/>
+      <c r="MJ52" s="12" t="n"/>
+      <c r="MK52" s="12" t="n"/>
+      <c r="ML52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="B53" s="4" t="n"/>
@@ -18263,6 +20715,47 @@
       <c r="KR53" s="8" t="n"/>
       <c r="KS53" s="8" t="n"/>
       <c r="KT53" s="7" t="n"/>
+      <c r="KX53" s="4" t="n"/>
+      <c r="KY53" s="8" t="n"/>
+      <c r="KZ53" s="8" t="n"/>
+      <c r="LA53" s="8" t="n"/>
+      <c r="LB53" s="8" t="n"/>
+      <c r="LC53" s="8" t="n"/>
+      <c r="LD53" s="8" t="n"/>
+      <c r="LE53" s="8" t="n"/>
+      <c r="LF53" s="8" t="n"/>
+      <c r="LG53" s="8" t="n"/>
+      <c r="LH53" s="8" t="n"/>
+      <c r="LI53" s="8" t="n"/>
+      <c r="LJ53" s="8" t="n"/>
+      <c r="LK53" s="8" t="n"/>
+      <c r="LL53" s="8" t="n"/>
+      <c r="LM53" s="8" t="n"/>
+      <c r="LN53" s="8" t="n"/>
+      <c r="LO53" s="8" t="n"/>
+      <c r="LP53" s="8" t="n"/>
+      <c r="LQ53" s="8" t="n"/>
+      <c r="LR53" s="8" t="n"/>
+      <c r="LS53" s="8" t="n"/>
+      <c r="LT53" s="8" t="n"/>
+      <c r="LU53" s="8" t="n"/>
+      <c r="LV53" s="8" t="n"/>
+      <c r="LW53" s="8" t="n"/>
+      <c r="LX53" s="8" t="n"/>
+      <c r="LY53" s="8" t="n"/>
+      <c r="LZ53" s="8" t="n"/>
+      <c r="MA53" s="8" t="n"/>
+      <c r="MB53" s="8" t="n"/>
+      <c r="MC53" s="8" t="n"/>
+      <c r="MD53" s="8" t="n"/>
+      <c r="ME53" s="8" t="n"/>
+      <c r="MF53" s="8" t="n"/>
+      <c r="MG53" s="8" t="n"/>
+      <c r="MH53" s="8" t="n"/>
+      <c r="MI53" s="8" t="n"/>
+      <c r="MJ53" s="8" t="n"/>
+      <c r="MK53" s="8" t="n"/>
+      <c r="ML53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="B54" s="4" t="n"/>
@@ -18284,7 +20777,7 @@
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>73.8kg</t>
+          <t>80kg</t>
         </is>
       </c>
       <c r="J54" s="17" t="n">
@@ -18301,7 +20794,7 @@
       </c>
       <c r="N54" s="14" t="inlineStr">
         <is>
-          <t>70kg</t>
+          <t>76.2kg</t>
         </is>
       </c>
       <c r="O54" s="17" t="n">
@@ -18318,7 +20811,7 @@
       </c>
       <c r="S54" s="14" t="inlineStr">
         <is>
-          <t>70kg</t>
+          <t>76.2kg</t>
         </is>
       </c>
       <c r="T54" s="17" t="n">
@@ -18335,7 +20828,7 @@
       </c>
       <c r="X54" s="14" t="inlineStr">
         <is>
-          <t>70kg</t>
+          <t>76.2kg</t>
         </is>
       </c>
       <c r="Y54" s="17" t="n">
@@ -18352,7 +20845,7 @@
       </c>
       <c r="AC54" s="14" t="inlineStr">
         <is>
-          <t>70kg</t>
+          <t>76.2kg</t>
         </is>
       </c>
       <c r="AD54" s="17" t="n">
@@ -18393,7 +20886,7 @@
       </c>
       <c r="BA54" s="14" t="inlineStr">
         <is>
-          <t>76.2kg</t>
+          <t>82.5kg</t>
         </is>
       </c>
       <c r="BB54" s="15" t="n">
@@ -18410,7 +20903,7 @@
       </c>
       <c r="BF54" s="14" t="inlineStr">
         <is>
-          <t>71.2kg</t>
+          <t>77.5kg</t>
         </is>
       </c>
       <c r="BG54" s="15" t="n">
@@ -18427,7 +20920,7 @@
       </c>
       <c r="BK54" s="14" t="inlineStr">
         <is>
-          <t>71.2kg</t>
+          <t>77.5kg</t>
         </is>
       </c>
       <c r="BL54" s="15" t="n">
@@ -18444,7 +20937,7 @@
       </c>
       <c r="BP54" s="14" t="inlineStr">
         <is>
-          <t>71.2kg</t>
+          <t>77.5kg</t>
         </is>
       </c>
       <c r="BQ54" s="15" t="n">
@@ -18461,7 +20954,7 @@
       </c>
       <c r="BU54" s="14" t="inlineStr">
         <is>
-          <t>71.2kg</t>
+          <t>77.5kg</t>
         </is>
       </c>
       <c r="BV54" s="15" t="n">
@@ -18502,7 +20995,7 @@
       </c>
       <c r="CS54" s="14" t="inlineStr">
         <is>
-          <t>77.5kg</t>
+          <t>85kg</t>
         </is>
       </c>
       <c r="CT54" s="17" t="n">
@@ -18521,7 +21014,7 @@
       </c>
       <c r="CX54" s="14" t="inlineStr">
         <is>
-          <t>71.2kg</t>
+          <t>77.5kg</t>
         </is>
       </c>
       <c r="CY54" s="15" t="n">
@@ -18577,7 +21070,7 @@
       </c>
       <c r="EK54" s="14" t="inlineStr">
         <is>
-          <t>67.5kg</t>
+          <t>73.8kg</t>
         </is>
       </c>
       <c r="EL54" s="15" t="n">
@@ -18594,7 +21087,7 @@
       </c>
       <c r="EP54" s="14" t="inlineStr">
         <is>
-          <t>63.8kg</t>
+          <t>68.8kg</t>
         </is>
       </c>
       <c r="EQ54" s="15" t="n">
@@ -18611,7 +21104,7 @@
       </c>
       <c r="EU54" s="14" t="inlineStr">
         <is>
-          <t>63.8kg</t>
+          <t>68.8kg</t>
         </is>
       </c>
       <c r="EV54" s="15" t="n">
@@ -18662,7 +21155,7 @@
       </c>
       <c r="GC54" s="14" t="inlineStr">
         <is>
-          <t>77.5kg</t>
+          <t>85kg</t>
         </is>
       </c>
       <c r="GD54" s="17" t="n">
@@ -18681,7 +21174,7 @@
       </c>
       <c r="GH54" s="14" t="inlineStr">
         <is>
-          <t>71.2kg</t>
+          <t>77.5kg</t>
         </is>
       </c>
       <c r="GI54" s="15" t="n">
@@ -18737,7 +21230,7 @@
       </c>
       <c r="HU54" s="14" t="inlineStr">
         <is>
-          <t>80kg</t>
+          <t>87.5kg</t>
         </is>
       </c>
       <c r="HV54" s="15" t="n">
@@ -18754,7 +21247,7 @@
       </c>
       <c r="HZ54" s="14" t="inlineStr">
         <is>
-          <t>73.8kg</t>
+          <t>80kg</t>
         </is>
       </c>
       <c r="IA54" s="17" t="n">
@@ -18771,7 +21264,7 @@
       </c>
       <c r="IE54" s="14" t="inlineStr">
         <is>
-          <t>73.8kg</t>
+          <t>80kg</t>
         </is>
       </c>
       <c r="IF54" s="17" t="n">
@@ -18788,7 +21281,7 @@
       </c>
       <c r="IJ54" s="14" t="inlineStr">
         <is>
-          <t>73.8kg</t>
+          <t>80kg</t>
         </is>
       </c>
       <c r="IK54" s="17" t="n">
@@ -18822,13 +21315,31 @@
         </is>
       </c>
       <c r="JH54" s="8" t="n"/>
-      <c r="JI54" s="11" t="inlineStr"/>
+      <c r="JI54" s="13" t="inlineStr">
+        <is>
+          <t>Weighted Muscle-Ups</t>
+        </is>
+      </c>
       <c r="JJ54" s="6" t="n"/>
       <c r="JK54" s="8" t="n"/>
-      <c r="JL54" s="12" t="n"/>
-      <c r="JM54" s="12" t="n"/>
-      <c r="JN54" s="12" t="n"/>
-      <c r="JO54" s="12" t="n"/>
+      <c r="JL54" s="14" t="inlineStr">
+        <is>
+          <t>2-3x1</t>
+        </is>
+      </c>
+      <c r="JM54" s="14" t="inlineStr">
+        <is>
+          <t>15kg</t>
+        </is>
+      </c>
+      <c r="JN54" s="15" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="JO54" s="16" t="inlineStr">
+        <is>
+          <t>Crisp technique only (can go up to ~60% if perfect). Long rests.</t>
+        </is>
+      </c>
       <c r="JP54" s="8" t="n"/>
       <c r="JQ54" s="12" t="n"/>
       <c r="JR54" s="12" t="n"/>
@@ -18860,6 +21371,103 @@
       <c r="KR54" s="12" t="n"/>
       <c r="KS54" s="12" t="n"/>
       <c r="KT54" s="7" t="n"/>
+      <c r="KX54" s="4" t="n"/>
+      <c r="KY54" s="10" t="inlineStr">
+        <is>
+          <t>Day 6</t>
+        </is>
+      </c>
+      <c r="KZ54" s="8" t="n"/>
+      <c r="LA54" s="13" t="inlineStr">
+        <is>
+          <t>Weighted Muscle-Ups</t>
+        </is>
+      </c>
+      <c r="LB54" s="6" t="n"/>
+      <c r="LC54" s="8" t="n"/>
+      <c r="LD54" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="LE54" s="14" t="inlineStr">
+        <is>
+          <t>18.8kg</t>
+        </is>
+      </c>
+      <c r="LF54" s="15" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="LG54" s="16" t="inlineStr">
+        <is>
+          <t>Warm-up (progress through BW → ~70–80%)</t>
+        </is>
+      </c>
+      <c r="LH54" s="8" t="n"/>
+      <c r="LI54" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="LJ54" s="14" t="inlineStr">
+        <is>
+          <t>25kg</t>
+        </is>
+      </c>
+      <c r="LK54" s="15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="LL54" s="16" t="inlineStr">
+        <is>
+          <t>Last warm-up</t>
+        </is>
+      </c>
+      <c r="LM54" s="8" t="n"/>
+      <c r="LN54" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="LO54" s="14" t="inlineStr">
+        <is>
+          <t>27.5kg</t>
+        </is>
+      </c>
+      <c r="LP54" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="LQ54" s="16" t="inlineStr">
+        <is>
+          <t>PB attempt</t>
+        </is>
+      </c>
+      <c r="LR54" s="8" t="n"/>
+      <c r="LS54" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="LT54" s="14" t="inlineStr">
+        <is>
+          <t>27.5kg</t>
+        </is>
+      </c>
+      <c r="LU54" s="15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="LV54" s="16" t="inlineStr">
+        <is>
+          <t>Optional 102% if PB was snappy</t>
+        </is>
+      </c>
+      <c r="LW54" s="8" t="n"/>
+      <c r="LX54" s="12" t="n"/>
+      <c r="LY54" s="12" t="n"/>
+      <c r="LZ54" s="12" t="n"/>
+      <c r="MA54" s="12" t="n"/>
+      <c r="MB54" s="8" t="n"/>
+      <c r="MC54" s="12" t="n"/>
+      <c r="MD54" s="12" t="n"/>
+      <c r="ME54" s="12" t="n"/>
+      <c r="MF54" s="12" t="n"/>
+      <c r="MG54" s="8" t="n"/>
+      <c r="MH54" s="12" t="n"/>
+      <c r="MI54" s="12" t="n"/>
+      <c r="MJ54" s="12" t="n"/>
+      <c r="MK54" s="12" t="n"/>
+      <c r="ML54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="B55" s="4" t="n"/>
@@ -18877,7 +21485,7 @@
       </c>
       <c r="I55" s="14" t="inlineStr">
         <is>
-          <t>52.5kg</t>
+          <t>57.5kg</t>
         </is>
       </c>
       <c r="J55" s="15" t="n">
@@ -18894,7 +21502,7 @@
       </c>
       <c r="N55" s="14" t="inlineStr">
         <is>
-          <t>52.5kg</t>
+          <t>57.5kg</t>
         </is>
       </c>
       <c r="O55" s="15" t="n">
@@ -18911,7 +21519,7 @@
       </c>
       <c r="S55" s="14" t="inlineStr">
         <is>
-          <t>52.5kg</t>
+          <t>57.5kg</t>
         </is>
       </c>
       <c r="T55" s="15" t="n">
@@ -18958,7 +21566,7 @@
       </c>
       <c r="BA55" s="14" t="inlineStr">
         <is>
-          <t>53.8kg</t>
+          <t>58.8kg</t>
         </is>
       </c>
       <c r="BB55" s="17" t="n">
@@ -18975,7 +21583,7 @@
       </c>
       <c r="BF55" s="14" t="inlineStr">
         <is>
-          <t>53.8kg</t>
+          <t>58.8kg</t>
         </is>
       </c>
       <c r="BG55" s="17" t="n">
@@ -18992,7 +21600,7 @@
       </c>
       <c r="BK55" s="14" t="inlineStr">
         <is>
-          <t>53.8kg</t>
+          <t>58.8kg</t>
         </is>
       </c>
       <c r="BL55" s="17" t="n">
@@ -19039,7 +21647,7 @@
       </c>
       <c r="CS55" s="14" t="inlineStr">
         <is>
-          <t>53.8kg</t>
+          <t>58.8kg</t>
         </is>
       </c>
       <c r="CT55" s="17" t="n">
@@ -19056,7 +21664,7 @@
       </c>
       <c r="CX55" s="14" t="inlineStr">
         <is>
-          <t>53.8kg</t>
+          <t>58.8kg</t>
         </is>
       </c>
       <c r="CY55" s="17" t="n">
@@ -19073,7 +21681,7 @@
       </c>
       <c r="DC55" s="14" t="inlineStr">
         <is>
-          <t>53.8kg</t>
+          <t>58.8kg</t>
         </is>
       </c>
       <c r="DD55" s="17" t="n">
@@ -19120,7 +21728,7 @@
       </c>
       <c r="EK55" s="14" t="inlineStr">
         <is>
-          <t>48.8kg</t>
+          <t>52.5kg</t>
         </is>
       </c>
       <c r="EL55" s="15" t="n">
@@ -19137,7 +21745,7 @@
       </c>
       <c r="EP55" s="14" t="inlineStr">
         <is>
-          <t>48.8kg</t>
+          <t>52.5kg</t>
         </is>
       </c>
       <c r="EQ55" s="15" t="n">
@@ -19189,7 +21797,7 @@
       </c>
       <c r="GC55" s="14" t="inlineStr">
         <is>
-          <t>53.8kg</t>
+          <t>58.8kg</t>
         </is>
       </c>
       <c r="GD55" s="17" t="n">
@@ -19206,7 +21814,7 @@
       </c>
       <c r="GH55" s="14" t="inlineStr">
         <is>
-          <t>53.8kg</t>
+          <t>58.8kg</t>
         </is>
       </c>
       <c r="GI55" s="17" t="n">
@@ -19223,7 +21831,7 @@
       </c>
       <c r="GM55" s="14" t="inlineStr">
         <is>
-          <t>53.8kg</t>
+          <t>58.8kg</t>
         </is>
       </c>
       <c r="GN55" s="17" t="n">
@@ -19270,7 +21878,7 @@
       </c>
       <c r="HU55" s="14" t="inlineStr">
         <is>
-          <t>53.8kg</t>
+          <t>58.8kg</t>
         </is>
       </c>
       <c r="HV55" s="17" t="n">
@@ -19287,7 +21895,7 @@
       </c>
       <c r="HZ55" s="14" t="inlineStr">
         <is>
-          <t>53.8kg</t>
+          <t>58.8kg</t>
         </is>
       </c>
       <c r="IA55" s="17" t="n">
@@ -19304,7 +21912,7 @@
       </c>
       <c r="IE55" s="14" t="inlineStr">
         <is>
-          <t>53.8kg</t>
+          <t>58.8kg</t>
         </is>
       </c>
       <c r="IF55" s="17" t="n">
@@ -19377,6 +21985,47 @@
       <c r="KR55" s="12" t="n"/>
       <c r="KS55" s="12" t="n"/>
       <c r="KT55" s="7" t="n"/>
+      <c r="KX55" s="4" t="n"/>
+      <c r="KY55" s="6" t="n"/>
+      <c r="KZ55" s="8" t="n"/>
+      <c r="LA55" s="11" t="inlineStr"/>
+      <c r="LB55" s="6" t="n"/>
+      <c r="LC55" s="8" t="n"/>
+      <c r="LD55" s="12" t="n"/>
+      <c r="LE55" s="12" t="n"/>
+      <c r="LF55" s="12" t="n"/>
+      <c r="LG55" s="12" t="n"/>
+      <c r="LH55" s="8" t="n"/>
+      <c r="LI55" s="12" t="n"/>
+      <c r="LJ55" s="12" t="n"/>
+      <c r="LK55" s="12" t="n"/>
+      <c r="LL55" s="12" t="n"/>
+      <c r="LM55" s="8" t="n"/>
+      <c r="LN55" s="12" t="n"/>
+      <c r="LO55" s="12" t="n"/>
+      <c r="LP55" s="12" t="n"/>
+      <c r="LQ55" s="12" t="n"/>
+      <c r="LR55" s="8" t="n"/>
+      <c r="LS55" s="12" t="n"/>
+      <c r="LT55" s="12" t="n"/>
+      <c r="LU55" s="12" t="n"/>
+      <c r="LV55" s="12" t="n"/>
+      <c r="LW55" s="8" t="n"/>
+      <c r="LX55" s="12" t="n"/>
+      <c r="LY55" s="12" t="n"/>
+      <c r="LZ55" s="12" t="n"/>
+      <c r="MA55" s="12" t="n"/>
+      <c r="MB55" s="8" t="n"/>
+      <c r="MC55" s="12" t="n"/>
+      <c r="MD55" s="12" t="n"/>
+      <c r="ME55" s="12" t="n"/>
+      <c r="MF55" s="12" t="n"/>
+      <c r="MG55" s="8" t="n"/>
+      <c r="MH55" s="12" t="n"/>
+      <c r="MI55" s="12" t="n"/>
+      <c r="MJ55" s="12" t="n"/>
+      <c r="MK55" s="12" t="n"/>
+      <c r="ML55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="B56" s="4" t="n"/>
@@ -20028,6 +22677,47 @@
       <c r="KR56" s="12" t="n"/>
       <c r="KS56" s="12" t="n"/>
       <c r="KT56" s="7" t="n"/>
+      <c r="KX56" s="4" t="n"/>
+      <c r="KY56" s="6" t="n"/>
+      <c r="KZ56" s="8" t="n"/>
+      <c r="LA56" s="11" t="inlineStr"/>
+      <c r="LB56" s="6" t="n"/>
+      <c r="LC56" s="8" t="n"/>
+      <c r="LD56" s="12" t="n"/>
+      <c r="LE56" s="12" t="n"/>
+      <c r="LF56" s="12" t="n"/>
+      <c r="LG56" s="12" t="n"/>
+      <c r="LH56" s="8" t="n"/>
+      <c r="LI56" s="12" t="n"/>
+      <c r="LJ56" s="12" t="n"/>
+      <c r="LK56" s="12" t="n"/>
+      <c r="LL56" s="12" t="n"/>
+      <c r="LM56" s="8" t="n"/>
+      <c r="LN56" s="12" t="n"/>
+      <c r="LO56" s="12" t="n"/>
+      <c r="LP56" s="12" t="n"/>
+      <c r="LQ56" s="12" t="n"/>
+      <c r="LR56" s="8" t="n"/>
+      <c r="LS56" s="12" t="n"/>
+      <c r="LT56" s="12" t="n"/>
+      <c r="LU56" s="12" t="n"/>
+      <c r="LV56" s="12" t="n"/>
+      <c r="LW56" s="8" t="n"/>
+      <c r="LX56" s="12" t="n"/>
+      <c r="LY56" s="12" t="n"/>
+      <c r="LZ56" s="12" t="n"/>
+      <c r="MA56" s="12" t="n"/>
+      <c r="MB56" s="8" t="n"/>
+      <c r="MC56" s="12" t="n"/>
+      <c r="MD56" s="12" t="n"/>
+      <c r="ME56" s="12" t="n"/>
+      <c r="MF56" s="12" t="n"/>
+      <c r="MG56" s="8" t="n"/>
+      <c r="MH56" s="12" t="n"/>
+      <c r="MI56" s="12" t="n"/>
+      <c r="MJ56" s="12" t="n"/>
+      <c r="MK56" s="12" t="n"/>
+      <c r="ML56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="B57" s="4" t="n"/>
@@ -20329,6 +23019,47 @@
       <c r="KR57" s="12" t="n"/>
       <c r="KS57" s="12" t="n"/>
       <c r="KT57" s="7" t="n"/>
+      <c r="KX57" s="4" t="n"/>
+      <c r="KY57" s="6" t="n"/>
+      <c r="KZ57" s="8" t="n"/>
+      <c r="LA57" s="11" t="inlineStr"/>
+      <c r="LB57" s="6" t="n"/>
+      <c r="LC57" s="8" t="n"/>
+      <c r="LD57" s="12" t="n"/>
+      <c r="LE57" s="12" t="n"/>
+      <c r="LF57" s="12" t="n"/>
+      <c r="LG57" s="12" t="n"/>
+      <c r="LH57" s="8" t="n"/>
+      <c r="LI57" s="12" t="n"/>
+      <c r="LJ57" s="12" t="n"/>
+      <c r="LK57" s="12" t="n"/>
+      <c r="LL57" s="12" t="n"/>
+      <c r="LM57" s="8" t="n"/>
+      <c r="LN57" s="12" t="n"/>
+      <c r="LO57" s="12" t="n"/>
+      <c r="LP57" s="12" t="n"/>
+      <c r="LQ57" s="12" t="n"/>
+      <c r="LR57" s="8" t="n"/>
+      <c r="LS57" s="12" t="n"/>
+      <c r="LT57" s="12" t="n"/>
+      <c r="LU57" s="12" t="n"/>
+      <c r="LV57" s="12" t="n"/>
+      <c r="LW57" s="8" t="n"/>
+      <c r="LX57" s="12" t="n"/>
+      <c r="LY57" s="12" t="n"/>
+      <c r="LZ57" s="12" t="n"/>
+      <c r="MA57" s="12" t="n"/>
+      <c r="MB57" s="8" t="n"/>
+      <c r="MC57" s="12" t="n"/>
+      <c r="MD57" s="12" t="n"/>
+      <c r="ME57" s="12" t="n"/>
+      <c r="MF57" s="12" t="n"/>
+      <c r="MG57" s="8" t="n"/>
+      <c r="MH57" s="12" t="n"/>
+      <c r="MI57" s="12" t="n"/>
+      <c r="MJ57" s="12" t="n"/>
+      <c r="MK57" s="12" t="n"/>
+      <c r="ML57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="B58" s="4" t="n"/>
@@ -20618,6 +23349,47 @@
       <c r="KR58" s="12" t="n"/>
       <c r="KS58" s="12" t="n"/>
       <c r="KT58" s="7" t="n"/>
+      <c r="KX58" s="4" t="n"/>
+      <c r="KY58" s="6" t="n"/>
+      <c r="KZ58" s="8" t="n"/>
+      <c r="LA58" s="11" t="inlineStr"/>
+      <c r="LB58" s="6" t="n"/>
+      <c r="LC58" s="8" t="n"/>
+      <c r="LD58" s="12" t="n"/>
+      <c r="LE58" s="12" t="n"/>
+      <c r="LF58" s="12" t="n"/>
+      <c r="LG58" s="12" t="n"/>
+      <c r="LH58" s="8" t="n"/>
+      <c r="LI58" s="12" t="n"/>
+      <c r="LJ58" s="12" t="n"/>
+      <c r="LK58" s="12" t="n"/>
+      <c r="LL58" s="12" t="n"/>
+      <c r="LM58" s="8" t="n"/>
+      <c r="LN58" s="12" t="n"/>
+      <c r="LO58" s="12" t="n"/>
+      <c r="LP58" s="12" t="n"/>
+      <c r="LQ58" s="12" t="n"/>
+      <c r="LR58" s="8" t="n"/>
+      <c r="LS58" s="12" t="n"/>
+      <c r="LT58" s="12" t="n"/>
+      <c r="LU58" s="12" t="n"/>
+      <c r="LV58" s="12" t="n"/>
+      <c r="LW58" s="8" t="n"/>
+      <c r="LX58" s="12" t="n"/>
+      <c r="LY58" s="12" t="n"/>
+      <c r="LZ58" s="12" t="n"/>
+      <c r="MA58" s="12" t="n"/>
+      <c r="MB58" s="8" t="n"/>
+      <c r="MC58" s="12" t="n"/>
+      <c r="MD58" s="12" t="n"/>
+      <c r="ME58" s="12" t="n"/>
+      <c r="MF58" s="12" t="n"/>
+      <c r="MG58" s="8" t="n"/>
+      <c r="MH58" s="12" t="n"/>
+      <c r="MI58" s="12" t="n"/>
+      <c r="MJ58" s="12" t="n"/>
+      <c r="MK58" s="12" t="n"/>
+      <c r="ML58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="B59" s="4" t="n"/>
@@ -20907,6 +23679,47 @@
       <c r="KR59" s="12" t="n"/>
       <c r="KS59" s="12" t="n"/>
       <c r="KT59" s="7" t="n"/>
+      <c r="KX59" s="4" t="n"/>
+      <c r="KY59" s="6" t="n"/>
+      <c r="KZ59" s="8" t="n"/>
+      <c r="LA59" s="11" t="inlineStr"/>
+      <c r="LB59" s="6" t="n"/>
+      <c r="LC59" s="8" t="n"/>
+      <c r="LD59" s="12" t="n"/>
+      <c r="LE59" s="12" t="n"/>
+      <c r="LF59" s="12" t="n"/>
+      <c r="LG59" s="12" t="n"/>
+      <c r="LH59" s="8" t="n"/>
+      <c r="LI59" s="12" t="n"/>
+      <c r="LJ59" s="12" t="n"/>
+      <c r="LK59" s="12" t="n"/>
+      <c r="LL59" s="12" t="n"/>
+      <c r="LM59" s="8" t="n"/>
+      <c r="LN59" s="12" t="n"/>
+      <c r="LO59" s="12" t="n"/>
+      <c r="LP59" s="12" t="n"/>
+      <c r="LQ59" s="12" t="n"/>
+      <c r="LR59" s="8" t="n"/>
+      <c r="LS59" s="12" t="n"/>
+      <c r="LT59" s="12" t="n"/>
+      <c r="LU59" s="12" t="n"/>
+      <c r="LV59" s="12" t="n"/>
+      <c r="LW59" s="8" t="n"/>
+      <c r="LX59" s="12" t="n"/>
+      <c r="LY59" s="12" t="n"/>
+      <c r="LZ59" s="12" t="n"/>
+      <c r="MA59" s="12" t="n"/>
+      <c r="MB59" s="8" t="n"/>
+      <c r="MC59" s="12" t="n"/>
+      <c r="MD59" s="12" t="n"/>
+      <c r="ME59" s="12" t="n"/>
+      <c r="MF59" s="12" t="n"/>
+      <c r="MG59" s="8" t="n"/>
+      <c r="MH59" s="12" t="n"/>
+      <c r="MI59" s="12" t="n"/>
+      <c r="MJ59" s="12" t="n"/>
+      <c r="MK59" s="12" t="n"/>
+      <c r="ML59" s="7" t="n"/>
     </row>
     <row r="60">
       <c r="B60" s="4" t="n"/>
@@ -21196,6 +24009,47 @@
       <c r="KR60" s="12" t="n"/>
       <c r="KS60" s="12" t="n"/>
       <c r="KT60" s="7" t="n"/>
+      <c r="KX60" s="4" t="n"/>
+      <c r="KY60" s="6" t="n"/>
+      <c r="KZ60" s="8" t="n"/>
+      <c r="LA60" s="11" t="inlineStr"/>
+      <c r="LB60" s="6" t="n"/>
+      <c r="LC60" s="8" t="n"/>
+      <c r="LD60" s="12" t="n"/>
+      <c r="LE60" s="12" t="n"/>
+      <c r="LF60" s="12" t="n"/>
+      <c r="LG60" s="12" t="n"/>
+      <c r="LH60" s="8" t="n"/>
+      <c r="LI60" s="12" t="n"/>
+      <c r="LJ60" s="12" t="n"/>
+      <c r="LK60" s="12" t="n"/>
+      <c r="LL60" s="12" t="n"/>
+      <c r="LM60" s="8" t="n"/>
+      <c r="LN60" s="12" t="n"/>
+      <c r="LO60" s="12" t="n"/>
+      <c r="LP60" s="12" t="n"/>
+      <c r="LQ60" s="12" t="n"/>
+      <c r="LR60" s="8" t="n"/>
+      <c r="LS60" s="12" t="n"/>
+      <c r="LT60" s="12" t="n"/>
+      <c r="LU60" s="12" t="n"/>
+      <c r="LV60" s="12" t="n"/>
+      <c r="LW60" s="8" t="n"/>
+      <c r="LX60" s="12" t="n"/>
+      <c r="LY60" s="12" t="n"/>
+      <c r="LZ60" s="12" t="n"/>
+      <c r="MA60" s="12" t="n"/>
+      <c r="MB60" s="8" t="n"/>
+      <c r="MC60" s="12" t="n"/>
+      <c r="MD60" s="12" t="n"/>
+      <c r="ME60" s="12" t="n"/>
+      <c r="MF60" s="12" t="n"/>
+      <c r="MG60" s="8" t="n"/>
+      <c r="MH60" s="12" t="n"/>
+      <c r="MI60" s="12" t="n"/>
+      <c r="MJ60" s="12" t="n"/>
+      <c r="MK60" s="12" t="n"/>
+      <c r="ML60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="B61" s="4" t="n"/>
@@ -21485,6 +24339,47 @@
       <c r="KR61" s="12" t="n"/>
       <c r="KS61" s="12" t="n"/>
       <c r="KT61" s="7" t="n"/>
+      <c r="KX61" s="4" t="n"/>
+      <c r="KY61" s="6" t="n"/>
+      <c r="KZ61" s="8" t="n"/>
+      <c r="LA61" s="11" t="inlineStr"/>
+      <c r="LB61" s="6" t="n"/>
+      <c r="LC61" s="8" t="n"/>
+      <c r="LD61" s="12" t="n"/>
+      <c r="LE61" s="12" t="n"/>
+      <c r="LF61" s="12" t="n"/>
+      <c r="LG61" s="12" t="n"/>
+      <c r="LH61" s="8" t="n"/>
+      <c r="LI61" s="12" t="n"/>
+      <c r="LJ61" s="12" t="n"/>
+      <c r="LK61" s="12" t="n"/>
+      <c r="LL61" s="12" t="n"/>
+      <c r="LM61" s="8" t="n"/>
+      <c r="LN61" s="12" t="n"/>
+      <c r="LO61" s="12" t="n"/>
+      <c r="LP61" s="12" t="n"/>
+      <c r="LQ61" s="12" t="n"/>
+      <c r="LR61" s="8" t="n"/>
+      <c r="LS61" s="12" t="n"/>
+      <c r="LT61" s="12" t="n"/>
+      <c r="LU61" s="12" t="n"/>
+      <c r="LV61" s="12" t="n"/>
+      <c r="LW61" s="8" t="n"/>
+      <c r="LX61" s="12" t="n"/>
+      <c r="LY61" s="12" t="n"/>
+      <c r="LZ61" s="12" t="n"/>
+      <c r="MA61" s="12" t="n"/>
+      <c r="MB61" s="8" t="n"/>
+      <c r="MC61" s="12" t="n"/>
+      <c r="MD61" s="12" t="n"/>
+      <c r="ME61" s="12" t="n"/>
+      <c r="MF61" s="12" t="n"/>
+      <c r="MG61" s="8" t="n"/>
+      <c r="MH61" s="12" t="n"/>
+      <c r="MI61" s="12" t="n"/>
+      <c r="MJ61" s="12" t="n"/>
+      <c r="MK61" s="12" t="n"/>
+      <c r="ML61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="B62" s="4" t="n"/>
@@ -21774,6 +24669,47 @@
       <c r="KR62" s="8" t="n"/>
       <c r="KS62" s="8" t="n"/>
       <c r="KT62" s="7" t="n"/>
+      <c r="KX62" s="4" t="n"/>
+      <c r="KY62" s="8" t="n"/>
+      <c r="KZ62" s="8" t="n"/>
+      <c r="LA62" s="8" t="n"/>
+      <c r="LB62" s="8" t="n"/>
+      <c r="LC62" s="8" t="n"/>
+      <c r="LD62" s="8" t="n"/>
+      <c r="LE62" s="8" t="n"/>
+      <c r="LF62" s="8" t="n"/>
+      <c r="LG62" s="8" t="n"/>
+      <c r="LH62" s="8" t="n"/>
+      <c r="LI62" s="8" t="n"/>
+      <c r="LJ62" s="8" t="n"/>
+      <c r="LK62" s="8" t="n"/>
+      <c r="LL62" s="8" t="n"/>
+      <c r="LM62" s="8" t="n"/>
+      <c r="LN62" s="8" t="n"/>
+      <c r="LO62" s="8" t="n"/>
+      <c r="LP62" s="8" t="n"/>
+      <c r="LQ62" s="8" t="n"/>
+      <c r="LR62" s="8" t="n"/>
+      <c r="LS62" s="8" t="n"/>
+      <c r="LT62" s="8" t="n"/>
+      <c r="LU62" s="8" t="n"/>
+      <c r="LV62" s="8" t="n"/>
+      <c r="LW62" s="8" t="n"/>
+      <c r="LX62" s="8" t="n"/>
+      <c r="LY62" s="8" t="n"/>
+      <c r="LZ62" s="8" t="n"/>
+      <c r="MA62" s="8" t="n"/>
+      <c r="MB62" s="8" t="n"/>
+      <c r="MC62" s="8" t="n"/>
+      <c r="MD62" s="8" t="n"/>
+      <c r="ME62" s="8" t="n"/>
+      <c r="MF62" s="8" t="n"/>
+      <c r="MG62" s="8" t="n"/>
+      <c r="MH62" s="8" t="n"/>
+      <c r="MI62" s="8" t="n"/>
+      <c r="MJ62" s="8" t="n"/>
+      <c r="MK62" s="8" t="n"/>
+      <c r="ML62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="B63" s="4" t="n"/>
@@ -22091,6 +25027,51 @@
       <c r="KR63" s="12" t="n"/>
       <c r="KS63" s="12" t="n"/>
       <c r="KT63" s="7" t="n"/>
+      <c r="KX63" s="4" t="n"/>
+      <c r="KY63" s="10" t="inlineStr">
+        <is>
+          <t>Day 7</t>
+        </is>
+      </c>
+      <c r="KZ63" s="8" t="n"/>
+      <c r="LA63" s="11" t="inlineStr"/>
+      <c r="LB63" s="6" t="n"/>
+      <c r="LC63" s="8" t="n"/>
+      <c r="LD63" s="12" t="n"/>
+      <c r="LE63" s="12" t="n"/>
+      <c r="LF63" s="12" t="n"/>
+      <c r="LG63" s="12" t="n"/>
+      <c r="LH63" s="8" t="n"/>
+      <c r="LI63" s="12" t="n"/>
+      <c r="LJ63" s="12" t="n"/>
+      <c r="LK63" s="12" t="n"/>
+      <c r="LL63" s="12" t="n"/>
+      <c r="LM63" s="8" t="n"/>
+      <c r="LN63" s="12" t="n"/>
+      <c r="LO63" s="12" t="n"/>
+      <c r="LP63" s="12" t="n"/>
+      <c r="LQ63" s="12" t="n"/>
+      <c r="LR63" s="8" t="n"/>
+      <c r="LS63" s="12" t="n"/>
+      <c r="LT63" s="12" t="n"/>
+      <c r="LU63" s="12" t="n"/>
+      <c r="LV63" s="12" t="n"/>
+      <c r="LW63" s="8" t="n"/>
+      <c r="LX63" s="12" t="n"/>
+      <c r="LY63" s="12" t="n"/>
+      <c r="LZ63" s="12" t="n"/>
+      <c r="MA63" s="12" t="n"/>
+      <c r="MB63" s="8" t="n"/>
+      <c r="MC63" s="12" t="n"/>
+      <c r="MD63" s="12" t="n"/>
+      <c r="ME63" s="12" t="n"/>
+      <c r="MF63" s="12" t="n"/>
+      <c r="MG63" s="8" t="n"/>
+      <c r="MH63" s="12" t="n"/>
+      <c r="MI63" s="12" t="n"/>
+      <c r="MJ63" s="12" t="n"/>
+      <c r="MK63" s="12" t="n"/>
+      <c r="ML63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="B64" s="4" t="n"/>
@@ -22380,6 +25361,47 @@
       <c r="KR64" s="12" t="n"/>
       <c r="KS64" s="12" t="n"/>
       <c r="KT64" s="7" t="n"/>
+      <c r="KX64" s="4" t="n"/>
+      <c r="KY64" s="6" t="n"/>
+      <c r="KZ64" s="8" t="n"/>
+      <c r="LA64" s="11" t="inlineStr"/>
+      <c r="LB64" s="6" t="n"/>
+      <c r="LC64" s="8" t="n"/>
+      <c r="LD64" s="12" t="n"/>
+      <c r="LE64" s="12" t="n"/>
+      <c r="LF64" s="12" t="n"/>
+      <c r="LG64" s="12" t="n"/>
+      <c r="LH64" s="8" t="n"/>
+      <c r="LI64" s="12" t="n"/>
+      <c r="LJ64" s="12" t="n"/>
+      <c r="LK64" s="12" t="n"/>
+      <c r="LL64" s="12" t="n"/>
+      <c r="LM64" s="8" t="n"/>
+      <c r="LN64" s="12" t="n"/>
+      <c r="LO64" s="12" t="n"/>
+      <c r="LP64" s="12" t="n"/>
+      <c r="LQ64" s="12" t="n"/>
+      <c r="LR64" s="8" t="n"/>
+      <c r="LS64" s="12" t="n"/>
+      <c r="LT64" s="12" t="n"/>
+      <c r="LU64" s="12" t="n"/>
+      <c r="LV64" s="12" t="n"/>
+      <c r="LW64" s="8" t="n"/>
+      <c r="LX64" s="12" t="n"/>
+      <c r="LY64" s="12" t="n"/>
+      <c r="LZ64" s="12" t="n"/>
+      <c r="MA64" s="12" t="n"/>
+      <c r="MB64" s="8" t="n"/>
+      <c r="MC64" s="12" t="n"/>
+      <c r="MD64" s="12" t="n"/>
+      <c r="ME64" s="12" t="n"/>
+      <c r="MF64" s="12" t="n"/>
+      <c r="MG64" s="8" t="n"/>
+      <c r="MH64" s="12" t="n"/>
+      <c r="MI64" s="12" t="n"/>
+      <c r="MJ64" s="12" t="n"/>
+      <c r="MK64" s="12" t="n"/>
+      <c r="ML64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="B65" s="4" t="n"/>
@@ -22669,6 +25691,47 @@
       <c r="KR65" s="12" t="n"/>
       <c r="KS65" s="12" t="n"/>
       <c r="KT65" s="7" t="n"/>
+      <c r="KX65" s="4" t="n"/>
+      <c r="KY65" s="6" t="n"/>
+      <c r="KZ65" s="8" t="n"/>
+      <c r="LA65" s="11" t="inlineStr"/>
+      <c r="LB65" s="6" t="n"/>
+      <c r="LC65" s="8" t="n"/>
+      <c r="LD65" s="12" t="n"/>
+      <c r="LE65" s="12" t="n"/>
+      <c r="LF65" s="12" t="n"/>
+      <c r="LG65" s="12" t="n"/>
+      <c r="LH65" s="8" t="n"/>
+      <c r="LI65" s="12" t="n"/>
+      <c r="LJ65" s="12" t="n"/>
+      <c r="LK65" s="12" t="n"/>
+      <c r="LL65" s="12" t="n"/>
+      <c r="LM65" s="8" t="n"/>
+      <c r="LN65" s="12" t="n"/>
+      <c r="LO65" s="12" t="n"/>
+      <c r="LP65" s="12" t="n"/>
+      <c r="LQ65" s="12" t="n"/>
+      <c r="LR65" s="8" t="n"/>
+      <c r="LS65" s="12" t="n"/>
+      <c r="LT65" s="12" t="n"/>
+      <c r="LU65" s="12" t="n"/>
+      <c r="LV65" s="12" t="n"/>
+      <c r="LW65" s="8" t="n"/>
+      <c r="LX65" s="12" t="n"/>
+      <c r="LY65" s="12" t="n"/>
+      <c r="LZ65" s="12" t="n"/>
+      <c r="MA65" s="12" t="n"/>
+      <c r="MB65" s="8" t="n"/>
+      <c r="MC65" s="12" t="n"/>
+      <c r="MD65" s="12" t="n"/>
+      <c r="ME65" s="12" t="n"/>
+      <c r="MF65" s="12" t="n"/>
+      <c r="MG65" s="8" t="n"/>
+      <c r="MH65" s="12" t="n"/>
+      <c r="MI65" s="12" t="n"/>
+      <c r="MJ65" s="12" t="n"/>
+      <c r="MK65" s="12" t="n"/>
+      <c r="ML65" s="7" t="n"/>
     </row>
     <row r="66">
       <c r="B66" s="4" t="n"/>
@@ -22958,6 +26021,47 @@
       <c r="KR66" s="12" t="n"/>
       <c r="KS66" s="12" t="n"/>
       <c r="KT66" s="7" t="n"/>
+      <c r="KX66" s="4" t="n"/>
+      <c r="KY66" s="6" t="n"/>
+      <c r="KZ66" s="8" t="n"/>
+      <c r="LA66" s="11" t="inlineStr"/>
+      <c r="LB66" s="6" t="n"/>
+      <c r="LC66" s="8" t="n"/>
+      <c r="LD66" s="12" t="n"/>
+      <c r="LE66" s="12" t="n"/>
+      <c r="LF66" s="12" t="n"/>
+      <c r="LG66" s="12" t="n"/>
+      <c r="LH66" s="8" t="n"/>
+      <c r="LI66" s="12" t="n"/>
+      <c r="LJ66" s="12" t="n"/>
+      <c r="LK66" s="12" t="n"/>
+      <c r="LL66" s="12" t="n"/>
+      <c r="LM66" s="8" t="n"/>
+      <c r="LN66" s="12" t="n"/>
+      <c r="LO66" s="12" t="n"/>
+      <c r="LP66" s="12" t="n"/>
+      <c r="LQ66" s="12" t="n"/>
+      <c r="LR66" s="8" t="n"/>
+      <c r="LS66" s="12" t="n"/>
+      <c r="LT66" s="12" t="n"/>
+      <c r="LU66" s="12" t="n"/>
+      <c r="LV66" s="12" t="n"/>
+      <c r="LW66" s="8" t="n"/>
+      <c r="LX66" s="12" t="n"/>
+      <c r="LY66" s="12" t="n"/>
+      <c r="LZ66" s="12" t="n"/>
+      <c r="MA66" s="12" t="n"/>
+      <c r="MB66" s="8" t="n"/>
+      <c r="MC66" s="12" t="n"/>
+      <c r="MD66" s="12" t="n"/>
+      <c r="ME66" s="12" t="n"/>
+      <c r="MF66" s="12" t="n"/>
+      <c r="MG66" s="8" t="n"/>
+      <c r="MH66" s="12" t="n"/>
+      <c r="MI66" s="12" t="n"/>
+      <c r="MJ66" s="12" t="n"/>
+      <c r="MK66" s="12" t="n"/>
+      <c r="ML66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="B67" s="4" t="n"/>
@@ -23247,6 +26351,47 @@
       <c r="KR67" s="12" t="n"/>
       <c r="KS67" s="12" t="n"/>
       <c r="KT67" s="7" t="n"/>
+      <c r="KX67" s="4" t="n"/>
+      <c r="KY67" s="6" t="n"/>
+      <c r="KZ67" s="8" t="n"/>
+      <c r="LA67" s="11" t="inlineStr"/>
+      <c r="LB67" s="6" t="n"/>
+      <c r="LC67" s="8" t="n"/>
+      <c r="LD67" s="12" t="n"/>
+      <c r="LE67" s="12" t="n"/>
+      <c r="LF67" s="12" t="n"/>
+      <c r="LG67" s="12" t="n"/>
+      <c r="LH67" s="8" t="n"/>
+      <c r="LI67" s="12" t="n"/>
+      <c r="LJ67" s="12" t="n"/>
+      <c r="LK67" s="12" t="n"/>
+      <c r="LL67" s="12" t="n"/>
+      <c r="LM67" s="8" t="n"/>
+      <c r="LN67" s="12" t="n"/>
+      <c r="LO67" s="12" t="n"/>
+      <c r="LP67" s="12" t="n"/>
+      <c r="LQ67" s="12" t="n"/>
+      <c r="LR67" s="8" t="n"/>
+      <c r="LS67" s="12" t="n"/>
+      <c r="LT67" s="12" t="n"/>
+      <c r="LU67" s="12" t="n"/>
+      <c r="LV67" s="12" t="n"/>
+      <c r="LW67" s="8" t="n"/>
+      <c r="LX67" s="12" t="n"/>
+      <c r="LY67" s="12" t="n"/>
+      <c r="LZ67" s="12" t="n"/>
+      <c r="MA67" s="12" t="n"/>
+      <c r="MB67" s="8" t="n"/>
+      <c r="MC67" s="12" t="n"/>
+      <c r="MD67" s="12" t="n"/>
+      <c r="ME67" s="12" t="n"/>
+      <c r="MF67" s="12" t="n"/>
+      <c r="MG67" s="8" t="n"/>
+      <c r="MH67" s="12" t="n"/>
+      <c r="MI67" s="12" t="n"/>
+      <c r="MJ67" s="12" t="n"/>
+      <c r="MK67" s="12" t="n"/>
+      <c r="ML67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="B68" s="4" t="n"/>
@@ -23536,6 +26681,47 @@
       <c r="KR68" s="12" t="n"/>
       <c r="KS68" s="12" t="n"/>
       <c r="KT68" s="7" t="n"/>
+      <c r="KX68" s="4" t="n"/>
+      <c r="KY68" s="6" t="n"/>
+      <c r="KZ68" s="8" t="n"/>
+      <c r="LA68" s="11" t="inlineStr"/>
+      <c r="LB68" s="6" t="n"/>
+      <c r="LC68" s="8" t="n"/>
+      <c r="LD68" s="12" t="n"/>
+      <c r="LE68" s="12" t="n"/>
+      <c r="LF68" s="12" t="n"/>
+      <c r="LG68" s="12" t="n"/>
+      <c r="LH68" s="8" t="n"/>
+      <c r="LI68" s="12" t="n"/>
+      <c r="LJ68" s="12" t="n"/>
+      <c r="LK68" s="12" t="n"/>
+      <c r="LL68" s="12" t="n"/>
+      <c r="LM68" s="8" t="n"/>
+      <c r="LN68" s="12" t="n"/>
+      <c r="LO68" s="12" t="n"/>
+      <c r="LP68" s="12" t="n"/>
+      <c r="LQ68" s="12" t="n"/>
+      <c r="LR68" s="8" t="n"/>
+      <c r="LS68" s="12" t="n"/>
+      <c r="LT68" s="12" t="n"/>
+      <c r="LU68" s="12" t="n"/>
+      <c r="LV68" s="12" t="n"/>
+      <c r="LW68" s="8" t="n"/>
+      <c r="LX68" s="12" t="n"/>
+      <c r="LY68" s="12" t="n"/>
+      <c r="LZ68" s="12" t="n"/>
+      <c r="MA68" s="12" t="n"/>
+      <c r="MB68" s="8" t="n"/>
+      <c r="MC68" s="12" t="n"/>
+      <c r="MD68" s="12" t="n"/>
+      <c r="ME68" s="12" t="n"/>
+      <c r="MF68" s="12" t="n"/>
+      <c r="MG68" s="8" t="n"/>
+      <c r="MH68" s="12" t="n"/>
+      <c r="MI68" s="12" t="n"/>
+      <c r="MJ68" s="12" t="n"/>
+      <c r="MK68" s="12" t="n"/>
+      <c r="ML68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="B69" s="4" t="n"/>
@@ -23825,6 +27011,47 @@
       <c r="KR69" s="12" t="n"/>
       <c r="KS69" s="12" t="n"/>
       <c r="KT69" s="7" t="n"/>
+      <c r="KX69" s="4" t="n"/>
+      <c r="KY69" s="6" t="n"/>
+      <c r="KZ69" s="8" t="n"/>
+      <c r="LA69" s="11" t="inlineStr"/>
+      <c r="LB69" s="6" t="n"/>
+      <c r="LC69" s="8" t="n"/>
+      <c r="LD69" s="12" t="n"/>
+      <c r="LE69" s="12" t="n"/>
+      <c r="LF69" s="12" t="n"/>
+      <c r="LG69" s="12" t="n"/>
+      <c r="LH69" s="8" t="n"/>
+      <c r="LI69" s="12" t="n"/>
+      <c r="LJ69" s="12" t="n"/>
+      <c r="LK69" s="12" t="n"/>
+      <c r="LL69" s="12" t="n"/>
+      <c r="LM69" s="8" t="n"/>
+      <c r="LN69" s="12" t="n"/>
+      <c r="LO69" s="12" t="n"/>
+      <c r="LP69" s="12" t="n"/>
+      <c r="LQ69" s="12" t="n"/>
+      <c r="LR69" s="8" t="n"/>
+      <c r="LS69" s="12" t="n"/>
+      <c r="LT69" s="12" t="n"/>
+      <c r="LU69" s="12" t="n"/>
+      <c r="LV69" s="12" t="n"/>
+      <c r="LW69" s="8" t="n"/>
+      <c r="LX69" s="12" t="n"/>
+      <c r="LY69" s="12" t="n"/>
+      <c r="LZ69" s="12" t="n"/>
+      <c r="MA69" s="12" t="n"/>
+      <c r="MB69" s="8" t="n"/>
+      <c r="MC69" s="12" t="n"/>
+      <c r="MD69" s="12" t="n"/>
+      <c r="ME69" s="12" t="n"/>
+      <c r="MF69" s="12" t="n"/>
+      <c r="MG69" s="8" t="n"/>
+      <c r="MH69" s="12" t="n"/>
+      <c r="MI69" s="12" t="n"/>
+      <c r="MJ69" s="12" t="n"/>
+      <c r="MK69" s="12" t="n"/>
+      <c r="ML69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="B70" s="4" t="n"/>
@@ -24114,6 +27341,47 @@
       <c r="KR70" s="12" t="n"/>
       <c r="KS70" s="12" t="n"/>
       <c r="KT70" s="7" t="n"/>
+      <c r="KX70" s="4" t="n"/>
+      <c r="KY70" s="6" t="n"/>
+      <c r="KZ70" s="8" t="n"/>
+      <c r="LA70" s="11" t="inlineStr"/>
+      <c r="LB70" s="6" t="n"/>
+      <c r="LC70" s="8" t="n"/>
+      <c r="LD70" s="12" t="n"/>
+      <c r="LE70" s="12" t="n"/>
+      <c r="LF70" s="12" t="n"/>
+      <c r="LG70" s="12" t="n"/>
+      <c r="LH70" s="8" t="n"/>
+      <c r="LI70" s="12" t="n"/>
+      <c r="LJ70" s="12" t="n"/>
+      <c r="LK70" s="12" t="n"/>
+      <c r="LL70" s="12" t="n"/>
+      <c r="LM70" s="8" t="n"/>
+      <c r="LN70" s="12" t="n"/>
+      <c r="LO70" s="12" t="n"/>
+      <c r="LP70" s="12" t="n"/>
+      <c r="LQ70" s="12" t="n"/>
+      <c r="LR70" s="8" t="n"/>
+      <c r="LS70" s="12" t="n"/>
+      <c r="LT70" s="12" t="n"/>
+      <c r="LU70" s="12" t="n"/>
+      <c r="LV70" s="12" t="n"/>
+      <c r="LW70" s="8" t="n"/>
+      <c r="LX70" s="12" t="n"/>
+      <c r="LY70" s="12" t="n"/>
+      <c r="LZ70" s="12" t="n"/>
+      <c r="MA70" s="12" t="n"/>
+      <c r="MB70" s="8" t="n"/>
+      <c r="MC70" s="12" t="n"/>
+      <c r="MD70" s="12" t="n"/>
+      <c r="ME70" s="12" t="n"/>
+      <c r="MF70" s="12" t="n"/>
+      <c r="MG70" s="8" t="n"/>
+      <c r="MH70" s="12" t="n"/>
+      <c r="MI70" s="12" t="n"/>
+      <c r="MJ70" s="12" t="n"/>
+      <c r="MK70" s="12" t="n"/>
+      <c r="ML70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="B71" s="18" t="n"/>
@@ -24403,9 +27671,50 @@
       <c r="KR71" s="19" t="n"/>
       <c r="KS71" s="19" t="n"/>
       <c r="KT71" s="20" t="n"/>
+      <c r="KX71" s="18" t="n"/>
+      <c r="KY71" s="19" t="n"/>
+      <c r="KZ71" s="19" t="n"/>
+      <c r="LA71" s="19" t="n"/>
+      <c r="LB71" s="19" t="n"/>
+      <c r="LC71" s="19" t="n"/>
+      <c r="LD71" s="19" t="n"/>
+      <c r="LE71" s="19" t="n"/>
+      <c r="LF71" s="19" t="n"/>
+      <c r="LG71" s="19" t="n"/>
+      <c r="LH71" s="19" t="n"/>
+      <c r="LI71" s="19" t="n"/>
+      <c r="LJ71" s="19" t="n"/>
+      <c r="LK71" s="19" t="n"/>
+      <c r="LL71" s="19" t="n"/>
+      <c r="LM71" s="19" t="n"/>
+      <c r="LN71" s="19" t="n"/>
+      <c r="LO71" s="19" t="n"/>
+      <c r="LP71" s="19" t="n"/>
+      <c r="LQ71" s="19" t="n"/>
+      <c r="LR71" s="19" t="n"/>
+      <c r="LS71" s="19" t="n"/>
+      <c r="LT71" s="19" t="n"/>
+      <c r="LU71" s="19" t="n"/>
+      <c r="LV71" s="19" t="n"/>
+      <c r="LW71" s="19" t="n"/>
+      <c r="LX71" s="19" t="n"/>
+      <c r="LY71" s="19" t="n"/>
+      <c r="LZ71" s="19" t="n"/>
+      <c r="MA71" s="19" t="n"/>
+      <c r="MB71" s="19" t="n"/>
+      <c r="MC71" s="19" t="n"/>
+      <c r="MD71" s="19" t="n"/>
+      <c r="ME71" s="19" t="n"/>
+      <c r="MF71" s="19" t="n"/>
+      <c r="MG71" s="19" t="n"/>
+      <c r="MH71" s="19" t="n"/>
+      <c r="MI71" s="19" t="n"/>
+      <c r="MJ71" s="19" t="n"/>
+      <c r="MK71" s="19" t="n"/>
+      <c r="ML71" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="497">
+  <mergeCells count="568">
     <mergeCell ref="EG67:EH67"/>
     <mergeCell ref="CM18:CM25"/>
     <mergeCell ref="CO42:CP42"/>
@@ -24415,6 +27724,8 @@
     <mergeCell ref="JI52:JJ52"/>
     <mergeCell ref="CO31:CP31"/>
     <mergeCell ref="HQ33:HR33"/>
+    <mergeCell ref="LA64:LB64"/>
+    <mergeCell ref="LA51:LB51"/>
     <mergeCell ref="EE9:EE16"/>
     <mergeCell ref="AW33:AX33"/>
     <mergeCell ref="FY39:FZ39"/>
@@ -24422,20 +27733,25 @@
     <mergeCell ref="EG64:EH64"/>
     <mergeCell ref="HQ45:HR45"/>
     <mergeCell ref="GG6:GJ6"/>
+    <mergeCell ref="MH6:MK6"/>
+    <mergeCell ref="LA9:LB9"/>
     <mergeCell ref="AU54:AU61"/>
     <mergeCell ref="CO57:CP57"/>
     <mergeCell ref="HQ46:HR46"/>
     <mergeCell ref="JI42:JJ42"/>
+    <mergeCell ref="LA11:LB11"/>
     <mergeCell ref="AW59:AX59"/>
     <mergeCell ref="FY46:FZ46"/>
     <mergeCell ref="FY21:FZ21"/>
     <mergeCell ref="EG11:EH11"/>
     <mergeCell ref="HQ48:HR48"/>
+    <mergeCell ref="KY18:KY25"/>
     <mergeCell ref="E55:F55"/>
     <mergeCell ref="FY23:FZ23"/>
     <mergeCell ref="E67:F67"/>
     <mergeCell ref="JI37:JJ37"/>
     <mergeCell ref="E48:F48"/>
+    <mergeCell ref="LA39:LB39"/>
     <mergeCell ref="CM63:CM70"/>
     <mergeCell ref="KK6:KN6"/>
     <mergeCell ref="W6:Z6"/>
@@ -24455,6 +27771,7 @@
     <mergeCell ref="AW41:AX41"/>
     <mergeCell ref="CO32:CP32"/>
     <mergeCell ref="HQ34:HR34"/>
+    <mergeCell ref="LA65:LB65"/>
     <mergeCell ref="JI68:JJ68"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="JI55:JJ55"/>
@@ -24465,12 +27782,14 @@
     <mergeCell ref="HQ36:HR36"/>
     <mergeCell ref="FY32:FZ32"/>
     <mergeCell ref="E18:F18"/>
+    <mergeCell ref="LN6:LQ6"/>
     <mergeCell ref="AW36:AX36"/>
     <mergeCell ref="AW67:AX67"/>
     <mergeCell ref="FY29:FZ29"/>
     <mergeCell ref="C18:C25"/>
     <mergeCell ref="CO63:CP63"/>
     <mergeCell ref="EG19:EH19"/>
+    <mergeCell ref="LA12:LB12"/>
     <mergeCell ref="JG18:JG25"/>
     <mergeCell ref="E29:F29"/>
     <mergeCell ref="CD6:CG6"/>
@@ -24482,6 +27801,7 @@
     <mergeCell ref="E69:F69"/>
     <mergeCell ref="HQ54:HR54"/>
     <mergeCell ref="JI23:JJ23"/>
+    <mergeCell ref="LA14:LB14"/>
     <mergeCell ref="EG58:EH58"/>
     <mergeCell ref="E31:F31"/>
     <mergeCell ref="EG33:EH33"/>
@@ -24522,9 +27842,13 @@
     <mergeCell ref="FY48:FZ48"/>
     <mergeCell ref="HQ39:HR39"/>
     <mergeCell ref="JI29:JJ29"/>
+    <mergeCell ref="LX6:MA6"/>
+    <mergeCell ref="LA20:LB20"/>
     <mergeCell ref="EG10:EH10"/>
     <mergeCell ref="H6:K6"/>
     <mergeCell ref="FD6:FG6"/>
+    <mergeCell ref="KY3:MK3"/>
+    <mergeCell ref="LA22:LB22"/>
     <mergeCell ref="DL6:DO6"/>
     <mergeCell ref="C27:C34"/>
     <mergeCell ref="EG41:EH41"/>
@@ -24545,6 +27869,7 @@
     <mergeCell ref="C45:C52"/>
     <mergeCell ref="HQ19:HR19"/>
     <mergeCell ref="E63:F63"/>
+    <mergeCell ref="LA33:LB33"/>
     <mergeCell ref="FW18:FW25"/>
     <mergeCell ref="BO6:BR6"/>
     <mergeCell ref="AW65:AX65"/>
@@ -24552,11 +27877,14 @@
     <mergeCell ref="FY45:FZ45"/>
     <mergeCell ref="AW58:AX58"/>
     <mergeCell ref="E27:F27"/>
+    <mergeCell ref="LA34:LB34"/>
     <mergeCell ref="FY20:FZ20"/>
     <mergeCell ref="CO16:CP16"/>
+    <mergeCell ref="KY54:KY61"/>
     <mergeCell ref="EE36:EE43"/>
     <mergeCell ref="AW60:AX60"/>
     <mergeCell ref="EG31:EH31"/>
+    <mergeCell ref="LA36:LB36"/>
     <mergeCell ref="C3:AO3"/>
     <mergeCell ref="E22:F22"/>
     <mergeCell ref="JG27:JG34"/>
@@ -24573,6 +27901,9 @@
     <mergeCell ref="FY40:FZ40"/>
     <mergeCell ref="FY67:FZ67"/>
     <mergeCell ref="HQ58:HR58"/>
+    <mergeCell ref="KY9:KY16"/>
+    <mergeCell ref="LA29:LB29"/>
+    <mergeCell ref="LA23:LB23"/>
     <mergeCell ref="KA6:KD6"/>
     <mergeCell ref="AW15:AX15"/>
     <mergeCell ref="E40:F40"/>
@@ -24581,19 +27912,25 @@
     <mergeCell ref="JG9:JG16"/>
     <mergeCell ref="EG29:EH29"/>
     <mergeCell ref="FY69:FZ69"/>
+    <mergeCell ref="KY36:KY43"/>
     <mergeCell ref="DG6:DJ6"/>
     <mergeCell ref="HQ60:HR60"/>
     <mergeCell ref="CM9:CM16"/>
     <mergeCell ref="JG63:JG70"/>
+    <mergeCell ref="LA54:LB54"/>
+    <mergeCell ref="LD6:LG6"/>
     <mergeCell ref="AW10:AX10"/>
     <mergeCell ref="HQ25:HR25"/>
     <mergeCell ref="JI16:JJ16"/>
+    <mergeCell ref="LA56:LB56"/>
     <mergeCell ref="HQ22:HR22"/>
     <mergeCell ref="EG56:EH56"/>
+    <mergeCell ref="LA49:LB49"/>
     <mergeCell ref="JI45:JJ45"/>
     <mergeCell ref="E66:F66"/>
     <mergeCell ref="CO37:CP37"/>
     <mergeCell ref="CO18:CP18"/>
+    <mergeCell ref="LA57:LB57"/>
     <mergeCell ref="HQ13:HR13"/>
     <mergeCell ref="EG39:EH39"/>
     <mergeCell ref="JI47:JJ47"/>
@@ -24620,9 +27957,11 @@
     <mergeCell ref="E41:F41"/>
     <mergeCell ref="CO12:CP12"/>
     <mergeCell ref="EG52:EH52"/>
+    <mergeCell ref="LA45:LB45"/>
     <mergeCell ref="EG70:EH70"/>
     <mergeCell ref="JG3:KS3"/>
     <mergeCell ref="E56:F56"/>
+    <mergeCell ref="LA32:LB32"/>
     <mergeCell ref="JI59:JJ59"/>
     <mergeCell ref="E43:F43"/>
     <mergeCell ref="CO14:CP14"/>
@@ -24633,11 +27972,13 @@
     <mergeCell ref="CO38:CP38"/>
     <mergeCell ref="AW34:AX34"/>
     <mergeCell ref="FI6:FL6"/>
+    <mergeCell ref="LA58:LB58"/>
     <mergeCell ref="JI61:JJ61"/>
     <mergeCell ref="HQ30:HR30"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="AL6:AO6"/>
     <mergeCell ref="JI48:JJ48"/>
+    <mergeCell ref="LA50:LB50"/>
     <mergeCell ref="CO40:CP40"/>
     <mergeCell ref="CO27:CP27"/>
     <mergeCell ref="AW30:AX30"/>
@@ -24645,16 +27986,20 @@
     <mergeCell ref="FY54:FZ54"/>
     <mergeCell ref="HQ23:HR23"/>
     <mergeCell ref="HQ29:HR29"/>
+    <mergeCell ref="LA60:LB60"/>
     <mergeCell ref="AW42:AX42"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="AW29:AX29"/>
     <mergeCell ref="FW45:FW52"/>
     <mergeCell ref="HO36:HO43"/>
+    <mergeCell ref="KY63:KY70"/>
     <mergeCell ref="FY56:FZ56"/>
     <mergeCell ref="AW31:AX31"/>
     <mergeCell ref="HY6:IB6"/>
     <mergeCell ref="GB6:GE6"/>
+    <mergeCell ref="LA70:LB70"/>
     <mergeCell ref="JI66:JJ66"/>
+    <mergeCell ref="LI6:LL6"/>
     <mergeCell ref="FY18:FZ18"/>
     <mergeCell ref="JI38:JJ38"/>
     <mergeCell ref="HF6:HI6"/>
@@ -24677,6 +28022,7 @@
     <mergeCell ref="FW9:FW16"/>
     <mergeCell ref="E65:F65"/>
     <mergeCell ref="CO30:CP30"/>
+    <mergeCell ref="LA25:LB25"/>
     <mergeCell ref="KF6:KI6"/>
     <mergeCell ref="KP6:KS6"/>
     <mergeCell ref="R6:U6"/>
@@ -24690,6 +28036,7 @@
     <mergeCell ref="FY27:FZ27"/>
     <mergeCell ref="CO41:CP41"/>
     <mergeCell ref="CO33:CP33"/>
+    <mergeCell ref="LA66:LB66"/>
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="AW52:AX52"/>
     <mergeCell ref="CO43:CP43"/>
@@ -24698,11 +28045,13 @@
     <mergeCell ref="EG66:EH66"/>
     <mergeCell ref="FW3:HI3"/>
     <mergeCell ref="E14:F14"/>
+    <mergeCell ref="LA13:LB13"/>
     <mergeCell ref="AW37:AX37"/>
     <mergeCell ref="EG68:EH68"/>
     <mergeCell ref="CM54:CM61"/>
     <mergeCell ref="AW47:AX47"/>
     <mergeCell ref="JI57:JJ57"/>
+    <mergeCell ref="LA15:LB15"/>
     <mergeCell ref="CO59:CP59"/>
     <mergeCell ref="EG28:EH28"/>
     <mergeCell ref="GL6:GO6"/>
@@ -24712,6 +28061,7 @@
     <mergeCell ref="AU45:AU52"/>
     <mergeCell ref="HQ50:HR50"/>
     <mergeCell ref="JI19:JJ19"/>
+    <mergeCell ref="LA10:LB10"/>
     <mergeCell ref="AW63:AX63"/>
     <mergeCell ref="CO54:CP54"/>
     <mergeCell ref="FY25:FZ25"/>
@@ -24730,14 +28080,17 @@
     <mergeCell ref="EG16:EH16"/>
     <mergeCell ref="HQ47:HR47"/>
     <mergeCell ref="FW36:FW43"/>
+    <mergeCell ref="LA28:LB28"/>
     <mergeCell ref="FY14:FZ14"/>
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="IS6:IV6"/>
     <mergeCell ref="FY68:FZ68"/>
+    <mergeCell ref="LA30:LB30"/>
     <mergeCell ref="CO34:CP34"/>
     <mergeCell ref="CO9:CP9"/>
     <mergeCell ref="FY43:FZ43"/>
     <mergeCell ref="EG49:EH49"/>
+    <mergeCell ref="LA67:LB67"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="AW9:AX9"/>
     <mergeCell ref="FY15:FZ15"/>
@@ -24747,12 +28100,14 @@
     <mergeCell ref="JI13:JJ13"/>
     <mergeCell ref="AW45:AX45"/>
     <mergeCell ref="HQ38:HR38"/>
+    <mergeCell ref="LA69:LB69"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="JI65:JJ65"/>
     <mergeCell ref="AW55:AX55"/>
     <mergeCell ref="HO45:HO52"/>
     <mergeCell ref="EG69:EH69"/>
     <mergeCell ref="HQ40:HR40"/>
+    <mergeCell ref="LS6:LV6"/>
     <mergeCell ref="AW40:AX40"/>
     <mergeCell ref="EY6:FB6"/>
     <mergeCell ref="JI27:JJ27"/>
@@ -24761,12 +28116,14 @@
     <mergeCell ref="FY33:FZ33"/>
     <mergeCell ref="JI20:JJ20"/>
     <mergeCell ref="EG23:EH23"/>
+    <mergeCell ref="LA16:LB16"/>
     <mergeCell ref="E33:F33"/>
     <mergeCell ref="CO64:CP64"/>
     <mergeCell ref="HQ66:HR66"/>
     <mergeCell ref="FY13:FZ13"/>
     <mergeCell ref="JI22:JJ22"/>
     <mergeCell ref="CO39:CP39"/>
+    <mergeCell ref="LA18:LB18"/>
     <mergeCell ref="AW66:AX66"/>
     <mergeCell ref="EG37:EH37"/>
     <mergeCell ref="FY28:FZ28"/>
@@ -24786,6 +28143,7 @@
     <mergeCell ref="CO11:CP11"/>
     <mergeCell ref="BJ6:BM6"/>
     <mergeCell ref="JI40:JJ40"/>
+    <mergeCell ref="LA31:LB31"/>
     <mergeCell ref="JI15:JJ15"/>
     <mergeCell ref="JI12:JJ12"/>
     <mergeCell ref="CO50:CP50"/>
@@ -24800,7 +28158,9 @@
     <mergeCell ref="E23:F23"/>
     <mergeCell ref="EG12:EH12"/>
     <mergeCell ref="HQ43:HR43"/>
+    <mergeCell ref="LA24:LB24"/>
     <mergeCell ref="FY34:FZ34"/>
+    <mergeCell ref="LA42:LB42"/>
     <mergeCell ref="FY64:FZ64"/>
     <mergeCell ref="E34:F34"/>
     <mergeCell ref="DQ6:DT6"/>
@@ -24810,6 +28170,7 @@
     <mergeCell ref="JI34:JJ34"/>
     <mergeCell ref="JI28:JJ28"/>
     <mergeCell ref="E49:F49"/>
+    <mergeCell ref="LA19:LB19"/>
     <mergeCell ref="JV6:JY6"/>
     <mergeCell ref="E36:F36"/>
     <mergeCell ref="EG38:EH38"/>
@@ -24823,27 +28184,36 @@
     <mergeCell ref="EG27:EH27"/>
     <mergeCell ref="HQ21:HR21"/>
     <mergeCell ref="HO18:HO25"/>
+    <mergeCell ref="LA52:LB52"/>
     <mergeCell ref="JG36:JG43"/>
+    <mergeCell ref="KY27:KY34"/>
     <mergeCell ref="AU18:AU25"/>
     <mergeCell ref="JI41:JJ41"/>
     <mergeCell ref="CO58:CP58"/>
+    <mergeCell ref="LA37:LB37"/>
     <mergeCell ref="CO20:CP20"/>
     <mergeCell ref="AW23:AX23"/>
     <mergeCell ref="HQ16:HR16"/>
     <mergeCell ref="JI56:JJ56"/>
+    <mergeCell ref="LA47:LB47"/>
     <mergeCell ref="BT6:BW6"/>
     <mergeCell ref="JI43:JJ43"/>
     <mergeCell ref="EE63:EE70"/>
     <mergeCell ref="FY49:FZ49"/>
     <mergeCell ref="HQ18:HR18"/>
+    <mergeCell ref="LA38:LB38"/>
+    <mergeCell ref="MC6:MF6"/>
     <mergeCell ref="HQ51:HR51"/>
     <mergeCell ref="JG54:JG61"/>
+    <mergeCell ref="KY45:KY52"/>
     <mergeCell ref="AW64:AX64"/>
     <mergeCell ref="EE27:EE34"/>
     <mergeCell ref="AW51:AX51"/>
+    <mergeCell ref="LA63:LB63"/>
     <mergeCell ref="FY55:FZ55"/>
     <mergeCell ref="JI25:JJ25"/>
     <mergeCell ref="JI36:JJ36"/>
+    <mergeCell ref="LA27:LB27"/>
     <mergeCell ref="JI33:JJ33"/>
     <mergeCell ref="EG46:EH46"/>
     <mergeCell ref="JI54:JJ54"/>
@@ -24861,13 +28231,17 @@
     <mergeCell ref="HQ24:HR24"/>
     <mergeCell ref="AZ6:BC6"/>
     <mergeCell ref="AW14:AX14"/>
+    <mergeCell ref="LA55:LB55"/>
     <mergeCell ref="ET6:EW6"/>
     <mergeCell ref="FY70:FZ70"/>
+    <mergeCell ref="LA59:LB59"/>
     <mergeCell ref="AG6:AJ6"/>
+    <mergeCell ref="LA46:LB46"/>
     <mergeCell ref="CO36:CP36"/>
     <mergeCell ref="E70:F70"/>
     <mergeCell ref="JI49:JJ49"/>
     <mergeCell ref="FY63:FZ63"/>
+    <mergeCell ref="LA40:LB40"/>
     <mergeCell ref="E57:F57"/>
     <mergeCell ref="EG59:EH59"/>
     <mergeCell ref="FY50:FZ50"/>
@@ -24876,10 +28250,13 @@
     <mergeCell ref="CO21:CP21"/>
     <mergeCell ref="EG61:EH61"/>
     <mergeCell ref="JI50:JJ50"/>
+    <mergeCell ref="LA41:LB41"/>
     <mergeCell ref="CO23:CP23"/>
     <mergeCell ref="FW63:FW70"/>
     <mergeCell ref="HQ37:HR37"/>
+    <mergeCell ref="LA68:LB68"/>
     <mergeCell ref="JI64:JJ64"/>
+    <mergeCell ref="LA43:LB43"/>
     <mergeCell ref="HA6:HD6"/>
     <mergeCell ref="JI39:JJ39"/>
     <mergeCell ref="E60:F60"/>
@@ -24899,10 +28276,13 @@
     <mergeCell ref="AU27:AU34"/>
     <mergeCell ref="AW22:AX22"/>
     <mergeCell ref="EE54:EE61"/>
+    <mergeCell ref="LA21:LB21"/>
     <mergeCell ref="M6:P6"/>
     <mergeCell ref="CO55:CP55"/>
     <mergeCell ref="ID6:IG6"/>
+    <mergeCell ref="LA61:LB61"/>
     <mergeCell ref="JG45:JG52"/>
+    <mergeCell ref="LA48:LB48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24914,7 +28294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25028,13 +28408,27 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>82.5</v>
+        <v>79.58333333333333</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>82.5</v>
+        <v>79.58333333333333</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91.78125</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>91.78125</v>
       </c>
     </row>
   </sheetData>
